--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -2713,6 +2713,51 @@
     <t>Active</t>
   </si>
   <si>
+    <t>999754600</t>
+  </si>
+  <si>
+    <t>Chị Loan</t>
+  </si>
+  <si>
+    <t>6/2, Đường Số 6</t>
+  </si>
+  <si>
+    <t>999762653</t>
+  </si>
+  <si>
+    <t>Cà Phê Thúy Vy</t>
+  </si>
+  <si>
+    <t>Số 1351, Đường Nguyễn Thị Định</t>
+  </si>
+  <si>
+    <t>999765789</t>
+  </si>
+  <si>
+    <t>TH Hoa Phượng</t>
+  </si>
+  <si>
+    <t>34/33, Đường Số 2</t>
+  </si>
+  <si>
+    <t>2344002</t>
+  </si>
+  <si>
+    <t>Thịnh Thoa</t>
+  </si>
+  <si>
+    <t>34, Đường 4</t>
+  </si>
+  <si>
+    <t>2004898</t>
+  </si>
+  <si>
+    <t>Tạp Hóa Kim Thoa</t>
+  </si>
+  <si>
+    <t>40 Cảng Phú Hữu, Nguyễn Duy Trinh</t>
+  </si>
+  <si>
     <t>3362</t>
   </si>
   <si>
@@ -2722,51 +2767,6 @@
     <t>107, Lò Lu</t>
   </si>
   <si>
-    <t>999754600</t>
-  </si>
-  <si>
-    <t>Chị Loan</t>
-  </si>
-  <si>
-    <t>6/2, Đường Số 6</t>
-  </si>
-  <si>
-    <t>999762653</t>
-  </si>
-  <si>
-    <t>Cà Phê Thúy Vy</t>
-  </si>
-  <si>
-    <t>Số 1351, Đường Nguyễn Thị Định</t>
-  </si>
-  <si>
-    <t>999765789</t>
-  </si>
-  <si>
-    <t>TH Hoa Phượng</t>
-  </si>
-  <si>
-    <t>34/33, Đường Số 2</t>
-  </si>
-  <si>
-    <t>2344002</t>
-  </si>
-  <si>
-    <t>Thịnh Thoa</t>
-  </si>
-  <si>
-    <t>34, Đường 4</t>
-  </si>
-  <si>
-    <t>2004898</t>
-  </si>
-  <si>
-    <t>Tạp Hóa Kim Thoa</t>
-  </si>
-  <si>
-    <t>40 Cảng Phú Hữu, Nguyễn Duy Trinh</t>
-  </si>
-  <si>
     <t>1-6JP933U</t>
   </si>
   <si>
@@ -2878,6 +2878,48 @@
     <t>MSC_BEV_Chương trình TBTN_Tủ mát Nước giải khát_HCM_All2026_T10</t>
   </si>
   <si>
+    <t>2432200</t>
+  </si>
+  <si>
+    <t>G-Net Tycoon</t>
+  </si>
+  <si>
+    <t>Số 117A, Đường 39</t>
+  </si>
+  <si>
+    <t>2451874</t>
+  </si>
+  <si>
+    <t>Quán Cơm Bảo An</t>
+  </si>
+  <si>
+    <t>242, Đường 57 - CL</t>
+  </si>
+  <si>
+    <t>3136368</t>
+  </si>
+  <si>
+    <t>Chợ Sạch 24H</t>
+  </si>
+  <si>
+    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
+  </si>
+  <si>
+    <t>3063948</t>
+  </si>
+  <si>
+    <t>Cà Phê Chị Tuyết</t>
+  </si>
+  <si>
+    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
+  </si>
+  <si>
+    <t>2894640</t>
+  </si>
+  <si>
+    <t>Mino Mart</t>
+  </si>
+  <si>
     <t>2128924</t>
   </si>
   <si>
@@ -2887,46 +2929,13 @@
     <t>22/10 Đường 990, Nguyễn Duy Trinh</t>
   </si>
   <si>
-    <t>2432200</t>
-  </si>
-  <si>
-    <t>G-Net Tycoon</t>
-  </si>
-  <si>
-    <t>Số 117A, Đường 39</t>
-  </si>
-  <si>
-    <t>2451874</t>
-  </si>
-  <si>
-    <t>Quán Cơm Bảo An</t>
-  </si>
-  <si>
-    <t>242, Đường 57 - CL</t>
-  </si>
-  <si>
-    <t>2894640</t>
-  </si>
-  <si>
-    <t>Mino Mart</t>
-  </si>
-  <si>
-    <t>3063948</t>
-  </si>
-  <si>
-    <t>Cà Phê Chị Tuyết</t>
-  </si>
-  <si>
-    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
-  </si>
-  <si>
-    <t>3136368</t>
-  </si>
-  <si>
-    <t>Chợ Sạch 24H</t>
-  </si>
-  <si>
-    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
+    <t>999191040</t>
+  </si>
+  <si>
+    <t>Tạp Hóa Sáu Tèo</t>
+  </si>
+  <si>
+    <t>250, Trường Lưu</t>
   </si>
   <si>
     <t>999115327</t>
@@ -2936,15 +2945,6 @@
   </si>
   <si>
     <t>Số 313, Lê Văn Thịnh</t>
-  </si>
-  <si>
-    <t>999191040</t>
-  </si>
-  <si>
-    <t>Tạp Hóa Sáu Tèo</t>
-  </si>
-  <si>
-    <t>250, Trường Lưu</t>
   </si>
   <si>
     <t>999210374</t>
@@ -42092,16 +42092,16 @@
         <v>50</v>
       </c>
       <c r="M311" s="3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="N311" s="3" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="P311" s="3" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="Q311" s="3" t="s">
         <v>46</v>
@@ -42134,7 +42134,7 @@
         <v>10</v>
       </c>
       <c r="AA311" s="7">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="AB311" s="7">
         <v>1</v>
@@ -42164,7 +42164,7 @@
         <v>58</v>
       </c>
       <c r="AK311" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>46</v>
@@ -42176,7 +42176,7 @@
         <v>58</v>
       </c>
       <c r="AO311" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
     </row>
     <row r="312" spans="1:41" x14ac:dyDescent="0.25">
@@ -42217,16 +42217,16 @@
         <v>50</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q312" s="3" t="s">
         <v>46</v>
@@ -42259,7 +42259,7 @@
         <v>10</v>
       </c>
       <c r="AA312" s="7">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AB312" s="7">
         <v>1</v>
@@ -42289,7 +42289,7 @@
         <v>58</v>
       </c>
       <c r="AK312" s="6">
-        <v>46312.58308098379</v>
+        <v>46310.439036655094</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>46</v>
@@ -42301,7 +42301,7 @@
         <v>58</v>
       </c>
       <c r="AO312" s="6">
-        <v>46312.58308098379</v>
+        <v>46310.439036655094</v>
       </c>
     </row>
     <row r="313" spans="1:41" x14ac:dyDescent="0.25">
@@ -42342,16 +42342,16 @@
         <v>50</v>
       </c>
       <c r="M313" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N313" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P313" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q313" s="3" t="s">
         <v>46</v>
@@ -42414,7 +42414,7 @@
         <v>58</v>
       </c>
       <c r="AK313" s="6">
-        <v>46310.439036655094</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL313" s="3" t="s">
         <v>46</v>
@@ -42426,7 +42426,7 @@
         <v>58</v>
       </c>
       <c r="AO313" s="6">
-        <v>46310.439036655094</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="314" spans="1:41" x14ac:dyDescent="0.25">
@@ -42455,28 +42455,28 @@
         <v>45</v>
       </c>
       <c r="I314" s="3" t="s">
-        <v>909</v>
+        <v>271</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>910</v>
+        <v>272</v>
       </c>
       <c r="K314" s="3" t="s">
-        <v>911</v>
+        <v>273</v>
       </c>
       <c r="L314" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M314" s="3" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="N314" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="O314" s="3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="P314" s="3" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="Q314" s="3" t="s">
         <v>46</v>
@@ -42539,7 +42539,7 @@
         <v>58</v>
       </c>
       <c r="AK314" s="6">
-        <v>46301.30899568287</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL314" s="3" t="s">
         <v>46</v>
@@ -42551,7 +42551,7 @@
         <v>58</v>
       </c>
       <c r="AO314" s="6">
-        <v>46301.30899568287</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="315" spans="1:41" x14ac:dyDescent="0.25">
@@ -42580,28 +42580,28 @@
         <v>45</v>
       </c>
       <c r="I315" s="3" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
       <c r="K315" s="3" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="L315" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M315" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="N315" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="O315" s="3" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="P315" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="Q315" s="3" t="s">
         <v>46</v>
@@ -42634,7 +42634,7 @@
         <v>10</v>
       </c>
       <c r="AA315" s="7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB315" s="7">
         <v>1</v>
@@ -42664,7 +42664,7 @@
         <v>58</v>
       </c>
       <c r="AK315" s="6">
-        <v>46301.5776272338</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL315" s="3" t="s">
         <v>46</v>
@@ -42676,7 +42676,7 @@
         <v>58</v>
       </c>
       <c r="AO315" s="6">
-        <v>46301.5776272338</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="316" spans="1:41" x14ac:dyDescent="0.25">
@@ -42705,28 +42705,28 @@
         <v>45</v>
       </c>
       <c r="I316" s="3" t="s">
-        <v>322</v>
+        <v>150</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>323</v>
+        <v>151</v>
       </c>
       <c r="K316" s="3" t="s">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="L316" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M316" s="3" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="N316" s="3" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="O316" s="3" t="s">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="P316" s="3" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="Q316" s="3" t="s">
         <v>46</v>
@@ -42759,7 +42759,7 @@
         <v>10</v>
       </c>
       <c r="AA316" s="7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB316" s="7">
         <v>1</v>
@@ -42789,7 +42789,7 @@
         <v>58</v>
       </c>
       <c r="AK316" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL316" s="3" t="s">
         <v>46</v>
@@ -42801,7 +42801,7 @@
         <v>58</v>
       </c>
       <c r="AO316" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="317" spans="1:41" x14ac:dyDescent="0.25">
@@ -42830,28 +42830,28 @@
         <v>45</v>
       </c>
       <c r="I317" s="3" t="s">
-        <v>150</v>
+        <v>909</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>151</v>
+        <v>910</v>
       </c>
       <c r="K317" s="3" t="s">
-        <v>152</v>
+        <v>911</v>
       </c>
       <c r="L317" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M317" s="3" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="N317" s="3" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="O317" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="P317" s="3" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="Q317" s="3" t="s">
         <v>46</v>
@@ -42967,16 +42967,16 @@
         <v>50</v>
       </c>
       <c r="M318" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="P318" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Q318" s="3" t="s">
         <v>46</v>
@@ -43039,7 +43039,7 @@
         <v>58</v>
       </c>
       <c r="AK318" s="6">
-        <v>46298.66540524305</v>
+        <v>46316.79383703704</v>
       </c>
       <c r="AL318" s="3" t="s">
         <v>46</v>
@@ -43051,7 +43051,7 @@
         <v>58</v>
       </c>
       <c r="AO318" s="6">
-        <v>46298.66540524305</v>
+        <v>46316.79383703704</v>
       </c>
     </row>
     <row r="319" spans="1:41" x14ac:dyDescent="0.25">
@@ -43080,28 +43080,28 @@
         <v>45</v>
       </c>
       <c r="I319" s="3" t="s">
-        <v>915</v>
+        <v>138</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>916</v>
+        <v>139</v>
       </c>
       <c r="K319" s="3" t="s">
-        <v>917</v>
+        <v>140</v>
       </c>
       <c r="L319" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M319" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N319" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P319" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q319" s="3" t="s">
         <v>46</v>
@@ -43134,7 +43134,7 @@
         <v>10</v>
       </c>
       <c r="AA319" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB319" s="7">
         <v>1</v>
@@ -43164,7 +43164,7 @@
         <v>58</v>
       </c>
       <c r="AK319" s="6">
-        <v>46316.79383703704</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL319" s="3" t="s">
         <v>46</v>
@@ -43176,7 +43176,7 @@
         <v>58</v>
       </c>
       <c r="AO319" s="6">
-        <v>46316.79383703704</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="320" spans="1:41" x14ac:dyDescent="0.25">
@@ -43205,28 +43205,28 @@
         <v>45</v>
       </c>
       <c r="I320" s="3" t="s">
-        <v>138</v>
+        <v>915</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>139</v>
+        <v>916</v>
       </c>
       <c r="K320" s="3" t="s">
-        <v>140</v>
+        <v>917</v>
       </c>
       <c r="L320" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N320" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O320" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P320" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q320" s="3" t="s">
         <v>46</v>
@@ -43259,7 +43259,7 @@
         <v>10</v>
       </c>
       <c r="AA320" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB320" s="7">
         <v>1</v>
@@ -43289,7 +43289,7 @@
         <v>58</v>
       </c>
       <c r="AK320" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL320" s="3" t="s">
         <v>46</v>
@@ -43301,7 +43301,7 @@
         <v>58</v>
       </c>
       <c r="AO320" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="321" spans="1:41" x14ac:dyDescent="0.25">
@@ -44854,13 +44854,13 @@
         <v>128</v>
       </c>
       <c r="Q333" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R333" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S333" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T333" s="3" t="s">
         <v>894</v>
@@ -46229,13 +46229,13 @@
         <v>134</v>
       </c>
       <c r="Q344" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R344" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S344" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T344" s="3" t="s">
         <v>894</v>
@@ -46455,37 +46455,37 @@
         <v>921</v>
       </c>
       <c r="I346" s="3" t="s">
-        <v>378</v>
+        <v>939</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>379</v>
+        <v>744</v>
       </c>
       <c r="K346" s="3" t="s">
-        <v>380</v>
+        <v>940</v>
       </c>
       <c r="L346" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M346" s="3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="N346" s="3" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="O346" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="P346" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="Q346" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R346" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S346" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T346" s="3" t="s">
         <v>894</v>
@@ -46509,7 +46509,7 @@
         <v>46</v>
       </c>
       <c r="AA346" s="7">
-        <v>156000</v>
+        <v>2416326</v>
       </c>
       <c r="AB346" s="7">
         <v>31</v>
@@ -46580,37 +46580,37 @@
         <v>921</v>
       </c>
       <c r="I347" s="3" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>744</v>
+        <v>949</v>
       </c>
       <c r="K347" s="3" t="s">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="L347" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M347" s="3" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="N347" s="3" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="O347" s="3" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="P347" s="3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="Q347" s="5">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="R347" s="5">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="S347" s="5">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T347" s="3" t="s">
         <v>894</v>
@@ -46634,7 +46634,7 @@
         <v>46</v>
       </c>
       <c r="AA347" s="7">
-        <v>2416326</v>
+        <v>2359523</v>
       </c>
       <c r="AB347" s="7">
         <v>31</v>
@@ -46705,37 +46705,37 @@
         <v>921</v>
       </c>
       <c r="I348" s="3" t="s">
-        <v>948</v>
+        <v>755</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>949</v>
+        <v>756</v>
       </c>
       <c r="K348" s="3" t="s">
-        <v>950</v>
+        <v>757</v>
       </c>
       <c r="L348" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M348" s="3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="N348" s="3" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="O348" s="3" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="P348" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="Q348" s="5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="R348" s="5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="S348" s="5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="T348" s="3" t="s">
         <v>894</v>
@@ -46759,7 +46759,7 @@
         <v>46</v>
       </c>
       <c r="AA348" s="7">
-        <v>2359523</v>
+        <v>2580460</v>
       </c>
       <c r="AB348" s="7">
         <v>31</v>
@@ -46830,37 +46830,37 @@
         <v>921</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>755</v>
+        <v>464</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>756</v>
+        <v>465</v>
       </c>
       <c r="K349" s="3" t="s">
-        <v>757</v>
+        <v>466</v>
       </c>
       <c r="L349" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M349" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="N349" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="O349" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="P349" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="Q349" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="R349" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="S349" s="5">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="T349" s="3" t="s">
         <v>894</v>
@@ -46884,7 +46884,7 @@
         <v>46</v>
       </c>
       <c r="AA349" s="7">
-        <v>2580460</v>
+        <v>570000</v>
       </c>
       <c r="AB349" s="7">
         <v>31</v>
@@ -46955,13 +46955,13 @@
         <v>921</v>
       </c>
       <c r="I350" s="3" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="K350" s="3" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="L350" s="3" t="s">
         <v>50</v>
@@ -46979,13 +46979,13 @@
         <v>128</v>
       </c>
       <c r="Q350" s="5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="R350" s="5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="S350" s="5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="T350" s="3" t="s">
         <v>894</v>
@@ -47009,7 +47009,7 @@
         <v>46</v>
       </c>
       <c r="AA350" s="7">
-        <v>570000</v>
+        <v>925650</v>
       </c>
       <c r="AB350" s="7">
         <v>31</v>
@@ -47080,13 +47080,13 @@
         <v>921</v>
       </c>
       <c r="I351" s="3" t="s">
-        <v>473</v>
+        <v>535</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>474</v>
+        <v>536</v>
       </c>
       <c r="K351" s="3" t="s">
-        <v>475</v>
+        <v>537</v>
       </c>
       <c r="L351" s="3" t="s">
         <v>50</v>
@@ -47104,13 +47104,13 @@
         <v>128</v>
       </c>
       <c r="Q351" s="5">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="R351" s="5">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="S351" s="5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T351" s="3" t="s">
         <v>894</v>
@@ -47134,7 +47134,7 @@
         <v>46</v>
       </c>
       <c r="AA351" s="7">
-        <v>925650</v>
+        <v>590000</v>
       </c>
       <c r="AB351" s="7">
         <v>31</v>
@@ -47205,13 +47205,13 @@
         <v>921</v>
       </c>
       <c r="I352" s="3" t="s">
-        <v>535</v>
+        <v>575</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>536</v>
+        <v>576</v>
       </c>
       <c r="K352" s="3" t="s">
-        <v>537</v>
+        <v>577</v>
       </c>
       <c r="L352" s="3" t="s">
         <v>50</v>
@@ -47229,13 +47229,13 @@
         <v>128</v>
       </c>
       <c r="Q352" s="5">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="R352" s="5">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="S352" s="5">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T352" s="3" t="s">
         <v>894</v>
@@ -47259,7 +47259,7 @@
         <v>46</v>
       </c>
       <c r="AA352" s="7">
-        <v>590000</v>
+        <v>2566500</v>
       </c>
       <c r="AB352" s="7">
         <v>31</v>
@@ -47330,13 +47330,13 @@
         <v>921</v>
       </c>
       <c r="I353" s="3" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="K353" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L353" s="3" t="s">
         <v>50</v>
@@ -47354,13 +47354,13 @@
         <v>128</v>
       </c>
       <c r="Q353" s="5">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="R353" s="5">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="S353" s="5">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="T353" s="3" t="s">
         <v>894</v>
@@ -47383,8 +47383,8 @@
       <c r="Z353" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA353" s="7">
-        <v>2566500</v>
+      <c r="AA353" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB353" s="7">
         <v>31</v>
@@ -47455,37 +47455,37 @@
         <v>921</v>
       </c>
       <c r="I354" s="3" t="s">
-        <v>578</v>
+        <v>89</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>579</v>
+        <v>90</v>
       </c>
       <c r="K354" s="3" t="s">
-        <v>580</v>
+        <v>91</v>
       </c>
       <c r="L354" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M354" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="N354" s="3" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O354" s="3" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="P354" s="3" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="Q354" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R354" s="5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="S354" s="5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="T354" s="3" t="s">
         <v>894</v>
@@ -47508,8 +47508,8 @@
       <c r="Z354" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA354" s="3" t="s">
-        <v>46</v>
+      <c r="AA354" s="7">
+        <v>1246838</v>
       </c>
       <c r="AB354" s="7">
         <v>31</v>
@@ -47580,37 +47580,37 @@
         <v>921</v>
       </c>
       <c r="I355" s="3" t="s">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>660</v>
+        <v>700</v>
       </c>
       <c r="K355" s="3" t="s">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="L355" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M355" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N355" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O355" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="P355" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="Q355" s="5">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R355" s="5">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="S355" s="5">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="T355" s="3" t="s">
         <v>894</v>
@@ -47634,7 +47634,7 @@
         <v>46</v>
       </c>
       <c r="AA355" s="7">
-        <v>290939</v>
+        <v>339000</v>
       </c>
       <c r="AB355" s="7">
         <v>31</v>
@@ -47705,37 +47705,37 @@
         <v>921</v>
       </c>
       <c r="I356" s="3" t="s">
-        <v>89</v>
+        <v>659</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>90</v>
+        <v>660</v>
       </c>
       <c r="K356" s="3" t="s">
-        <v>91</v>
+        <v>661</v>
       </c>
       <c r="L356" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M356" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="N356" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="O356" s="3" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P356" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="Q356" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R356" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S356" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>894</v>
@@ -47759,7 +47759,7 @@
         <v>46</v>
       </c>
       <c r="AA356" s="7">
-        <v>1246838</v>
+        <v>290939</v>
       </c>
       <c r="AB356" s="7">
         <v>31</v>
@@ -47830,37 +47830,37 @@
         <v>921</v>
       </c>
       <c r="I357" s="3" t="s">
-        <v>699</v>
+        <v>378</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>700</v>
+        <v>379</v>
       </c>
       <c r="K357" s="3" t="s">
-        <v>701</v>
+        <v>380</v>
       </c>
       <c r="L357" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M357" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="N357" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="O357" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="P357" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="Q357" s="5">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="R357" s="5">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="S357" s="5">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="T357" s="3" t="s">
         <v>894</v>
@@ -47884,7 +47884,7 @@
         <v>46</v>
       </c>
       <c r="AA357" s="7">
-        <v>339000</v>
+        <v>156000</v>
       </c>
       <c r="AB357" s="7">
         <v>31</v>
@@ -47955,13 +47955,13 @@
         <v>951</v>
       </c>
       <c r="I358" s="3" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="K358" s="3" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="L358" s="3" t="s">
         <v>50</v>
@@ -48092,22 +48092,22 @@
         <v>50</v>
       </c>
       <c r="M359" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N359" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O359" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P359" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q359" s="5">
         <v>2</v>
       </c>
       <c r="R359" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S359" s="5">
         <v>2</v>
@@ -48134,7 +48134,7 @@
         <v>46</v>
       </c>
       <c r="AA359" s="7">
-        <v>646676</v>
+        <v>1211240</v>
       </c>
       <c r="AB359" s="7">
         <v>1</v>
@@ -48205,37 +48205,37 @@
         <v>45</v>
       </c>
       <c r="I360" s="3" t="s">
-        <v>109</v>
+        <v>958</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>110</v>
+        <v>959</v>
       </c>
       <c r="K360" s="3" t="s">
-        <v>111</v>
+        <v>960</v>
       </c>
       <c r="L360" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M360" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N360" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O360" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P360" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q360" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R360" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S360" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T360" s="3" t="s">
         <v>894</v>
@@ -48259,7 +48259,7 @@
         <v>46</v>
       </c>
       <c r="AA360" s="7">
-        <v>558000</v>
+        <v>663000</v>
       </c>
       <c r="AB360" s="7">
         <v>1</v>
@@ -48286,10 +48286,10 @@
         <v>0</v>
       </c>
       <c r="AJ360" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK360" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
       <c r="AL360" s="3" t="s">
         <v>46</v>
@@ -48298,10 +48298,10 @@
         <v>46</v>
       </c>
       <c r="AN360" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO360" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
     </row>
     <row r="361" spans="1:41" x14ac:dyDescent="0.25">
@@ -48330,37 +48330,37 @@
         <v>45</v>
       </c>
       <c r="I361" s="3" t="s">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>136</v>
+        <v>287</v>
       </c>
       <c r="K361" s="3" t="s">
-        <v>137</v>
+        <v>288</v>
       </c>
       <c r="L361" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M361" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N361" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P361" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q361" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R361" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S361" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T361" s="3" t="s">
         <v>894</v>
@@ -48383,8 +48383,8 @@
       <c r="Z361" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA361" s="7">
-        <v>536250</v>
+      <c r="AA361" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB361" s="7">
         <v>1</v>
@@ -48411,10 +48411,10 @@
         <v>0</v>
       </c>
       <c r="AJ361" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK361" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
       <c r="AL361" s="3" t="s">
         <v>46</v>
@@ -48423,10 +48423,10 @@
         <v>46</v>
       </c>
       <c r="AN361" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO361" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
     </row>
     <row r="362" spans="1:41" x14ac:dyDescent="0.25">
@@ -48455,28 +48455,28 @@
         <v>45</v>
       </c>
       <c r="I362" s="3" t="s">
-        <v>144</v>
+        <v>292</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>145</v>
+        <v>293</v>
       </c>
       <c r="K362" s="3" t="s">
-        <v>146</v>
+        <v>294</v>
       </c>
       <c r="L362" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M362" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="N362" s="3" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="O362" s="3" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="P362" s="3" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="Q362" s="5">
         <v>2</v>
@@ -48509,7 +48509,7 @@
         <v>46</v>
       </c>
       <c r="AA362" s="7">
-        <v>2736757</v>
+        <v>87000</v>
       </c>
       <c r="AB362" s="7">
         <v>1</v>
@@ -48580,28 +48580,28 @@
         <v>45</v>
       </c>
       <c r="I363" s="3" t="s">
-        <v>958</v>
+        <v>728</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>959</v>
+        <v>729</v>
       </c>
       <c r="K363" s="3" t="s">
-        <v>960</v>
+        <v>730</v>
       </c>
       <c r="L363" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M363" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N363" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P363" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q363" s="5">
         <v>2</v>
@@ -48634,7 +48634,7 @@
         <v>46</v>
       </c>
       <c r="AA363" s="7">
-        <v>1211240</v>
+        <v>1567312</v>
       </c>
       <c r="AB363" s="7">
         <v>1</v>
@@ -48705,13 +48705,13 @@
         <v>45</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>961</v>
+        <v>322</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>962</v>
+        <v>323</v>
       </c>
       <c r="K364" s="3" t="s">
-        <v>963</v>
+        <v>324</v>
       </c>
       <c r="L364" s="3" t="s">
         <v>50</v>
@@ -48729,13 +48729,13 @@
         <v>108</v>
       </c>
       <c r="Q364" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R364" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S364" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T364" s="3" t="s">
         <v>894</v>
@@ -48759,7 +48759,7 @@
         <v>46</v>
       </c>
       <c r="AA364" s="7">
-        <v>663000</v>
+        <v>5131620</v>
       </c>
       <c r="AB364" s="7">
         <v>1</v>
@@ -48786,10 +48786,10 @@
         <v>0</v>
       </c>
       <c r="AJ364" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK364" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL364" s="3" t="s">
         <v>46</v>
@@ -48798,10 +48798,10 @@
         <v>46</v>
       </c>
       <c r="AN364" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO364" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="365" spans="1:41" x14ac:dyDescent="0.25">
@@ -48830,28 +48830,28 @@
         <v>45</v>
       </c>
       <c r="I365" s="3" t="s">
-        <v>722</v>
+        <v>422</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>723</v>
+        <v>423</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>724</v>
+        <v>424</v>
       </c>
       <c r="L365" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M365" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N365" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O365" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P365" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q365" s="5">
         <v>2</v>
@@ -48884,7 +48884,7 @@
         <v>46</v>
       </c>
       <c r="AA365" s="7">
-        <v>1227480</v>
+        <v>698000</v>
       </c>
       <c r="AB365" s="7">
         <v>1</v>
@@ -48955,37 +48955,37 @@
         <v>45</v>
       </c>
       <c r="I366" s="3" t="s">
-        <v>286</v>
+        <v>772</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>287</v>
+        <v>773</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>288</v>
+        <v>774</v>
       </c>
       <c r="L366" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P366" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q366" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R366" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S366" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T366" s="3" t="s">
         <v>894</v>
@@ -49008,8 +49008,8 @@
       <c r="Z366" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA366" s="3" t="s">
-        <v>46</v>
+      <c r="AA366" s="7">
+        <v>2482921</v>
       </c>
       <c r="AB366" s="7">
         <v>1</v>
@@ -49036,10 +49036,10 @@
         <v>0</v>
       </c>
       <c r="AJ366" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK366" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL366" s="3" t="s">
         <v>46</v>
@@ -49048,10 +49048,10 @@
         <v>46</v>
       </c>
       <c r="AN366" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO366" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="367" spans="1:41" x14ac:dyDescent="0.25">
@@ -49080,28 +49080,28 @@
         <v>45</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>292</v>
+        <v>464</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>293</v>
+        <v>465</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>294</v>
+        <v>466</v>
       </c>
       <c r="L367" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M367" s="3" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="N367" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="P367" s="3" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="Q367" s="5">
         <v>2</v>
@@ -49134,7 +49134,7 @@
         <v>46</v>
       </c>
       <c r="AA367" s="7">
-        <v>87000</v>
+        <v>1156433</v>
       </c>
       <c r="AB367" s="7">
         <v>1</v>
@@ -49205,28 +49205,28 @@
         <v>45</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>728</v>
+        <v>473</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>729</v>
+        <v>474</v>
       </c>
       <c r="K368" s="3" t="s">
-        <v>730</v>
+        <v>475</v>
       </c>
       <c r="L368" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M368" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N368" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P368" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q368" s="5">
         <v>2</v>
@@ -49259,7 +49259,7 @@
         <v>46</v>
       </c>
       <c r="AA368" s="7">
-        <v>1567312</v>
+        <v>839166</v>
       </c>
       <c r="AB368" s="7">
         <v>1</v>
@@ -49330,28 +49330,28 @@
         <v>45</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>930</v>
+        <v>962</v>
       </c>
       <c r="K369" s="3" t="s">
-        <v>931</v>
+        <v>963</v>
       </c>
       <c r="L369" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M369" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N369" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P369" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q369" s="5">
         <v>2</v>
@@ -49384,7 +49384,7 @@
         <v>46</v>
       </c>
       <c r="AA369" s="7">
-        <v>3025200</v>
+        <v>771000</v>
       </c>
       <c r="AB369" s="7">
         <v>1</v>
@@ -49461,31 +49461,31 @@
         <v>965</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>813</v>
+        <v>966</v>
       </c>
       <c r="L370" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M370" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P370" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q370" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R370" s="5">
         <v>2</v>
       </c>
       <c r="S370" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T370" s="3" t="s">
         <v>894</v>
@@ -49509,7 +49509,7 @@
         <v>46</v>
       </c>
       <c r="AA370" s="7">
-        <v>468000</v>
+        <v>744240</v>
       </c>
       <c r="AB370" s="7">
         <v>1</v>
@@ -49580,13 +49580,13 @@
         <v>45</v>
       </c>
       <c r="I371" s="3" t="s">
-        <v>322</v>
+        <v>925</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>323</v>
+        <v>926</v>
       </c>
       <c r="K371" s="3" t="s">
-        <v>324</v>
+        <v>927</v>
       </c>
       <c r="L371" s="3" t="s">
         <v>50</v>
@@ -49633,8 +49633,8 @@
       <c r="Z371" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA371" s="7">
-        <v>5131620</v>
+      <c r="AA371" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB371" s="7">
         <v>1</v>
@@ -49705,37 +49705,37 @@
         <v>45</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>740</v>
+        <v>393</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>741</v>
+        <v>394</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>742</v>
+        <v>395</v>
       </c>
       <c r="L372" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M372" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="P372" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="Q372" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R372" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S372" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T372" s="3" t="s">
         <v>894</v>
@@ -49759,7 +49759,7 @@
         <v>46</v>
       </c>
       <c r="AA372" s="7">
-        <v>87000</v>
+        <v>692000</v>
       </c>
       <c r="AB372" s="7">
         <v>1</v>
@@ -49786,10 +49786,10 @@
         <v>0</v>
       </c>
       <c r="AJ372" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK372" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL372" s="3" t="s">
         <v>46</v>
@@ -49798,10 +49798,10 @@
         <v>46</v>
       </c>
       <c r="AN372" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO372" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="373" spans="1:41" x14ac:dyDescent="0.25">
@@ -49955,37 +49955,37 @@
         <v>45</v>
       </c>
       <c r="I374" s="3" t="s">
-        <v>393</v>
+        <v>740</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>394</v>
+        <v>741</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>395</v>
+        <v>742</v>
       </c>
       <c r="L374" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M374" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="N374" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="P374" s="3" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="Q374" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R374" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S374" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T374" s="3" t="s">
         <v>894</v>
@@ -50009,7 +50009,7 @@
         <v>46</v>
       </c>
       <c r="AA374" s="7">
-        <v>692000</v>
+        <v>87000</v>
       </c>
       <c r="AB374" s="7">
         <v>1</v>
@@ -50036,10 +50036,10 @@
         <v>0</v>
       </c>
       <c r="AJ374" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK374" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL374" s="3" t="s">
         <v>46</v>
@@ -50048,10 +50048,10 @@
         <v>46</v>
       </c>
       <c r="AN374" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO374" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="375" spans="1:41" x14ac:dyDescent="0.25">
@@ -50080,37 +50080,37 @@
         <v>45</v>
       </c>
       <c r="I375" s="3" t="s">
-        <v>925</v>
+        <v>967</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>926</v>
+        <v>968</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>927</v>
+        <v>813</v>
       </c>
       <c r="L375" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M375" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N375" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O375" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P375" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q375" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R375" s="5">
         <v>2</v>
       </c>
       <c r="S375" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T375" s="3" t="s">
         <v>894</v>
@@ -50133,8 +50133,8 @@
       <c r="Z375" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA375" s="3" t="s">
-        <v>46</v>
+      <c r="AA375" s="7">
+        <v>468000</v>
       </c>
       <c r="AB375" s="7">
         <v>1</v>
@@ -50205,28 +50205,28 @@
         <v>45</v>
       </c>
       <c r="I376" s="3" t="s">
-        <v>966</v>
+        <v>929</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>967</v>
+        <v>930</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>968</v>
+        <v>931</v>
       </c>
       <c r="L376" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M376" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N376" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P376" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q376" s="5">
         <v>2</v>
@@ -50259,7 +50259,7 @@
         <v>46</v>
       </c>
       <c r="AA376" s="7">
-        <v>744240</v>
+        <v>3025200</v>
       </c>
       <c r="AB376" s="7">
         <v>1</v>
@@ -50330,28 +50330,28 @@
         <v>45</v>
       </c>
       <c r="I377" s="3" t="s">
-        <v>969</v>
+        <v>722</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>970</v>
+        <v>723</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>971</v>
+        <v>724</v>
       </c>
       <c r="L377" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M377" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N377" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P377" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q377" s="5">
         <v>2</v>
@@ -50384,7 +50384,7 @@
         <v>46</v>
       </c>
       <c r="AA377" s="7">
-        <v>771000</v>
+        <v>1227480</v>
       </c>
       <c r="AB377" s="7">
         <v>1</v>
@@ -50455,28 +50455,28 @@
         <v>45</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>422</v>
+        <v>144</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>423</v>
+        <v>145</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>424</v>
+        <v>146</v>
       </c>
       <c r="L378" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M378" s="3" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="N378" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="O378" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="P378" s="3" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="Q378" s="5">
         <v>2</v>
@@ -50509,7 +50509,7 @@
         <v>46</v>
       </c>
       <c r="AA378" s="7">
-        <v>698000</v>
+        <v>2736757</v>
       </c>
       <c r="AB378" s="7">
         <v>1</v>
@@ -50580,28 +50580,28 @@
         <v>45</v>
       </c>
       <c r="I379" s="3" t="s">
-        <v>772</v>
+        <v>135</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>773</v>
+        <v>136</v>
       </c>
       <c r="K379" s="3" t="s">
-        <v>774</v>
+        <v>137</v>
       </c>
       <c r="L379" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M379" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N379" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P379" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q379" s="5">
         <v>2</v>
@@ -50634,7 +50634,7 @@
         <v>46</v>
       </c>
       <c r="AA379" s="7">
-        <v>2482921</v>
+        <v>536250</v>
       </c>
       <c r="AB379" s="7">
         <v>1</v>
@@ -50705,28 +50705,28 @@
         <v>45</v>
       </c>
       <c r="I380" s="3" t="s">
-        <v>464</v>
+        <v>109</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>465</v>
+        <v>110</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="L380" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M380" s="3" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N380" s="3" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="O380" s="3" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="P380" s="3" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="Q380" s="5">
         <v>2</v>
@@ -50759,7 +50759,7 @@
         <v>46</v>
       </c>
       <c r="AA380" s="7">
-        <v>1156433</v>
+        <v>558000</v>
       </c>
       <c r="AB380" s="7">
         <v>1</v>
@@ -50830,34 +50830,34 @@
         <v>45</v>
       </c>
       <c r="I381" s="3" t="s">
-        <v>473</v>
+        <v>969</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>474</v>
+        <v>970</v>
       </c>
       <c r="K381" s="3" t="s">
-        <v>475</v>
+        <v>971</v>
       </c>
       <c r="L381" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M381" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N381" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P381" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q381" s="5">
         <v>2</v>
       </c>
       <c r="R381" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S381" s="5">
         <v>2</v>
@@ -50884,7 +50884,7 @@
         <v>46</v>
       </c>
       <c r="AA381" s="7">
-        <v>839166</v>
+        <v>646676</v>
       </c>
       <c r="AB381" s="7">
         <v>1</v>
@@ -50967,16 +50967,16 @@
         <v>50</v>
       </c>
       <c r="M382" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N382" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O382" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P382" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q382" s="5">
         <v>2</v>
@@ -51009,7 +51009,7 @@
         <v>46</v>
       </c>
       <c r="AA382" s="7">
-        <v>384000</v>
+        <v>362000</v>
       </c>
       <c r="AB382" s="7">
         <v>1</v>
@@ -51217,16 +51217,16 @@
         <v>50</v>
       </c>
       <c r="M384" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N384" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O384" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P384" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q384" s="5">
         <v>2</v>
@@ -51259,7 +51259,7 @@
         <v>46</v>
       </c>
       <c r="AA384" s="7">
-        <v>362000</v>
+        <v>384000</v>
       </c>
       <c r="AB384" s="7">
         <v>1</v>
@@ -52455,13 +52455,13 @@
         <v>45</v>
       </c>
       <c r="I394" s="3" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="L394" s="3" t="s">
         <v>50</v>
@@ -53205,13 +53205,13 @@
         <v>45</v>
       </c>
       <c r="I400" s="3" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="L400" s="3" t="s">
         <v>50</v>
@@ -53729,13 +53729,13 @@
         <v>128</v>
       </c>
       <c r="Q404" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R404" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S404" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T404" s="3" t="s">
         <v>894</v>
@@ -55205,10 +55205,10 @@
         <v>999</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>813</v>
@@ -57604,13 +57604,13 @@
         <v>156</v>
       </c>
       <c r="Q435" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R435" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S435" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T435" s="3" t="s">
         <v>894</v>
@@ -58729,13 +58729,13 @@
         <v>134</v>
       </c>
       <c r="Q444" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R444" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S444" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T444" s="3" t="s">
         <v>894</v>
@@ -60205,13 +60205,13 @@
         <v>921</v>
       </c>
       <c r="I456" s="3" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="J456" s="3" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="L456" s="3" t="s">
         <v>50</v>
@@ -60854,13 +60854,13 @@
         <v>128</v>
       </c>
       <c r="Q461" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R461" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S461" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T461" s="3" t="s">
         <v>894</v>
@@ -61354,13 +61354,13 @@
         <v>156</v>
       </c>
       <c r="Q465" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R465" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S465" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T465" s="3" t="s">
         <v>894</v>
@@ -61455,13 +61455,13 @@
         <v>45</v>
       </c>
       <c r="I466" s="3" t="s">
-        <v>955</v>
+        <v>969</v>
       </c>
       <c r="J466" s="3" t="s">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>957</v>
+        <v>971</v>
       </c>
       <c r="L466" s="3" t="s">
         <v>50</v>
@@ -61854,13 +61854,13 @@
         <v>156</v>
       </c>
       <c r="Q469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T469" s="3" t="s">
         <v>894</v>
@@ -62229,13 +62229,13 @@
         <v>156</v>
       </c>
       <c r="Q472" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R472" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S472" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T472" s="3" t="s">
         <v>894</v>
@@ -62354,13 +62354,13 @@
         <v>156</v>
       </c>
       <c r="Q473" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R473" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S473" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T473" s="3" t="s">
         <v>894</v>
@@ -62604,13 +62604,13 @@
         <v>156</v>
       </c>
       <c r="Q475" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R475" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S475" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T475" s="3" t="s">
         <v>894</v>
@@ -62705,10 +62705,10 @@
         <v>45</v>
       </c>
       <c r="I476" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="J476" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="K476" s="3" t="s">
         <v>813</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -2713,6 +2713,15 @@
     <t>Active</t>
   </si>
   <si>
+    <t>3362</t>
+  </si>
+  <si>
+    <t>Thủy Kết</t>
+  </si>
+  <si>
+    <t>107, Lò Lu</t>
+  </si>
+  <si>
     <t>999754600</t>
   </si>
   <si>
@@ -2758,15 +2767,6 @@
     <t>40 Cảng Phú Hữu, Nguyễn Duy Trinh</t>
   </si>
   <si>
-    <t>3362</t>
-  </si>
-  <si>
-    <t>Thủy Kết</t>
-  </si>
-  <si>
-    <t>107, Lò Lu</t>
-  </si>
-  <si>
     <t>1-6JP933U</t>
   </si>
   <si>
@@ -2878,6 +2878,15 @@
     <t>MSC_BEV_Chương trình TBTN_Tủ mát Nước giải khát_HCM_All2026_T10</t>
   </si>
   <si>
+    <t>2128924</t>
+  </si>
+  <si>
+    <t>Tạp Hoá Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>22/10 Đường 990, Nguyễn Duy Trinh</t>
+  </si>
+  <si>
     <t>2432200</t>
   </si>
   <si>
@@ -2896,6 +2905,21 @@
     <t>242, Đường 57 - CL</t>
   </si>
   <si>
+    <t>2894640</t>
+  </si>
+  <si>
+    <t>Mino Mart</t>
+  </si>
+  <si>
+    <t>3063948</t>
+  </si>
+  <si>
+    <t>Cà Phê Chị Tuyết</t>
+  </si>
+  <si>
+    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
+  </si>
+  <si>
     <t>3136368</t>
   </si>
   <si>
@@ -2905,28 +2929,13 @@
     <t>35 Đường Số 12, Bưng Ông Thoàn</t>
   </si>
   <si>
-    <t>3063948</t>
-  </si>
-  <si>
-    <t>Cà Phê Chị Tuyết</t>
-  </si>
-  <si>
-    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
-  </si>
-  <si>
-    <t>2894640</t>
-  </si>
-  <si>
-    <t>Mino Mart</t>
-  </si>
-  <si>
-    <t>2128924</t>
-  </si>
-  <si>
-    <t>Tạp Hoá Hồng Ngọc</t>
-  </si>
-  <si>
-    <t>22/10 Đường 990, Nguyễn Duy Trinh</t>
+    <t>999115327</t>
+  </si>
+  <si>
+    <t>Hà Thủy</t>
+  </si>
+  <si>
+    <t>Số 313, Lê Văn Thịnh</t>
   </si>
   <si>
     <t>999191040</t>
@@ -2936,15 +2945,6 @@
   </si>
   <si>
     <t>250, Trường Lưu</t>
-  </si>
-  <si>
-    <t>999115327</t>
-  </si>
-  <si>
-    <t>Hà Thủy</t>
-  </si>
-  <si>
-    <t>Số 313, Lê Văn Thịnh</t>
   </si>
   <si>
     <t>999210374</t>
@@ -42092,16 +42092,16 @@
         <v>50</v>
       </c>
       <c r="M311" s="3" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="N311" s="3" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="P311" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="Q311" s="3" t="s">
         <v>46</v>
@@ -42134,7 +42134,7 @@
         <v>10</v>
       </c>
       <c r="AA311" s="7">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AB311" s="7">
         <v>1</v>
@@ -42164,7 +42164,7 @@
         <v>58</v>
       </c>
       <c r="AK311" s="6">
-        <v>46312.58308098379</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>46</v>
@@ -42176,7 +42176,7 @@
         <v>58</v>
       </c>
       <c r="AO311" s="6">
-        <v>46312.58308098379</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="312" spans="1:41" x14ac:dyDescent="0.25">
@@ -42217,16 +42217,16 @@
         <v>50</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q312" s="3" t="s">
         <v>46</v>
@@ -42259,7 +42259,7 @@
         <v>10</v>
       </c>
       <c r="AA312" s="7">
-        <v>10</v>
+        <v>10.75</v>
       </c>
       <c r="AB312" s="7">
         <v>1</v>
@@ -42289,7 +42289,7 @@
         <v>58</v>
       </c>
       <c r="AK312" s="6">
-        <v>46310.439036655094</v>
+        <v>46312.58308098379</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>46</v>
@@ -42301,7 +42301,7 @@
         <v>58</v>
       </c>
       <c r="AO312" s="6">
-        <v>46310.439036655094</v>
+        <v>46312.58308098379</v>
       </c>
     </row>
     <row r="313" spans="1:41" x14ac:dyDescent="0.25">
@@ -42342,16 +42342,16 @@
         <v>50</v>
       </c>
       <c r="M313" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N313" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P313" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Q313" s="3" t="s">
         <v>46</v>
@@ -42414,7 +42414,7 @@
         <v>58</v>
       </c>
       <c r="AK313" s="6">
-        <v>46301.30899568287</v>
+        <v>46310.439036655094</v>
       </c>
       <c r="AL313" s="3" t="s">
         <v>46</v>
@@ -42426,7 +42426,7 @@
         <v>58</v>
       </c>
       <c r="AO313" s="6">
-        <v>46301.30899568287</v>
+        <v>46310.439036655094</v>
       </c>
     </row>
     <row r="314" spans="1:41" x14ac:dyDescent="0.25">
@@ -42455,28 +42455,28 @@
         <v>45</v>
       </c>
       <c r="I314" s="3" t="s">
-        <v>271</v>
+        <v>909</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>272</v>
+        <v>910</v>
       </c>
       <c r="K314" s="3" t="s">
-        <v>273</v>
+        <v>911</v>
       </c>
       <c r="L314" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M314" s="3" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="N314" s="3" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="O314" s="3" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="P314" s="3" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="Q314" s="3" t="s">
         <v>46</v>
@@ -42539,7 +42539,7 @@
         <v>58</v>
       </c>
       <c r="AK314" s="6">
-        <v>46301.5776272338</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL314" s="3" t="s">
         <v>46</v>
@@ -42551,7 +42551,7 @@
         <v>58</v>
       </c>
       <c r="AO314" s="6">
-        <v>46301.5776272338</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="315" spans="1:41" x14ac:dyDescent="0.25">
@@ -42580,28 +42580,28 @@
         <v>45</v>
       </c>
       <c r="I315" s="3" t="s">
-        <v>322</v>
+        <v>271</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="K315" s="3" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="L315" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M315" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="N315" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="O315" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="P315" s="3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="Q315" s="3" t="s">
         <v>46</v>
@@ -42634,7 +42634,7 @@
         <v>10</v>
       </c>
       <c r="AA315" s="7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB315" s="7">
         <v>1</v>
@@ -42664,7 +42664,7 @@
         <v>58</v>
       </c>
       <c r="AK315" s="6">
-        <v>46303.59483915509</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL315" s="3" t="s">
         <v>46</v>
@@ -42676,7 +42676,7 @@
         <v>58</v>
       </c>
       <c r="AO315" s="6">
-        <v>46303.59483915509</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="316" spans="1:41" x14ac:dyDescent="0.25">
@@ -42705,28 +42705,28 @@
         <v>45</v>
       </c>
       <c r="I316" s="3" t="s">
-        <v>150</v>
+        <v>322</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>151</v>
+        <v>323</v>
       </c>
       <c r="K316" s="3" t="s">
-        <v>152</v>
+        <v>324</v>
       </c>
       <c r="L316" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M316" s="3" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="N316" s="3" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="O316" s="3" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="P316" s="3" t="s">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="Q316" s="3" t="s">
         <v>46</v>
@@ -42759,7 +42759,7 @@
         <v>10</v>
       </c>
       <c r="AA316" s="7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB316" s="7">
         <v>1</v>
@@ -42789,7 +42789,7 @@
         <v>58</v>
       </c>
       <c r="AK316" s="6">
-        <v>46298.66540524305</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL316" s="3" t="s">
         <v>46</v>
@@ -42801,7 +42801,7 @@
         <v>58</v>
       </c>
       <c r="AO316" s="6">
-        <v>46298.66540524305</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="317" spans="1:41" x14ac:dyDescent="0.25">
@@ -42830,28 +42830,28 @@
         <v>45</v>
       </c>
       <c r="I317" s="3" t="s">
-        <v>909</v>
+        <v>150</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>910</v>
+        <v>151</v>
       </c>
       <c r="K317" s="3" t="s">
-        <v>911</v>
+        <v>152</v>
       </c>
       <c r="L317" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M317" s="3" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="N317" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="O317" s="3" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="P317" s="3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="Q317" s="3" t="s">
         <v>46</v>
@@ -42967,16 +42967,16 @@
         <v>50</v>
       </c>
       <c r="M318" s="3" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="P318" s="3" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="Q318" s="3" t="s">
         <v>46</v>
@@ -43039,7 +43039,7 @@
         <v>58</v>
       </c>
       <c r="AK318" s="6">
-        <v>46316.79383703704</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL318" s="3" t="s">
         <v>46</v>
@@ -43051,7 +43051,7 @@
         <v>58</v>
       </c>
       <c r="AO318" s="6">
-        <v>46316.79383703704</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="319" spans="1:41" x14ac:dyDescent="0.25">
@@ -43080,28 +43080,28 @@
         <v>45</v>
       </c>
       <c r="I319" s="3" t="s">
-        <v>138</v>
+        <v>915</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>139</v>
+        <v>916</v>
       </c>
       <c r="K319" s="3" t="s">
-        <v>140</v>
+        <v>917</v>
       </c>
       <c r="L319" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M319" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N319" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P319" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q319" s="3" t="s">
         <v>46</v>
@@ -43134,7 +43134,7 @@
         <v>10</v>
       </c>
       <c r="AA319" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB319" s="7">
         <v>1</v>
@@ -43164,7 +43164,7 @@
         <v>58</v>
       </c>
       <c r="AK319" s="6">
-        <v>46303.59483915509</v>
+        <v>46316.79383703704</v>
       </c>
       <c r="AL319" s="3" t="s">
         <v>46</v>
@@ -43176,7 +43176,7 @@
         <v>58</v>
       </c>
       <c r="AO319" s="6">
-        <v>46303.59483915509</v>
+        <v>46316.79383703704</v>
       </c>
     </row>
     <row r="320" spans="1:41" x14ac:dyDescent="0.25">
@@ -43205,28 +43205,28 @@
         <v>45</v>
       </c>
       <c r="I320" s="3" t="s">
-        <v>915</v>
+        <v>138</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>916</v>
+        <v>139</v>
       </c>
       <c r="K320" s="3" t="s">
-        <v>917</v>
+        <v>140</v>
       </c>
       <c r="L320" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N320" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O320" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P320" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Q320" s="3" t="s">
         <v>46</v>
@@ -43259,7 +43259,7 @@
         <v>10</v>
       </c>
       <c r="AA320" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB320" s="7">
         <v>1</v>
@@ -43289,7 +43289,7 @@
         <v>58</v>
       </c>
       <c r="AK320" s="6">
-        <v>46298.66540524305</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL320" s="3" t="s">
         <v>46</v>
@@ -43301,7 +43301,7 @@
         <v>58</v>
       </c>
       <c r="AO320" s="6">
-        <v>46298.66540524305</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="321" spans="1:41" x14ac:dyDescent="0.25">
@@ -46455,37 +46455,37 @@
         <v>921</v>
       </c>
       <c r="I346" s="3" t="s">
-        <v>939</v>
+        <v>378</v>
       </c>
       <c r="J346" s="3" t="s">
-        <v>744</v>
+        <v>379</v>
       </c>
       <c r="K346" s="3" t="s">
-        <v>940</v>
+        <v>380</v>
       </c>
       <c r="L346" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M346" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="N346" s="3" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="O346" s="3" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="P346" s="3" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="Q346" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R346" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S346" s="5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T346" s="3" t="s">
         <v>894</v>
@@ -46509,7 +46509,7 @@
         <v>46</v>
       </c>
       <c r="AA346" s="7">
-        <v>2416326</v>
+        <v>156000</v>
       </c>
       <c r="AB346" s="7">
         <v>31</v>
@@ -46580,37 +46580,37 @@
         <v>921</v>
       </c>
       <c r="I347" s="3" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="J347" s="3" t="s">
-        <v>949</v>
+        <v>744</v>
       </c>
       <c r="K347" s="3" t="s">
-        <v>950</v>
+        <v>940</v>
       </c>
       <c r="L347" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M347" s="3" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="N347" s="3" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="O347" s="3" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="P347" s="3" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="Q347" s="5">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="R347" s="5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="S347" s="5">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="T347" s="3" t="s">
         <v>894</v>
@@ -46634,7 +46634,7 @@
         <v>46</v>
       </c>
       <c r="AA347" s="7">
-        <v>2359523</v>
+        <v>2416326</v>
       </c>
       <c r="AB347" s="7">
         <v>31</v>
@@ -46705,37 +46705,37 @@
         <v>921</v>
       </c>
       <c r="I348" s="3" t="s">
-        <v>755</v>
+        <v>948</v>
       </c>
       <c r="J348" s="3" t="s">
-        <v>756</v>
+        <v>949</v>
       </c>
       <c r="K348" s="3" t="s">
-        <v>757</v>
+        <v>950</v>
       </c>
       <c r="L348" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M348" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N348" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="O348" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="P348" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Q348" s="5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="R348" s="5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="S348" s="5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="T348" s="3" t="s">
         <v>894</v>
@@ -46759,7 +46759,7 @@
         <v>46</v>
       </c>
       <c r="AA348" s="7">
-        <v>2580460</v>
+        <v>2359523</v>
       </c>
       <c r="AB348" s="7">
         <v>31</v>
@@ -46830,37 +46830,37 @@
         <v>921</v>
       </c>
       <c r="I349" s="3" t="s">
-        <v>464</v>
+        <v>755</v>
       </c>
       <c r="J349" s="3" t="s">
-        <v>465</v>
+        <v>756</v>
       </c>
       <c r="K349" s="3" t="s">
-        <v>466</v>
+        <v>757</v>
       </c>
       <c r="L349" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M349" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N349" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O349" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="P349" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="Q349" s="5">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="R349" s="5">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="S349" s="5">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="T349" s="3" t="s">
         <v>894</v>
@@ -46884,7 +46884,7 @@
         <v>46</v>
       </c>
       <c r="AA349" s="7">
-        <v>570000</v>
+        <v>2580460</v>
       </c>
       <c r="AB349" s="7">
         <v>31</v>
@@ -46955,13 +46955,13 @@
         <v>921</v>
       </c>
       <c r="I350" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="J350" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="K350" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="L350" s="3" t="s">
         <v>50</v>
@@ -46979,13 +46979,13 @@
         <v>128</v>
       </c>
       <c r="Q350" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="R350" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="S350" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="T350" s="3" t="s">
         <v>894</v>
@@ -47009,7 +47009,7 @@
         <v>46</v>
       </c>
       <c r="AA350" s="7">
-        <v>925650</v>
+        <v>570000</v>
       </c>
       <c r="AB350" s="7">
         <v>31</v>
@@ -47080,13 +47080,13 @@
         <v>921</v>
       </c>
       <c r="I351" s="3" t="s">
-        <v>535</v>
+        <v>473</v>
       </c>
       <c r="J351" s="3" t="s">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="K351" s="3" t="s">
-        <v>537</v>
+        <v>475</v>
       </c>
       <c r="L351" s="3" t="s">
         <v>50</v>
@@ -47104,13 +47104,13 @@
         <v>128</v>
       </c>
       <c r="Q351" s="5">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R351" s="5">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="S351" s="5">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="T351" s="3" t="s">
         <v>894</v>
@@ -47134,7 +47134,7 @@
         <v>46</v>
       </c>
       <c r="AA351" s="7">
-        <v>590000</v>
+        <v>925650</v>
       </c>
       <c r="AB351" s="7">
         <v>31</v>
@@ -47205,13 +47205,13 @@
         <v>921</v>
       </c>
       <c r="I352" s="3" t="s">
-        <v>575</v>
+        <v>535</v>
       </c>
       <c r="J352" s="3" t="s">
-        <v>576</v>
+        <v>536</v>
       </c>
       <c r="K352" s="3" t="s">
-        <v>577</v>
+        <v>537</v>
       </c>
       <c r="L352" s="3" t="s">
         <v>50</v>
@@ -47229,13 +47229,13 @@
         <v>128</v>
       </c>
       <c r="Q352" s="5">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="R352" s="5">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="S352" s="5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="T352" s="3" t="s">
         <v>894</v>
@@ -47259,7 +47259,7 @@
         <v>46</v>
       </c>
       <c r="AA352" s="7">
-        <v>2566500</v>
+        <v>590000</v>
       </c>
       <c r="AB352" s="7">
         <v>31</v>
@@ -47330,13 +47330,13 @@
         <v>921</v>
       </c>
       <c r="I353" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="J353" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="K353" s="3" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="L353" s="3" t="s">
         <v>50</v>
@@ -47354,13 +47354,13 @@
         <v>128</v>
       </c>
       <c r="Q353" s="5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="R353" s="5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="S353" s="5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="T353" s="3" t="s">
         <v>894</v>
@@ -47383,8 +47383,8 @@
       <c r="Z353" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA353" s="3" t="s">
-        <v>46</v>
+      <c r="AA353" s="7">
+        <v>2566500</v>
       </c>
       <c r="AB353" s="7">
         <v>31</v>
@@ -47455,37 +47455,37 @@
         <v>921</v>
       </c>
       <c r="I354" s="3" t="s">
-        <v>89</v>
+        <v>578</v>
       </c>
       <c r="J354" s="3" t="s">
-        <v>90</v>
+        <v>579</v>
       </c>
       <c r="K354" s="3" t="s">
-        <v>91</v>
+        <v>580</v>
       </c>
       <c r="L354" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M354" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="N354" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="O354" s="3" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P354" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="Q354" s="5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R354" s="5">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="S354" s="5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="T354" s="3" t="s">
         <v>894</v>
@@ -47508,8 +47508,8 @@
       <c r="Z354" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA354" s="7">
-        <v>1246838</v>
+      <c r="AA354" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB354" s="7">
         <v>31</v>
@@ -47580,37 +47580,37 @@
         <v>921</v>
       </c>
       <c r="I355" s="3" t="s">
-        <v>699</v>
+        <v>659</v>
       </c>
       <c r="J355" s="3" t="s">
-        <v>700</v>
+        <v>660</v>
       </c>
       <c r="K355" s="3" t="s">
-        <v>701</v>
+        <v>661</v>
       </c>
       <c r="L355" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M355" s="3" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="N355" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="O355" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="P355" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="Q355" s="5">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="R355" s="5">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="S355" s="5">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="T355" s="3" t="s">
         <v>894</v>
@@ -47634,7 +47634,7 @@
         <v>46</v>
       </c>
       <c r="AA355" s="7">
-        <v>339000</v>
+        <v>290939</v>
       </c>
       <c r="AB355" s="7">
         <v>31</v>
@@ -47705,37 +47705,37 @@
         <v>921</v>
       </c>
       <c r="I356" s="3" t="s">
-        <v>659</v>
+        <v>89</v>
       </c>
       <c r="J356" s="3" t="s">
-        <v>660</v>
+        <v>90</v>
       </c>
       <c r="K356" s="3" t="s">
-        <v>661</v>
+        <v>91</v>
       </c>
       <c r="L356" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M356" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="N356" s="3" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O356" s="3" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="P356" s="3" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="Q356" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R356" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S356" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>894</v>
@@ -47759,7 +47759,7 @@
         <v>46</v>
       </c>
       <c r="AA356" s="7">
-        <v>290939</v>
+        <v>1246838</v>
       </c>
       <c r="AB356" s="7">
         <v>31</v>
@@ -47830,37 +47830,37 @@
         <v>921</v>
       </c>
       <c r="I357" s="3" t="s">
-        <v>378</v>
+        <v>699</v>
       </c>
       <c r="J357" s="3" t="s">
-        <v>379</v>
+        <v>700</v>
       </c>
       <c r="K357" s="3" t="s">
-        <v>380</v>
+        <v>701</v>
       </c>
       <c r="L357" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M357" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N357" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O357" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="P357" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="Q357" s="5">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="R357" s="5">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="S357" s="5">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="T357" s="3" t="s">
         <v>894</v>
@@ -47884,7 +47884,7 @@
         <v>46</v>
       </c>
       <c r="AA357" s="7">
-        <v>156000</v>
+        <v>339000</v>
       </c>
       <c r="AB357" s="7">
         <v>31</v>
@@ -47955,13 +47955,13 @@
         <v>951</v>
       </c>
       <c r="I358" s="3" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="K358" s="3" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="L358" s="3" t="s">
         <v>50</v>
@@ -48092,22 +48092,22 @@
         <v>50</v>
       </c>
       <c r="M359" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N359" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O359" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P359" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q359" s="5">
         <v>2</v>
       </c>
       <c r="R359" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S359" s="5">
         <v>2</v>
@@ -48134,7 +48134,7 @@
         <v>46</v>
       </c>
       <c r="AA359" s="7">
-        <v>1211240</v>
+        <v>646676</v>
       </c>
       <c r="AB359" s="7">
         <v>1</v>
@@ -48205,37 +48205,37 @@
         <v>45</v>
       </c>
       <c r="I360" s="3" t="s">
-        <v>958</v>
+        <v>109</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>959</v>
+        <v>110</v>
       </c>
       <c r="K360" s="3" t="s">
-        <v>960</v>
+        <v>111</v>
       </c>
       <c r="L360" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M360" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N360" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O360" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P360" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T360" s="3" t="s">
         <v>894</v>
@@ -48259,7 +48259,7 @@
         <v>46</v>
       </c>
       <c r="AA360" s="7">
-        <v>663000</v>
+        <v>558000</v>
       </c>
       <c r="AB360" s="7">
         <v>1</v>
@@ -48286,10 +48286,10 @@
         <v>0</v>
       </c>
       <c r="AJ360" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK360" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL360" s="3" t="s">
         <v>46</v>
@@ -48298,10 +48298,10 @@
         <v>46</v>
       </c>
       <c r="AN360" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO360" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="361" spans="1:41" x14ac:dyDescent="0.25">
@@ -48330,37 +48330,37 @@
         <v>45</v>
       </c>
       <c r="I361" s="3" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="K361" s="3" t="s">
-        <v>288</v>
+        <v>137</v>
       </c>
       <c r="L361" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M361" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N361" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P361" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T361" s="3" t="s">
         <v>894</v>
@@ -48383,8 +48383,8 @@
       <c r="Z361" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA361" s="3" t="s">
-        <v>46</v>
+      <c r="AA361" s="7">
+        <v>536250</v>
       </c>
       <c r="AB361" s="7">
         <v>1</v>
@@ -48411,10 +48411,10 @@
         <v>0</v>
       </c>
       <c r="AJ361" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK361" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL361" s="3" t="s">
         <v>46</v>
@@ -48423,10 +48423,10 @@
         <v>46</v>
       </c>
       <c r="AN361" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO361" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="362" spans="1:41" x14ac:dyDescent="0.25">
@@ -48455,28 +48455,28 @@
         <v>45</v>
       </c>
       <c r="I362" s="3" t="s">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="K362" s="3" t="s">
-        <v>294</v>
+        <v>146</v>
       </c>
       <c r="L362" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M362" s="3" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="N362" s="3" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="O362" s="3" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="P362" s="3" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="Q362" s="5">
         <v>2</v>
@@ -48509,7 +48509,7 @@
         <v>46</v>
       </c>
       <c r="AA362" s="7">
-        <v>87000</v>
+        <v>2736757</v>
       </c>
       <c r="AB362" s="7">
         <v>1</v>
@@ -48580,28 +48580,28 @@
         <v>45</v>
       </c>
       <c r="I363" s="3" t="s">
-        <v>728</v>
+        <v>958</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>729</v>
+        <v>959</v>
       </c>
       <c r="K363" s="3" t="s">
-        <v>730</v>
+        <v>960</v>
       </c>
       <c r="L363" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M363" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N363" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P363" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q363" s="5">
         <v>2</v>
@@ -48634,7 +48634,7 @@
         <v>46</v>
       </c>
       <c r="AA363" s="7">
-        <v>1567312</v>
+        <v>1211240</v>
       </c>
       <c r="AB363" s="7">
         <v>1</v>
@@ -48705,13 +48705,13 @@
         <v>45</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>322</v>
+        <v>961</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>323</v>
+        <v>962</v>
       </c>
       <c r="K364" s="3" t="s">
-        <v>324</v>
+        <v>963</v>
       </c>
       <c r="L364" s="3" t="s">
         <v>50</v>
@@ -48729,13 +48729,13 @@
         <v>108</v>
       </c>
       <c r="Q364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T364" s="3" t="s">
         <v>894</v>
@@ -48759,7 +48759,7 @@
         <v>46</v>
       </c>
       <c r="AA364" s="7">
-        <v>5131620</v>
+        <v>663000</v>
       </c>
       <c r="AB364" s="7">
         <v>1</v>
@@ -48786,10 +48786,10 @@
         <v>0</v>
       </c>
       <c r="AJ364" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK364" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
       <c r="AL364" s="3" t="s">
         <v>46</v>
@@ -48798,10 +48798,10 @@
         <v>46</v>
       </c>
       <c r="AN364" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO364" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
     </row>
     <row r="365" spans="1:41" x14ac:dyDescent="0.25">
@@ -48830,28 +48830,28 @@
         <v>45</v>
       </c>
       <c r="I365" s="3" t="s">
-        <v>422</v>
+        <v>722</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>423</v>
+        <v>723</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>424</v>
+        <v>724</v>
       </c>
       <c r="L365" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M365" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N365" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O365" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P365" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q365" s="5">
         <v>2</v>
@@ -48884,7 +48884,7 @@
         <v>46</v>
       </c>
       <c r="AA365" s="7">
-        <v>698000</v>
+        <v>1227480</v>
       </c>
       <c r="AB365" s="7">
         <v>1</v>
@@ -48955,37 +48955,37 @@
         <v>45</v>
       </c>
       <c r="I366" s="3" t="s">
-        <v>772</v>
+        <v>286</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>773</v>
+        <v>287</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>774</v>
+        <v>288</v>
       </c>
       <c r="L366" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P366" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T366" s="3" t="s">
         <v>894</v>
@@ -49008,8 +49008,8 @@
       <c r="Z366" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA366" s="7">
-        <v>2482921</v>
+      <c r="AA366" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB366" s="7">
         <v>1</v>
@@ -49036,10 +49036,10 @@
         <v>0</v>
       </c>
       <c r="AJ366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
       <c r="AL366" s="3" t="s">
         <v>46</v>
@@ -49048,10 +49048,10 @@
         <v>46</v>
       </c>
       <c r="AN366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
     </row>
     <row r="367" spans="1:41" x14ac:dyDescent="0.25">
@@ -49080,28 +49080,28 @@
         <v>45</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>464</v>
+        <v>292</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>465</v>
+        <v>293</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>466</v>
+        <v>294</v>
       </c>
       <c r="L367" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M367" s="3" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N367" s="3" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="P367" s="3" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="Q367" s="5">
         <v>2</v>
@@ -49134,7 +49134,7 @@
         <v>46</v>
       </c>
       <c r="AA367" s="7">
-        <v>1156433</v>
+        <v>87000</v>
       </c>
       <c r="AB367" s="7">
         <v>1</v>
@@ -49205,28 +49205,28 @@
         <v>45</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>473</v>
+        <v>728</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>474</v>
+        <v>729</v>
       </c>
       <c r="K368" s="3" t="s">
-        <v>475</v>
+        <v>730</v>
       </c>
       <c r="L368" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M368" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N368" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P368" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q368" s="5">
         <v>2</v>
@@ -49259,7 +49259,7 @@
         <v>46</v>
       </c>
       <c r="AA368" s="7">
-        <v>839166</v>
+        <v>1567312</v>
       </c>
       <c r="AB368" s="7">
         <v>1</v>
@@ -49330,28 +49330,28 @@
         <v>45</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>961</v>
+        <v>929</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>962</v>
+        <v>930</v>
       </c>
       <c r="K369" s="3" t="s">
-        <v>963</v>
+        <v>931</v>
       </c>
       <c r="L369" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M369" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N369" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P369" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q369" s="5">
         <v>2</v>
@@ -49384,7 +49384,7 @@
         <v>46</v>
       </c>
       <c r="AA369" s="7">
-        <v>771000</v>
+        <v>3025200</v>
       </c>
       <c r="AB369" s="7">
         <v>1</v>
@@ -49461,31 +49461,31 @@
         <v>965</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>966</v>
+        <v>813</v>
       </c>
       <c r="L370" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M370" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P370" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R370" s="5">
         <v>2</v>
       </c>
       <c r="S370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T370" s="3" t="s">
         <v>894</v>
@@ -49509,7 +49509,7 @@
         <v>46</v>
       </c>
       <c r="AA370" s="7">
-        <v>744240</v>
+        <v>468000</v>
       </c>
       <c r="AB370" s="7">
         <v>1</v>
@@ -49580,13 +49580,13 @@
         <v>45</v>
       </c>
       <c r="I371" s="3" t="s">
-        <v>925</v>
+        <v>322</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>926</v>
+        <v>323</v>
       </c>
       <c r="K371" s="3" t="s">
-        <v>927</v>
+        <v>324</v>
       </c>
       <c r="L371" s="3" t="s">
         <v>50</v>
@@ -49633,8 +49633,8 @@
       <c r="Z371" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA371" s="3" t="s">
-        <v>46</v>
+      <c r="AA371" s="7">
+        <v>5131620</v>
       </c>
       <c r="AB371" s="7">
         <v>1</v>
@@ -49705,37 +49705,37 @@
         <v>45</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>393</v>
+        <v>740</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>394</v>
+        <v>741</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>395</v>
+        <v>742</v>
       </c>
       <c r="L372" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M372" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="P372" s="3" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="Q372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T372" s="3" t="s">
         <v>894</v>
@@ -49759,7 +49759,7 @@
         <v>46</v>
       </c>
       <c r="AA372" s="7">
-        <v>692000</v>
+        <v>87000</v>
       </c>
       <c r="AB372" s="7">
         <v>1</v>
@@ -49786,10 +49786,10 @@
         <v>0</v>
       </c>
       <c r="AJ372" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK372" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL372" s="3" t="s">
         <v>46</v>
@@ -49798,10 +49798,10 @@
         <v>46</v>
       </c>
       <c r="AN372" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO372" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="373" spans="1:41" x14ac:dyDescent="0.25">
@@ -49955,37 +49955,37 @@
         <v>45</v>
       </c>
       <c r="I374" s="3" t="s">
-        <v>740</v>
+        <v>393</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>741</v>
+        <v>394</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>742</v>
+        <v>395</v>
       </c>
       <c r="L374" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M374" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="N374" s="3" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="P374" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="Q374" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R374" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S374" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T374" s="3" t="s">
         <v>894</v>
@@ -50009,7 +50009,7 @@
         <v>46</v>
       </c>
       <c r="AA374" s="7">
-        <v>87000</v>
+        <v>692000</v>
       </c>
       <c r="AB374" s="7">
         <v>1</v>
@@ -50036,10 +50036,10 @@
         <v>0</v>
       </c>
       <c r="AJ374" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK374" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL374" s="3" t="s">
         <v>46</v>
@@ -50048,10 +50048,10 @@
         <v>46</v>
       </c>
       <c r="AN374" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO374" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="375" spans="1:41" x14ac:dyDescent="0.25">
@@ -50080,37 +50080,37 @@
         <v>45</v>
       </c>
       <c r="I375" s="3" t="s">
-        <v>967</v>
+        <v>925</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>968</v>
+        <v>926</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>813</v>
+        <v>927</v>
       </c>
       <c r="L375" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M375" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N375" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O375" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P375" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q375" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R375" s="5">
         <v>2</v>
       </c>
       <c r="S375" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T375" s="3" t="s">
         <v>894</v>
@@ -50133,8 +50133,8 @@
       <c r="Z375" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA375" s="7">
-        <v>468000</v>
+      <c r="AA375" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB375" s="7">
         <v>1</v>
@@ -50205,28 +50205,28 @@
         <v>45</v>
       </c>
       <c r="I376" s="3" t="s">
-        <v>929</v>
+        <v>966</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>930</v>
+        <v>967</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>931</v>
+        <v>968</v>
       </c>
       <c r="L376" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M376" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N376" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P376" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q376" s="5">
         <v>2</v>
@@ -50259,7 +50259,7 @@
         <v>46</v>
       </c>
       <c r="AA376" s="7">
-        <v>3025200</v>
+        <v>744240</v>
       </c>
       <c r="AB376" s="7">
         <v>1</v>
@@ -50330,28 +50330,28 @@
         <v>45</v>
       </c>
       <c r="I377" s="3" t="s">
-        <v>722</v>
+        <v>969</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>723</v>
+        <v>970</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>724</v>
+        <v>971</v>
       </c>
       <c r="L377" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M377" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N377" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P377" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q377" s="5">
         <v>2</v>
@@ -50384,7 +50384,7 @@
         <v>46</v>
       </c>
       <c r="AA377" s="7">
-        <v>1227480</v>
+        <v>771000</v>
       </c>
       <c r="AB377" s="7">
         <v>1</v>
@@ -50455,28 +50455,28 @@
         <v>45</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>144</v>
+        <v>422</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>145</v>
+        <v>423</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>146</v>
+        <v>424</v>
       </c>
       <c r="L378" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M378" s="3" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="N378" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="O378" s="3" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="P378" s="3" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="Q378" s="5">
         <v>2</v>
@@ -50509,7 +50509,7 @@
         <v>46</v>
       </c>
       <c r="AA378" s="7">
-        <v>2736757</v>
+        <v>698000</v>
       </c>
       <c r="AB378" s="7">
         <v>1</v>
@@ -50580,28 +50580,28 @@
         <v>45</v>
       </c>
       <c r="I379" s="3" t="s">
-        <v>135</v>
+        <v>772</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>136</v>
+        <v>773</v>
       </c>
       <c r="K379" s="3" t="s">
-        <v>137</v>
+        <v>774</v>
       </c>
       <c r="L379" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M379" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N379" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P379" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q379" s="5">
         <v>2</v>
@@ -50634,7 +50634,7 @@
         <v>46</v>
       </c>
       <c r="AA379" s="7">
-        <v>536250</v>
+        <v>2482921</v>
       </c>
       <c r="AB379" s="7">
         <v>1</v>
@@ -50705,28 +50705,28 @@
         <v>45</v>
       </c>
       <c r="I380" s="3" t="s">
-        <v>109</v>
+        <v>464</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>110</v>
+        <v>465</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>111</v>
+        <v>466</v>
       </c>
       <c r="L380" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M380" s="3" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="N380" s="3" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="O380" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="P380" s="3" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="Q380" s="5">
         <v>2</v>
@@ -50759,7 +50759,7 @@
         <v>46</v>
       </c>
       <c r="AA380" s="7">
-        <v>558000</v>
+        <v>1156433</v>
       </c>
       <c r="AB380" s="7">
         <v>1</v>
@@ -50830,34 +50830,34 @@
         <v>45</v>
       </c>
       <c r="I381" s="3" t="s">
-        <v>969</v>
+        <v>473</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>970</v>
+        <v>474</v>
       </c>
       <c r="K381" s="3" t="s">
-        <v>971</v>
+        <v>475</v>
       </c>
       <c r="L381" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M381" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N381" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P381" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q381" s="5">
         <v>2</v>
       </c>
       <c r="R381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S381" s="5">
         <v>2</v>
@@ -50884,7 +50884,7 @@
         <v>46</v>
       </c>
       <c r="AA381" s="7">
-        <v>646676</v>
+        <v>839166</v>
       </c>
       <c r="AB381" s="7">
         <v>1</v>
@@ -50967,16 +50967,16 @@
         <v>50</v>
       </c>
       <c r="M382" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N382" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O382" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P382" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q382" s="5">
         <v>2</v>
@@ -51009,7 +51009,7 @@
         <v>46</v>
       </c>
       <c r="AA382" s="7">
-        <v>362000</v>
+        <v>384000</v>
       </c>
       <c r="AB382" s="7">
         <v>1</v>
@@ -51217,16 +51217,16 @@
         <v>50</v>
       </c>
       <c r="M384" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N384" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O384" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P384" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q384" s="5">
         <v>2</v>
@@ -51259,7 +51259,7 @@
         <v>46</v>
       </c>
       <c r="AA384" s="7">
-        <v>384000</v>
+        <v>362000</v>
       </c>
       <c r="AB384" s="7">
         <v>1</v>
@@ -52455,13 +52455,13 @@
         <v>45</v>
       </c>
       <c r="I394" s="3" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="L394" s="3" t="s">
         <v>50</v>
@@ -53205,13 +53205,13 @@
         <v>45</v>
       </c>
       <c r="I400" s="3" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="L400" s="3" t="s">
         <v>50</v>
@@ -55205,10 +55205,10 @@
         <v>999</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>813</v>
@@ -60205,13 +60205,13 @@
         <v>921</v>
       </c>
       <c r="I456" s="3" t="s">
-        <v>915</v>
+        <v>900</v>
       </c>
       <c r="J456" s="3" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="L456" s="3" t="s">
         <v>50</v>
@@ -61455,13 +61455,13 @@
         <v>45</v>
       </c>
       <c r="I466" s="3" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="J466" s="3" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="L466" s="3" t="s">
         <v>50</v>
@@ -62705,10 +62705,10 @@
         <v>45</v>
       </c>
       <c r="I476" s="3" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="J476" s="3" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="K476" s="3" t="s">
         <v>813</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15371" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15369" uniqueCount="1039">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -43383,8 +43383,8 @@
       <c r="Z321" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA321" s="3" t="s">
-        <v>46</v>
+      <c r="AA321" s="7">
+        <v>388301</v>
       </c>
       <c r="AB321" s="7">
         <v>31</v>
@@ -43732,7 +43732,7 @@
         <v>10</v>
       </c>
       <c r="R324" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S324" s="5">
         <v>10</v>
@@ -43979,13 +43979,13 @@
         <v>82</v>
       </c>
       <c r="Q326" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R326" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S326" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T326" s="3" t="s">
         <v>894</v>
@@ -44104,13 +44104,13 @@
         <v>72</v>
       </c>
       <c r="Q327" s="5">
+        <v>31</v>
+      </c>
+      <c r="R327" s="5">
         <v>30</v>
       </c>
-      <c r="R327" s="5">
-        <v>29</v>
-      </c>
       <c r="S327" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T327" s="3" t="s">
         <v>894</v>
@@ -44354,13 +44354,13 @@
         <v>128</v>
       </c>
       <c r="Q329" s="5">
+        <v>27</v>
+      </c>
+      <c r="R329" s="5">
         <v>26</v>
       </c>
-      <c r="R329" s="5">
-        <v>25</v>
-      </c>
       <c r="S329" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T329" s="3" t="s">
         <v>894</v>
@@ -45104,13 +45104,13 @@
         <v>128</v>
       </c>
       <c r="Q335" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R335" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S335" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T335" s="3" t="s">
         <v>894</v>
@@ -45854,13 +45854,13 @@
         <v>128</v>
       </c>
       <c r="Q341" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R341" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S341" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T341" s="3" t="s">
         <v>894</v>
@@ -45979,13 +45979,13 @@
         <v>72</v>
       </c>
       <c r="Q342" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R342" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S342" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T342" s="3" t="s">
         <v>894</v>
@@ -46729,13 +46729,13 @@
         <v>134</v>
       </c>
       <c r="Q348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T348" s="3" t="s">
         <v>894</v>
@@ -47104,13 +47104,13 @@
         <v>128</v>
       </c>
       <c r="Q351" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R351" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S351" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T351" s="3" t="s">
         <v>894</v>
@@ -47604,13 +47604,13 @@
         <v>128</v>
       </c>
       <c r="Q355" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R355" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S355" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T355" s="3" t="s">
         <v>894</v>
@@ -47729,13 +47729,13 @@
         <v>72</v>
       </c>
       <c r="Q356" s="5">
+        <v>30</v>
+      </c>
+      <c r="R356" s="5">
         <v>29</v>
       </c>
-      <c r="R356" s="5">
-        <v>28</v>
-      </c>
       <c r="S356" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>894</v>
@@ -48509,7 +48509,7 @@
         <v>46</v>
       </c>
       <c r="AA362" s="7">
-        <v>2736757</v>
+        <v>3118775</v>
       </c>
       <c r="AB362" s="7">
         <v>1</v>
@@ -51979,13 +51979,13 @@
         <v>72</v>
       </c>
       <c r="Q390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T390" s="3" t="s">
         <v>894</v>
@@ -52229,13 +52229,13 @@
         <v>128</v>
       </c>
       <c r="Q392" s="5">
+        <v>29</v>
+      </c>
+      <c r="R392" s="5">
         <v>28</v>
       </c>
-      <c r="R392" s="5">
-        <v>27</v>
-      </c>
       <c r="S392" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T392" s="3" t="s">
         <v>894</v>
@@ -52384,7 +52384,7 @@
         <v>46</v>
       </c>
       <c r="AA393" s="7">
-        <v>2736757</v>
+        <v>3118775</v>
       </c>
       <c r="AB393" s="7">
         <v>31</v>
@@ -53104,13 +53104,13 @@
         <v>128</v>
       </c>
       <c r="Q399" s="5">
+        <v>28</v>
+      </c>
+      <c r="R399" s="5">
         <v>27</v>
       </c>
-      <c r="R399" s="5">
-        <v>26</v>
-      </c>
       <c r="S399" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T399" s="3" t="s">
         <v>894</v>
@@ -53259,7 +53259,7 @@
         <v>46</v>
       </c>
       <c r="AA400" s="7">
-        <v>20517221</v>
+        <v>39525221</v>
       </c>
       <c r="AB400" s="7">
         <v>31</v>
@@ -54104,13 +54104,13 @@
         <v>128</v>
       </c>
       <c r="Q407" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R407" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S407" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T407" s="3" t="s">
         <v>894</v>
@@ -54979,13 +54979,13 @@
         <v>128</v>
       </c>
       <c r="Q414" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R414" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S414" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T414" s="3" t="s">
         <v>894</v>
@@ -55104,13 +55104,13 @@
         <v>72</v>
       </c>
       <c r="Q415" s="5">
+        <v>32</v>
+      </c>
+      <c r="R415" s="5">
         <v>31</v>
       </c>
-      <c r="R415" s="5">
-        <v>30</v>
-      </c>
       <c r="S415" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T415" s="3" t="s">
         <v>894</v>
@@ -55604,13 +55604,13 @@
         <v>134</v>
       </c>
       <c r="Q419" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R419" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S419" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T419" s="3" t="s">
         <v>894</v>
@@ -55884,7 +55884,7 @@
         <v>46</v>
       </c>
       <c r="AA421" s="7">
-        <v>2156236</v>
+        <v>2434791</v>
       </c>
       <c r="AB421" s="7">
         <v>31</v>
@@ -57229,13 +57229,13 @@
         <v>128</v>
       </c>
       <c r="Q432" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R432" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S432" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T432" s="3" t="s">
         <v>894</v>
@@ -57354,13 +57354,13 @@
         <v>72</v>
       </c>
       <c r="Q433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T433" s="3" t="s">
         <v>894</v>
@@ -57479,13 +57479,13 @@
         <v>54</v>
       </c>
       <c r="Q434" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R434" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S434" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T434" s="3" t="s">
         <v>894</v>
@@ -57854,13 +57854,13 @@
         <v>128</v>
       </c>
       <c r="Q437" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R437" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S437" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T437" s="3" t="s">
         <v>894</v>
@@ -58354,13 +58354,13 @@
         <v>54</v>
       </c>
       <c r="Q441" s="5">
+        <v>31</v>
+      </c>
+      <c r="R441" s="5">
         <v>30</v>
       </c>
-      <c r="R441" s="5">
-        <v>29</v>
-      </c>
       <c r="S441" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T441" s="3" t="s">
         <v>894</v>
@@ -59854,13 +59854,13 @@
         <v>128</v>
       </c>
       <c r="Q453" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R453" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S453" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T453" s="3" t="s">
         <v>894</v>
@@ -60259,7 +60259,7 @@
         <v>46</v>
       </c>
       <c r="AA456" s="7">
-        <v>15155995</v>
+        <v>22791835</v>
       </c>
       <c r="AB456" s="7">
         <v>31</v>
@@ -61008,8 +61008,8 @@
       <c r="Z462" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA462" s="3" t="s">
-        <v>46</v>
+      <c r="AA462" s="7">
+        <v>1103427</v>
       </c>
       <c r="AB462" s="7">
         <v>31</v>
@@ -61229,13 +61229,13 @@
         <v>72</v>
       </c>
       <c r="Q464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T464" s="3" t="s">
         <v>894</v>
@@ -61604,13 +61604,13 @@
         <v>128</v>
       </c>
       <c r="Q467" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R467" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S467" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T467" s="3" t="s">
         <v>894</v>
@@ -61979,13 +61979,13 @@
         <v>54</v>
       </c>
       <c r="Q470" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R470" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S470" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T470" s="3" t="s">
         <v>894</v>
@@ -62979,13 +62979,13 @@
         <v>134</v>
       </c>
       <c r="Q478" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R478" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S478" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T478" s="3" t="s">
         <v>894</v>
@@ -63104,13 +63104,13 @@
         <v>72</v>
       </c>
       <c r="Q479" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R479" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S479" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T479" s="3" t="s">
         <v>894</v>
@@ -63354,13 +63354,13 @@
         <v>72</v>
       </c>
       <c r="Q481" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R481" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S481" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T481" s="3" t="s">
         <v>894</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15354" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15339" uniqueCount="1039">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -2614,6 +2614,15 @@
     <t>2, Lê Hiến Mai</t>
   </si>
   <si>
+    <t>3126571</t>
+  </si>
+  <si>
+    <t>Quán Nước Cô Giàu</t>
+  </si>
+  <si>
+    <t>438, Mai Chí Thọ</t>
+  </si>
+  <si>
     <t>99916768</t>
   </si>
   <si>
@@ -2632,6 +2641,69 @@
     <t>49, Nguyễn Tư Nghiêm</t>
   </si>
   <si>
+    <t>99926585</t>
+  </si>
+  <si>
+    <t>Daily Mart</t>
+  </si>
+  <si>
+    <t>D43 Dragon, Đường 15</t>
+  </si>
+  <si>
+    <t>999305122</t>
+  </si>
+  <si>
+    <t>Minh Hải 1</t>
+  </si>
+  <si>
+    <t>34, Lò Lu</t>
+  </si>
+  <si>
+    <t>999754600</t>
+  </si>
+  <si>
+    <t>Chị Loan</t>
+  </si>
+  <si>
+    <t>6/2, Đường Số 6</t>
+  </si>
+  <si>
+    <t>Đạt</t>
+  </si>
+  <si>
+    <t>POSM</t>
+  </si>
+  <si>
+    <t>97KM04228</t>
+  </si>
+  <si>
+    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>999762653</t>
+  </si>
+  <si>
+    <t>Cà Phê Thúy Vy</t>
+  </si>
+  <si>
+    <t>Số 1351, Đường Nguyễn Thị Định</t>
+  </si>
+  <si>
+    <t>999765789</t>
+  </si>
+  <si>
+    <t>TH Hoa Phượng</t>
+  </si>
+  <si>
+    <t>34/33, Đường Số 2</t>
+  </si>
+  <si>
     <t>99918654</t>
   </si>
   <si>
@@ -2650,33 +2722,6 @@
     <t>74A, Đường Cầu Bình</t>
   </si>
   <si>
-    <t>99926585</t>
-  </si>
-  <si>
-    <t>Daily Mart</t>
-  </si>
-  <si>
-    <t>D43 Dragon, Đường 15</t>
-  </si>
-  <si>
-    <t>999305122</t>
-  </si>
-  <si>
-    <t>Minh Hải 1</t>
-  </si>
-  <si>
-    <t>34, Lò Lu</t>
-  </si>
-  <si>
-    <t>3126571</t>
-  </si>
-  <si>
-    <t>Quán Nước Cô Giàu</t>
-  </si>
-  <si>
-    <t>438, Mai Chí Thọ</t>
-  </si>
-  <si>
     <t>4264</t>
   </si>
   <si>
@@ -2695,51 +2740,6 @@
     <t>22 Đường 18, Long Phước</t>
   </si>
   <si>
-    <t>Đạt</t>
-  </si>
-  <si>
-    <t>POSM</t>
-  </si>
-  <si>
-    <t>97KM04228</t>
-  </si>
-  <si>
-    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
-  </si>
-  <si>
-    <t>Cai</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>999754600</t>
-  </si>
-  <si>
-    <t>Chị Loan</t>
-  </si>
-  <si>
-    <t>6/2, Đường Số 6</t>
-  </si>
-  <si>
-    <t>999762653</t>
-  </si>
-  <si>
-    <t>Cà Phê Thúy Vy</t>
-  </si>
-  <si>
-    <t>Số 1351, Đường Nguyễn Thị Định</t>
-  </si>
-  <si>
-    <t>999765789</t>
-  </si>
-  <si>
-    <t>TH Hoa Phượng</t>
-  </si>
-  <si>
-    <t>34/33, Đường Số 2</t>
-  </si>
-  <si>
     <t>2344002</t>
   </si>
   <si>
@@ -2878,6 +2878,15 @@
     <t>MSC_BEV_Chương trình TBTN_Tủ mát Nước giải khát_HCM_All2026_T10</t>
   </si>
   <si>
+    <t>2128924</t>
+  </si>
+  <si>
+    <t>Tạp Hoá Hồng Ngọc</t>
+  </si>
+  <si>
+    <t>22/10 Đường 990, Nguyễn Duy Trinh</t>
+  </si>
+  <si>
     <t>2432200</t>
   </si>
   <si>
@@ -2896,6 +2905,30 @@
     <t>242, Đường 57 - CL</t>
   </si>
   <si>
+    <t>2894640</t>
+  </si>
+  <si>
+    <t>Mino Mart</t>
+  </si>
+  <si>
+    <t>3063948</t>
+  </si>
+  <si>
+    <t>Cà Phê Chị Tuyết</t>
+  </si>
+  <si>
+    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
+  </si>
+  <si>
+    <t>3136368</t>
+  </si>
+  <si>
+    <t>Chợ Sạch 24H</t>
+  </si>
+  <si>
+    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
+  </si>
+  <si>
     <t>999115327</t>
   </si>
   <si>
@@ -2914,6 +2947,15 @@
     <t>250, Trường Lưu</t>
   </si>
   <si>
+    <t>999210374</t>
+  </si>
+  <si>
+    <t>Tạp Hóa 79</t>
+  </si>
+  <si>
+    <t>Số 79, Đường 11</t>
+  </si>
+  <si>
     <t>999305440</t>
   </si>
   <si>
@@ -2921,48 +2963,6 @@
   </si>
   <si>
     <t>136, Đường 35CL</t>
-  </si>
-  <si>
-    <t>999210374</t>
-  </si>
-  <si>
-    <t>Tạp Hóa 79</t>
-  </si>
-  <si>
-    <t>Số 79, Đường 11</t>
-  </si>
-  <si>
-    <t>3136368</t>
-  </si>
-  <si>
-    <t>Chợ Sạch 24H</t>
-  </si>
-  <si>
-    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
-  </si>
-  <si>
-    <t>3063948</t>
-  </si>
-  <si>
-    <t>Cà Phê Chị Tuyết</t>
-  </si>
-  <si>
-    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
-  </si>
-  <si>
-    <t>2894640</t>
-  </si>
-  <si>
-    <t>Mino Mart</t>
-  </si>
-  <si>
-    <t>2128924</t>
-  </si>
-  <si>
-    <t>Tạp Hoá Hồng Ngọc</t>
-  </si>
-  <si>
-    <t>22/10 Đường 990, Nguyễn Duy Trinh</t>
   </si>
   <si>
     <t>1-6MQR6L</t>
@@ -40717,16 +40717,16 @@
         <v>50</v>
       </c>
       <c r="M300" s="3" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="N300" s="3" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="O300" s="3" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="P300" s="3" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="Q300" s="3" t="s">
         <v>46</v>
@@ -40789,7 +40789,7 @@
         <v>58</v>
       </c>
       <c r="AK300" s="6">
-        <v>46315.54901207176</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL300" s="3" t="s">
         <v>46</v>
@@ -40801,7 +40801,7 @@
         <v>58</v>
       </c>
       <c r="AO300" s="6">
-        <v>46315.54901207176</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="301" spans="1:41" x14ac:dyDescent="0.25">
@@ -40830,28 +40830,28 @@
         <v>46</v>
       </c>
       <c r="I301" s="3" t="s">
-        <v>870</v>
+        <v>455</v>
       </c>
       <c r="J301" s="3" t="s">
-        <v>871</v>
+        <v>456</v>
       </c>
       <c r="K301" s="3" t="s">
-        <v>872</v>
+        <v>457</v>
       </c>
       <c r="L301" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M301" s="3" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="N301" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="O301" s="3" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="P301" s="3" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="Q301" s="3" t="s">
         <v>46</v>
@@ -40914,7 +40914,7 @@
         <v>58</v>
       </c>
       <c r="AK301" s="6">
-        <v>46301.30899568287</v>
+        <v>46302.48940038194</v>
       </c>
       <c r="AL301" s="3" t="s">
         <v>46</v>
@@ -40926,7 +40926,7 @@
         <v>58</v>
       </c>
       <c r="AO301" s="6">
-        <v>46301.30899568287</v>
+        <v>46302.48940038194</v>
       </c>
     </row>
     <row r="302" spans="1:41" x14ac:dyDescent="0.25">
@@ -40955,28 +40955,28 @@
         <v>46</v>
       </c>
       <c r="I302" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="K302" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="L302" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M302" s="3" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="N302" s="3" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="O302" s="3" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="P302" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="Q302" s="3" t="s">
         <v>46</v>
@@ -41039,7 +41039,7 @@
         <v>58</v>
       </c>
       <c r="AK302" s="6">
-        <v>46301.5776272338</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL302" s="3" t="s">
         <v>46</v>
@@ -41051,7 +41051,7 @@
         <v>58</v>
       </c>
       <c r="AO302" s="6">
-        <v>46301.5776272338</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="303" spans="1:41" x14ac:dyDescent="0.25">
@@ -41080,28 +41080,28 @@
         <v>46</v>
       </c>
       <c r="I303" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="K303" s="3" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="L303" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M303" s="3" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="N303" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="O303" s="3" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="P303" s="3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="Q303" s="3" t="s">
         <v>46</v>
@@ -41205,13 +41205,13 @@
         <v>46</v>
       </c>
       <c r="I304" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="K304" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="L304" s="3" t="s">
         <v>50</v>
@@ -41330,13 +41330,13 @@
         <v>46</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K305" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L305" s="3" t="s">
         <v>50</v>
@@ -41577,31 +41577,31 @@
         <v>45</v>
       </c>
       <c r="H307" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="K307" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="L307" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M307" s="3" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="N307" s="3" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="O307" s="3" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="P307" s="3" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="Q307" s="3" t="s">
         <v>46</v>
@@ -41613,7 +41613,7 @@
         <v>46</v>
       </c>
       <c r="T307" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U307" s="3" t="s">
         <v>46</v>
@@ -41630,41 +41630,41 @@
       <c r="Y307" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB307" s="3" t="s">
-        <v>46</v>
+      <c r="Z307" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA307" s="7">
+        <v>10.75</v>
+      </c>
+      <c r="AB307" s="7">
+        <v>1</v>
       </c>
       <c r="AC307" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD307" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE307" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF307" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI307" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH307" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI307" s="3">
+        <v>0</v>
       </c>
       <c r="AJ307" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK307" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
       <c r="AL307" s="3" t="s">
         <v>46</v>
@@ -41676,7 +41676,7 @@
         <v>58</v>
       </c>
       <c r="AO307" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
     </row>
     <row r="308" spans="1:41" x14ac:dyDescent="0.25">
@@ -41702,31 +41702,31 @@
         <v>45</v>
       </c>
       <c r="H308" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I308" s="3" t="s">
-        <v>455</v>
+        <v>891</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>456</v>
+        <v>892</v>
       </c>
       <c r="K308" s="3" t="s">
-        <v>457</v>
+        <v>893</v>
       </c>
       <c r="L308" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M308" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N308" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="O308" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P308" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Q308" s="3" t="s">
         <v>46</v>
@@ -41738,7 +41738,7 @@
         <v>46</v>
       </c>
       <c r="T308" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U308" s="3" t="s">
         <v>46</v>
@@ -41755,41 +41755,41 @@
       <c r="Y308" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB308" s="3" t="s">
-        <v>46</v>
+      <c r="Z308" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA308" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB308" s="7">
+        <v>1</v>
       </c>
       <c r="AC308" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD308" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE308" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF308" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI308" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH308" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI308" s="3">
+        <v>0</v>
       </c>
       <c r="AJ308" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK308" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
       <c r="AL308" s="3" t="s">
         <v>46</v>
@@ -41801,7 +41801,7 @@
         <v>58</v>
       </c>
       <c r="AO308" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
     </row>
     <row r="309" spans="1:41" x14ac:dyDescent="0.25">
@@ -41827,16 +41827,16 @@
         <v>45</v>
       </c>
       <c r="H309" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I309" s="3" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="K309" s="3" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="L309" s="3" t="s">
         <v>50</v>
@@ -41863,7 +41863,7 @@
         <v>46</v>
       </c>
       <c r="T309" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U309" s="3" t="s">
         <v>46</v>
@@ -41880,41 +41880,41 @@
       <c r="Y309" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB309" s="3" t="s">
-        <v>46</v>
+      <c r="Z309" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA309" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB309" s="7">
+        <v>1</v>
       </c>
       <c r="AC309" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD309" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE309" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF309" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI309" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH309" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI309" s="3">
+        <v>0</v>
       </c>
       <c r="AJ309" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK309" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL309" s="3" t="s">
         <v>46</v>
@@ -41926,7 +41926,7 @@
         <v>58</v>
       </c>
       <c r="AO309" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="310" spans="1:41" x14ac:dyDescent="0.25">
@@ -41955,28 +41955,28 @@
         <v>45</v>
       </c>
       <c r="I310" s="3" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="J310" s="3" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="K310" s="3" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="L310" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M310" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N310" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="P310" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Q310" s="3" t="s">
         <v>46</v>
@@ -41988,7 +41988,7 @@
         <v>46</v>
       </c>
       <c r="T310" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U310" s="3" t="s">
         <v>46</v>
@@ -42015,19 +42015,19 @@
         <v>1</v>
       </c>
       <c r="AC310" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD310" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE310" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF310" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG310" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH310" s="7">
         <v>1</v>
@@ -42039,7 +42039,7 @@
         <v>58</v>
       </c>
       <c r="AK310" s="6">
-        <v>46304.293035104165</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL310" s="3" t="s">
         <v>46</v>
@@ -42051,7 +42051,7 @@
         <v>58</v>
       </c>
       <c r="AO310" s="6">
-        <v>46304.293035104165</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="311" spans="1:41" x14ac:dyDescent="0.25">
@@ -42092,16 +42092,16 @@
         <v>50</v>
       </c>
       <c r="M311" s="3" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="N311" s="3" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="P311" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="Q311" s="3" t="s">
         <v>46</v>
@@ -42113,7 +42113,7 @@
         <v>46</v>
       </c>
       <c r="T311" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U311" s="3" t="s">
         <v>46</v>
@@ -42134,25 +42134,25 @@
         <v>10</v>
       </c>
       <c r="AA311" s="7">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AB311" s="7">
         <v>1</v>
       </c>
       <c r="AC311" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD311" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE311" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF311" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG311" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH311" s="7">
         <v>1</v>
@@ -42164,7 +42164,7 @@
         <v>58</v>
       </c>
       <c r="AK311" s="6">
-        <v>46312.58308098379</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>46</v>
@@ -42176,7 +42176,7 @@
         <v>58</v>
       </c>
       <c r="AO311" s="6">
-        <v>46312.58308098379</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="312" spans="1:41" x14ac:dyDescent="0.25">
@@ -42217,16 +42217,16 @@
         <v>50</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q312" s="3" t="s">
         <v>46</v>
@@ -42238,7 +42238,7 @@
         <v>46</v>
       </c>
       <c r="T312" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U312" s="3" t="s">
         <v>46</v>
@@ -42265,19 +42265,19 @@
         <v>1</v>
       </c>
       <c r="AC312" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD312" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE312" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF312" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG312" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH312" s="7">
         <v>1</v>
@@ -42289,7 +42289,7 @@
         <v>58</v>
       </c>
       <c r="AK312" s="6">
-        <v>46310.439036655094</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>46</v>
@@ -42301,7 +42301,7 @@
         <v>58</v>
       </c>
       <c r="AO312" s="6">
-        <v>46310.439036655094</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="313" spans="1:41" x14ac:dyDescent="0.25">
@@ -42363,7 +42363,7 @@
         <v>46</v>
       </c>
       <c r="T313" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U313" s="3" t="s">
         <v>46</v>
@@ -42390,19 +42390,19 @@
         <v>1</v>
       </c>
       <c r="AC313" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD313" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE313" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF313" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG313" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH313" s="7">
         <v>1</v>
@@ -42414,7 +42414,7 @@
         <v>58</v>
       </c>
       <c r="AK313" s="6">
-        <v>46301.30899568287</v>
+        <v>46304.293035104165</v>
       </c>
       <c r="AL313" s="3" t="s">
         <v>46</v>
@@ -42426,7 +42426,7 @@
         <v>58</v>
       </c>
       <c r="AO313" s="6">
-        <v>46301.30899568287</v>
+        <v>46304.293035104165</v>
       </c>
     </row>
     <row r="314" spans="1:41" x14ac:dyDescent="0.25">
@@ -42488,7 +42488,7 @@
         <v>46</v>
       </c>
       <c r="T314" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U314" s="3" t="s">
         <v>46</v>
@@ -42515,19 +42515,19 @@
         <v>1</v>
       </c>
       <c r="AC314" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD314" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE314" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF314" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG314" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH314" s="7">
         <v>1</v>
@@ -42613,7 +42613,7 @@
         <v>46</v>
       </c>
       <c r="T315" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U315" s="3" t="s">
         <v>46</v>
@@ -42640,19 +42640,19 @@
         <v>1</v>
       </c>
       <c r="AC315" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD315" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE315" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF315" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG315" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH315" s="7">
         <v>1</v>
@@ -42738,7 +42738,7 @@
         <v>46</v>
       </c>
       <c r="T316" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U316" s="3" t="s">
         <v>46</v>
@@ -42765,19 +42765,19 @@
         <v>1</v>
       </c>
       <c r="AC316" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD316" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE316" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF316" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG316" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH316" s="7">
         <v>1</v>
@@ -42863,7 +42863,7 @@
         <v>46</v>
       </c>
       <c r="T317" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U317" s="3" t="s">
         <v>46</v>
@@ -42890,19 +42890,19 @@
         <v>1</v>
       </c>
       <c r="AC317" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD317" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE317" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF317" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG317" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH317" s="7">
         <v>1</v>
@@ -42955,28 +42955,28 @@
         <v>45</v>
       </c>
       <c r="I318" s="3" t="s">
-        <v>912</v>
+        <v>138</v>
       </c>
       <c r="J318" s="3" t="s">
-        <v>913</v>
+        <v>139</v>
       </c>
       <c r="K318" s="3" t="s">
-        <v>914</v>
+        <v>140</v>
       </c>
       <c r="L318" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M318" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P318" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q318" s="3" t="s">
         <v>46</v>
@@ -42988,7 +42988,7 @@
         <v>46</v>
       </c>
       <c r="T318" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U318" s="3" t="s">
         <v>46</v>
@@ -43009,25 +43009,25 @@
         <v>10</v>
       </c>
       <c r="AA318" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB318" s="7">
         <v>1</v>
       </c>
       <c r="AC318" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD318" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE318" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF318" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG318" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH318" s="7">
         <v>1</v>
@@ -43039,7 +43039,7 @@
         <v>58</v>
       </c>
       <c r="AK318" s="6">
-        <v>46316.79383703704</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL318" s="3" t="s">
         <v>46</v>
@@ -43051,7 +43051,7 @@
         <v>58</v>
       </c>
       <c r="AO318" s="6">
-        <v>46316.79383703704</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="319" spans="1:41" x14ac:dyDescent="0.25">
@@ -43080,28 +43080,28 @@
         <v>45</v>
       </c>
       <c r="I319" s="3" t="s">
-        <v>138</v>
+        <v>912</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>139</v>
+        <v>913</v>
       </c>
       <c r="K319" s="3" t="s">
-        <v>140</v>
+        <v>914</v>
       </c>
       <c r="L319" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M319" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N319" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P319" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q319" s="3" t="s">
         <v>46</v>
@@ -43113,7 +43113,7 @@
         <v>46</v>
       </c>
       <c r="T319" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U319" s="3" t="s">
         <v>46</v>
@@ -43134,25 +43134,25 @@
         <v>10</v>
       </c>
       <c r="AA319" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB319" s="7">
         <v>1</v>
       </c>
       <c r="AC319" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD319" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE319" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF319" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG319" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH319" s="7">
         <v>1</v>
@@ -43164,7 +43164,7 @@
         <v>58</v>
       </c>
       <c r="AK319" s="6">
-        <v>46303.59483915509</v>
+        <v>46316.79383703704</v>
       </c>
       <c r="AL319" s="3" t="s">
         <v>46</v>
@@ -43176,7 +43176,7 @@
         <v>58</v>
       </c>
       <c r="AO319" s="6">
-        <v>46303.59483915509</v>
+        <v>46316.79383703704</v>
       </c>
     </row>
     <row r="320" spans="1:41" x14ac:dyDescent="0.25">
@@ -43238,7 +43238,7 @@
         <v>46</v>
       </c>
       <c r="T320" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U320" s="3" t="s">
         <v>46</v>
@@ -43265,19 +43265,19 @@
         <v>1</v>
       </c>
       <c r="AC320" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD320" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE320" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF320" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG320" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH320" s="7">
         <v>1</v>
@@ -43363,7 +43363,7 @@
         <v>14</v>
       </c>
       <c r="T321" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U321" s="3" t="s">
         <v>46</v>
@@ -43390,7 +43390,7 @@
         <v>31</v>
       </c>
       <c r="AC321" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD321" s="3" t="s">
         <v>922</v>
@@ -43399,10 +43399,10 @@
         <v>923</v>
       </c>
       <c r="AF321" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG321" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH321" s="7">
         <v>12400000</v>
@@ -43488,7 +43488,7 @@
         <v>16</v>
       </c>
       <c r="T322" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U322" s="3" t="s">
         <v>46</v>
@@ -43515,7 +43515,7 @@
         <v>31</v>
       </c>
       <c r="AC322" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD322" s="3" t="s">
         <v>922</v>
@@ -43524,10 +43524,10 @@
         <v>923</v>
       </c>
       <c r="AF322" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG322" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH322" s="7">
         <v>12400000</v>
@@ -43613,7 +43613,7 @@
         <v>14</v>
       </c>
       <c r="T323" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U323" s="3" t="s">
         <v>46</v>
@@ -43640,7 +43640,7 @@
         <v>31</v>
       </c>
       <c r="AC323" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD323" s="3" t="s">
         <v>922</v>
@@ -43649,10 +43649,10 @@
         <v>923</v>
       </c>
       <c r="AF323" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG323" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH323" s="7">
         <v>12400000</v>
@@ -43738,7 +43738,7 @@
         <v>10</v>
       </c>
       <c r="T324" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U324" s="3" t="s">
         <v>46</v>
@@ -43765,7 +43765,7 @@
         <v>31</v>
       </c>
       <c r="AC324" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD324" s="3" t="s">
         <v>922</v>
@@ -43774,10 +43774,10 @@
         <v>923</v>
       </c>
       <c r="AF324" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG324" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH324" s="7">
         <v>12400000</v>
@@ -43854,16 +43854,16 @@
         <v>128</v>
       </c>
       <c r="Q325" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R325" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S325" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T325" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U325" s="3" t="s">
         <v>46</v>
@@ -43890,7 +43890,7 @@
         <v>31</v>
       </c>
       <c r="AC325" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD325" s="3" t="s">
         <v>922</v>
@@ -43899,10 +43899,10 @@
         <v>923</v>
       </c>
       <c r="AF325" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG325" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH325" s="7">
         <v>12400000</v>
@@ -43979,16 +43979,16 @@
         <v>82</v>
       </c>
       <c r="Q326" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R326" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S326" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T326" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U326" s="3" t="s">
         <v>46</v>
@@ -44009,13 +44009,13 @@
         <v>46</v>
       </c>
       <c r="AA326" s="7">
-        <v>1764000</v>
+        <v>1829136</v>
       </c>
       <c r="AB326" s="7">
         <v>31</v>
       </c>
       <c r="AC326" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD326" s="3" t="s">
         <v>922</v>
@@ -44024,10 +44024,10 @@
         <v>923</v>
       </c>
       <c r="AF326" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG326" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH326" s="7">
         <v>12400000</v>
@@ -44113,7 +44113,7 @@
         <v>31</v>
       </c>
       <c r="T327" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U327" s="3" t="s">
         <v>46</v>
@@ -44134,13 +44134,13 @@
         <v>46</v>
       </c>
       <c r="AA327" s="7">
-        <v>374309</v>
+        <v>773477</v>
       </c>
       <c r="AB327" s="7">
         <v>31</v>
       </c>
       <c r="AC327" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD327" s="3" t="s">
         <v>922</v>
@@ -44149,10 +44149,10 @@
         <v>923</v>
       </c>
       <c r="AF327" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG327" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH327" s="7">
         <v>12400000</v>
@@ -44238,7 +44238,7 @@
         <v>32</v>
       </c>
       <c r="T328" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U328" s="3" t="s">
         <v>46</v>
@@ -44259,13 +44259,13 @@
         <v>46</v>
       </c>
       <c r="AA328" s="7">
-        <v>4436089</v>
+        <v>4940489</v>
       </c>
       <c r="AB328" s="7">
         <v>31</v>
       </c>
       <c r="AC328" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD328" s="3" t="s">
         <v>922</v>
@@ -44274,10 +44274,10 @@
         <v>923</v>
       </c>
       <c r="AF328" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG328" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH328" s="7">
         <v>12400000</v>
@@ -44354,16 +44354,16 @@
         <v>128</v>
       </c>
       <c r="Q329" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R329" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S329" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T329" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U329" s="3" t="s">
         <v>46</v>
@@ -44384,13 +44384,13 @@
         <v>46</v>
       </c>
       <c r="AA329" s="7">
-        <v>1076567</v>
+        <v>1475735</v>
       </c>
       <c r="AB329" s="7">
         <v>31</v>
       </c>
       <c r="AC329" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD329" s="3" t="s">
         <v>922</v>
@@ -44399,10 +44399,10 @@
         <v>923</v>
       </c>
       <c r="AF329" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG329" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH329" s="7">
         <v>12400000</v>
@@ -44488,7 +44488,7 @@
         <v>15</v>
       </c>
       <c r="T330" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U330" s="3" t="s">
         <v>46</v>
@@ -44515,7 +44515,7 @@
         <v>31</v>
       </c>
       <c r="AC330" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD330" s="3" t="s">
         <v>922</v>
@@ -44524,10 +44524,10 @@
         <v>923</v>
       </c>
       <c r="AF330" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG330" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH330" s="7">
         <v>12400000</v>
@@ -44613,7 +44613,7 @@
         <v>19</v>
       </c>
       <c r="T331" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U331" s="3" t="s">
         <v>46</v>
@@ -44640,7 +44640,7 @@
         <v>31</v>
       </c>
       <c r="AC331" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD331" s="3" t="s">
         <v>922</v>
@@ -44649,10 +44649,10 @@
         <v>923</v>
       </c>
       <c r="AF331" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG331" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH331" s="7">
         <v>12400000</v>
@@ -44738,7 +44738,7 @@
         <v>4</v>
       </c>
       <c r="T332" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U332" s="3" t="s">
         <v>46</v>
@@ -44765,7 +44765,7 @@
         <v>31</v>
       </c>
       <c r="AC332" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD332" s="3" t="s">
         <v>922</v>
@@ -44774,10 +44774,10 @@
         <v>923</v>
       </c>
       <c r="AF332" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG332" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH332" s="7">
         <v>12400000</v>
@@ -44854,16 +44854,16 @@
         <v>128</v>
       </c>
       <c r="Q333" s="5">
+        <v>31</v>
+      </c>
+      <c r="R333" s="5">
         <v>30</v>
       </c>
-      <c r="R333" s="5">
-        <v>29</v>
-      </c>
       <c r="S333" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T333" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U333" s="3" t="s">
         <v>46</v>
@@ -44890,7 +44890,7 @@
         <v>31</v>
       </c>
       <c r="AC333" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD333" s="3" t="s">
         <v>922</v>
@@ -44899,10 +44899,10 @@
         <v>923</v>
       </c>
       <c r="AF333" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG333" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH333" s="7">
         <v>12400000</v>
@@ -44988,7 +44988,7 @@
         <v>10</v>
       </c>
       <c r="T334" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U334" s="3" t="s">
         <v>46</v>
@@ -45015,7 +45015,7 @@
         <v>31</v>
       </c>
       <c r="AC334" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD334" s="3" t="s">
         <v>922</v>
@@ -45024,10 +45024,10 @@
         <v>923</v>
       </c>
       <c r="AF334" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG334" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH334" s="7">
         <v>12400000</v>
@@ -45104,16 +45104,16 @@
         <v>128</v>
       </c>
       <c r="Q335" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R335" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S335" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T335" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U335" s="3" t="s">
         <v>46</v>
@@ -45140,7 +45140,7 @@
         <v>31</v>
       </c>
       <c r="AC335" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD335" s="3" t="s">
         <v>922</v>
@@ -45149,10 +45149,10 @@
         <v>923</v>
       </c>
       <c r="AF335" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG335" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH335" s="7">
         <v>12400000</v>
@@ -45238,7 +45238,7 @@
         <v>5</v>
       </c>
       <c r="T336" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U336" s="3" t="s">
         <v>46</v>
@@ -45265,7 +45265,7 @@
         <v>31</v>
       </c>
       <c r="AC336" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD336" s="3" t="s">
         <v>922</v>
@@ -45274,10 +45274,10 @@
         <v>923</v>
       </c>
       <c r="AF336" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG336" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH336" s="7">
         <v>12400000</v>
@@ -45363,7 +45363,7 @@
         <v>8</v>
       </c>
       <c r="T337" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U337" s="3" t="s">
         <v>46</v>
@@ -45390,7 +45390,7 @@
         <v>31</v>
       </c>
       <c r="AC337" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD337" s="3" t="s">
         <v>922</v>
@@ -45399,10 +45399,10 @@
         <v>923</v>
       </c>
       <c r="AF337" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG337" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH337" s="7">
         <v>12400000</v>
@@ -45479,16 +45479,16 @@
         <v>128</v>
       </c>
       <c r="Q338" s="5">
+        <v>37</v>
+      </c>
+      <c r="R338" s="5">
         <v>36</v>
       </c>
-      <c r="R338" s="5">
-        <v>35</v>
-      </c>
       <c r="S338" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T338" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U338" s="3" t="s">
         <v>46</v>
@@ -45509,13 +45509,13 @@
         <v>46</v>
       </c>
       <c r="AA338" s="7">
-        <v>2359847</v>
+        <v>2692847</v>
       </c>
       <c r="AB338" s="7">
         <v>31</v>
       </c>
       <c r="AC338" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD338" s="3" t="s">
         <v>922</v>
@@ -45524,10 +45524,10 @@
         <v>923</v>
       </c>
       <c r="AF338" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG338" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH338" s="7">
         <v>12400000</v>
@@ -45613,7 +45613,7 @@
         <v>12</v>
       </c>
       <c r="T339" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U339" s="3" t="s">
         <v>46</v>
@@ -45640,7 +45640,7 @@
         <v>31</v>
       </c>
       <c r="AC339" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD339" s="3" t="s">
         <v>922</v>
@@ -45649,10 +45649,10 @@
         <v>923</v>
       </c>
       <c r="AF339" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG339" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH339" s="7">
         <v>12400000</v>
@@ -45738,7 +45738,7 @@
         <v>29</v>
       </c>
       <c r="T340" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U340" s="3" t="s">
         <v>46</v>
@@ -45759,13 +45759,13 @@
         <v>46</v>
       </c>
       <c r="AA340" s="7">
-        <v>1926136</v>
+        <v>2658048</v>
       </c>
       <c r="AB340" s="7">
         <v>31</v>
       </c>
       <c r="AC340" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD340" s="3" t="s">
         <v>922</v>
@@ -45774,10 +45774,10 @@
         <v>923</v>
       </c>
       <c r="AF340" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG340" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH340" s="7">
         <v>12400000</v>
@@ -45863,7 +45863,7 @@
         <v>13</v>
       </c>
       <c r="T341" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U341" s="3" t="s">
         <v>46</v>
@@ -45884,13 +45884,13 @@
         <v>46</v>
       </c>
       <c r="AA341" s="7">
-        <v>1413947</v>
+        <v>2094371</v>
       </c>
       <c r="AB341" s="7">
         <v>31</v>
       </c>
       <c r="AC341" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD341" s="3" t="s">
         <v>922</v>
@@ -45899,10 +45899,10 @@
         <v>923</v>
       </c>
       <c r="AF341" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG341" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH341" s="7">
         <v>12400000</v>
@@ -45988,7 +45988,7 @@
         <v>31</v>
       </c>
       <c r="T342" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U342" s="3" t="s">
         <v>46</v>
@@ -46009,13 +46009,13 @@
         <v>46</v>
       </c>
       <c r="AA342" s="7">
-        <v>14329214</v>
+        <v>14698814</v>
       </c>
       <c r="AB342" s="7">
         <v>31</v>
       </c>
       <c r="AC342" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD342" s="3" t="s">
         <v>922</v>
@@ -46024,10 +46024,10 @@
         <v>923</v>
       </c>
       <c r="AF342" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG342" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH342" s="7">
         <v>18600000</v>
@@ -46113,7 +46113,7 @@
         <v>19</v>
       </c>
       <c r="T343" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U343" s="3" t="s">
         <v>46</v>
@@ -46134,13 +46134,13 @@
         <v>46</v>
       </c>
       <c r="AA343" s="7">
-        <v>13603200</v>
+        <v>16505200</v>
       </c>
       <c r="AB343" s="7">
         <v>31</v>
       </c>
       <c r="AC343" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD343" s="3" t="s">
         <v>922</v>
@@ -46149,10 +46149,10 @@
         <v>923</v>
       </c>
       <c r="AF343" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG343" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH343" s="7">
         <v>18600000</v>
@@ -46238,7 +46238,7 @@
         <v>10</v>
       </c>
       <c r="T344" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U344" s="3" t="s">
         <v>46</v>
@@ -46259,13 +46259,13 @@
         <v>46</v>
       </c>
       <c r="AA344" s="7">
-        <v>1003079</v>
+        <v>1703169</v>
       </c>
       <c r="AB344" s="7">
         <v>31</v>
       </c>
       <c r="AC344" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD344" s="3" t="s">
         <v>922</v>
@@ -46274,10 +46274,10 @@
         <v>923</v>
       </c>
       <c r="AF344" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG344" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH344" s="7">
         <v>12400000</v>
@@ -46363,7 +46363,7 @@
         <v>8</v>
       </c>
       <c r="T345" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U345" s="3" t="s">
         <v>46</v>
@@ -46390,7 +46390,7 @@
         <v>31</v>
       </c>
       <c r="AC345" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD345" s="3" t="s">
         <v>922</v>
@@ -46399,10 +46399,10 @@
         <v>923</v>
       </c>
       <c r="AF345" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG345" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH345" s="7">
         <v>12400000</v>
@@ -46488,7 +46488,7 @@
         <v>13</v>
       </c>
       <c r="T346" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U346" s="3" t="s">
         <v>46</v>
@@ -46515,7 +46515,7 @@
         <v>31</v>
       </c>
       <c r="AC346" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD346" s="3" t="s">
         <v>922</v>
@@ -46524,10 +46524,10 @@
         <v>923</v>
       </c>
       <c r="AF346" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG346" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH346" s="7">
         <v>12400000</v>
@@ -46613,7 +46613,7 @@
         <v>7</v>
       </c>
       <c r="T347" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U347" s="3" t="s">
         <v>46</v>
@@ -46640,7 +46640,7 @@
         <v>31</v>
       </c>
       <c r="AC347" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD347" s="3" t="s">
         <v>922</v>
@@ -46649,10 +46649,10 @@
         <v>923</v>
       </c>
       <c r="AF347" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG347" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH347" s="7">
         <v>12400000</v>
@@ -46738,7 +46738,7 @@
         <v>28</v>
       </c>
       <c r="T348" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U348" s="3" t="s">
         <v>46</v>
@@ -46765,7 +46765,7 @@
         <v>31</v>
       </c>
       <c r="AC348" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD348" s="3" t="s">
         <v>922</v>
@@ -46774,10 +46774,10 @@
         <v>923</v>
       </c>
       <c r="AF348" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG348" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH348" s="7">
         <v>12400000</v>
@@ -46863,7 +46863,7 @@
         <v>15</v>
       </c>
       <c r="T349" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U349" s="3" t="s">
         <v>46</v>
@@ -46884,13 +46884,13 @@
         <v>46</v>
       </c>
       <c r="AA349" s="7">
-        <v>2580460</v>
+        <v>3308110</v>
       </c>
       <c r="AB349" s="7">
         <v>31</v>
       </c>
       <c r="AC349" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD349" s="3" t="s">
         <v>922</v>
@@ -46899,10 +46899,10 @@
         <v>923</v>
       </c>
       <c r="AF349" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG349" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH349" s="7">
         <v>12400000</v>
@@ -46979,16 +46979,16 @@
         <v>128</v>
       </c>
       <c r="Q350" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R350" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S350" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T350" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U350" s="3" t="s">
         <v>46</v>
@@ -47015,7 +47015,7 @@
         <v>31</v>
       </c>
       <c r="AC350" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD350" s="3" t="s">
         <v>922</v>
@@ -47024,10 +47024,10 @@
         <v>923</v>
       </c>
       <c r="AF350" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG350" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH350" s="7">
         <v>12400000</v>
@@ -47104,16 +47104,16 @@
         <v>128</v>
       </c>
       <c r="Q351" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R351" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S351" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T351" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U351" s="3" t="s">
         <v>46</v>
@@ -47140,7 +47140,7 @@
         <v>31</v>
       </c>
       <c r="AC351" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD351" s="3" t="s">
         <v>922</v>
@@ -47149,10 +47149,10 @@
         <v>923</v>
       </c>
       <c r="AF351" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG351" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH351" s="7">
         <v>12400000</v>
@@ -47238,7 +47238,7 @@
         <v>6</v>
       </c>
       <c r="T352" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U352" s="3" t="s">
         <v>46</v>
@@ -47265,7 +47265,7 @@
         <v>31</v>
       </c>
       <c r="AC352" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD352" s="3" t="s">
         <v>922</v>
@@ -47274,10 +47274,10 @@
         <v>923</v>
       </c>
       <c r="AF352" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG352" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH352" s="7">
         <v>12400000</v>
@@ -47363,7 +47363,7 @@
         <v>29</v>
       </c>
       <c r="T353" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U353" s="3" t="s">
         <v>46</v>
@@ -47384,13 +47384,13 @@
         <v>46</v>
       </c>
       <c r="AA353" s="7">
-        <v>2566500</v>
+        <v>3978150</v>
       </c>
       <c r="AB353" s="7">
         <v>31</v>
       </c>
       <c r="AC353" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD353" s="3" t="s">
         <v>922</v>
@@ -47399,10 +47399,10 @@
         <v>923</v>
       </c>
       <c r="AF353" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG353" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH353" s="7">
         <v>12400000</v>
@@ -47488,7 +47488,7 @@
         <v>21</v>
       </c>
       <c r="T354" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U354" s="3" t="s">
         <v>46</v>
@@ -47515,7 +47515,7 @@
         <v>31</v>
       </c>
       <c r="AC354" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD354" s="3" t="s">
         <v>922</v>
@@ -47524,10 +47524,10 @@
         <v>923</v>
       </c>
       <c r="AF354" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG354" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH354" s="7">
         <v>12400000</v>
@@ -47604,16 +47604,16 @@
         <v>128</v>
       </c>
       <c r="Q355" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R355" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S355" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T355" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U355" s="3" t="s">
         <v>46</v>
@@ -47634,13 +47634,13 @@
         <v>46</v>
       </c>
       <c r="AA355" s="7">
-        <v>290939</v>
+        <v>393939</v>
       </c>
       <c r="AB355" s="7">
         <v>31</v>
       </c>
       <c r="AC355" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD355" s="3" t="s">
         <v>922</v>
@@ -47649,10 +47649,10 @@
         <v>923</v>
       </c>
       <c r="AF355" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG355" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH355" s="7">
         <v>12400000</v>
@@ -47738,7 +47738,7 @@
         <v>30</v>
       </c>
       <c r="T356" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U356" s="3" t="s">
         <v>46</v>
@@ -47765,7 +47765,7 @@
         <v>31</v>
       </c>
       <c r="AC356" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD356" s="3" t="s">
         <v>922</v>
@@ -47774,10 +47774,10 @@
         <v>923</v>
       </c>
       <c r="AF356" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG356" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH356" s="7">
         <v>12400000</v>
@@ -47863,7 +47863,7 @@
         <v>35</v>
       </c>
       <c r="T357" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U357" s="3" t="s">
         <v>46</v>
@@ -47890,7 +47890,7 @@
         <v>31</v>
       </c>
       <c r="AC357" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD357" s="3" t="s">
         <v>922</v>
@@ -47899,10 +47899,10 @@
         <v>923</v>
       </c>
       <c r="AF357" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG357" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH357" s="7">
         <v>12400000</v>
@@ -47988,7 +47988,7 @@
         <v>12</v>
       </c>
       <c r="T358" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U358" s="3" t="s">
         <v>46</v>
@@ -48015,7 +48015,7 @@
         <v>31</v>
       </c>
       <c r="AC358" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD358" s="3" t="s">
         <v>922</v>
@@ -48024,10 +48024,10 @@
         <v>923</v>
       </c>
       <c r="AF358" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG358" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH358" s="7">
         <v>12400000</v>
@@ -48092,28 +48092,28 @@
         <v>50</v>
       </c>
       <c r="M359" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="N359" s="3" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="O359" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="P359" s="3" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="Q359" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R359" s="5">
         <v>2</v>
       </c>
       <c r="S359" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T359" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U359" s="3" t="s">
         <v>46</v>
@@ -48134,7 +48134,7 @@
         <v>46</v>
       </c>
       <c r="AA359" s="7">
-        <v>1211240</v>
+        <v>646676</v>
       </c>
       <c r="AB359" s="7">
         <v>1</v>
@@ -48205,40 +48205,40 @@
         <v>45</v>
       </c>
       <c r="I360" s="3" t="s">
-        <v>958</v>
+        <v>109</v>
       </c>
       <c r="J360" s="3" t="s">
-        <v>959</v>
+        <v>110</v>
       </c>
       <c r="K360" s="3" t="s">
-        <v>960</v>
+        <v>111</v>
       </c>
       <c r="L360" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M360" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N360" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O360" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P360" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S360" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T360" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U360" s="3" t="s">
         <v>46</v>
@@ -48259,7 +48259,7 @@
         <v>46</v>
       </c>
       <c r="AA360" s="7">
-        <v>663000</v>
+        <v>558000</v>
       </c>
       <c r="AB360" s="7">
         <v>1</v>
@@ -48286,10 +48286,10 @@
         <v>0</v>
       </c>
       <c r="AJ360" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK360" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL360" s="3" t="s">
         <v>46</v>
@@ -48298,10 +48298,10 @@
         <v>46</v>
       </c>
       <c r="AN360" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO360" s="6">
-        <v>46304.905077118055</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="361" spans="1:41" x14ac:dyDescent="0.25">
@@ -48330,40 +48330,40 @@
         <v>45</v>
       </c>
       <c r="I361" s="3" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="J361" s="3" t="s">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="K361" s="3" t="s">
-        <v>288</v>
+        <v>137</v>
       </c>
       <c r="L361" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M361" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N361" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O361" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P361" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S361" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T361" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U361" s="3" t="s">
         <v>46</v>
@@ -48383,8 +48383,8 @@
       <c r="Z361" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA361" s="3" t="s">
-        <v>46</v>
+      <c r="AA361" s="7">
+        <v>536250</v>
       </c>
       <c r="AB361" s="7">
         <v>1</v>
@@ -48411,10 +48411,10 @@
         <v>0</v>
       </c>
       <c r="AJ361" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK361" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL361" s="3" t="s">
         <v>46</v>
@@ -48423,10 +48423,10 @@
         <v>46</v>
       </c>
       <c r="AN361" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO361" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="362" spans="1:41" x14ac:dyDescent="0.25">
@@ -48455,28 +48455,28 @@
         <v>45</v>
       </c>
       <c r="I362" s="3" t="s">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c r="J362" s="3" t="s">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="K362" s="3" t="s">
-        <v>294</v>
+        <v>146</v>
       </c>
       <c r="L362" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M362" s="3" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="N362" s="3" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="O362" s="3" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="P362" s="3" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="Q362" s="5">
         <v>2</v>
@@ -48488,7 +48488,7 @@
         <v>2</v>
       </c>
       <c r="T362" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U362" s="3" t="s">
         <v>46</v>
@@ -48509,7 +48509,7 @@
         <v>46</v>
       </c>
       <c r="AA362" s="7">
-        <v>87000</v>
+        <v>3118775</v>
       </c>
       <c r="AB362" s="7">
         <v>1</v>
@@ -48580,28 +48580,28 @@
         <v>45</v>
       </c>
       <c r="I363" s="3" t="s">
-        <v>728</v>
+        <v>958</v>
       </c>
       <c r="J363" s="3" t="s">
-        <v>729</v>
+        <v>959</v>
       </c>
       <c r="K363" s="3" t="s">
-        <v>730</v>
+        <v>960</v>
       </c>
       <c r="L363" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M363" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N363" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O363" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P363" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q363" s="5">
         <v>2</v>
@@ -48613,7 +48613,7 @@
         <v>2</v>
       </c>
       <c r="T363" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U363" s="3" t="s">
         <v>46</v>
@@ -48634,7 +48634,7 @@
         <v>46</v>
       </c>
       <c r="AA363" s="7">
-        <v>1567312</v>
+        <v>1211240</v>
       </c>
       <c r="AB363" s="7">
         <v>1</v>
@@ -48705,40 +48705,40 @@
         <v>45</v>
       </c>
       <c r="I364" s="3" t="s">
-        <v>422</v>
+        <v>961</v>
       </c>
       <c r="J364" s="3" t="s">
-        <v>423</v>
+        <v>962</v>
       </c>
       <c r="K364" s="3" t="s">
-        <v>424</v>
+        <v>963</v>
       </c>
       <c r="L364" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M364" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N364" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O364" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P364" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S364" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T364" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U364" s="3" t="s">
         <v>46</v>
@@ -48759,7 +48759,7 @@
         <v>46</v>
       </c>
       <c r="AA364" s="7">
-        <v>698000</v>
+        <v>663000</v>
       </c>
       <c r="AB364" s="7">
         <v>1</v>
@@ -48786,10 +48786,10 @@
         <v>0</v>
       </c>
       <c r="AJ364" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK364" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
       <c r="AL364" s="3" t="s">
         <v>46</v>
@@ -48798,10 +48798,10 @@
         <v>46</v>
       </c>
       <c r="AN364" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO364" s="6">
-        <v>46296.93825494213</v>
+        <v>46304.905077118055</v>
       </c>
     </row>
     <row r="365" spans="1:41" x14ac:dyDescent="0.25">
@@ -48830,13 +48830,13 @@
         <v>45</v>
       </c>
       <c r="I365" s="3" t="s">
-        <v>772</v>
+        <v>722</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>773</v>
+        <v>723</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>774</v>
+        <v>724</v>
       </c>
       <c r="L365" s="3" t="s">
         <v>50</v>
@@ -48863,7 +48863,7 @@
         <v>2</v>
       </c>
       <c r="T365" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U365" s="3" t="s">
         <v>46</v>
@@ -48884,7 +48884,7 @@
         <v>46</v>
       </c>
       <c r="AA365" s="7">
-        <v>2482921</v>
+        <v>1227480</v>
       </c>
       <c r="AB365" s="7">
         <v>1</v>
@@ -48955,40 +48955,40 @@
         <v>45</v>
       </c>
       <c r="I366" s="3" t="s">
-        <v>464</v>
+        <v>286</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>465</v>
+        <v>287</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>466</v>
+        <v>288</v>
       </c>
       <c r="L366" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P366" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T366" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U366" s="3" t="s">
         <v>46</v>
@@ -49008,8 +49008,8 @@
       <c r="Z366" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA366" s="7">
-        <v>1156433</v>
+      <c r="AA366" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB366" s="7">
         <v>1</v>
@@ -49036,10 +49036,10 @@
         <v>0</v>
       </c>
       <c r="AJ366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
       <c r="AL366" s="3" t="s">
         <v>46</v>
@@ -49048,10 +49048,10 @@
         <v>46</v>
       </c>
       <c r="AN366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
     </row>
     <row r="367" spans="1:41" x14ac:dyDescent="0.25">
@@ -49080,28 +49080,28 @@
         <v>45</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>473</v>
+        <v>292</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>474</v>
+        <v>293</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>475</v>
+        <v>294</v>
       </c>
       <c r="L367" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M367" s="3" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N367" s="3" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="P367" s="3" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="Q367" s="5">
         <v>2</v>
@@ -49113,7 +49113,7 @@
         <v>2</v>
       </c>
       <c r="T367" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U367" s="3" t="s">
         <v>46</v>
@@ -49134,7 +49134,7 @@
         <v>46</v>
       </c>
       <c r="AA367" s="7">
-        <v>839166</v>
+        <v>87000</v>
       </c>
       <c r="AB367" s="7">
         <v>1</v>
@@ -49205,28 +49205,28 @@
         <v>45</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>961</v>
+        <v>728</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>962</v>
+        <v>729</v>
       </c>
       <c r="K368" s="3" t="s">
-        <v>963</v>
+        <v>730</v>
       </c>
       <c r="L368" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M368" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N368" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P368" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q368" s="5">
         <v>2</v>
@@ -49238,7 +49238,7 @@
         <v>2</v>
       </c>
       <c r="T368" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U368" s="3" t="s">
         <v>46</v>
@@ -49259,7 +49259,7 @@
         <v>46</v>
       </c>
       <c r="AA368" s="7">
-        <v>384000</v>
+        <v>1567312</v>
       </c>
       <c r="AB368" s="7">
         <v>1</v>
@@ -49330,40 +49330,40 @@
         <v>45</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>823</v>
+        <v>929</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>824</v>
+        <v>930</v>
       </c>
       <c r="K369" s="3" t="s">
-        <v>825</v>
+        <v>931</v>
       </c>
       <c r="L369" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M369" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N369" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P369" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T369" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U369" s="3" t="s">
         <v>46</v>
@@ -49384,7 +49384,7 @@
         <v>46</v>
       </c>
       <c r="AA369" s="7">
-        <v>85805</v>
+        <v>3227033</v>
       </c>
       <c r="AB369" s="7">
         <v>1</v>
@@ -49411,10 +49411,10 @@
         <v>0</v>
       </c>
       <c r="AJ369" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK369" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL369" s="3" t="s">
         <v>46</v>
@@ -49423,10 +49423,10 @@
         <v>46</v>
       </c>
       <c r="AN369" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO369" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="370" spans="1:41" x14ac:dyDescent="0.25">
@@ -49461,34 +49461,34 @@
         <v>965</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>966</v>
+        <v>813</v>
       </c>
       <c r="L370" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M370" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P370" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R370" s="5">
         <v>2</v>
       </c>
       <c r="S370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T370" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U370" s="3" t="s">
         <v>46</v>
@@ -49509,7 +49509,7 @@
         <v>46</v>
       </c>
       <c r="AA370" s="7">
-        <v>362000</v>
+        <v>468000</v>
       </c>
       <c r="AB370" s="7">
         <v>1</v>
@@ -49580,28 +49580,28 @@
         <v>45</v>
       </c>
       <c r="I371" s="3" t="s">
-        <v>575</v>
+        <v>322</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>576</v>
+        <v>323</v>
       </c>
       <c r="K371" s="3" t="s">
-        <v>577</v>
+        <v>324</v>
       </c>
       <c r="L371" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M371" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N371" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O371" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P371" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q371" s="5">
         <v>2</v>
@@ -49613,7 +49613,7 @@
         <v>2</v>
       </c>
       <c r="T371" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U371" s="3" t="s">
         <v>46</v>
@@ -49634,7 +49634,7 @@
         <v>46</v>
       </c>
       <c r="AA371" s="7">
-        <v>453000</v>
+        <v>5131620</v>
       </c>
       <c r="AB371" s="7">
         <v>1</v>
@@ -49705,40 +49705,40 @@
         <v>45</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>967</v>
+        <v>740</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>968</v>
+        <v>741</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>969</v>
+        <v>742</v>
       </c>
       <c r="L372" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M372" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="P372" s="3" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="Q372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T372" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U372" s="3" t="s">
         <v>46</v>
@@ -49758,8 +49758,8 @@
       <c r="Z372" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA372" s="3" t="s">
-        <v>46</v>
+      <c r="AA372" s="7">
+        <v>183000</v>
       </c>
       <c r="AB372" s="7">
         <v>1</v>
@@ -49786,10 +49786,10 @@
         <v>0</v>
       </c>
       <c r="AJ372" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK372" s="6">
-        <v>46307.91045501157</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL372" s="3" t="s">
         <v>46</v>
@@ -49798,10 +49798,10 @@
         <v>46</v>
       </c>
       <c r="AN372" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO372" s="6">
-        <v>46307.91045501157</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="373" spans="1:41" x14ac:dyDescent="0.25">
@@ -49830,28 +49830,28 @@
         <v>45</v>
       </c>
       <c r="I373" s="3" t="s">
-        <v>693</v>
+        <v>378</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>694</v>
+        <v>379</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>695</v>
+        <v>380</v>
       </c>
       <c r="L373" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M373" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N373" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O373" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P373" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q373" s="5">
         <v>2</v>
@@ -49863,7 +49863,7 @@
         <v>2</v>
       </c>
       <c r="T373" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U373" s="3" t="s">
         <v>46</v>
@@ -49884,7 +49884,7 @@
         <v>46</v>
       </c>
       <c r="AA373" s="7">
-        <v>6224400</v>
+        <v>471000</v>
       </c>
       <c r="AB373" s="7">
         <v>1</v>
@@ -49911,10 +49911,10 @@
         <v>0</v>
       </c>
       <c r="AJ373" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK373" s="6">
-        <v>46306.863362881944</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL373" s="3" t="s">
         <v>46</v>
@@ -49923,10 +49923,10 @@
         <v>46</v>
       </c>
       <c r="AN373" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO373" s="6">
-        <v>46306.863362881944</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="374" spans="1:41" x14ac:dyDescent="0.25">
@@ -49955,28 +49955,28 @@
         <v>45</v>
       </c>
       <c r="I374" s="3" t="s">
-        <v>879</v>
+        <v>393</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>880</v>
+        <v>394</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>881</v>
+        <v>395</v>
       </c>
       <c r="L374" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M374" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N374" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P374" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q374" s="5">
         <v>2</v>
@@ -49988,7 +49988,7 @@
         <v>2</v>
       </c>
       <c r="T374" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U374" s="3" t="s">
         <v>46</v>
@@ -50009,7 +50009,7 @@
         <v>46</v>
       </c>
       <c r="AA374" s="7">
-        <v>1928113</v>
+        <v>692000</v>
       </c>
       <c r="AB374" s="7">
         <v>1</v>
@@ -50039,7 +50039,7 @@
         <v>58</v>
       </c>
       <c r="AK374" s="6">
-        <v>46303.59483915509</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL374" s="3" t="s">
         <v>46</v>
@@ -50051,7 +50051,7 @@
         <v>58</v>
       </c>
       <c r="AO374" s="6">
-        <v>46303.59483915509</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="375" spans="1:41" x14ac:dyDescent="0.25">
@@ -50080,13 +50080,13 @@
         <v>45</v>
       </c>
       <c r="I375" s="3" t="s">
-        <v>970</v>
+        <v>925</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>972</v>
+        <v>927</v>
       </c>
       <c r="L375" s="3" t="s">
         <v>50</v>
@@ -50113,7 +50113,7 @@
         <v>2</v>
       </c>
       <c r="T375" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U375" s="3" t="s">
         <v>46</v>
@@ -50133,8 +50133,8 @@
       <c r="Z375" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA375" s="7">
-        <v>471000</v>
+      <c r="AA375" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB375" s="7">
         <v>1</v>
@@ -50205,28 +50205,28 @@
         <v>45</v>
       </c>
       <c r="I376" s="3" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="L376" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M376" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N376" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O376" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P376" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q376" s="5">
         <v>2</v>
@@ -50238,7 +50238,7 @@
         <v>2</v>
       </c>
       <c r="T376" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U376" s="3" t="s">
         <v>46</v>
@@ -50259,7 +50259,7 @@
         <v>46</v>
       </c>
       <c r="AA376" s="7">
-        <v>771000</v>
+        <v>744240</v>
       </c>
       <c r="AB376" s="7">
         <v>1</v>
@@ -50330,28 +50330,28 @@
         <v>45</v>
       </c>
       <c r="I377" s="3" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="L377" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M377" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N377" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P377" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q377" s="5">
         <v>2</v>
@@ -50363,7 +50363,7 @@
         <v>2</v>
       </c>
       <c r="T377" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U377" s="3" t="s">
         <v>46</v>
@@ -50384,7 +50384,7 @@
         <v>46</v>
       </c>
       <c r="AA377" s="7">
-        <v>744240</v>
+        <v>771000</v>
       </c>
       <c r="AB377" s="7">
         <v>1</v>
@@ -50455,28 +50455,28 @@
         <v>45</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>925</v>
+        <v>422</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>926</v>
+        <v>423</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>927</v>
+        <v>424</v>
       </c>
       <c r="L378" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M378" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N378" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O378" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P378" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q378" s="5">
         <v>2</v>
@@ -50488,7 +50488,7 @@
         <v>2</v>
       </c>
       <c r="T378" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U378" s="3" t="s">
         <v>46</v>
@@ -50508,8 +50508,8 @@
       <c r="Z378" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA378" s="3" t="s">
-        <v>46</v>
+      <c r="AA378" s="7">
+        <v>698000</v>
       </c>
       <c r="AB378" s="7">
         <v>1</v>
@@ -50580,28 +50580,28 @@
         <v>45</v>
       </c>
       <c r="I379" s="3" t="s">
-        <v>393</v>
+        <v>772</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>394</v>
+        <v>773</v>
       </c>
       <c r="K379" s="3" t="s">
-        <v>395</v>
+        <v>774</v>
       </c>
       <c r="L379" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M379" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N379" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P379" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q379" s="5">
         <v>2</v>
@@ -50613,7 +50613,7 @@
         <v>2</v>
       </c>
       <c r="T379" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U379" s="3" t="s">
         <v>46</v>
@@ -50634,7 +50634,7 @@
         <v>46</v>
       </c>
       <c r="AA379" s="7">
-        <v>692000</v>
+        <v>2482921</v>
       </c>
       <c r="AB379" s="7">
         <v>1</v>
@@ -50661,10 +50661,10 @@
         <v>0</v>
       </c>
       <c r="AJ379" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK379" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL379" s="3" t="s">
         <v>46</v>
@@ -50673,10 +50673,10 @@
         <v>46</v>
       </c>
       <c r="AN379" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO379" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="380" spans="1:41" x14ac:dyDescent="0.25">
@@ -50705,13 +50705,13 @@
         <v>45</v>
       </c>
       <c r="I380" s="3" t="s">
-        <v>378</v>
+        <v>464</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>379</v>
+        <v>465</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>380</v>
+        <v>466</v>
       </c>
       <c r="L380" s="3" t="s">
         <v>50</v>
@@ -50738,7 +50738,7 @@
         <v>2</v>
       </c>
       <c r="T380" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U380" s="3" t="s">
         <v>46</v>
@@ -50759,7 +50759,7 @@
         <v>46</v>
       </c>
       <c r="AA380" s="7">
-        <v>471000</v>
+        <v>1442933</v>
       </c>
       <c r="AB380" s="7">
         <v>1</v>
@@ -50830,40 +50830,40 @@
         <v>45</v>
       </c>
       <c r="I381" s="3" t="s">
-        <v>740</v>
+        <v>473</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>741</v>
+        <v>474</v>
       </c>
       <c r="K381" s="3" t="s">
-        <v>742</v>
+        <v>475</v>
       </c>
       <c r="L381" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M381" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="N381" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P381" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="Q381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T381" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U381" s="3" t="s">
         <v>46</v>
@@ -50884,7 +50884,7 @@
         <v>46</v>
       </c>
       <c r="AA381" s="7">
-        <v>87000</v>
+        <v>839166</v>
       </c>
       <c r="AB381" s="7">
         <v>1</v>
@@ -50955,13 +50955,13 @@
         <v>45</v>
       </c>
       <c r="I382" s="3" t="s">
-        <v>322</v>
+        <v>972</v>
       </c>
       <c r="J382" s="3" t="s">
-        <v>323</v>
+        <v>973</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>324</v>
+        <v>974</v>
       </c>
       <c r="L382" s="3" t="s">
         <v>50</v>
@@ -50988,7 +50988,7 @@
         <v>2</v>
       </c>
       <c r="T382" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U382" s="3" t="s">
         <v>46</v>
@@ -51009,7 +51009,7 @@
         <v>46</v>
       </c>
       <c r="AA382" s="7">
-        <v>5131620</v>
+        <v>384000</v>
       </c>
       <c r="AB382" s="7">
         <v>1</v>
@@ -51080,40 +51080,40 @@
         <v>45</v>
       </c>
       <c r="I383" s="3" t="s">
-        <v>979</v>
+        <v>823</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>980</v>
+        <v>824</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="L383" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M383" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N383" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O383" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P383" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q383" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R383" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S383" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T383" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U383" s="3" t="s">
         <v>46</v>
@@ -51134,7 +51134,7 @@
         <v>46</v>
       </c>
       <c r="AA383" s="7">
-        <v>468000</v>
+        <v>85805</v>
       </c>
       <c r="AB383" s="7">
         <v>1</v>
@@ -51161,10 +51161,10 @@
         <v>0</v>
       </c>
       <c r="AJ383" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK383" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL383" s="3" t="s">
         <v>46</v>
@@ -51173,10 +51173,10 @@
         <v>46</v>
       </c>
       <c r="AN383" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO383" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="384" spans="1:41" x14ac:dyDescent="0.25">
@@ -51205,13 +51205,13 @@
         <v>45</v>
       </c>
       <c r="I384" s="3" t="s">
-        <v>929</v>
+        <v>975</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>930</v>
+        <v>976</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>931</v>
+        <v>977</v>
       </c>
       <c r="L384" s="3" t="s">
         <v>50</v>
@@ -51238,7 +51238,7 @@
         <v>2</v>
       </c>
       <c r="T384" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U384" s="3" t="s">
         <v>46</v>
@@ -51259,7 +51259,7 @@
         <v>46</v>
       </c>
       <c r="AA384" s="7">
-        <v>3025200</v>
+        <v>362000</v>
       </c>
       <c r="AB384" s="7">
         <v>1</v>
@@ -51330,28 +51330,28 @@
         <v>45</v>
       </c>
       <c r="I385" s="3" t="s">
-        <v>722</v>
+        <v>978</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>723</v>
+        <v>979</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>724</v>
+        <v>980</v>
       </c>
       <c r="L385" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M385" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N385" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O385" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P385" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q385" s="5">
         <v>2</v>
@@ -51363,7 +51363,7 @@
         <v>2</v>
       </c>
       <c r="T385" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U385" s="3" t="s">
         <v>46</v>
@@ -51384,7 +51384,7 @@
         <v>46</v>
       </c>
       <c r="AA385" s="7">
-        <v>1227480</v>
+        <v>471000</v>
       </c>
       <c r="AB385" s="7">
         <v>1</v>
@@ -51455,28 +51455,28 @@
         <v>45</v>
       </c>
       <c r="I386" s="3" t="s">
-        <v>144</v>
+        <v>876</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>145</v>
+        <v>877</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>146</v>
+        <v>878</v>
       </c>
       <c r="L386" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M386" s="3" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="N386" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="O386" s="3" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="P386" s="3" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="Q386" s="5">
         <v>2</v>
@@ -51488,7 +51488,7 @@
         <v>2</v>
       </c>
       <c r="T386" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U386" s="3" t="s">
         <v>46</v>
@@ -51509,7 +51509,7 @@
         <v>46</v>
       </c>
       <c r="AA386" s="7">
-        <v>3118775</v>
+        <v>1928113</v>
       </c>
       <c r="AB386" s="7">
         <v>1</v>
@@ -51536,10 +51536,10 @@
         <v>0</v>
       </c>
       <c r="AJ386" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK386" s="6">
-        <v>46296.93825494213</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL386" s="3" t="s">
         <v>46</v>
@@ -51548,10 +51548,10 @@
         <v>46</v>
       </c>
       <c r="AN386" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO386" s="6">
-        <v>46296.93825494213</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="387" spans="1:41" x14ac:dyDescent="0.25">
@@ -51580,28 +51580,28 @@
         <v>45</v>
       </c>
       <c r="I387" s="3" t="s">
-        <v>135</v>
+        <v>575</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>136</v>
+        <v>576</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>137</v>
+        <v>577</v>
       </c>
       <c r="L387" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M387" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N387" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O387" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P387" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q387" s="5">
         <v>2</v>
@@ -51613,7 +51613,7 @@
         <v>2</v>
       </c>
       <c r="T387" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U387" s="3" t="s">
         <v>46</v>
@@ -51634,7 +51634,7 @@
         <v>46</v>
       </c>
       <c r="AA387" s="7">
-        <v>536250</v>
+        <v>645000</v>
       </c>
       <c r="AB387" s="7">
         <v>1</v>
@@ -51705,28 +51705,28 @@
         <v>45</v>
       </c>
       <c r="I388" s="3" t="s">
-        <v>109</v>
+        <v>981</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>110</v>
+        <v>982</v>
       </c>
       <c r="K388" s="3" t="s">
-        <v>111</v>
+        <v>983</v>
       </c>
       <c r="L388" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M388" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N388" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O388" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P388" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q388" s="5">
         <v>2</v>
@@ -51738,7 +51738,7 @@
         <v>2</v>
       </c>
       <c r="T388" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U388" s="3" t="s">
         <v>46</v>
@@ -51758,8 +51758,8 @@
       <c r="Z388" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA388" s="7">
-        <v>558000</v>
+      <c r="AA388" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB388" s="7">
         <v>1</v>
@@ -51786,10 +51786,10 @@
         <v>0</v>
       </c>
       <c r="AJ388" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK388" s="6">
-        <v>46296.93825494213</v>
+        <v>46307.91045501157</v>
       </c>
       <c r="AL388" s="3" t="s">
         <v>46</v>
@@ -51798,10 +51798,10 @@
         <v>46</v>
       </c>
       <c r="AN388" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO388" s="6">
-        <v>46296.93825494213</v>
+        <v>46307.91045501157</v>
       </c>
     </row>
     <row r="389" spans="1:41" x14ac:dyDescent="0.25">
@@ -51830,40 +51830,40 @@
         <v>45</v>
       </c>
       <c r="I389" s="3" t="s">
-        <v>981</v>
+        <v>693</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>982</v>
+        <v>694</v>
       </c>
       <c r="K389" s="3" t="s">
-        <v>983</v>
+        <v>695</v>
       </c>
       <c r="L389" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M389" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N389" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O389" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P389" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q389" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R389" s="5">
         <v>2</v>
       </c>
       <c r="S389" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T389" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U389" s="3" t="s">
         <v>46</v>
@@ -51884,7 +51884,7 @@
         <v>46</v>
       </c>
       <c r="AA389" s="7">
-        <v>646676</v>
+        <v>6224400</v>
       </c>
       <c r="AB389" s="7">
         <v>1</v>
@@ -51911,10 +51911,10 @@
         <v>0</v>
       </c>
       <c r="AJ389" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK389" s="6">
-        <v>46296.93825494213</v>
+        <v>46306.863362881944</v>
       </c>
       <c r="AL389" s="3" t="s">
         <v>46</v>
@@ -51923,10 +51923,10 @@
         <v>46</v>
       </c>
       <c r="AN389" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO389" s="6">
-        <v>46296.93825494213</v>
+        <v>46306.863362881944</v>
       </c>
     </row>
     <row r="390" spans="1:41" x14ac:dyDescent="0.25">
@@ -51988,7 +51988,7 @@
         <v>31</v>
       </c>
       <c r="T390" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U390" s="3" t="s">
         <v>46</v>
@@ -52009,13 +52009,13 @@
         <v>46</v>
       </c>
       <c r="AA390" s="7">
-        <v>68309267</v>
+        <v>69477167</v>
       </c>
       <c r="AB390" s="7">
         <v>31</v>
       </c>
       <c r="AC390" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD390" s="3" t="s">
         <v>922</v>
@@ -52024,10 +52024,10 @@
         <v>923</v>
       </c>
       <c r="AF390" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG390" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH390" s="7">
         <v>6200000</v>
@@ -52113,7 +52113,7 @@
         <v>33</v>
       </c>
       <c r="T391" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U391" s="3" t="s">
         <v>46</v>
@@ -52140,7 +52140,7 @@
         <v>31</v>
       </c>
       <c r="AC391" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD391" s="3" t="s">
         <v>922</v>
@@ -52149,10 +52149,10 @@
         <v>923</v>
       </c>
       <c r="AF391" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG391" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH391" s="7">
         <v>6200000</v>
@@ -52229,16 +52229,16 @@
         <v>128</v>
       </c>
       <c r="Q392" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R392" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S392" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T392" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U392" s="3" t="s">
         <v>46</v>
@@ -52259,13 +52259,13 @@
         <v>46</v>
       </c>
       <c r="AA392" s="7">
-        <v>3039458</v>
+        <v>4069058</v>
       </c>
       <c r="AB392" s="7">
         <v>31</v>
       </c>
       <c r="AC392" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD392" s="3" t="s">
         <v>922</v>
@@ -52274,10 +52274,10 @@
         <v>923</v>
       </c>
       <c r="AF392" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG392" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH392" s="7">
         <v>6200000</v>
@@ -52363,7 +52363,7 @@
         <v>14</v>
       </c>
       <c r="T393" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U393" s="3" t="s">
         <v>46</v>
@@ -52390,7 +52390,7 @@
         <v>31</v>
       </c>
       <c r="AC393" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD393" s="3" t="s">
         <v>922</v>
@@ -52399,10 +52399,10 @@
         <v>923</v>
       </c>
       <c r="AF393" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG393" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH393" s="7">
         <v>6200000</v>
@@ -52488,7 +52488,7 @@
         <v>10</v>
       </c>
       <c r="T394" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U394" s="3" t="s">
         <v>46</v>
@@ -52515,7 +52515,7 @@
         <v>31</v>
       </c>
       <c r="AC394" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD394" s="3" t="s">
         <v>922</v>
@@ -52524,10 +52524,10 @@
         <v>923</v>
       </c>
       <c r="AF394" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG394" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH394" s="7">
         <v>6200000</v>
@@ -52613,7 +52613,7 @@
         <v>15</v>
       </c>
       <c r="T395" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U395" s="3" t="s">
         <v>46</v>
@@ -52634,13 +52634,13 @@
         <v>46</v>
       </c>
       <c r="AA395" s="7">
-        <v>1178000</v>
+        <v>1819500</v>
       </c>
       <c r="AB395" s="7">
         <v>31</v>
       </c>
       <c r="AC395" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD395" s="3" t="s">
         <v>922</v>
@@ -52649,10 +52649,10 @@
         <v>923</v>
       </c>
       <c r="AF395" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG395" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH395" s="7">
         <v>6200000</v>
@@ -52738,7 +52738,7 @@
         <v>17</v>
       </c>
       <c r="T396" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U396" s="3" t="s">
         <v>46</v>
@@ -52765,7 +52765,7 @@
         <v>31</v>
       </c>
       <c r="AC396" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD396" s="3" t="s">
         <v>922</v>
@@ -52774,10 +52774,10 @@
         <v>923</v>
       </c>
       <c r="AF396" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG396" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH396" s="7">
         <v>6200000</v>
@@ -52863,7 +52863,7 @@
         <v>6</v>
       </c>
       <c r="T397" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U397" s="3" t="s">
         <v>46</v>
@@ -52890,7 +52890,7 @@
         <v>31</v>
       </c>
       <c r="AC397" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD397" s="3" t="s">
         <v>922</v>
@@ -52899,10 +52899,10 @@
         <v>923</v>
       </c>
       <c r="AF397" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG397" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH397" s="7">
         <v>6200000</v>
@@ -52988,7 +52988,7 @@
         <v>13</v>
       </c>
       <c r="T398" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U398" s="3" t="s">
         <v>46</v>
@@ -53015,7 +53015,7 @@
         <v>31</v>
       </c>
       <c r="AC398" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD398" s="3" t="s">
         <v>922</v>
@@ -53024,10 +53024,10 @@
         <v>923</v>
       </c>
       <c r="AF398" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG398" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH398" s="7">
         <v>6200000</v>
@@ -53104,16 +53104,16 @@
         <v>128</v>
       </c>
       <c r="Q399" s="5">
+        <v>30</v>
+      </c>
+      <c r="R399" s="5">
         <v>29</v>
       </c>
-      <c r="R399" s="5">
-        <v>28</v>
-      </c>
       <c r="S399" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T399" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U399" s="3" t="s">
         <v>46</v>
@@ -53140,7 +53140,7 @@
         <v>31</v>
       </c>
       <c r="AC399" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD399" s="3" t="s">
         <v>922</v>
@@ -53149,10 +53149,10 @@
         <v>923</v>
       </c>
       <c r="AF399" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG399" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH399" s="7">
         <v>6200000</v>
@@ -53238,7 +53238,7 @@
         <v>12</v>
       </c>
       <c r="T400" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U400" s="3" t="s">
         <v>46</v>
@@ -53265,7 +53265,7 @@
         <v>31</v>
       </c>
       <c r="AC400" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD400" s="3" t="s">
         <v>922</v>
@@ -53274,10 +53274,10 @@
         <v>923</v>
       </c>
       <c r="AF400" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG400" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH400" s="7">
         <v>6200000</v>
@@ -53363,7 +53363,7 @@
         <v>30</v>
       </c>
       <c r="T401" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U401" s="3" t="s">
         <v>46</v>
@@ -53390,7 +53390,7 @@
         <v>31</v>
       </c>
       <c r="AC401" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD401" s="3" t="s">
         <v>922</v>
@@ -53399,10 +53399,10 @@
         <v>923</v>
       </c>
       <c r="AF401" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG401" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH401" s="7">
         <v>6200000</v>
@@ -53488,7 +53488,7 @@
         <v>15</v>
       </c>
       <c r="T402" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U402" s="3" t="s">
         <v>46</v>
@@ -53515,7 +53515,7 @@
         <v>31</v>
       </c>
       <c r="AC402" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD402" s="3" t="s">
         <v>922</v>
@@ -53524,10 +53524,10 @@
         <v>923</v>
       </c>
       <c r="AF402" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG402" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH402" s="7">
         <v>6200000</v>
@@ -53613,7 +53613,7 @@
         <v>10</v>
       </c>
       <c r="T403" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U403" s="3" t="s">
         <v>46</v>
@@ -53640,7 +53640,7 @@
         <v>31</v>
       </c>
       <c r="AC403" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD403" s="3" t="s">
         <v>922</v>
@@ -53649,10 +53649,10 @@
         <v>923</v>
       </c>
       <c r="AF403" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG403" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH403" s="7">
         <v>6200000</v>
@@ -53729,16 +53729,16 @@
         <v>128</v>
       </c>
       <c r="Q404" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R404" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S404" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T404" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U404" s="3" t="s">
         <v>46</v>
@@ -53765,7 +53765,7 @@
         <v>31</v>
       </c>
       <c r="AC404" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD404" s="3" t="s">
         <v>922</v>
@@ -53774,10 +53774,10 @@
         <v>923</v>
       </c>
       <c r="AF404" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG404" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH404" s="7">
         <v>6200000</v>
@@ -53854,16 +53854,16 @@
         <v>128</v>
       </c>
       <c r="Q405" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R405" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S405" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T405" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U405" s="3" t="s">
         <v>46</v>
@@ -53884,13 +53884,13 @@
         <v>46</v>
       </c>
       <c r="AA405" s="7">
-        <v>1156433</v>
+        <v>1442933</v>
       </c>
       <c r="AB405" s="7">
         <v>31</v>
       </c>
       <c r="AC405" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD405" s="3" t="s">
         <v>922</v>
@@ -53899,10 +53899,10 @@
         <v>923</v>
       </c>
       <c r="AF405" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG405" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH405" s="7">
         <v>6200000</v>
@@ -53988,7 +53988,7 @@
         <v>13</v>
       </c>
       <c r="T406" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U406" s="3" t="s">
         <v>46</v>
@@ -54015,7 +54015,7 @@
         <v>31</v>
       </c>
       <c r="AC406" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD406" s="3" t="s">
         <v>922</v>
@@ -54024,10 +54024,10 @@
         <v>923</v>
       </c>
       <c r="AF406" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG406" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH406" s="7">
         <v>6200000</v>
@@ -54104,16 +54104,16 @@
         <v>128</v>
       </c>
       <c r="Q407" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R407" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S407" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T407" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U407" s="3" t="s">
         <v>46</v>
@@ -54140,7 +54140,7 @@
         <v>31</v>
       </c>
       <c r="AC407" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD407" s="3" t="s">
         <v>922</v>
@@ -54149,10 +54149,10 @@
         <v>923</v>
       </c>
       <c r="AF407" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG407" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH407" s="7">
         <v>6200000</v>
@@ -54238,7 +54238,7 @@
         <v>8</v>
       </c>
       <c r="T408" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U408" s="3" t="s">
         <v>46</v>
@@ -54265,7 +54265,7 @@
         <v>31</v>
       </c>
       <c r="AC408" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD408" s="3" t="s">
         <v>922</v>
@@ -54274,10 +54274,10 @@
         <v>923</v>
       </c>
       <c r="AF408" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG408" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH408" s="7">
         <v>6200000</v>
@@ -54363,7 +54363,7 @@
         <v>8</v>
       </c>
       <c r="T409" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U409" s="3" t="s">
         <v>46</v>
@@ -54390,7 +54390,7 @@
         <v>31</v>
       </c>
       <c r="AC409" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD409" s="3" t="s">
         <v>922</v>
@@ -54399,10 +54399,10 @@
         <v>923</v>
       </c>
       <c r="AF409" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG409" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH409" s="7">
         <v>6200000</v>
@@ -54488,7 +54488,7 @@
         <v>26</v>
       </c>
       <c r="T410" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U410" s="3" t="s">
         <v>46</v>
@@ -54509,13 +54509,13 @@
         <v>46</v>
       </c>
       <c r="AA410" s="7">
-        <v>453000</v>
+        <v>645000</v>
       </c>
       <c r="AB410" s="7">
         <v>31</v>
       </c>
       <c r="AC410" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD410" s="3" t="s">
         <v>922</v>
@@ -54524,10 +54524,10 @@
         <v>923</v>
       </c>
       <c r="AF410" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG410" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH410" s="7">
         <v>6200000</v>
@@ -54613,7 +54613,7 @@
         <v>21</v>
       </c>
       <c r="T411" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U411" s="3" t="s">
         <v>46</v>
@@ -54640,7 +54640,7 @@
         <v>31</v>
       </c>
       <c r="AC411" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD411" s="3" t="s">
         <v>922</v>
@@ -54649,10 +54649,10 @@
         <v>923</v>
       </c>
       <c r="AF411" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG411" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH411" s="7">
         <v>6200000</v>
@@ -54705,13 +54705,13 @@
         <v>45</v>
       </c>
       <c r="I412" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L412" s="3" t="s">
         <v>50</v>
@@ -54738,7 +54738,7 @@
         <v>14</v>
       </c>
       <c r="T412" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U412" s="3" t="s">
         <v>46</v>
@@ -54765,7 +54765,7 @@
         <v>31</v>
       </c>
       <c r="AC412" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD412" s="3" t="s">
         <v>922</v>
@@ -54774,10 +54774,10 @@
         <v>923</v>
       </c>
       <c r="AF412" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG412" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH412" s="7">
         <v>6200000</v>
@@ -54863,7 +54863,7 @@
         <v>14</v>
       </c>
       <c r="T413" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U413" s="3" t="s">
         <v>46</v>
@@ -54890,7 +54890,7 @@
         <v>31</v>
       </c>
       <c r="AC413" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD413" s="3" t="s">
         <v>922</v>
@@ -54899,10 +54899,10 @@
         <v>923</v>
       </c>
       <c r="AF413" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG413" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH413" s="7">
         <v>6200000</v>
@@ -54979,16 +54979,16 @@
         <v>128</v>
       </c>
       <c r="Q414" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R414" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S414" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T414" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U414" s="3" t="s">
         <v>46</v>
@@ -55015,7 +55015,7 @@
         <v>31</v>
       </c>
       <c r="AC414" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD414" s="3" t="s">
         <v>922</v>
@@ -55024,10 +55024,10 @@
         <v>923</v>
       </c>
       <c r="AF414" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG414" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH414" s="7">
         <v>6200000</v>
@@ -55113,7 +55113,7 @@
         <v>32</v>
       </c>
       <c r="T415" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U415" s="3" t="s">
         <v>46</v>
@@ -55134,13 +55134,13 @@
         <v>46</v>
       </c>
       <c r="AA415" s="7">
-        <v>1164200</v>
+        <v>1693464</v>
       </c>
       <c r="AB415" s="7">
         <v>31</v>
       </c>
       <c r="AC415" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD415" s="3" t="s">
         <v>922</v>
@@ -55149,10 +55149,10 @@
         <v>923</v>
       </c>
       <c r="AF415" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG415" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH415" s="7">
         <v>18600000</v>
@@ -55205,10 +55205,10 @@
         <v>999</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>813</v>
@@ -55238,7 +55238,7 @@
         <v>9</v>
       </c>
       <c r="T416" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U416" s="3" t="s">
         <v>46</v>
@@ -55265,7 +55265,7 @@
         <v>31</v>
       </c>
       <c r="AC416" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD416" s="3" t="s">
         <v>922</v>
@@ -55274,10 +55274,10 @@
         <v>923</v>
       </c>
       <c r="AF416" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG416" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH416" s="7">
         <v>18600000</v>
@@ -55363,7 +55363,7 @@
         <v>11</v>
       </c>
       <c r="T417" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U417" s="3" t="s">
         <v>46</v>
@@ -55390,7 +55390,7 @@
         <v>31</v>
       </c>
       <c r="AC417" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD417" s="3" t="s">
         <v>922</v>
@@ -55399,10 +55399,10 @@
         <v>923</v>
       </c>
       <c r="AF417" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG417" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH417" s="7">
         <v>18600000</v>
@@ -55488,7 +55488,7 @@
         <v>14</v>
       </c>
       <c r="T418" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U418" s="3" t="s">
         <v>46</v>
@@ -55515,7 +55515,7 @@
         <v>31</v>
       </c>
       <c r="AC418" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD418" s="3" t="s">
         <v>922</v>
@@ -55524,10 +55524,10 @@
         <v>923</v>
       </c>
       <c r="AF418" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG418" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH418" s="7">
         <v>18600000</v>
@@ -55604,16 +55604,16 @@
         <v>134</v>
       </c>
       <c r="Q419" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R419" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S419" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T419" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U419" s="3" t="s">
         <v>46</v>
@@ -55640,7 +55640,7 @@
         <v>31</v>
       </c>
       <c r="AC419" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD419" s="3" t="s">
         <v>922</v>
@@ -55649,10 +55649,10 @@
         <v>923</v>
       </c>
       <c r="AF419" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG419" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH419" s="7">
         <v>18600000</v>
@@ -55738,7 +55738,7 @@
         <v>10</v>
       </c>
       <c r="T420" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U420" s="3" t="s">
         <v>46</v>
@@ -55765,7 +55765,7 @@
         <v>31</v>
       </c>
       <c r="AC420" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD420" s="3" t="s">
         <v>922</v>
@@ -55774,10 +55774,10 @@
         <v>923</v>
       </c>
       <c r="AF420" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG420" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH420" s="7">
         <v>18600000</v>
@@ -55863,7 +55863,7 @@
         <v>15</v>
       </c>
       <c r="T421" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U421" s="3" t="s">
         <v>46</v>
@@ -55890,7 +55890,7 @@
         <v>31</v>
       </c>
       <c r="AC421" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD421" s="3" t="s">
         <v>922</v>
@@ -55899,10 +55899,10 @@
         <v>923</v>
       </c>
       <c r="AF421" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG421" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH421" s="7">
         <v>18600000</v>
@@ -55988,7 +55988,7 @@
         <v>9</v>
       </c>
       <c r="T422" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U422" s="3" t="s">
         <v>46</v>
@@ -56015,7 +56015,7 @@
         <v>31</v>
       </c>
       <c r="AC422" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD422" s="3" t="s">
         <v>922</v>
@@ -56024,10 +56024,10 @@
         <v>923</v>
       </c>
       <c r="AF422" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG422" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH422" s="7">
         <v>12400000</v>
@@ -56113,7 +56113,7 @@
         <v>6</v>
       </c>
       <c r="T423" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U423" s="3" t="s">
         <v>46</v>
@@ -56134,13 +56134,13 @@
         <v>46</v>
       </c>
       <c r="AA423" s="7">
-        <v>1780573</v>
+        <v>2150021</v>
       </c>
       <c r="AB423" s="7">
         <v>31</v>
       </c>
       <c r="AC423" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD423" s="3" t="s">
         <v>922</v>
@@ -56149,10 +56149,10 @@
         <v>923</v>
       </c>
       <c r="AF423" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG423" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH423" s="7">
         <v>12400000</v>
@@ -56238,7 +56238,7 @@
         <v>9</v>
       </c>
       <c r="T424" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U424" s="3" t="s">
         <v>46</v>
@@ -56265,7 +56265,7 @@
         <v>31</v>
       </c>
       <c r="AC424" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD424" s="3" t="s">
         <v>922</v>
@@ -56274,10 +56274,10 @@
         <v>923</v>
       </c>
       <c r="AF424" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG424" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH424" s="7">
         <v>12400000</v>
@@ -56354,16 +56354,16 @@
         <v>128</v>
       </c>
       <c r="Q425" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R425" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S425" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T425" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U425" s="3" t="s">
         <v>46</v>
@@ -56390,7 +56390,7 @@
         <v>31</v>
       </c>
       <c r="AC425" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD425" s="3" t="s">
         <v>922</v>
@@ -56399,10 +56399,10 @@
         <v>923</v>
       </c>
       <c r="AF425" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG425" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH425" s="7">
         <v>12400000</v>
@@ -56488,7 +56488,7 @@
         <v>17</v>
       </c>
       <c r="T426" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U426" s="3" t="s">
         <v>46</v>
@@ -56515,7 +56515,7 @@
         <v>31</v>
       </c>
       <c r="AC426" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD426" s="3" t="s">
         <v>922</v>
@@ -56524,10 +56524,10 @@
         <v>923</v>
       </c>
       <c r="AF426" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG426" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH426" s="7">
         <v>12400000</v>
@@ -56613,7 +56613,7 @@
         <v>13</v>
       </c>
       <c r="T427" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U427" s="3" t="s">
         <v>46</v>
@@ -56640,7 +56640,7 @@
         <v>31</v>
       </c>
       <c r="AC427" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD427" s="3" t="s">
         <v>922</v>
@@ -56649,10 +56649,10 @@
         <v>923</v>
       </c>
       <c r="AF427" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG427" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH427" s="7">
         <v>12400000</v>
@@ -56738,7 +56738,7 @@
         <v>15</v>
       </c>
       <c r="T428" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U428" s="3" t="s">
         <v>46</v>
@@ -56765,7 +56765,7 @@
         <v>31</v>
       </c>
       <c r="AC428" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD428" s="3" t="s">
         <v>922</v>
@@ -56774,10 +56774,10 @@
         <v>923</v>
       </c>
       <c r="AF428" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG428" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH428" s="7">
         <v>12400000</v>
@@ -56863,7 +56863,7 @@
         <v>14</v>
       </c>
       <c r="T429" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U429" s="3" t="s">
         <v>46</v>
@@ -56890,7 +56890,7 @@
         <v>31</v>
       </c>
       <c r="AC429" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD429" s="3" t="s">
         <v>922</v>
@@ -56899,10 +56899,10 @@
         <v>923</v>
       </c>
       <c r="AF429" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG429" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH429" s="7">
         <v>12400000</v>
@@ -56988,7 +56988,7 @@
         <v>27</v>
       </c>
       <c r="T430" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U430" s="3" t="s">
         <v>46</v>
@@ -57009,13 +57009,13 @@
         <v>46</v>
       </c>
       <c r="AA430" s="7">
-        <v>962500</v>
+        <v>1252900</v>
       </c>
       <c r="AB430" s="7">
         <v>31</v>
       </c>
       <c r="AC430" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD430" s="3" t="s">
         <v>922</v>
@@ -57024,10 +57024,10 @@
         <v>923</v>
       </c>
       <c r="AF430" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG430" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH430" s="7">
         <v>12400000</v>
@@ -57080,13 +57080,13 @@
         <v>921</v>
       </c>
       <c r="I431" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K431" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L431" s="3" t="s">
         <v>50</v>
@@ -57113,7 +57113,7 @@
         <v>14</v>
       </c>
       <c r="T431" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U431" s="3" t="s">
         <v>46</v>
@@ -57140,7 +57140,7 @@
         <v>31</v>
       </c>
       <c r="AC431" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD431" s="3" t="s">
         <v>922</v>
@@ -57149,10 +57149,10 @@
         <v>923</v>
       </c>
       <c r="AF431" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG431" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH431" s="7">
         <v>12400000</v>
@@ -57229,16 +57229,16 @@
         <v>128</v>
       </c>
       <c r="Q432" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R432" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S432" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T432" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U432" s="3" t="s">
         <v>46</v>
@@ -57265,7 +57265,7 @@
         <v>31</v>
       </c>
       <c r="AC432" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD432" s="3" t="s">
         <v>922</v>
@@ -57274,10 +57274,10 @@
         <v>923</v>
       </c>
       <c r="AF432" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG432" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH432" s="7">
         <v>12400000</v>
@@ -57363,7 +57363,7 @@
         <v>32</v>
       </c>
       <c r="T433" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U433" s="3" t="s">
         <v>46</v>
@@ -57390,7 +57390,7 @@
         <v>31</v>
       </c>
       <c r="AC433" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD433" s="3" t="s">
         <v>922</v>
@@ -57399,10 +57399,10 @@
         <v>923</v>
       </c>
       <c r="AF433" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG433" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH433" s="7">
         <v>12400000</v>
@@ -57488,7 +57488,7 @@
         <v>27</v>
       </c>
       <c r="T434" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U434" s="3" t="s">
         <v>46</v>
@@ -57515,7 +57515,7 @@
         <v>31</v>
       </c>
       <c r="AC434" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD434" s="3" t="s">
         <v>922</v>
@@ -57524,10 +57524,10 @@
         <v>923</v>
       </c>
       <c r="AF434" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG434" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH434" s="7">
         <v>12400000</v>
@@ -57613,7 +57613,7 @@
         <v>12</v>
       </c>
       <c r="T435" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U435" s="3" t="s">
         <v>46</v>
@@ -57640,7 +57640,7 @@
         <v>31</v>
       </c>
       <c r="AC435" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD435" s="3" t="s">
         <v>922</v>
@@ -57649,10 +57649,10 @@
         <v>923</v>
       </c>
       <c r="AF435" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG435" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH435" s="7">
         <v>12400000</v>
@@ -57738,7 +57738,7 @@
         <v>33</v>
       </c>
       <c r="T436" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U436" s="3" t="s">
         <v>46</v>
@@ -57759,13 +57759,13 @@
         <v>46</v>
       </c>
       <c r="AA436" s="7">
-        <v>3084711</v>
+        <v>4011791</v>
       </c>
       <c r="AB436" s="7">
         <v>31</v>
       </c>
       <c r="AC436" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD436" s="3" t="s">
         <v>922</v>
@@ -57774,10 +57774,10 @@
         <v>923</v>
       </c>
       <c r="AF436" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG436" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH436" s="7">
         <v>12400000</v>
@@ -57854,16 +57854,16 @@
         <v>128</v>
       </c>
       <c r="Q437" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R437" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S437" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T437" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U437" s="3" t="s">
         <v>46</v>
@@ -57890,7 +57890,7 @@
         <v>31</v>
       </c>
       <c r="AC437" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD437" s="3" t="s">
         <v>922</v>
@@ -57899,10 +57899,10 @@
         <v>923</v>
       </c>
       <c r="AF437" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG437" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH437" s="7">
         <v>12400000</v>
@@ -57988,7 +57988,7 @@
         <v>17</v>
       </c>
       <c r="T438" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U438" s="3" t="s">
         <v>46</v>
@@ -58015,7 +58015,7 @@
         <v>31</v>
       </c>
       <c r="AC438" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD438" s="3" t="s">
         <v>922</v>
@@ -58024,10 +58024,10 @@
         <v>923</v>
       </c>
       <c r="AF438" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG438" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH438" s="7">
         <v>12400000</v>
@@ -58113,7 +58113,7 @@
         <v>13</v>
       </c>
       <c r="T439" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U439" s="3" t="s">
         <v>46</v>
@@ -58140,7 +58140,7 @@
         <v>31</v>
       </c>
       <c r="AC439" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD439" s="3" t="s">
         <v>922</v>
@@ -58149,10 +58149,10 @@
         <v>923</v>
       </c>
       <c r="AF439" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG439" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH439" s="7">
         <v>12400000</v>
@@ -58238,7 +58238,7 @@
         <v>15</v>
       </c>
       <c r="T440" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U440" s="3" t="s">
         <v>46</v>
@@ -58265,7 +58265,7 @@
         <v>31</v>
       </c>
       <c r="AC440" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD440" s="3" t="s">
         <v>922</v>
@@ -58274,10 +58274,10 @@
         <v>923</v>
       </c>
       <c r="AF440" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG440" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH440" s="7">
         <v>12400000</v>
@@ -58354,16 +58354,16 @@
         <v>54</v>
       </c>
       <c r="Q441" s="5">
+        <v>33</v>
+      </c>
+      <c r="R441" s="5">
         <v>32</v>
       </c>
-      <c r="R441" s="5">
-        <v>31</v>
-      </c>
       <c r="S441" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T441" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U441" s="3" t="s">
         <v>46</v>
@@ -58384,13 +58384,13 @@
         <v>46</v>
       </c>
       <c r="AA441" s="7">
-        <v>1854160</v>
+        <v>3237002</v>
       </c>
       <c r="AB441" s="7">
         <v>31</v>
       </c>
       <c r="AC441" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD441" s="3" t="s">
         <v>922</v>
@@ -58399,10 +58399,10 @@
         <v>923</v>
       </c>
       <c r="AF441" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG441" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH441" s="7">
         <v>12400000</v>
@@ -58488,7 +58488,7 @@
         <v>17</v>
       </c>
       <c r="T442" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U442" s="3" t="s">
         <v>46</v>
@@ -58515,7 +58515,7 @@
         <v>31</v>
       </c>
       <c r="AC442" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD442" s="3" t="s">
         <v>922</v>
@@ -58524,10 +58524,10 @@
         <v>923</v>
       </c>
       <c r="AF442" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG442" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH442" s="7">
         <v>12400000</v>
@@ -58613,7 +58613,7 @@
         <v>14</v>
       </c>
       <c r="T443" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U443" s="3" t="s">
         <v>46</v>
@@ -58640,7 +58640,7 @@
         <v>31</v>
       </c>
       <c r="AC443" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD443" s="3" t="s">
         <v>922</v>
@@ -58649,10 +58649,10 @@
         <v>923</v>
       </c>
       <c r="AF443" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG443" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH443" s="7">
         <v>12400000</v>
@@ -58738,7 +58738,7 @@
         <v>10</v>
       </c>
       <c r="T444" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U444" s="3" t="s">
         <v>46</v>
@@ -58765,7 +58765,7 @@
         <v>31</v>
       </c>
       <c r="AC444" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD444" s="3" t="s">
         <v>922</v>
@@ -58774,10 +58774,10 @@
         <v>923</v>
       </c>
       <c r="AF444" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG444" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH444" s="7">
         <v>12400000</v>
@@ -58863,7 +58863,7 @@
         <v>9</v>
       </c>
       <c r="T445" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U445" s="3" t="s">
         <v>46</v>
@@ -58890,7 +58890,7 @@
         <v>31</v>
       </c>
       <c r="AC445" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD445" s="3" t="s">
         <v>922</v>
@@ -58899,10 +58899,10 @@
         <v>923</v>
       </c>
       <c r="AF445" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG445" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH445" s="7">
         <v>12400000</v>
@@ -58988,7 +58988,7 @@
         <v>8</v>
       </c>
       <c r="T446" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U446" s="3" t="s">
         <v>46</v>
@@ -59015,7 +59015,7 @@
         <v>31</v>
       </c>
       <c r="AC446" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD446" s="3" t="s">
         <v>922</v>
@@ -59024,10 +59024,10 @@
         <v>923</v>
       </c>
       <c r="AF446" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG446" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH446" s="7">
         <v>12400000</v>
@@ -59113,7 +59113,7 @@
         <v>13</v>
       </c>
       <c r="T447" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U447" s="3" t="s">
         <v>46</v>
@@ -59140,7 +59140,7 @@
         <v>31</v>
       </c>
       <c r="AC447" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD447" s="3" t="s">
         <v>922</v>
@@ -59149,10 +59149,10 @@
         <v>923</v>
       </c>
       <c r="AF447" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG447" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH447" s="7">
         <v>12400000</v>
@@ -59238,7 +59238,7 @@
         <v>19</v>
       </c>
       <c r="T448" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U448" s="3" t="s">
         <v>46</v>
@@ -59265,7 +59265,7 @@
         <v>31</v>
       </c>
       <c r="AC448" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD448" s="3" t="s">
         <v>922</v>
@@ -59274,10 +59274,10 @@
         <v>923</v>
       </c>
       <c r="AF448" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG448" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH448" s="7">
         <v>12400000</v>
@@ -59363,7 +59363,7 @@
         <v>8</v>
       </c>
       <c r="T449" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U449" s="3" t="s">
         <v>46</v>
@@ -59384,13 +59384,13 @@
         <v>46</v>
       </c>
       <c r="AA449" s="7">
-        <v>1391208</v>
+        <v>3245368</v>
       </c>
       <c r="AB449" s="7">
         <v>31</v>
       </c>
       <c r="AC449" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD449" s="3" t="s">
         <v>922</v>
@@ -59399,10 +59399,10 @@
         <v>923</v>
       </c>
       <c r="AF449" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG449" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH449" s="7">
         <v>12400000</v>
@@ -59488,7 +59488,7 @@
         <v>10</v>
       </c>
       <c r="T450" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U450" s="3" t="s">
         <v>46</v>
@@ -59515,7 +59515,7 @@
         <v>31</v>
       </c>
       <c r="AC450" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD450" s="3" t="s">
         <v>922</v>
@@ -59524,10 +59524,10 @@
         <v>923</v>
       </c>
       <c r="AF450" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG450" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH450" s="7">
         <v>12400000</v>
@@ -59613,7 +59613,7 @@
         <v>13</v>
       </c>
       <c r="T451" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U451" s="3" t="s">
         <v>46</v>
@@ -59640,7 +59640,7 @@
         <v>31</v>
       </c>
       <c r="AC451" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD451" s="3" t="s">
         <v>922</v>
@@ -59649,10 +59649,10 @@
         <v>923</v>
       </c>
       <c r="AF451" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG451" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH451" s="7">
         <v>12400000</v>
@@ -59738,7 +59738,7 @@
         <v>16</v>
       </c>
       <c r="T452" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U452" s="3" t="s">
         <v>46</v>
@@ -59765,7 +59765,7 @@
         <v>31</v>
       </c>
       <c r="AC452" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD452" s="3" t="s">
         <v>922</v>
@@ -59774,10 +59774,10 @@
         <v>923</v>
       </c>
       <c r="AF452" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG452" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH452" s="7">
         <v>12400000</v>
@@ -59854,16 +59854,16 @@
         <v>128</v>
       </c>
       <c r="Q453" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R453" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S453" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T453" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U453" s="3" t="s">
         <v>46</v>
@@ -59890,7 +59890,7 @@
         <v>31</v>
       </c>
       <c r="AC453" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD453" s="3" t="s">
         <v>922</v>
@@ -59899,10 +59899,10 @@
         <v>923</v>
       </c>
       <c r="AF453" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG453" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH453" s="7">
         <v>12400000</v>
@@ -59988,7 +59988,7 @@
         <v>8</v>
       </c>
       <c r="T454" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U454" s="3" t="s">
         <v>46</v>
@@ -60015,7 +60015,7 @@
         <v>31</v>
       </c>
       <c r="AC454" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD454" s="3" t="s">
         <v>922</v>
@@ -60024,10 +60024,10 @@
         <v>923</v>
       </c>
       <c r="AF454" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG454" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH454" s="7">
         <v>12400000</v>
@@ -60113,7 +60113,7 @@
         <v>9</v>
       </c>
       <c r="T455" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U455" s="3" t="s">
         <v>46</v>
@@ -60140,7 +60140,7 @@
         <v>31</v>
       </c>
       <c r="AC455" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD455" s="3" t="s">
         <v>922</v>
@@ -60149,10 +60149,10 @@
         <v>923</v>
       </c>
       <c r="AF455" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG455" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH455" s="7">
         <v>12400000</v>
@@ -60238,7 +60238,7 @@
         <v>14</v>
       </c>
       <c r="T456" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U456" s="3" t="s">
         <v>46</v>
@@ -60265,7 +60265,7 @@
         <v>31</v>
       </c>
       <c r="AC456" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD456" s="3" t="s">
         <v>922</v>
@@ -60274,10 +60274,10 @@
         <v>923</v>
       </c>
       <c r="AF456" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG456" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH456" s="7">
         <v>12400000</v>
@@ -60363,7 +60363,7 @@
         <v>31</v>
       </c>
       <c r="T457" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U457" s="3" t="s">
         <v>46</v>
@@ -60390,7 +60390,7 @@
         <v>31</v>
       </c>
       <c r="AC457" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD457" s="3" t="s">
         <v>922</v>
@@ -60399,10 +60399,10 @@
         <v>923</v>
       </c>
       <c r="AF457" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG457" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH457" s="7">
         <v>12400000</v>
@@ -60488,7 +60488,7 @@
         <v>15</v>
       </c>
       <c r="T458" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U458" s="3" t="s">
         <v>46</v>
@@ -60515,7 +60515,7 @@
         <v>31</v>
       </c>
       <c r="AC458" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD458" s="3" t="s">
         <v>922</v>
@@ -60524,10 +60524,10 @@
         <v>923</v>
       </c>
       <c r="AF458" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG458" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH458" s="7">
         <v>12400000</v>
@@ -60613,7 +60613,7 @@
         <v>11</v>
       </c>
       <c r="T459" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U459" s="3" t="s">
         <v>46</v>
@@ -60640,7 +60640,7 @@
         <v>31</v>
       </c>
       <c r="AC459" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD459" s="3" t="s">
         <v>922</v>
@@ -60649,10 +60649,10 @@
         <v>923</v>
       </c>
       <c r="AF459" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG459" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH459" s="7">
         <v>12400000</v>
@@ -60738,7 +60738,7 @@
         <v>10</v>
       </c>
       <c r="T460" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U460" s="3" t="s">
         <v>46</v>
@@ -60765,7 +60765,7 @@
         <v>31</v>
       </c>
       <c r="AC460" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD460" s="3" t="s">
         <v>922</v>
@@ -60774,10 +60774,10 @@
         <v>923</v>
       </c>
       <c r="AF460" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG460" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH460" s="7">
         <v>12400000</v>
@@ -60854,16 +60854,16 @@
         <v>128</v>
       </c>
       <c r="Q461" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R461" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S461" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T461" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U461" s="3" t="s">
         <v>46</v>
@@ -60890,7 +60890,7 @@
         <v>31</v>
       </c>
       <c r="AC461" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD461" s="3" t="s">
         <v>922</v>
@@ -60899,10 +60899,10 @@
         <v>923</v>
       </c>
       <c r="AF461" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG461" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH461" s="7">
         <v>12400000</v>
@@ -60988,7 +60988,7 @@
         <v>8</v>
       </c>
       <c r="T462" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U462" s="3" t="s">
         <v>46</v>
@@ -61015,7 +61015,7 @@
         <v>31</v>
       </c>
       <c r="AC462" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD462" s="3" t="s">
         <v>922</v>
@@ -61024,10 +61024,10 @@
         <v>923</v>
       </c>
       <c r="AF462" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG462" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH462" s="7">
         <v>12400000</v>
@@ -61113,7 +61113,7 @@
         <v>14</v>
       </c>
       <c r="T463" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U463" s="3" t="s">
         <v>46</v>
@@ -61140,7 +61140,7 @@
         <v>31</v>
       </c>
       <c r="AC463" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD463" s="3" t="s">
         <v>922</v>
@@ -61149,10 +61149,10 @@
         <v>923</v>
       </c>
       <c r="AF463" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG463" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH463" s="7">
         <v>12400000</v>
@@ -61238,7 +61238,7 @@
         <v>31</v>
       </c>
       <c r="T464" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U464" s="3" t="s">
         <v>46</v>
@@ -61265,7 +61265,7 @@
         <v>31</v>
       </c>
       <c r="AC464" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD464" s="3" t="s">
         <v>922</v>
@@ -61274,10 +61274,10 @@
         <v>923</v>
       </c>
       <c r="AF464" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG464" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH464" s="7">
         <v>6200000</v>
@@ -61363,7 +61363,7 @@
         <v>10</v>
       </c>
       <c r="T465" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U465" s="3" t="s">
         <v>46</v>
@@ -61390,7 +61390,7 @@
         <v>31</v>
       </c>
       <c r="AC465" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD465" s="3" t="s">
         <v>922</v>
@@ -61399,10 +61399,10 @@
         <v>923</v>
       </c>
       <c r="AF465" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG465" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH465" s="7">
         <v>6200000</v>
@@ -61455,13 +61455,13 @@
         <v>45</v>
       </c>
       <c r="I466" s="3" t="s">
-        <v>981</v>
+        <v>955</v>
       </c>
       <c r="J466" s="3" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="L466" s="3" t="s">
         <v>50</v>
@@ -61488,7 +61488,7 @@
         <v>10</v>
       </c>
       <c r="T466" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U466" s="3" t="s">
         <v>46</v>
@@ -61515,7 +61515,7 @@
         <v>31</v>
       </c>
       <c r="AC466" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD466" s="3" t="s">
         <v>922</v>
@@ -61524,10 +61524,10 @@
         <v>923</v>
       </c>
       <c r="AF466" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG466" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH466" s="7">
         <v>6200000</v>
@@ -61604,16 +61604,16 @@
         <v>128</v>
       </c>
       <c r="Q467" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R467" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S467" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T467" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U467" s="3" t="s">
         <v>46</v>
@@ -61634,13 +61634,13 @@
         <v>46</v>
       </c>
       <c r="AA467" s="7">
-        <v>712800</v>
+        <v>942800</v>
       </c>
       <c r="AB467" s="7">
         <v>31</v>
       </c>
       <c r="AC467" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD467" s="3" t="s">
         <v>922</v>
@@ -61649,10 +61649,10 @@
         <v>923</v>
       </c>
       <c r="AF467" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG467" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH467" s="7">
         <v>6200000</v>
@@ -61738,7 +61738,7 @@
         <v>14</v>
       </c>
       <c r="T468" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U468" s="3" t="s">
         <v>46</v>
@@ -61765,7 +61765,7 @@
         <v>31</v>
       </c>
       <c r="AC468" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD468" s="3" t="s">
         <v>922</v>
@@ -61774,10 +61774,10 @@
         <v>923</v>
       </c>
       <c r="AF468" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG468" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH468" s="7">
         <v>6200000</v>
@@ -61863,7 +61863,7 @@
         <v>11</v>
       </c>
       <c r="T469" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U469" s="3" t="s">
         <v>46</v>
@@ -61890,7 +61890,7 @@
         <v>31</v>
       </c>
       <c r="AC469" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD469" s="3" t="s">
         <v>922</v>
@@ -61899,10 +61899,10 @@
         <v>923</v>
       </c>
       <c r="AF469" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG469" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH469" s="7">
         <v>6200000</v>
@@ -61979,16 +61979,16 @@
         <v>54</v>
       </c>
       <c r="Q470" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R470" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S470" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T470" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U470" s="3" t="s">
         <v>46</v>
@@ -62009,13 +62009,13 @@
         <v>46</v>
       </c>
       <c r="AA470" s="7">
-        <v>910800</v>
+        <v>1165291</v>
       </c>
       <c r="AB470" s="7">
         <v>31</v>
       </c>
       <c r="AC470" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD470" s="3" t="s">
         <v>922</v>
@@ -62024,10 +62024,10 @@
         <v>923</v>
       </c>
       <c r="AF470" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG470" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH470" s="7">
         <v>6200000</v>
@@ -62113,7 +62113,7 @@
         <v>8</v>
       </c>
       <c r="T471" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U471" s="3" t="s">
         <v>46</v>
@@ -62140,7 +62140,7 @@
         <v>31</v>
       </c>
       <c r="AC471" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD471" s="3" t="s">
         <v>922</v>
@@ -62149,10 +62149,10 @@
         <v>923</v>
       </c>
       <c r="AF471" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG471" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH471" s="7">
         <v>6200000</v>
@@ -62238,7 +62238,7 @@
         <v>8</v>
       </c>
       <c r="T472" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U472" s="3" t="s">
         <v>46</v>
@@ -62265,7 +62265,7 @@
         <v>31</v>
       </c>
       <c r="AC472" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD472" s="3" t="s">
         <v>922</v>
@@ -62274,10 +62274,10 @@
         <v>923</v>
       </c>
       <c r="AF472" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG472" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH472" s="7">
         <v>6200000</v>
@@ -62363,7 +62363,7 @@
         <v>8</v>
       </c>
       <c r="T473" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U473" s="3" t="s">
         <v>46</v>
@@ -62390,7 +62390,7 @@
         <v>31</v>
       </c>
       <c r="AC473" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD473" s="3" t="s">
         <v>922</v>
@@ -62399,10 +62399,10 @@
         <v>923</v>
       </c>
       <c r="AF473" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG473" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH473" s="7">
         <v>6200000</v>
@@ -62488,7 +62488,7 @@
         <v>19</v>
       </c>
       <c r="T474" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U474" s="3" t="s">
         <v>46</v>
@@ -62509,13 +62509,13 @@
         <v>46</v>
       </c>
       <c r="AA474" s="7">
-        <v>928100</v>
+        <v>1838900</v>
       </c>
       <c r="AB474" s="7">
         <v>31</v>
       </c>
       <c r="AC474" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD474" s="3" t="s">
         <v>922</v>
@@ -62524,10 +62524,10 @@
         <v>923</v>
       </c>
       <c r="AF474" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG474" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH474" s="7">
         <v>6200000</v>
@@ -62613,7 +62613,7 @@
         <v>10</v>
       </c>
       <c r="T475" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U475" s="3" t="s">
         <v>46</v>
@@ -62640,7 +62640,7 @@
         <v>31</v>
       </c>
       <c r="AC475" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD475" s="3" t="s">
         <v>922</v>
@@ -62649,10 +62649,10 @@
         <v>923</v>
       </c>
       <c r="AF475" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG475" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH475" s="7">
         <v>6200000</v>
@@ -62705,10 +62705,10 @@
         <v>45</v>
       </c>
       <c r="I476" s="3" t="s">
-        <v>979</v>
+        <v>964</v>
       </c>
       <c r="J476" s="3" t="s">
-        <v>980</v>
+        <v>965</v>
       </c>
       <c r="K476" s="3" t="s">
         <v>813</v>
@@ -62738,7 +62738,7 @@
         <v>9</v>
       </c>
       <c r="T476" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U476" s="3" t="s">
         <v>46</v>
@@ -62765,7 +62765,7 @@
         <v>31</v>
       </c>
       <c r="AC476" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD476" s="3" t="s">
         <v>922</v>
@@ -62774,10 +62774,10 @@
         <v>923</v>
       </c>
       <c r="AF476" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG476" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH476" s="7">
         <v>6200000</v>
@@ -62863,7 +62863,7 @@
         <v>6</v>
       </c>
       <c r="T477" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U477" s="3" t="s">
         <v>46</v>
@@ -62890,7 +62890,7 @@
         <v>31</v>
       </c>
       <c r="AC477" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD477" s="3" t="s">
         <v>922</v>
@@ -62899,10 +62899,10 @@
         <v>923</v>
       </c>
       <c r="AF477" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG477" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH477" s="7">
         <v>6200000</v>
@@ -62979,16 +62979,16 @@
         <v>134</v>
       </c>
       <c r="Q478" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R478" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S478" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T478" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U478" s="3" t="s">
         <v>46</v>
@@ -63015,7 +63015,7 @@
         <v>31</v>
       </c>
       <c r="AC478" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD478" s="3" t="s">
         <v>922</v>
@@ -63024,10 +63024,10 @@
         <v>923</v>
       </c>
       <c r="AF478" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG478" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH478" s="7">
         <v>6200000</v>
@@ -63104,16 +63104,16 @@
         <v>72</v>
       </c>
       <c r="Q479" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R479" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S479" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T479" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U479" s="3" t="s">
         <v>46</v>
@@ -63140,7 +63140,7 @@
         <v>31</v>
       </c>
       <c r="AC479" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD479" s="3" t="s">
         <v>922</v>
@@ -63149,10 +63149,10 @@
         <v>923</v>
       </c>
       <c r="AF479" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG479" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH479" s="7">
         <v>6200000</v>
@@ -63238,7 +63238,7 @@
         <v>9</v>
       </c>
       <c r="T480" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U480" s="3" t="s">
         <v>46</v>
@@ -63265,7 +63265,7 @@
         <v>31</v>
       </c>
       <c r="AC480" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD480" s="3" t="s">
         <v>922</v>
@@ -63274,10 +63274,10 @@
         <v>923</v>
       </c>
       <c r="AF480" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG480" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH480" s="7">
         <v>6200000</v>
@@ -63363,7 +63363,7 @@
         <v>17</v>
       </c>
       <c r="T481" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U481" s="3" t="s">
         <v>46</v>
@@ -63390,7 +63390,7 @@
         <v>31</v>
       </c>
       <c r="AC481" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD481" s="3" t="s">
         <v>922</v>
@@ -63399,10 +63399,10 @@
         <v>923</v>
       </c>
       <c r="AF481" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG481" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH481" s="7">
         <v>6200000</v>
@@ -63488,7 +63488,7 @@
         <v>11</v>
       </c>
       <c r="T482" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U482" s="3" t="s">
         <v>46</v>
@@ -63515,7 +63515,7 @@
         <v>31</v>
       </c>
       <c r="AC482" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD482" s="3" t="s">
         <v>922</v>
@@ -63524,10 +63524,10 @@
         <v>923</v>
       </c>
       <c r="AF482" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG482" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH482" s="7">
         <v>6200000</v>
@@ -63580,13 +63580,13 @@
         <v>45</v>
       </c>
       <c r="I483" s="3" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="J483" s="3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="K483" s="3" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="L483" s="3" t="s">
         <v>50</v>
@@ -63613,7 +63613,7 @@
         <v>10</v>
       </c>
       <c r="T483" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U483" s="3" t="s">
         <v>46</v>
@@ -63640,7 +63640,7 @@
         <v>31</v>
       </c>
       <c r="AC483" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD483" s="3" t="s">
         <v>922</v>
@@ -63649,10 +63649,10 @@
         <v>923</v>
       </c>
       <c r="AF483" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG483" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH483" s="7">
         <v>6200000</v>
@@ -63705,13 +63705,13 @@
         <v>45</v>
       </c>
       <c r="I484" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="J484" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="L484" s="3" t="s">
         <v>50</v>
@@ -63738,7 +63738,7 @@
         <v>16</v>
       </c>
       <c r="T484" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U484" s="3" t="s">
         <v>46</v>
@@ -63765,7 +63765,7 @@
         <v>31</v>
       </c>
       <c r="AC484" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD484" s="3" t="s">
         <v>922</v>
@@ -63774,10 +63774,10 @@
         <v>923</v>
       </c>
       <c r="AF484" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG484" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH484" s="7">
         <v>6200000</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15371" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15339" uniqueCount="1039">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -2614,6 +2614,15 @@
     <t>2, Lê Hiến Mai</t>
   </si>
   <si>
+    <t>3126571</t>
+  </si>
+  <si>
+    <t>Quán Nước Cô Giàu</t>
+  </si>
+  <si>
+    <t>438, Mai Chí Thọ</t>
+  </si>
+  <si>
     <t>99916768</t>
   </si>
   <si>
@@ -2632,6 +2641,69 @@
     <t>49, Nguyễn Tư Nghiêm</t>
   </si>
   <si>
+    <t>99926585</t>
+  </si>
+  <si>
+    <t>Daily Mart</t>
+  </si>
+  <si>
+    <t>D43 Dragon, Đường 15</t>
+  </si>
+  <si>
+    <t>999305122</t>
+  </si>
+  <si>
+    <t>Minh Hải 1</t>
+  </si>
+  <si>
+    <t>34, Lò Lu</t>
+  </si>
+  <si>
+    <t>999754600</t>
+  </si>
+  <si>
+    <t>Chị Loan</t>
+  </si>
+  <si>
+    <t>6/2, Đường Số 6</t>
+  </si>
+  <si>
+    <t>Đạt</t>
+  </si>
+  <si>
+    <t>POSM</t>
+  </si>
+  <si>
+    <t>97KM04228</t>
+  </si>
+  <si>
+    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>999762653</t>
+  </si>
+  <si>
+    <t>Cà Phê Thúy Vy</t>
+  </si>
+  <si>
+    <t>Số 1351, Đường Nguyễn Thị Định</t>
+  </si>
+  <si>
+    <t>999765789</t>
+  </si>
+  <si>
+    <t>TH Hoa Phượng</t>
+  </si>
+  <si>
+    <t>34/33, Đường Số 2</t>
+  </si>
+  <si>
     <t>99918654</t>
   </si>
   <si>
@@ -2650,33 +2722,6 @@
     <t>74A, Đường Cầu Bình</t>
   </si>
   <si>
-    <t>99926585</t>
-  </si>
-  <si>
-    <t>Daily Mart</t>
-  </si>
-  <si>
-    <t>D43 Dragon, Đường 15</t>
-  </si>
-  <si>
-    <t>999305122</t>
-  </si>
-  <si>
-    <t>Minh Hải 1</t>
-  </si>
-  <si>
-    <t>34, Lò Lu</t>
-  </si>
-  <si>
-    <t>3126571</t>
-  </si>
-  <si>
-    <t>Quán Nước Cô Giàu</t>
-  </si>
-  <si>
-    <t>438, Mai Chí Thọ</t>
-  </si>
-  <si>
     <t>4264</t>
   </si>
   <si>
@@ -2695,24 +2740,6 @@
     <t>22 Đường 18, Long Phước</t>
   </si>
   <si>
-    <t>Đạt</t>
-  </si>
-  <si>
-    <t>POSM</t>
-  </si>
-  <si>
-    <t>97KM04228</t>
-  </si>
-  <si>
-    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
-  </si>
-  <si>
-    <t>Cai</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
     <t>3362</t>
   </si>
   <si>
@@ -2722,33 +2749,6 @@
     <t>107, Lò Lu</t>
   </si>
   <si>
-    <t>999754600</t>
-  </si>
-  <si>
-    <t>Chị Loan</t>
-  </si>
-  <si>
-    <t>6/2, Đường Số 6</t>
-  </si>
-  <si>
-    <t>999762653</t>
-  </si>
-  <si>
-    <t>Cà Phê Thúy Vy</t>
-  </si>
-  <si>
-    <t>Số 1351, Đường Nguyễn Thị Định</t>
-  </si>
-  <si>
-    <t>999765789</t>
-  </si>
-  <si>
-    <t>TH Hoa Phượng</t>
-  </si>
-  <si>
-    <t>34/33, Đường Số 2</t>
-  </si>
-  <si>
     <t>2344002</t>
   </si>
   <si>
@@ -2905,6 +2905,57 @@
     <t>242, Đường 57 - CL</t>
   </si>
   <si>
+    <t>2894640</t>
+  </si>
+  <si>
+    <t>Mino Mart</t>
+  </si>
+  <si>
+    <t>3063948</t>
+  </si>
+  <si>
+    <t>Cà Phê Chị Tuyết</t>
+  </si>
+  <si>
+    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
+  </si>
+  <si>
+    <t>3136368</t>
+  </si>
+  <si>
+    <t>Chợ Sạch 24H</t>
+  </si>
+  <si>
+    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
+  </si>
+  <si>
+    <t>999115327</t>
+  </si>
+  <si>
+    <t>Hà Thủy</t>
+  </si>
+  <si>
+    <t>Số 313, Lê Văn Thịnh</t>
+  </si>
+  <si>
+    <t>999191040</t>
+  </si>
+  <si>
+    <t>Tạp Hóa Sáu Tèo</t>
+  </si>
+  <si>
+    <t>250, Trường Lưu</t>
+  </si>
+  <si>
+    <t>999210374</t>
+  </si>
+  <si>
+    <t>Tạp Hóa 79</t>
+  </si>
+  <si>
+    <t>Số 79, Đường 11</t>
+  </si>
+  <si>
     <t>999305440</t>
   </si>
   <si>
@@ -2912,57 +2963,6 @@
   </si>
   <si>
     <t>136, Đường 35CL</t>
-  </si>
-  <si>
-    <t>999210374</t>
-  </si>
-  <si>
-    <t>Tạp Hóa 79</t>
-  </si>
-  <si>
-    <t>Số 79, Đường 11</t>
-  </si>
-  <si>
-    <t>999191040</t>
-  </si>
-  <si>
-    <t>Tạp Hóa Sáu Tèo</t>
-  </si>
-  <si>
-    <t>250, Trường Lưu</t>
-  </si>
-  <si>
-    <t>999115327</t>
-  </si>
-  <si>
-    <t>Hà Thủy</t>
-  </si>
-  <si>
-    <t>Số 313, Lê Văn Thịnh</t>
-  </si>
-  <si>
-    <t>3136368</t>
-  </si>
-  <si>
-    <t>Chợ Sạch 24H</t>
-  </si>
-  <si>
-    <t>35 Đường Số 12, Bưng Ông Thoàn</t>
-  </si>
-  <si>
-    <t>3063948</t>
-  </si>
-  <si>
-    <t>Cà Phê Chị Tuyết</t>
-  </si>
-  <si>
-    <t>Đối Diện Cổng E, Đường Số 57 CL</t>
-  </si>
-  <si>
-    <t>2894640</t>
-  </si>
-  <si>
-    <t>Mino Mart</t>
   </si>
   <si>
     <t>1-6MQR6L</t>
@@ -4978,14 +4978,14 @@
       <c r="P14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>46</v>
+      <c r="Q14" s="5">
+        <v>1</v>
+      </c>
+      <c r="R14" s="5">
+        <v>1</v>
+      </c>
+      <c r="S14" s="5">
+        <v>1</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>46</v>
@@ -21353,14 +21353,14 @@
       <c r="P145" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q145" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R145" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S145" s="3" t="s">
-        <v>46</v>
+      <c r="Q145" s="5">
+        <v>1</v>
+      </c>
+      <c r="R145" s="5">
+        <v>1</v>
+      </c>
+      <c r="S145" s="5">
+        <v>1</v>
       </c>
       <c r="T145" s="3" t="s">
         <v>46</v>
@@ -21478,14 +21478,14 @@
       <c r="P146" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q146" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R146" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S146" s="3" t="s">
-        <v>46</v>
+      <c r="Q146" s="5">
+        <v>1</v>
+      </c>
+      <c r="R146" s="5">
+        <v>1</v>
+      </c>
+      <c r="S146" s="5">
+        <v>1</v>
       </c>
       <c r="T146" s="3" t="s">
         <v>46</v>
@@ -21603,14 +21603,14 @@
       <c r="P147" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q147" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R147" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S147" s="3" t="s">
-        <v>46</v>
+      <c r="Q147" s="5">
+        <v>1</v>
+      </c>
+      <c r="R147" s="5">
+        <v>1</v>
+      </c>
+      <c r="S147" s="5">
+        <v>1</v>
       </c>
       <c r="T147" s="3" t="s">
         <v>46</v>
@@ -22603,14 +22603,14 @@
       <c r="P155" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="Q155" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R155" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S155" s="3" t="s">
-        <v>46</v>
+      <c r="Q155" s="5">
+        <v>1</v>
+      </c>
+      <c r="R155" s="5">
+        <v>1</v>
+      </c>
+      <c r="S155" s="5">
+        <v>1</v>
       </c>
       <c r="T155" s="3" t="s">
         <v>46</v>
@@ -40717,16 +40717,16 @@
         <v>50</v>
       </c>
       <c r="M300" s="3" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="N300" s="3" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="O300" s="3" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="P300" s="3" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="Q300" s="3" t="s">
         <v>46</v>
@@ -40789,7 +40789,7 @@
         <v>58</v>
       </c>
       <c r="AK300" s="6">
-        <v>46315.54901207176</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL300" s="3" t="s">
         <v>46</v>
@@ -40801,7 +40801,7 @@
         <v>58</v>
       </c>
       <c r="AO300" s="6">
-        <v>46315.54901207176</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="301" spans="1:41" x14ac:dyDescent="0.25">
@@ -40830,28 +40830,28 @@
         <v>46</v>
       </c>
       <c r="I301" s="3" t="s">
-        <v>870</v>
+        <v>455</v>
       </c>
       <c r="J301" s="3" t="s">
-        <v>871</v>
+        <v>456</v>
       </c>
       <c r="K301" s="3" t="s">
-        <v>872</v>
+        <v>457</v>
       </c>
       <c r="L301" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M301" s="3" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="N301" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="O301" s="3" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="P301" s="3" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="Q301" s="3" t="s">
         <v>46</v>
@@ -40914,7 +40914,7 @@
         <v>58</v>
       </c>
       <c r="AK301" s="6">
-        <v>46301.30899568287</v>
+        <v>46302.48940038194</v>
       </c>
       <c r="AL301" s="3" t="s">
         <v>46</v>
@@ -40926,7 +40926,7 @@
         <v>58</v>
       </c>
       <c r="AO301" s="6">
-        <v>46301.30899568287</v>
+        <v>46302.48940038194</v>
       </c>
     </row>
     <row r="302" spans="1:41" x14ac:dyDescent="0.25">
@@ -40955,28 +40955,28 @@
         <v>46</v>
       </c>
       <c r="I302" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="K302" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="L302" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M302" s="3" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="N302" s="3" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="O302" s="3" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="P302" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="Q302" s="3" t="s">
         <v>46</v>
@@ -41039,7 +41039,7 @@
         <v>58</v>
       </c>
       <c r="AK302" s="6">
-        <v>46301.5776272338</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL302" s="3" t="s">
         <v>46</v>
@@ -41051,7 +41051,7 @@
         <v>58</v>
       </c>
       <c r="AO302" s="6">
-        <v>46301.5776272338</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="303" spans="1:41" x14ac:dyDescent="0.25">
@@ -41080,28 +41080,28 @@
         <v>46</v>
       </c>
       <c r="I303" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="K303" s="3" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="L303" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M303" s="3" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="N303" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="O303" s="3" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="P303" s="3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="Q303" s="3" t="s">
         <v>46</v>
@@ -41205,13 +41205,13 @@
         <v>46</v>
       </c>
       <c r="I304" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="K304" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="L304" s="3" t="s">
         <v>50</v>
@@ -41330,13 +41330,13 @@
         <v>46</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K305" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L305" s="3" t="s">
         <v>50</v>
@@ -41577,31 +41577,31 @@
         <v>45</v>
       </c>
       <c r="H307" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="K307" s="3" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="L307" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M307" s="3" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="N307" s="3" t="s">
-        <v>154</v>
+        <v>63</v>
       </c>
       <c r="O307" s="3" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="P307" s="3" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="Q307" s="3" t="s">
         <v>46</v>
@@ -41613,7 +41613,7 @@
         <v>46</v>
       </c>
       <c r="T307" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U307" s="3" t="s">
         <v>46</v>
@@ -41630,41 +41630,41 @@
       <c r="Y307" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB307" s="3" t="s">
-        <v>46</v>
+      <c r="Z307" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA307" s="7">
+        <v>10.75</v>
+      </c>
+      <c r="AB307" s="7">
+        <v>1</v>
       </c>
       <c r="AC307" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD307" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE307" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF307" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH307" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI307" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH307" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI307" s="3">
+        <v>0</v>
       </c>
       <c r="AJ307" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK307" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
       <c r="AL307" s="3" t="s">
         <v>46</v>
@@ -41676,7 +41676,7 @@
         <v>58</v>
       </c>
       <c r="AO307" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
     </row>
     <row r="308" spans="1:41" x14ac:dyDescent="0.25">
@@ -41702,31 +41702,31 @@
         <v>45</v>
       </c>
       <c r="H308" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I308" s="3" t="s">
-        <v>455</v>
+        <v>891</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>456</v>
+        <v>892</v>
       </c>
       <c r="K308" s="3" t="s">
-        <v>457</v>
+        <v>893</v>
       </c>
       <c r="L308" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M308" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N308" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="O308" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P308" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Q308" s="3" t="s">
         <v>46</v>
@@ -41738,7 +41738,7 @@
         <v>46</v>
       </c>
       <c r="T308" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U308" s="3" t="s">
         <v>46</v>
@@ -41755,41 +41755,41 @@
       <c r="Y308" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB308" s="3" t="s">
-        <v>46</v>
+      <c r="Z308" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA308" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB308" s="7">
+        <v>1</v>
       </c>
       <c r="AC308" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD308" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE308" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF308" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH308" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI308" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH308" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI308" s="3">
+        <v>0</v>
       </c>
       <c r="AJ308" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK308" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
       <c r="AL308" s="3" t="s">
         <v>46</v>
@@ -41801,7 +41801,7 @@
         <v>58</v>
       </c>
       <c r="AO308" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
     </row>
     <row r="309" spans="1:41" x14ac:dyDescent="0.25">
@@ -41827,16 +41827,16 @@
         <v>45</v>
       </c>
       <c r="H309" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I309" s="3" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="K309" s="3" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="L309" s="3" t="s">
         <v>50</v>
@@ -41863,7 +41863,7 @@
         <v>46</v>
       </c>
       <c r="T309" s="3" t="s">
-        <v>46</v>
+        <v>885</v>
       </c>
       <c r="U309" s="3" t="s">
         <v>46</v>
@@ -41880,41 +41880,41 @@
       <c r="Y309" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB309" s="3" t="s">
-        <v>46</v>
+      <c r="Z309" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA309" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB309" s="7">
+        <v>1</v>
       </c>
       <c r="AC309" s="3" t="s">
-        <v>46</v>
+        <v>886</v>
       </c>
       <c r="AD309" s="3" t="s">
-        <v>46</v>
+        <v>887</v>
       </c>
       <c r="AE309" s="3" t="s">
-        <v>46</v>
+        <v>888</v>
       </c>
       <c r="AF309" s="3" t="s">
-        <v>46</v>
+        <v>889</v>
       </c>
       <c r="AG309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH309" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI309" s="3" t="s">
-        <v>46</v>
+        <v>890</v>
+      </c>
+      <c r="AH309" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI309" s="3">
+        <v>0</v>
       </c>
       <c r="AJ309" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK309" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL309" s="3" t="s">
         <v>46</v>
@@ -41926,7 +41926,7 @@
         <v>58</v>
       </c>
       <c r="AO309" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="310" spans="1:41" x14ac:dyDescent="0.25">
@@ -41955,28 +41955,28 @@
         <v>45</v>
       </c>
       <c r="I310" s="3" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="J310" s="3" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="K310" s="3" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="L310" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M310" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="N310" s="3" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="P310" s="3" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="Q310" s="3" t="s">
         <v>46</v>
@@ -41988,7 +41988,7 @@
         <v>46</v>
       </c>
       <c r="T310" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U310" s="3" t="s">
         <v>46</v>
@@ -42015,19 +42015,19 @@
         <v>1</v>
       </c>
       <c r="AC310" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD310" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE310" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF310" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG310" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH310" s="7">
         <v>1</v>
@@ -42039,7 +42039,7 @@
         <v>58</v>
       </c>
       <c r="AK310" s="6">
-        <v>46304.293035104165</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL310" s="3" t="s">
         <v>46</v>
@@ -42051,7 +42051,7 @@
         <v>58</v>
       </c>
       <c r="AO310" s="6">
-        <v>46304.293035104165</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="311" spans="1:41" x14ac:dyDescent="0.25">
@@ -42113,7 +42113,7 @@
         <v>46</v>
       </c>
       <c r="T311" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U311" s="3" t="s">
         <v>46</v>
@@ -42140,19 +42140,19 @@
         <v>1</v>
       </c>
       <c r="AC311" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD311" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE311" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF311" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG311" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH311" s="7">
         <v>1</v>
@@ -42164,7 +42164,7 @@
         <v>58</v>
       </c>
       <c r="AK311" s="6">
-        <v>46298.66540524305</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>46</v>
@@ -42176,7 +42176,7 @@
         <v>58</v>
       </c>
       <c r="AO311" s="6">
-        <v>46298.66540524305</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="312" spans="1:41" x14ac:dyDescent="0.25">
@@ -42217,16 +42217,16 @@
         <v>50</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="Q312" s="3" t="s">
         <v>46</v>
@@ -42238,7 +42238,7 @@
         <v>46</v>
       </c>
       <c r="T312" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U312" s="3" t="s">
         <v>46</v>
@@ -42259,25 +42259,25 @@
         <v>10</v>
       </c>
       <c r="AA312" s="7">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AB312" s="7">
         <v>1</v>
       </c>
       <c r="AC312" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD312" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE312" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF312" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG312" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH312" s="7">
         <v>1</v>
@@ -42289,7 +42289,7 @@
         <v>58</v>
       </c>
       <c r="AK312" s="6">
-        <v>46312.58308098379</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>46</v>
@@ -42301,7 +42301,7 @@
         <v>58</v>
       </c>
       <c r="AO312" s="6">
-        <v>46312.58308098379</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="313" spans="1:41" x14ac:dyDescent="0.25">
@@ -42342,16 +42342,16 @@
         <v>50</v>
       </c>
       <c r="M313" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N313" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P313" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q313" s="3" t="s">
         <v>46</v>
@@ -42363,7 +42363,7 @@
         <v>46</v>
       </c>
       <c r="T313" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U313" s="3" t="s">
         <v>46</v>
@@ -42390,19 +42390,19 @@
         <v>1</v>
       </c>
       <c r="AC313" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD313" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE313" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF313" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG313" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH313" s="7">
         <v>1</v>
@@ -42414,7 +42414,7 @@
         <v>58</v>
       </c>
       <c r="AK313" s="6">
-        <v>46310.439036655094</v>
+        <v>46304.293035104165</v>
       </c>
       <c r="AL313" s="3" t="s">
         <v>46</v>
@@ -42426,7 +42426,7 @@
         <v>58</v>
       </c>
       <c r="AO313" s="6">
-        <v>46310.439036655094</v>
+        <v>46304.293035104165</v>
       </c>
     </row>
     <row r="314" spans="1:41" x14ac:dyDescent="0.25">
@@ -42488,7 +42488,7 @@
         <v>46</v>
       </c>
       <c r="T314" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U314" s="3" t="s">
         <v>46</v>
@@ -42515,19 +42515,19 @@
         <v>1</v>
       </c>
       <c r="AC314" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD314" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE314" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF314" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG314" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH314" s="7">
         <v>1</v>
@@ -42539,7 +42539,7 @@
         <v>58</v>
       </c>
       <c r="AK314" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL314" s="3" t="s">
         <v>46</v>
@@ -42551,7 +42551,7 @@
         <v>58</v>
       </c>
       <c r="AO314" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="315" spans="1:41" x14ac:dyDescent="0.25">
@@ -42613,7 +42613,7 @@
         <v>46</v>
       </c>
       <c r="T315" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U315" s="3" t="s">
         <v>46</v>
@@ -42640,19 +42640,19 @@
         <v>1</v>
       </c>
       <c r="AC315" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD315" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE315" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF315" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG315" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH315" s="7">
         <v>1</v>
@@ -42738,7 +42738,7 @@
         <v>46</v>
       </c>
       <c r="T316" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U316" s="3" t="s">
         <v>46</v>
@@ -42765,19 +42765,19 @@
         <v>1</v>
       </c>
       <c r="AC316" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD316" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE316" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF316" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG316" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH316" s="7">
         <v>1</v>
@@ -42863,7 +42863,7 @@
         <v>46</v>
       </c>
       <c r="T317" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U317" s="3" t="s">
         <v>46</v>
@@ -42890,19 +42890,19 @@
         <v>1</v>
       </c>
       <c r="AC317" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD317" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE317" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF317" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG317" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH317" s="7">
         <v>1</v>
@@ -42988,7 +42988,7 @@
         <v>46</v>
       </c>
       <c r="T318" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U318" s="3" t="s">
         <v>46</v>
@@ -43015,19 +43015,19 @@
         <v>1</v>
       </c>
       <c r="AC318" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD318" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE318" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF318" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG318" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH318" s="7">
         <v>1</v>
@@ -43113,7 +43113,7 @@
         <v>46</v>
       </c>
       <c r="T319" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U319" s="3" t="s">
         <v>46</v>
@@ -43140,19 +43140,19 @@
         <v>1</v>
       </c>
       <c r="AC319" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD319" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE319" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF319" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG319" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH319" s="7">
         <v>1</v>
@@ -43238,7 +43238,7 @@
         <v>46</v>
       </c>
       <c r="T320" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U320" s="3" t="s">
         <v>46</v>
@@ -43265,19 +43265,19 @@
         <v>1</v>
       </c>
       <c r="AC320" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD320" s="3" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="AE320" s="3" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="AF320" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG320" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH320" s="7">
         <v>1</v>
@@ -43363,7 +43363,7 @@
         <v>14</v>
       </c>
       <c r="T321" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U321" s="3" t="s">
         <v>46</v>
@@ -43383,14 +43383,14 @@
       <c r="Z321" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA321" s="3" t="s">
-        <v>46</v>
+      <c r="AA321" s="7">
+        <v>388301</v>
       </c>
       <c r="AB321" s="7">
         <v>31</v>
       </c>
       <c r="AC321" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD321" s="3" t="s">
         <v>922</v>
@@ -43399,10 +43399,10 @@
         <v>923</v>
       </c>
       <c r="AF321" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG321" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH321" s="7">
         <v>12400000</v>
@@ -43488,7 +43488,7 @@
         <v>16</v>
       </c>
       <c r="T322" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U322" s="3" t="s">
         <v>46</v>
@@ -43515,7 +43515,7 @@
         <v>31</v>
       </c>
       <c r="AC322" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD322" s="3" t="s">
         <v>922</v>
@@ -43524,10 +43524,10 @@
         <v>923</v>
       </c>
       <c r="AF322" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG322" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH322" s="7">
         <v>12400000</v>
@@ -43604,16 +43604,16 @@
         <v>118</v>
       </c>
       <c r="Q323" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R323" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S323" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T323" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U323" s="3" t="s">
         <v>46</v>
@@ -43640,7 +43640,7 @@
         <v>31</v>
       </c>
       <c r="AC323" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD323" s="3" t="s">
         <v>922</v>
@@ -43649,10 +43649,10 @@
         <v>923</v>
       </c>
       <c r="AF323" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG323" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH323" s="7">
         <v>12400000</v>
@@ -43729,16 +43729,16 @@
         <v>65</v>
       </c>
       <c r="Q324" s="5">
+        <v>11</v>
+      </c>
+      <c r="R324" s="5">
         <v>10</v>
       </c>
-      <c r="R324" s="5">
-        <v>8</v>
-      </c>
       <c r="S324" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T324" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U324" s="3" t="s">
         <v>46</v>
@@ -43765,7 +43765,7 @@
         <v>31</v>
       </c>
       <c r="AC324" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD324" s="3" t="s">
         <v>922</v>
@@ -43774,10 +43774,10 @@
         <v>923</v>
       </c>
       <c r="AF324" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG324" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH324" s="7">
         <v>12400000</v>
@@ -43854,16 +43854,16 @@
         <v>128</v>
       </c>
       <c r="Q325" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R325" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S325" s="5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T325" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U325" s="3" t="s">
         <v>46</v>
@@ -43890,7 +43890,7 @@
         <v>31</v>
       </c>
       <c r="AC325" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD325" s="3" t="s">
         <v>922</v>
@@ -43899,10 +43899,10 @@
         <v>923</v>
       </c>
       <c r="AF325" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG325" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH325" s="7">
         <v>12400000</v>
@@ -43979,16 +43979,16 @@
         <v>82</v>
       </c>
       <c r="Q326" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R326" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S326" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T326" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U326" s="3" t="s">
         <v>46</v>
@@ -44009,13 +44009,13 @@
         <v>46</v>
       </c>
       <c r="AA326" s="7">
-        <v>1764000</v>
+        <v>1829136</v>
       </c>
       <c r="AB326" s="7">
         <v>31</v>
       </c>
       <c r="AC326" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD326" s="3" t="s">
         <v>922</v>
@@ -44024,10 +44024,10 @@
         <v>923</v>
       </c>
       <c r="AF326" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG326" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH326" s="7">
         <v>12400000</v>
@@ -44104,16 +44104,16 @@
         <v>72</v>
       </c>
       <c r="Q327" s="5">
+        <v>31</v>
+      </c>
+      <c r="R327" s="5">
         <v>30</v>
       </c>
-      <c r="R327" s="5">
-        <v>29</v>
-      </c>
       <c r="S327" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T327" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U327" s="3" t="s">
         <v>46</v>
@@ -44134,13 +44134,13 @@
         <v>46</v>
       </c>
       <c r="AA327" s="7">
-        <v>374309</v>
+        <v>773477</v>
       </c>
       <c r="AB327" s="7">
         <v>31</v>
       </c>
       <c r="AC327" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD327" s="3" t="s">
         <v>922</v>
@@ -44149,10 +44149,10 @@
         <v>923</v>
       </c>
       <c r="AF327" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG327" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH327" s="7">
         <v>12400000</v>
@@ -44238,7 +44238,7 @@
         <v>32</v>
       </c>
       <c r="T328" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U328" s="3" t="s">
         <v>46</v>
@@ -44259,13 +44259,13 @@
         <v>46</v>
       </c>
       <c r="AA328" s="7">
-        <v>4436089</v>
+        <v>4940489</v>
       </c>
       <c r="AB328" s="7">
         <v>31</v>
       </c>
       <c r="AC328" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD328" s="3" t="s">
         <v>922</v>
@@ -44274,10 +44274,10 @@
         <v>923</v>
       </c>
       <c r="AF328" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG328" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH328" s="7">
         <v>12400000</v>
@@ -44354,16 +44354,16 @@
         <v>128</v>
       </c>
       <c r="Q329" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R329" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="S329" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="T329" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U329" s="3" t="s">
         <v>46</v>
@@ -44384,13 +44384,13 @@
         <v>46</v>
       </c>
       <c r="AA329" s="7">
-        <v>1076567</v>
+        <v>1475735</v>
       </c>
       <c r="AB329" s="7">
         <v>31</v>
       </c>
       <c r="AC329" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD329" s="3" t="s">
         <v>922</v>
@@ -44399,10 +44399,10 @@
         <v>923</v>
       </c>
       <c r="AF329" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG329" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH329" s="7">
         <v>12400000</v>
@@ -44479,16 +44479,16 @@
         <v>128</v>
       </c>
       <c r="Q330" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R330" s="5">
         <v>13</v>
       </c>
       <c r="S330" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T330" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U330" s="3" t="s">
         <v>46</v>
@@ -44515,7 +44515,7 @@
         <v>31</v>
       </c>
       <c r="AC330" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD330" s="3" t="s">
         <v>922</v>
@@ -44524,10 +44524,10 @@
         <v>923</v>
       </c>
       <c r="AF330" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG330" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH330" s="7">
         <v>12400000</v>
@@ -44613,7 +44613,7 @@
         <v>19</v>
       </c>
       <c r="T331" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U331" s="3" t="s">
         <v>46</v>
@@ -44640,7 +44640,7 @@
         <v>31</v>
       </c>
       <c r="AC331" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD331" s="3" t="s">
         <v>922</v>
@@ -44649,10 +44649,10 @@
         <v>923</v>
       </c>
       <c r="AF331" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG331" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH331" s="7">
         <v>12400000</v>
@@ -44738,7 +44738,7 @@
         <v>4</v>
       </c>
       <c r="T332" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U332" s="3" t="s">
         <v>46</v>
@@ -44765,7 +44765,7 @@
         <v>31</v>
       </c>
       <c r="AC332" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD332" s="3" t="s">
         <v>922</v>
@@ -44774,10 +44774,10 @@
         <v>923</v>
       </c>
       <c r="AF332" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG332" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH332" s="7">
         <v>12400000</v>
@@ -44854,16 +44854,16 @@
         <v>128</v>
       </c>
       <c r="Q333" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R333" s="5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S333" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="T333" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U333" s="3" t="s">
         <v>46</v>
@@ -44890,7 +44890,7 @@
         <v>31</v>
       </c>
       <c r="AC333" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD333" s="3" t="s">
         <v>922</v>
@@ -44899,10 +44899,10 @@
         <v>923</v>
       </c>
       <c r="AF333" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG333" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH333" s="7">
         <v>12400000</v>
@@ -44988,7 +44988,7 @@
         <v>10</v>
       </c>
       <c r="T334" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U334" s="3" t="s">
         <v>46</v>
@@ -45015,7 +45015,7 @@
         <v>31</v>
       </c>
       <c r="AC334" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD334" s="3" t="s">
         <v>922</v>
@@ -45024,10 +45024,10 @@
         <v>923</v>
       </c>
       <c r="AF334" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG334" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH334" s="7">
         <v>12400000</v>
@@ -45104,16 +45104,16 @@
         <v>128</v>
       </c>
       <c r="Q335" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R335" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S335" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T335" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U335" s="3" t="s">
         <v>46</v>
@@ -45140,7 +45140,7 @@
         <v>31</v>
       </c>
       <c r="AC335" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD335" s="3" t="s">
         <v>922</v>
@@ -45149,10 +45149,10 @@
         <v>923</v>
       </c>
       <c r="AF335" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG335" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH335" s="7">
         <v>12400000</v>
@@ -45229,16 +45229,16 @@
         <v>82</v>
       </c>
       <c r="Q336" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R336" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S336" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T336" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U336" s="3" t="s">
         <v>46</v>
@@ -45265,7 +45265,7 @@
         <v>31</v>
       </c>
       <c r="AC336" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD336" s="3" t="s">
         <v>922</v>
@@ -45274,10 +45274,10 @@
         <v>923</v>
       </c>
       <c r="AF336" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG336" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH336" s="7">
         <v>12400000</v>
@@ -45363,7 +45363,7 @@
         <v>8</v>
       </c>
       <c r="T337" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U337" s="3" t="s">
         <v>46</v>
@@ -45390,7 +45390,7 @@
         <v>31</v>
       </c>
       <c r="AC337" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD337" s="3" t="s">
         <v>922</v>
@@ -45399,10 +45399,10 @@
         <v>923</v>
       </c>
       <c r="AF337" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG337" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH337" s="7">
         <v>12400000</v>
@@ -45479,16 +45479,16 @@
         <v>128</v>
       </c>
       <c r="Q338" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R338" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S338" s="5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T338" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U338" s="3" t="s">
         <v>46</v>
@@ -45509,13 +45509,13 @@
         <v>46</v>
       </c>
       <c r="AA338" s="7">
-        <v>2359847</v>
+        <v>2692847</v>
       </c>
       <c r="AB338" s="7">
         <v>31</v>
       </c>
       <c r="AC338" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD338" s="3" t="s">
         <v>922</v>
@@ -45524,10 +45524,10 @@
         <v>923</v>
       </c>
       <c r="AF338" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG338" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH338" s="7">
         <v>12400000</v>
@@ -45613,7 +45613,7 @@
         <v>12</v>
       </c>
       <c r="T339" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U339" s="3" t="s">
         <v>46</v>
@@ -45640,7 +45640,7 @@
         <v>31</v>
       </c>
       <c r="AC339" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD339" s="3" t="s">
         <v>922</v>
@@ -45649,10 +45649,10 @@
         <v>923</v>
       </c>
       <c r="AF339" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG339" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH339" s="7">
         <v>12400000</v>
@@ -45729,16 +45729,16 @@
         <v>128</v>
       </c>
       <c r="Q340" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R340" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S340" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T340" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U340" s="3" t="s">
         <v>46</v>
@@ -45759,13 +45759,13 @@
         <v>46</v>
       </c>
       <c r="AA340" s="7">
-        <v>1926136</v>
+        <v>2658048</v>
       </c>
       <c r="AB340" s="7">
         <v>31</v>
       </c>
       <c r="AC340" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD340" s="3" t="s">
         <v>922</v>
@@ -45774,10 +45774,10 @@
         <v>923</v>
       </c>
       <c r="AF340" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG340" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH340" s="7">
         <v>12400000</v>
@@ -45854,16 +45854,16 @@
         <v>128</v>
       </c>
       <c r="Q341" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R341" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S341" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T341" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U341" s="3" t="s">
         <v>46</v>
@@ -45884,13 +45884,13 @@
         <v>46</v>
       </c>
       <c r="AA341" s="7">
-        <v>1413947</v>
+        <v>2094371</v>
       </c>
       <c r="AB341" s="7">
         <v>31</v>
       </c>
       <c r="AC341" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD341" s="3" t="s">
         <v>922</v>
@@ -45899,10 +45899,10 @@
         <v>923</v>
       </c>
       <c r="AF341" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG341" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH341" s="7">
         <v>12400000</v>
@@ -45979,16 +45979,16 @@
         <v>72</v>
       </c>
       <c r="Q342" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R342" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S342" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T342" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U342" s="3" t="s">
         <v>46</v>
@@ -46009,13 +46009,13 @@
         <v>46</v>
       </c>
       <c r="AA342" s="7">
-        <v>14329214</v>
+        <v>14698814</v>
       </c>
       <c r="AB342" s="7">
         <v>31</v>
       </c>
       <c r="AC342" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD342" s="3" t="s">
         <v>922</v>
@@ -46024,10 +46024,10 @@
         <v>923</v>
       </c>
       <c r="AF342" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG342" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH342" s="7">
         <v>18600000</v>
@@ -46113,7 +46113,7 @@
         <v>19</v>
       </c>
       <c r="T343" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U343" s="3" t="s">
         <v>46</v>
@@ -46134,13 +46134,13 @@
         <v>46</v>
       </c>
       <c r="AA343" s="7">
-        <v>13603200</v>
+        <v>16505200</v>
       </c>
       <c r="AB343" s="7">
         <v>31</v>
       </c>
       <c r="AC343" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD343" s="3" t="s">
         <v>922</v>
@@ -46149,10 +46149,10 @@
         <v>923</v>
       </c>
       <c r="AF343" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG343" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH343" s="7">
         <v>18600000</v>
@@ -46229,16 +46229,16 @@
         <v>134</v>
       </c>
       <c r="Q344" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R344" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S344" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T344" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U344" s="3" t="s">
         <v>46</v>
@@ -46259,13 +46259,13 @@
         <v>46</v>
       </c>
       <c r="AA344" s="7">
-        <v>1003079</v>
+        <v>1703169</v>
       </c>
       <c r="AB344" s="7">
         <v>31</v>
       </c>
       <c r="AC344" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD344" s="3" t="s">
         <v>922</v>
@@ -46274,10 +46274,10 @@
         <v>923</v>
       </c>
       <c r="AF344" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG344" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH344" s="7">
         <v>12400000</v>
@@ -46363,7 +46363,7 @@
         <v>8</v>
       </c>
       <c r="T345" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U345" s="3" t="s">
         <v>46</v>
@@ -46390,7 +46390,7 @@
         <v>31</v>
       </c>
       <c r="AC345" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD345" s="3" t="s">
         <v>922</v>
@@ -46399,10 +46399,10 @@
         <v>923</v>
       </c>
       <c r="AF345" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG345" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH345" s="7">
         <v>12400000</v>
@@ -46479,16 +46479,16 @@
         <v>128</v>
       </c>
       <c r="Q346" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R346" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S346" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T346" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U346" s="3" t="s">
         <v>46</v>
@@ -46515,7 +46515,7 @@
         <v>31</v>
       </c>
       <c r="AC346" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD346" s="3" t="s">
         <v>922</v>
@@ -46524,10 +46524,10 @@
         <v>923</v>
       </c>
       <c r="AF346" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG346" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH346" s="7">
         <v>12400000</v>
@@ -46613,7 +46613,7 @@
         <v>7</v>
       </c>
       <c r="T347" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U347" s="3" t="s">
         <v>46</v>
@@ -46640,7 +46640,7 @@
         <v>31</v>
       </c>
       <c r="AC347" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD347" s="3" t="s">
         <v>922</v>
@@ -46649,10 +46649,10 @@
         <v>923</v>
       </c>
       <c r="AF347" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG347" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH347" s="7">
         <v>12400000</v>
@@ -46729,16 +46729,16 @@
         <v>134</v>
       </c>
       <c r="Q348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S348" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T348" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U348" s="3" t="s">
         <v>46</v>
@@ -46765,7 +46765,7 @@
         <v>31</v>
       </c>
       <c r="AC348" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD348" s="3" t="s">
         <v>922</v>
@@ -46774,10 +46774,10 @@
         <v>923</v>
       </c>
       <c r="AF348" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG348" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH348" s="7">
         <v>12400000</v>
@@ -46854,16 +46854,16 @@
         <v>118</v>
       </c>
       <c r="Q349" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R349" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S349" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T349" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U349" s="3" t="s">
         <v>46</v>
@@ -46884,13 +46884,13 @@
         <v>46</v>
       </c>
       <c r="AA349" s="7">
-        <v>2580460</v>
+        <v>3308110</v>
       </c>
       <c r="AB349" s="7">
         <v>31</v>
       </c>
       <c r="AC349" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD349" s="3" t="s">
         <v>922</v>
@@ -46899,10 +46899,10 @@
         <v>923</v>
       </c>
       <c r="AF349" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG349" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH349" s="7">
         <v>12400000</v>
@@ -46979,16 +46979,16 @@
         <v>128</v>
       </c>
       <c r="Q350" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R350" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S350" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="T350" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U350" s="3" t="s">
         <v>46</v>
@@ -47015,7 +47015,7 @@
         <v>31</v>
       </c>
       <c r="AC350" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD350" s="3" t="s">
         <v>922</v>
@@ -47024,10 +47024,10 @@
         <v>923</v>
       </c>
       <c r="AF350" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG350" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH350" s="7">
         <v>12400000</v>
@@ -47104,16 +47104,16 @@
         <v>128</v>
       </c>
       <c r="Q351" s="5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R351" s="5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="S351" s="5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="T351" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U351" s="3" t="s">
         <v>46</v>
@@ -47140,7 +47140,7 @@
         <v>31</v>
       </c>
       <c r="AC351" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD351" s="3" t="s">
         <v>922</v>
@@ -47149,10 +47149,10 @@
         <v>923</v>
       </c>
       <c r="AF351" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG351" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH351" s="7">
         <v>12400000</v>
@@ -47238,7 +47238,7 @@
         <v>6</v>
       </c>
       <c r="T352" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U352" s="3" t="s">
         <v>46</v>
@@ -47265,7 +47265,7 @@
         <v>31</v>
       </c>
       <c r="AC352" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD352" s="3" t="s">
         <v>922</v>
@@ -47274,10 +47274,10 @@
         <v>923</v>
       </c>
       <c r="AF352" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG352" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH352" s="7">
         <v>12400000</v>
@@ -47354,16 +47354,16 @@
         <v>128</v>
       </c>
       <c r="Q353" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R353" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S353" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T353" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U353" s="3" t="s">
         <v>46</v>
@@ -47384,13 +47384,13 @@
         <v>46</v>
       </c>
       <c r="AA353" s="7">
-        <v>2566500</v>
+        <v>3978150</v>
       </c>
       <c r="AB353" s="7">
         <v>31</v>
       </c>
       <c r="AC353" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD353" s="3" t="s">
         <v>922</v>
@@ -47399,10 +47399,10 @@
         <v>923</v>
       </c>
       <c r="AF353" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG353" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH353" s="7">
         <v>12400000</v>
@@ -47488,7 +47488,7 @@
         <v>21</v>
       </c>
       <c r="T354" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U354" s="3" t="s">
         <v>46</v>
@@ -47515,7 +47515,7 @@
         <v>31</v>
       </c>
       <c r="AC354" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD354" s="3" t="s">
         <v>922</v>
@@ -47524,10 +47524,10 @@
         <v>923</v>
       </c>
       <c r="AF354" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG354" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH354" s="7">
         <v>12400000</v>
@@ -47604,16 +47604,16 @@
         <v>128</v>
       </c>
       <c r="Q355" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R355" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="S355" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T355" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U355" s="3" t="s">
         <v>46</v>
@@ -47634,13 +47634,13 @@
         <v>46</v>
       </c>
       <c r="AA355" s="7">
-        <v>290939</v>
+        <v>393939</v>
       </c>
       <c r="AB355" s="7">
         <v>31</v>
       </c>
       <c r="AC355" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD355" s="3" t="s">
         <v>922</v>
@@ -47649,10 +47649,10 @@
         <v>923</v>
       </c>
       <c r="AF355" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG355" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH355" s="7">
         <v>12400000</v>
@@ -47729,16 +47729,16 @@
         <v>72</v>
       </c>
       <c r="Q356" s="5">
+        <v>30</v>
+      </c>
+      <c r="R356" s="5">
         <v>29</v>
       </c>
-      <c r="R356" s="5">
-        <v>28</v>
-      </c>
       <c r="S356" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T356" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U356" s="3" t="s">
         <v>46</v>
@@ -47765,7 +47765,7 @@
         <v>31</v>
       </c>
       <c r="AC356" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD356" s="3" t="s">
         <v>922</v>
@@ -47774,10 +47774,10 @@
         <v>923</v>
       </c>
       <c r="AF356" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG356" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH356" s="7">
         <v>12400000</v>
@@ -47863,7 +47863,7 @@
         <v>35</v>
       </c>
       <c r="T357" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U357" s="3" t="s">
         <v>46</v>
@@ -47890,7 +47890,7 @@
         <v>31</v>
       </c>
       <c r="AC357" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD357" s="3" t="s">
         <v>922</v>
@@ -47899,10 +47899,10 @@
         <v>923</v>
       </c>
       <c r="AF357" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG357" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH357" s="7">
         <v>12400000</v>
@@ -47988,7 +47988,7 @@
         <v>12</v>
       </c>
       <c r="T358" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U358" s="3" t="s">
         <v>46</v>
@@ -48015,7 +48015,7 @@
         <v>31</v>
       </c>
       <c r="AC358" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD358" s="3" t="s">
         <v>922</v>
@@ -48024,10 +48024,10 @@
         <v>923</v>
       </c>
       <c r="AF358" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG358" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH358" s="7">
         <v>12400000</v>
@@ -48104,16 +48104,16 @@
         <v>134</v>
       </c>
       <c r="Q359" s="5">
+        <v>3</v>
+      </c>
+      <c r="R359" s="5">
         <v>2</v>
       </c>
-      <c r="R359" s="5">
-        <v>1</v>
-      </c>
       <c r="S359" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T359" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U359" s="3" t="s">
         <v>46</v>
@@ -48238,7 +48238,7 @@
         <v>2</v>
       </c>
       <c r="T360" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U360" s="3" t="s">
         <v>46</v>
@@ -48363,7 +48363,7 @@
         <v>2</v>
       </c>
       <c r="T361" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U361" s="3" t="s">
         <v>46</v>
@@ -48488,7 +48488,7 @@
         <v>2</v>
       </c>
       <c r="T362" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U362" s="3" t="s">
         <v>46</v>
@@ -48509,7 +48509,7 @@
         <v>46</v>
       </c>
       <c r="AA362" s="7">
-        <v>2736757</v>
+        <v>3118775</v>
       </c>
       <c r="AB362" s="7">
         <v>1</v>
@@ -48613,7 +48613,7 @@
         <v>2</v>
       </c>
       <c r="T363" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U363" s="3" t="s">
         <v>46</v>
@@ -48738,7 +48738,7 @@
         <v>1</v>
       </c>
       <c r="T364" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U364" s="3" t="s">
         <v>46</v>
@@ -48830,40 +48830,40 @@
         <v>45</v>
       </c>
       <c r="I365" s="3" t="s">
-        <v>286</v>
+        <v>722</v>
       </c>
       <c r="J365" s="3" t="s">
-        <v>287</v>
+        <v>723</v>
       </c>
       <c r="K365" s="3" t="s">
-        <v>288</v>
+        <v>724</v>
       </c>
       <c r="L365" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M365" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N365" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O365" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P365" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q365" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R365" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S365" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T365" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U365" s="3" t="s">
         <v>46</v>
@@ -48883,8 +48883,8 @@
       <c r="Z365" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA365" s="3" t="s">
-        <v>46</v>
+      <c r="AA365" s="7">
+        <v>1227480</v>
       </c>
       <c r="AB365" s="7">
         <v>1</v>
@@ -48911,10 +48911,10 @@
         <v>0</v>
       </c>
       <c r="AJ365" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK365" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL365" s="3" t="s">
         <v>46</v>
@@ -48923,10 +48923,10 @@
         <v>46</v>
       </c>
       <c r="AN365" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO365" s="6">
-        <v>46301.927933530096</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="366" spans="1:41" x14ac:dyDescent="0.25">
@@ -48955,40 +48955,40 @@
         <v>45</v>
       </c>
       <c r="I366" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J366" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="K366" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="L366" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M366" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N366" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O366" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P366" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S366" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T366" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U366" s="3" t="s">
         <v>46</v>
@@ -49008,8 +49008,8 @@
       <c r="Z366" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA366" s="7">
-        <v>87000</v>
+      <c r="AA366" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB366" s="7">
         <v>1</v>
@@ -49036,10 +49036,10 @@
         <v>0</v>
       </c>
       <c r="AJ366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
       <c r="AL366" s="3" t="s">
         <v>46</v>
@@ -49048,10 +49048,10 @@
         <v>46</v>
       </c>
       <c r="AN366" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO366" s="6">
-        <v>46296.93825494213</v>
+        <v>46301.927933530096</v>
       </c>
     </row>
     <row r="367" spans="1:41" x14ac:dyDescent="0.25">
@@ -49080,28 +49080,28 @@
         <v>45</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>728</v>
+        <v>292</v>
       </c>
       <c r="J367" s="3" t="s">
-        <v>729</v>
+        <v>293</v>
       </c>
       <c r="K367" s="3" t="s">
-        <v>730</v>
+        <v>294</v>
       </c>
       <c r="L367" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M367" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="N367" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="O367" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="P367" s="3" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="Q367" s="5">
         <v>2</v>
@@ -49113,7 +49113,7 @@
         <v>2</v>
       </c>
       <c r="T367" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U367" s="3" t="s">
         <v>46</v>
@@ -49134,7 +49134,7 @@
         <v>46</v>
       </c>
       <c r="AA367" s="7">
-        <v>1567312</v>
+        <v>87000</v>
       </c>
       <c r="AB367" s="7">
         <v>1</v>
@@ -49205,28 +49205,28 @@
         <v>45</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>322</v>
+        <v>728</v>
       </c>
       <c r="J368" s="3" t="s">
-        <v>323</v>
+        <v>729</v>
       </c>
       <c r="K368" s="3" t="s">
-        <v>324</v>
+        <v>730</v>
       </c>
       <c r="L368" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M368" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N368" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O368" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P368" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q368" s="5">
         <v>2</v>
@@ -49238,7 +49238,7 @@
         <v>2</v>
       </c>
       <c r="T368" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U368" s="3" t="s">
         <v>46</v>
@@ -49259,7 +49259,7 @@
         <v>46</v>
       </c>
       <c r="AA368" s="7">
-        <v>5131620</v>
+        <v>1567312</v>
       </c>
       <c r="AB368" s="7">
         <v>1</v>
@@ -49330,40 +49330,40 @@
         <v>45</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>740</v>
+        <v>929</v>
       </c>
       <c r="J369" s="3" t="s">
-        <v>741</v>
+        <v>930</v>
       </c>
       <c r="K369" s="3" t="s">
-        <v>742</v>
+        <v>931</v>
       </c>
       <c r="L369" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M369" s="3" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="N369" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="O369" s="3" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="P369" s="3" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
       <c r="Q369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S369" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T369" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U369" s="3" t="s">
         <v>46</v>
@@ -49384,7 +49384,7 @@
         <v>46</v>
       </c>
       <c r="AA369" s="7">
-        <v>87000</v>
+        <v>3227033</v>
       </c>
       <c r="AB369" s="7">
         <v>1</v>
@@ -49455,40 +49455,40 @@
         <v>45</v>
       </c>
       <c r="I370" s="3" t="s">
-        <v>925</v>
+        <v>964</v>
       </c>
       <c r="J370" s="3" t="s">
-        <v>926</v>
+        <v>965</v>
       </c>
       <c r="K370" s="3" t="s">
-        <v>927</v>
+        <v>813</v>
       </c>
       <c r="L370" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M370" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N370" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O370" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P370" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R370" s="5">
         <v>2</v>
       </c>
       <c r="S370" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T370" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U370" s="3" t="s">
         <v>46</v>
@@ -49508,8 +49508,8 @@
       <c r="Z370" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA370" s="3" t="s">
-        <v>46</v>
+      <c r="AA370" s="7">
+        <v>468000</v>
       </c>
       <c r="AB370" s="7">
         <v>1</v>
@@ -49580,28 +49580,28 @@
         <v>45</v>
       </c>
       <c r="I371" s="3" t="s">
-        <v>422</v>
+        <v>322</v>
       </c>
       <c r="J371" s="3" t="s">
-        <v>423</v>
+        <v>323</v>
       </c>
       <c r="K371" s="3" t="s">
-        <v>424</v>
+        <v>324</v>
       </c>
       <c r="L371" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M371" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N371" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O371" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P371" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q371" s="5">
         <v>2</v>
@@ -49613,7 +49613,7 @@
         <v>2</v>
       </c>
       <c r="T371" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U371" s="3" t="s">
         <v>46</v>
@@ -49634,7 +49634,7 @@
         <v>46</v>
       </c>
       <c r="AA371" s="7">
-        <v>698000</v>
+        <v>5131620</v>
       </c>
       <c r="AB371" s="7">
         <v>1</v>
@@ -49705,40 +49705,40 @@
         <v>45</v>
       </c>
       <c r="I372" s="3" t="s">
-        <v>772</v>
+        <v>740</v>
       </c>
       <c r="J372" s="3" t="s">
-        <v>773</v>
+        <v>741</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>774</v>
+        <v>742</v>
       </c>
       <c r="L372" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M372" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N372" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O372" s="3" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P372" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Q372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S372" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T372" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U372" s="3" t="s">
         <v>46</v>
@@ -49759,7 +49759,7 @@
         <v>46</v>
       </c>
       <c r="AA372" s="7">
-        <v>2482921</v>
+        <v>183000</v>
       </c>
       <c r="AB372" s="7">
         <v>1</v>
@@ -49830,13 +49830,13 @@
         <v>45</v>
       </c>
       <c r="I373" s="3" t="s">
-        <v>464</v>
+        <v>378</v>
       </c>
       <c r="J373" s="3" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>466</v>
+        <v>380</v>
       </c>
       <c r="L373" s="3" t="s">
         <v>50</v>
@@ -49863,7 +49863,7 @@
         <v>2</v>
       </c>
       <c r="T373" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U373" s="3" t="s">
         <v>46</v>
@@ -49884,7 +49884,7 @@
         <v>46</v>
       </c>
       <c r="AA373" s="7">
-        <v>1156433</v>
+        <v>471000</v>
       </c>
       <c r="AB373" s="7">
         <v>1</v>
@@ -49955,28 +49955,28 @@
         <v>45</v>
       </c>
       <c r="I374" s="3" t="s">
-        <v>473</v>
+        <v>393</v>
       </c>
       <c r="J374" s="3" t="s">
-        <v>474</v>
+        <v>394</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>475</v>
+        <v>395</v>
       </c>
       <c r="L374" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M374" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N374" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O374" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P374" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q374" s="5">
         <v>2</v>
@@ -49988,7 +49988,7 @@
         <v>2</v>
       </c>
       <c r="T374" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U374" s="3" t="s">
         <v>46</v>
@@ -50009,7 +50009,7 @@
         <v>46</v>
       </c>
       <c r="AA374" s="7">
-        <v>839166</v>
+        <v>692000</v>
       </c>
       <c r="AB374" s="7">
         <v>1</v>
@@ -50036,10 +50036,10 @@
         <v>0</v>
       </c>
       <c r="AJ374" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK374" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL374" s="3" t="s">
         <v>46</v>
@@ -50048,10 +50048,10 @@
         <v>46</v>
       </c>
       <c r="AN374" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO374" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="375" spans="1:41" x14ac:dyDescent="0.25">
@@ -50080,13 +50080,13 @@
         <v>45</v>
       </c>
       <c r="I375" s="3" t="s">
-        <v>693</v>
+        <v>925</v>
       </c>
       <c r="J375" s="3" t="s">
-        <v>694</v>
+        <v>926</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>695</v>
+        <v>927</v>
       </c>
       <c r="L375" s="3" t="s">
         <v>50</v>
@@ -50113,7 +50113,7 @@
         <v>2</v>
       </c>
       <c r="T375" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U375" s="3" t="s">
         <v>46</v>
@@ -50133,8 +50133,8 @@
       <c r="Z375" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA375" s="7">
-        <v>6224400</v>
+      <c r="AA375" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB375" s="7">
         <v>1</v>
@@ -50161,10 +50161,10 @@
         <v>0</v>
       </c>
       <c r="AJ375" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK375" s="6">
-        <v>46306.863362881944</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL375" s="3" t="s">
         <v>46</v>
@@ -50173,10 +50173,10 @@
         <v>46</v>
       </c>
       <c r="AN375" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO375" s="6">
-        <v>46306.863362881944</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="376" spans="1:41" x14ac:dyDescent="0.25">
@@ -50205,13 +50205,13 @@
         <v>45</v>
       </c>
       <c r="I376" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="J376" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="L376" s="3" t="s">
         <v>50</v>
@@ -50238,7 +50238,7 @@
         <v>2</v>
       </c>
       <c r="T376" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U376" s="3" t="s">
         <v>46</v>
@@ -50258,8 +50258,8 @@
       <c r="Z376" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA376" s="3" t="s">
-        <v>46</v>
+      <c r="AA376" s="7">
+        <v>744240</v>
       </c>
       <c r="AB376" s="7">
         <v>1</v>
@@ -50286,10 +50286,10 @@
         <v>0</v>
       </c>
       <c r="AJ376" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK376" s="6">
-        <v>46307.91045501157</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL376" s="3" t="s">
         <v>46</v>
@@ -50298,10 +50298,10 @@
         <v>46</v>
       </c>
       <c r="AN376" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO376" s="6">
-        <v>46307.91045501157</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="377" spans="1:41" x14ac:dyDescent="0.25">
@@ -50330,28 +50330,28 @@
         <v>45</v>
       </c>
       <c r="I377" s="3" t="s">
-        <v>575</v>
+        <v>969</v>
       </c>
       <c r="J377" s="3" t="s">
-        <v>576</v>
+        <v>970</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>577</v>
+        <v>971</v>
       </c>
       <c r="L377" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M377" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N377" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O377" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P377" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q377" s="5">
         <v>2</v>
@@ -50363,7 +50363,7 @@
         <v>2</v>
       </c>
       <c r="T377" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U377" s="3" t="s">
         <v>46</v>
@@ -50384,7 +50384,7 @@
         <v>46</v>
       </c>
       <c r="AA377" s="7">
-        <v>453000</v>
+        <v>771000</v>
       </c>
       <c r="AB377" s="7">
         <v>1</v>
@@ -50455,13 +50455,13 @@
         <v>45</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>879</v>
+        <v>422</v>
       </c>
       <c r="J378" s="3" t="s">
-        <v>880</v>
+        <v>423</v>
       </c>
       <c r="K378" s="3" t="s">
-        <v>881</v>
+        <v>424</v>
       </c>
       <c r="L378" s="3" t="s">
         <v>50</v>
@@ -50488,7 +50488,7 @@
         <v>2</v>
       </c>
       <c r="T378" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U378" s="3" t="s">
         <v>46</v>
@@ -50509,7 +50509,7 @@
         <v>46</v>
       </c>
       <c r="AA378" s="7">
-        <v>1928113</v>
+        <v>698000</v>
       </c>
       <c r="AB378" s="7">
         <v>1</v>
@@ -50536,10 +50536,10 @@
         <v>0</v>
       </c>
       <c r="AJ378" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK378" s="6">
-        <v>46303.59483915509</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL378" s="3" t="s">
         <v>46</v>
@@ -50548,10 +50548,10 @@
         <v>46</v>
       </c>
       <c r="AN378" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO378" s="6">
-        <v>46303.59483915509</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="379" spans="1:41" x14ac:dyDescent="0.25">
@@ -50580,28 +50580,28 @@
         <v>45</v>
       </c>
       <c r="I379" s="3" t="s">
-        <v>967</v>
+        <v>772</v>
       </c>
       <c r="J379" s="3" t="s">
-        <v>968</v>
+        <v>773</v>
       </c>
       <c r="K379" s="3" t="s">
-        <v>969</v>
+        <v>774</v>
       </c>
       <c r="L379" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M379" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="N379" s="3" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="O379" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="P379" s="3" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="Q379" s="5">
         <v>2</v>
@@ -50613,7 +50613,7 @@
         <v>2</v>
       </c>
       <c r="T379" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U379" s="3" t="s">
         <v>46</v>
@@ -50634,7 +50634,7 @@
         <v>46</v>
       </c>
       <c r="AA379" s="7">
-        <v>471000</v>
+        <v>2482921</v>
       </c>
       <c r="AB379" s="7">
         <v>1</v>
@@ -50705,13 +50705,13 @@
         <v>45</v>
       </c>
       <c r="I380" s="3" t="s">
-        <v>970</v>
+        <v>464</v>
       </c>
       <c r="J380" s="3" t="s">
-        <v>971</v>
+        <v>465</v>
       </c>
       <c r="K380" s="3" t="s">
-        <v>972</v>
+        <v>466</v>
       </c>
       <c r="L380" s="3" t="s">
         <v>50</v>
@@ -50738,7 +50738,7 @@
         <v>2</v>
       </c>
       <c r="T380" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U380" s="3" t="s">
         <v>46</v>
@@ -50759,7 +50759,7 @@
         <v>46</v>
       </c>
       <c r="AA380" s="7">
-        <v>362000</v>
+        <v>1442933</v>
       </c>
       <c r="AB380" s="7">
         <v>1</v>
@@ -50830,40 +50830,40 @@
         <v>45</v>
       </c>
       <c r="I381" s="3" t="s">
-        <v>823</v>
+        <v>473</v>
       </c>
       <c r="J381" s="3" t="s">
-        <v>824</v>
+        <v>474</v>
       </c>
       <c r="K381" s="3" t="s">
-        <v>825</v>
+        <v>475</v>
       </c>
       <c r="L381" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M381" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N381" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O381" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P381" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S381" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T381" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U381" s="3" t="s">
         <v>46</v>
@@ -50884,7 +50884,7 @@
         <v>46</v>
       </c>
       <c r="AA381" s="7">
-        <v>85805</v>
+        <v>839166</v>
       </c>
       <c r="AB381" s="7">
         <v>1</v>
@@ -50911,10 +50911,10 @@
         <v>0</v>
       </c>
       <c r="AJ381" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK381" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL381" s="3" t="s">
         <v>46</v>
@@ -50923,10 +50923,10 @@
         <v>46</v>
       </c>
       <c r="AN381" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO381" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="382" spans="1:41" x14ac:dyDescent="0.25">
@@ -50955,13 +50955,13 @@
         <v>45</v>
       </c>
       <c r="I382" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="J382" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="J382" s="3" t="s">
+      <c r="K382" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="K382" s="3" t="s">
-        <v>975</v>
       </c>
       <c r="L382" s="3" t="s">
         <v>50</v>
@@ -50988,7 +50988,7 @@
         <v>2</v>
       </c>
       <c r="T382" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U382" s="3" t="s">
         <v>46</v>
@@ -51080,40 +51080,40 @@
         <v>45</v>
       </c>
       <c r="I383" s="3" t="s">
-        <v>976</v>
+        <v>823</v>
       </c>
       <c r="J383" s="3" t="s">
-        <v>977</v>
+        <v>824</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>978</v>
+        <v>825</v>
       </c>
       <c r="L383" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M383" s="3" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="N383" s="3" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O383" s="3" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="P383" s="3" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="Q383" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R383" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S383" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T383" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U383" s="3" t="s">
         <v>46</v>
@@ -51134,7 +51134,7 @@
         <v>46</v>
       </c>
       <c r="AA383" s="7">
-        <v>771000</v>
+        <v>85805</v>
       </c>
       <c r="AB383" s="7">
         <v>1</v>
@@ -51161,10 +51161,10 @@
         <v>0</v>
       </c>
       <c r="AJ383" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK383" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
       <c r="AL383" s="3" t="s">
         <v>46</v>
@@ -51173,10 +51173,10 @@
         <v>46</v>
       </c>
       <c r="AN383" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO383" s="6">
-        <v>46296.93825494213</v>
+        <v>46302.79881820602</v>
       </c>
     </row>
     <row r="384" spans="1:41" x14ac:dyDescent="0.25">
@@ -51205,28 +51205,28 @@
         <v>45</v>
       </c>
       <c r="I384" s="3" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="J384" s="3" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="L384" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M384" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="N384" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="O384" s="3" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="P384" s="3" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="Q384" s="5">
         <v>2</v>
@@ -51238,7 +51238,7 @@
         <v>2</v>
       </c>
       <c r="T384" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U384" s="3" t="s">
         <v>46</v>
@@ -51259,7 +51259,7 @@
         <v>46</v>
       </c>
       <c r="AA384" s="7">
-        <v>744240</v>
+        <v>362000</v>
       </c>
       <c r="AB384" s="7">
         <v>1</v>
@@ -51330,13 +51330,13 @@
         <v>45</v>
       </c>
       <c r="I385" s="3" t="s">
-        <v>393</v>
+        <v>978</v>
       </c>
       <c r="J385" s="3" t="s">
-        <v>394</v>
+        <v>979</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>395</v>
+        <v>980</v>
       </c>
       <c r="L385" s="3" t="s">
         <v>50</v>
@@ -51363,7 +51363,7 @@
         <v>2</v>
       </c>
       <c r="T385" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U385" s="3" t="s">
         <v>46</v>
@@ -51384,7 +51384,7 @@
         <v>46</v>
       </c>
       <c r="AA385" s="7">
-        <v>692000</v>
+        <v>471000</v>
       </c>
       <c r="AB385" s="7">
         <v>1</v>
@@ -51411,10 +51411,10 @@
         <v>0</v>
       </c>
       <c r="AJ385" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AK385" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
       <c r="AL385" s="3" t="s">
         <v>46</v>
@@ -51423,10 +51423,10 @@
         <v>46</v>
       </c>
       <c r="AN385" s="3" t="s">
-        <v>58</v>
+        <v>924</v>
       </c>
       <c r="AO385" s="6">
-        <v>46302.79881820602</v>
+        <v>46296.93825494213</v>
       </c>
     </row>
     <row r="386" spans="1:41" x14ac:dyDescent="0.25">
@@ -51455,28 +51455,28 @@
         <v>45</v>
       </c>
       <c r="I386" s="3" t="s">
-        <v>378</v>
+        <v>876</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>379</v>
+        <v>877</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>380</v>
+        <v>878</v>
       </c>
       <c r="L386" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M386" s="3" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="N386" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="O386" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="P386" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="Q386" s="5">
         <v>2</v>
@@ -51488,7 +51488,7 @@
         <v>2</v>
       </c>
       <c r="T386" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U386" s="3" t="s">
         <v>46</v>
@@ -51509,7 +51509,7 @@
         <v>46</v>
       </c>
       <c r="AA386" s="7">
-        <v>471000</v>
+        <v>1928113</v>
       </c>
       <c r="AB386" s="7">
         <v>1</v>
@@ -51536,10 +51536,10 @@
         <v>0</v>
       </c>
       <c r="AJ386" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK386" s="6">
-        <v>46296.93825494213</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL386" s="3" t="s">
         <v>46</v>
@@ -51548,10 +51548,10 @@
         <v>46</v>
       </c>
       <c r="AN386" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO386" s="6">
-        <v>46296.93825494213</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="387" spans="1:41" x14ac:dyDescent="0.25">
@@ -51580,40 +51580,40 @@
         <v>45</v>
       </c>
       <c r="I387" s="3" t="s">
-        <v>982</v>
+        <v>575</v>
       </c>
       <c r="J387" s="3" t="s">
-        <v>983</v>
+        <v>576</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>813</v>
+        <v>577</v>
       </c>
       <c r="L387" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M387" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="N387" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="O387" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="P387" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="Q387" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R387" s="5">
         <v>2</v>
       </c>
       <c r="S387" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T387" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U387" s="3" t="s">
         <v>46</v>
@@ -51634,7 +51634,7 @@
         <v>46</v>
       </c>
       <c r="AA387" s="7">
-        <v>468000</v>
+        <v>645000</v>
       </c>
       <c r="AB387" s="7">
         <v>1</v>
@@ -51705,28 +51705,28 @@
         <v>45</v>
       </c>
       <c r="I388" s="3" t="s">
-        <v>929</v>
+        <v>981</v>
       </c>
       <c r="J388" s="3" t="s">
-        <v>930</v>
+        <v>982</v>
       </c>
       <c r="K388" s="3" t="s">
-        <v>931</v>
+        <v>983</v>
       </c>
       <c r="L388" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M388" s="3" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="N388" s="3" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="O388" s="3" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="P388" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="Q388" s="5">
         <v>2</v>
@@ -51738,7 +51738,7 @@
         <v>2</v>
       </c>
       <c r="T388" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U388" s="3" t="s">
         <v>46</v>
@@ -51758,8 +51758,8 @@
       <c r="Z388" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA388" s="7">
-        <v>3025200</v>
+      <c r="AA388" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB388" s="7">
         <v>1</v>
@@ -51786,10 +51786,10 @@
         <v>0</v>
       </c>
       <c r="AJ388" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK388" s="6">
-        <v>46296.93825494213</v>
+        <v>46307.91045501157</v>
       </c>
       <c r="AL388" s="3" t="s">
         <v>46</v>
@@ -51798,10 +51798,10 @@
         <v>46</v>
       </c>
       <c r="AN388" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO388" s="6">
-        <v>46296.93825494213</v>
+        <v>46307.91045501157</v>
       </c>
     </row>
     <row r="389" spans="1:41" x14ac:dyDescent="0.25">
@@ -51830,28 +51830,28 @@
         <v>45</v>
       </c>
       <c r="I389" s="3" t="s">
-        <v>722</v>
+        <v>693</v>
       </c>
       <c r="J389" s="3" t="s">
-        <v>723</v>
+        <v>694</v>
       </c>
       <c r="K389" s="3" t="s">
-        <v>724</v>
+        <v>695</v>
       </c>
       <c r="L389" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M389" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="N389" s="3" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="O389" s="3" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="P389" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="Q389" s="5">
         <v>2</v>
@@ -51863,7 +51863,7 @@
         <v>2</v>
       </c>
       <c r="T389" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U389" s="3" t="s">
         <v>46</v>
@@ -51884,7 +51884,7 @@
         <v>46</v>
       </c>
       <c r="AA389" s="7">
-        <v>1227480</v>
+        <v>6224400</v>
       </c>
       <c r="AB389" s="7">
         <v>1</v>
@@ -51911,10 +51911,10 @@
         <v>0</v>
       </c>
       <c r="AJ389" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AK389" s="6">
-        <v>46296.93825494213</v>
+        <v>46306.863362881944</v>
       </c>
       <c r="AL389" s="3" t="s">
         <v>46</v>
@@ -51923,10 +51923,10 @@
         <v>46</v>
       </c>
       <c r="AN389" s="3" t="s">
-        <v>924</v>
+        <v>58</v>
       </c>
       <c r="AO389" s="6">
-        <v>46296.93825494213</v>
+        <v>46306.863362881944</v>
       </c>
     </row>
     <row r="390" spans="1:41" x14ac:dyDescent="0.25">
@@ -51979,16 +51979,16 @@
         <v>72</v>
       </c>
       <c r="Q390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S390" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T390" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U390" s="3" t="s">
         <v>46</v>
@@ -52009,13 +52009,13 @@
         <v>46</v>
       </c>
       <c r="AA390" s="7">
-        <v>68309267</v>
+        <v>69477167</v>
       </c>
       <c r="AB390" s="7">
         <v>31</v>
       </c>
       <c r="AC390" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD390" s="3" t="s">
         <v>922</v>
@@ -52024,10 +52024,10 @@
         <v>923</v>
       </c>
       <c r="AF390" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG390" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH390" s="7">
         <v>6200000</v>
@@ -52113,7 +52113,7 @@
         <v>33</v>
       </c>
       <c r="T391" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U391" s="3" t="s">
         <v>46</v>
@@ -52140,7 +52140,7 @@
         <v>31</v>
       </c>
       <c r="AC391" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD391" s="3" t="s">
         <v>922</v>
@@ -52149,10 +52149,10 @@
         <v>923</v>
       </c>
       <c r="AF391" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG391" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH391" s="7">
         <v>6200000</v>
@@ -52229,16 +52229,16 @@
         <v>128</v>
       </c>
       <c r="Q392" s="5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R392" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S392" s="5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T392" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U392" s="3" t="s">
         <v>46</v>
@@ -52259,13 +52259,13 @@
         <v>46</v>
       </c>
       <c r="AA392" s="7">
-        <v>3039458</v>
+        <v>4069058</v>
       </c>
       <c r="AB392" s="7">
         <v>31</v>
       </c>
       <c r="AC392" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD392" s="3" t="s">
         <v>922</v>
@@ -52274,10 +52274,10 @@
         <v>923</v>
       </c>
       <c r="AF392" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG392" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH392" s="7">
         <v>6200000</v>
@@ -52363,7 +52363,7 @@
         <v>14</v>
       </c>
       <c r="T393" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U393" s="3" t="s">
         <v>46</v>
@@ -52384,13 +52384,13 @@
         <v>46</v>
       </c>
       <c r="AA393" s="7">
-        <v>2736757</v>
+        <v>3118775</v>
       </c>
       <c r="AB393" s="7">
         <v>31</v>
       </c>
       <c r="AC393" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD393" s="3" t="s">
         <v>922</v>
@@ -52399,10 +52399,10 @@
         <v>923</v>
       </c>
       <c r="AF393" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG393" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH393" s="7">
         <v>6200000</v>
@@ -52488,7 +52488,7 @@
         <v>10</v>
       </c>
       <c r="T394" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U394" s="3" t="s">
         <v>46</v>
@@ -52515,7 +52515,7 @@
         <v>31</v>
       </c>
       <c r="AC394" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD394" s="3" t="s">
         <v>922</v>
@@ -52524,10 +52524,10 @@
         <v>923</v>
       </c>
       <c r="AF394" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG394" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH394" s="7">
         <v>6200000</v>
@@ -52604,16 +52604,16 @@
         <v>118</v>
       </c>
       <c r="Q395" s="5">
+        <v>15</v>
+      </c>
+      <c r="R395" s="5">
         <v>13</v>
       </c>
-      <c r="R395" s="5">
-        <v>11</v>
-      </c>
       <c r="S395" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T395" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U395" s="3" t="s">
         <v>46</v>
@@ -52634,13 +52634,13 @@
         <v>46</v>
       </c>
       <c r="AA395" s="7">
-        <v>1178000</v>
+        <v>1819500</v>
       </c>
       <c r="AB395" s="7">
         <v>31</v>
       </c>
       <c r="AC395" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD395" s="3" t="s">
         <v>922</v>
@@ -52649,10 +52649,10 @@
         <v>923</v>
       </c>
       <c r="AF395" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG395" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH395" s="7">
         <v>6200000</v>
@@ -52729,16 +52729,16 @@
         <v>54</v>
       </c>
       <c r="Q396" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R396" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S396" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T396" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U396" s="3" t="s">
         <v>46</v>
@@ -52765,7 +52765,7 @@
         <v>31</v>
       </c>
       <c r="AC396" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD396" s="3" t="s">
         <v>922</v>
@@ -52774,10 +52774,10 @@
         <v>923</v>
       </c>
       <c r="AF396" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG396" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH396" s="7">
         <v>6200000</v>
@@ -52863,7 +52863,7 @@
         <v>6</v>
       </c>
       <c r="T397" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U397" s="3" t="s">
         <v>46</v>
@@ -52890,7 +52890,7 @@
         <v>31</v>
       </c>
       <c r="AC397" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD397" s="3" t="s">
         <v>922</v>
@@ -52899,10 +52899,10 @@
         <v>923</v>
       </c>
       <c r="AF397" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG397" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH397" s="7">
         <v>6200000</v>
@@ -52979,16 +52979,16 @@
         <v>128</v>
       </c>
       <c r="Q398" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R398" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S398" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T398" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U398" s="3" t="s">
         <v>46</v>
@@ -53015,7 +53015,7 @@
         <v>31</v>
       </c>
       <c r="AC398" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD398" s="3" t="s">
         <v>922</v>
@@ -53024,10 +53024,10 @@
         <v>923</v>
       </c>
       <c r="AF398" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG398" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH398" s="7">
         <v>6200000</v>
@@ -53104,16 +53104,16 @@
         <v>128</v>
       </c>
       <c r="Q399" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R399" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S399" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T399" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U399" s="3" t="s">
         <v>46</v>
@@ -53140,7 +53140,7 @@
         <v>31</v>
       </c>
       <c r="AC399" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD399" s="3" t="s">
         <v>922</v>
@@ -53149,10 +53149,10 @@
         <v>923</v>
       </c>
       <c r="AF399" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG399" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH399" s="7">
         <v>6200000</v>
@@ -53205,13 +53205,13 @@
         <v>45</v>
       </c>
       <c r="I400" s="3" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="L400" s="3" t="s">
         <v>50</v>
@@ -53238,7 +53238,7 @@
         <v>12</v>
       </c>
       <c r="T400" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U400" s="3" t="s">
         <v>46</v>
@@ -53259,13 +53259,13 @@
         <v>46</v>
       </c>
       <c r="AA400" s="7">
-        <v>20517221</v>
+        <v>39525221</v>
       </c>
       <c r="AB400" s="7">
         <v>31</v>
       </c>
       <c r="AC400" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD400" s="3" t="s">
         <v>922</v>
@@ -53274,10 +53274,10 @@
         <v>923</v>
       </c>
       <c r="AF400" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG400" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH400" s="7">
         <v>6200000</v>
@@ -53354,16 +53354,16 @@
         <v>54</v>
       </c>
       <c r="Q401" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R401" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S401" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T401" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U401" s="3" t="s">
         <v>46</v>
@@ -53390,7 +53390,7 @@
         <v>31</v>
       </c>
       <c r="AC401" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD401" s="3" t="s">
         <v>922</v>
@@ -53399,10 +53399,10 @@
         <v>923</v>
       </c>
       <c r="AF401" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG401" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH401" s="7">
         <v>6200000</v>
@@ -53479,16 +53479,16 @@
         <v>118</v>
       </c>
       <c r="Q402" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R402" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S402" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T402" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U402" s="3" t="s">
         <v>46</v>
@@ -53515,7 +53515,7 @@
         <v>31</v>
       </c>
       <c r="AC402" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD402" s="3" t="s">
         <v>922</v>
@@ -53524,10 +53524,10 @@
         <v>923</v>
       </c>
       <c r="AF402" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG402" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH402" s="7">
         <v>6200000</v>
@@ -53613,7 +53613,7 @@
         <v>10</v>
       </c>
       <c r="T403" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U403" s="3" t="s">
         <v>46</v>
@@ -53640,7 +53640,7 @@
         <v>31</v>
       </c>
       <c r="AC403" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD403" s="3" t="s">
         <v>922</v>
@@ -53649,10 +53649,10 @@
         <v>923</v>
       </c>
       <c r="AF403" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG403" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH403" s="7">
         <v>6200000</v>
@@ -53729,16 +53729,16 @@
         <v>128</v>
       </c>
       <c r="Q404" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R404" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S404" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T404" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U404" s="3" t="s">
         <v>46</v>
@@ -53765,7 +53765,7 @@
         <v>31</v>
       </c>
       <c r="AC404" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD404" s="3" t="s">
         <v>922</v>
@@ -53774,10 +53774,10 @@
         <v>923</v>
       </c>
       <c r="AF404" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG404" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH404" s="7">
         <v>6200000</v>
@@ -53854,16 +53854,16 @@
         <v>128</v>
       </c>
       <c r="Q405" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R405" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S405" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="T405" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U405" s="3" t="s">
         <v>46</v>
@@ -53884,13 +53884,13 @@
         <v>46</v>
       </c>
       <c r="AA405" s="7">
-        <v>1156433</v>
+        <v>1442933</v>
       </c>
       <c r="AB405" s="7">
         <v>31</v>
       </c>
       <c r="AC405" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD405" s="3" t="s">
         <v>922</v>
@@ -53899,10 +53899,10 @@
         <v>923</v>
       </c>
       <c r="AF405" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG405" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH405" s="7">
         <v>6200000</v>
@@ -53988,7 +53988,7 @@
         <v>13</v>
       </c>
       <c r="T406" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U406" s="3" t="s">
         <v>46</v>
@@ -54015,7 +54015,7 @@
         <v>31</v>
       </c>
       <c r="AC406" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD406" s="3" t="s">
         <v>922</v>
@@ -54024,10 +54024,10 @@
         <v>923</v>
       </c>
       <c r="AF406" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG406" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH406" s="7">
         <v>6200000</v>
@@ -54104,16 +54104,16 @@
         <v>128</v>
       </c>
       <c r="Q407" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R407" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S407" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T407" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U407" s="3" t="s">
         <v>46</v>
@@ -54140,7 +54140,7 @@
         <v>31</v>
       </c>
       <c r="AC407" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD407" s="3" t="s">
         <v>922</v>
@@ -54149,10 +54149,10 @@
         <v>923</v>
       </c>
       <c r="AF407" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG407" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH407" s="7">
         <v>6200000</v>
@@ -54238,7 +54238,7 @@
         <v>8</v>
       </c>
       <c r="T408" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U408" s="3" t="s">
         <v>46</v>
@@ -54265,7 +54265,7 @@
         <v>31</v>
       </c>
       <c r="AC408" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD408" s="3" t="s">
         <v>922</v>
@@ -54274,10 +54274,10 @@
         <v>923</v>
       </c>
       <c r="AF408" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG408" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH408" s="7">
         <v>6200000</v>
@@ -54363,7 +54363,7 @@
         <v>8</v>
       </c>
       <c r="T409" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U409" s="3" t="s">
         <v>46</v>
@@ -54390,7 +54390,7 @@
         <v>31</v>
       </c>
       <c r="AC409" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD409" s="3" t="s">
         <v>922</v>
@@ -54399,10 +54399,10 @@
         <v>923</v>
       </c>
       <c r="AF409" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG409" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH409" s="7">
         <v>6200000</v>
@@ -54479,16 +54479,16 @@
         <v>128</v>
       </c>
       <c r="Q410" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R410" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S410" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T410" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U410" s="3" t="s">
         <v>46</v>
@@ -54509,13 +54509,13 @@
         <v>46</v>
       </c>
       <c r="AA410" s="7">
-        <v>453000</v>
+        <v>645000</v>
       </c>
       <c r="AB410" s="7">
         <v>31</v>
       </c>
       <c r="AC410" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD410" s="3" t="s">
         <v>922</v>
@@ -54524,10 +54524,10 @@
         <v>923</v>
       </c>
       <c r="AF410" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG410" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH410" s="7">
         <v>6200000</v>
@@ -54613,7 +54613,7 @@
         <v>21</v>
       </c>
       <c r="T411" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U411" s="3" t="s">
         <v>46</v>
@@ -54640,7 +54640,7 @@
         <v>31</v>
       </c>
       <c r="AC411" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD411" s="3" t="s">
         <v>922</v>
@@ -54649,10 +54649,10 @@
         <v>923</v>
       </c>
       <c r="AF411" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG411" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH411" s="7">
         <v>6200000</v>
@@ -54705,13 +54705,13 @@
         <v>45</v>
       </c>
       <c r="I412" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L412" s="3" t="s">
         <v>50</v>
@@ -54738,7 +54738,7 @@
         <v>14</v>
       </c>
       <c r="T412" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U412" s="3" t="s">
         <v>46</v>
@@ -54765,7 +54765,7 @@
         <v>31</v>
       </c>
       <c r="AC412" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD412" s="3" t="s">
         <v>922</v>
@@ -54774,10 +54774,10 @@
         <v>923</v>
       </c>
       <c r="AF412" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG412" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH412" s="7">
         <v>6200000</v>
@@ -54863,7 +54863,7 @@
         <v>14</v>
       </c>
       <c r="T413" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U413" s="3" t="s">
         <v>46</v>
@@ -54890,7 +54890,7 @@
         <v>31</v>
       </c>
       <c r="AC413" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD413" s="3" t="s">
         <v>922</v>
@@ -54899,10 +54899,10 @@
         <v>923</v>
       </c>
       <c r="AF413" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG413" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH413" s="7">
         <v>6200000</v>
@@ -54979,16 +54979,16 @@
         <v>128</v>
       </c>
       <c r="Q414" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R414" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S414" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T414" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U414" s="3" t="s">
         <v>46</v>
@@ -55015,7 +55015,7 @@
         <v>31</v>
       </c>
       <c r="AC414" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD414" s="3" t="s">
         <v>922</v>
@@ -55024,10 +55024,10 @@
         <v>923</v>
       </c>
       <c r="AF414" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG414" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH414" s="7">
         <v>6200000</v>
@@ -55104,16 +55104,16 @@
         <v>72</v>
       </c>
       <c r="Q415" s="5">
+        <v>32</v>
+      </c>
+      <c r="R415" s="5">
         <v>31</v>
       </c>
-      <c r="R415" s="5">
-        <v>30</v>
-      </c>
       <c r="S415" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T415" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U415" s="3" t="s">
         <v>46</v>
@@ -55134,13 +55134,13 @@
         <v>46</v>
       </c>
       <c r="AA415" s="7">
-        <v>1164200</v>
+        <v>1693464</v>
       </c>
       <c r="AB415" s="7">
         <v>31</v>
       </c>
       <c r="AC415" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD415" s="3" t="s">
         <v>922</v>
@@ -55149,10 +55149,10 @@
         <v>923</v>
       </c>
       <c r="AF415" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG415" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH415" s="7">
         <v>18600000</v>
@@ -55205,10 +55205,10 @@
         <v>999</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>813</v>
@@ -55229,16 +55229,16 @@
         <v>134</v>
       </c>
       <c r="Q416" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R416" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S416" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T416" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U416" s="3" t="s">
         <v>46</v>
@@ -55265,7 +55265,7 @@
         <v>31</v>
       </c>
       <c r="AC416" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD416" s="3" t="s">
         <v>922</v>
@@ -55274,10 +55274,10 @@
         <v>923</v>
       </c>
       <c r="AF416" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG416" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH416" s="7">
         <v>18600000</v>
@@ -55363,7 +55363,7 @@
         <v>11</v>
       </c>
       <c r="T417" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U417" s="3" t="s">
         <v>46</v>
@@ -55390,7 +55390,7 @@
         <v>31</v>
       </c>
       <c r="AC417" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD417" s="3" t="s">
         <v>922</v>
@@ -55399,10 +55399,10 @@
         <v>923</v>
       </c>
       <c r="AF417" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG417" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH417" s="7">
         <v>18600000</v>
@@ -55488,7 +55488,7 @@
         <v>14</v>
       </c>
       <c r="T418" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U418" s="3" t="s">
         <v>46</v>
@@ -55515,7 +55515,7 @@
         <v>31</v>
       </c>
       <c r="AC418" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD418" s="3" t="s">
         <v>922</v>
@@ -55524,10 +55524,10 @@
         <v>923</v>
       </c>
       <c r="AF418" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG418" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH418" s="7">
         <v>18600000</v>
@@ -55604,16 +55604,16 @@
         <v>134</v>
       </c>
       <c r="Q419" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R419" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S419" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T419" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U419" s="3" t="s">
         <v>46</v>
@@ -55640,7 +55640,7 @@
         <v>31</v>
       </c>
       <c r="AC419" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD419" s="3" t="s">
         <v>922</v>
@@ -55649,10 +55649,10 @@
         <v>923</v>
       </c>
       <c r="AF419" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG419" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH419" s="7">
         <v>18600000</v>
@@ -55738,7 +55738,7 @@
         <v>10</v>
       </c>
       <c r="T420" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U420" s="3" t="s">
         <v>46</v>
@@ -55765,7 +55765,7 @@
         <v>31</v>
       </c>
       <c r="AC420" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD420" s="3" t="s">
         <v>922</v>
@@ -55774,10 +55774,10 @@
         <v>923</v>
       </c>
       <c r="AF420" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG420" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH420" s="7">
         <v>18600000</v>
@@ -55863,7 +55863,7 @@
         <v>15</v>
       </c>
       <c r="T421" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U421" s="3" t="s">
         <v>46</v>
@@ -55884,13 +55884,13 @@
         <v>46</v>
       </c>
       <c r="AA421" s="7">
-        <v>2156236</v>
+        <v>2434791</v>
       </c>
       <c r="AB421" s="7">
         <v>31</v>
       </c>
       <c r="AC421" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD421" s="3" t="s">
         <v>922</v>
@@ -55899,10 +55899,10 @@
         <v>923</v>
       </c>
       <c r="AF421" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG421" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH421" s="7">
         <v>18600000</v>
@@ -55988,7 +55988,7 @@
         <v>9</v>
       </c>
       <c r="T422" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U422" s="3" t="s">
         <v>46</v>
@@ -56015,7 +56015,7 @@
         <v>31</v>
       </c>
       <c r="AC422" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD422" s="3" t="s">
         <v>922</v>
@@ -56024,10 +56024,10 @@
         <v>923</v>
       </c>
       <c r="AF422" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG422" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH422" s="7">
         <v>12400000</v>
@@ -56113,7 +56113,7 @@
         <v>6</v>
       </c>
       <c r="T423" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U423" s="3" t="s">
         <v>46</v>
@@ -56134,13 +56134,13 @@
         <v>46</v>
       </c>
       <c r="AA423" s="7">
-        <v>1780573</v>
+        <v>2150021</v>
       </c>
       <c r="AB423" s="7">
         <v>31</v>
       </c>
       <c r="AC423" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD423" s="3" t="s">
         <v>922</v>
@@ -56149,10 +56149,10 @@
         <v>923</v>
       </c>
       <c r="AF423" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG423" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH423" s="7">
         <v>12400000</v>
@@ -56238,7 +56238,7 @@
         <v>9</v>
       </c>
       <c r="T424" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U424" s="3" t="s">
         <v>46</v>
@@ -56265,7 +56265,7 @@
         <v>31</v>
       </c>
       <c r="AC424" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD424" s="3" t="s">
         <v>922</v>
@@ -56274,10 +56274,10 @@
         <v>923</v>
       </c>
       <c r="AF424" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG424" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH424" s="7">
         <v>12400000</v>
@@ -56354,16 +56354,16 @@
         <v>128</v>
       </c>
       <c r="Q425" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R425" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S425" s="5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="T425" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U425" s="3" t="s">
         <v>46</v>
@@ -56390,7 +56390,7 @@
         <v>31</v>
       </c>
       <c r="AC425" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD425" s="3" t="s">
         <v>922</v>
@@ -56399,10 +56399,10 @@
         <v>923</v>
       </c>
       <c r="AF425" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG425" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH425" s="7">
         <v>12400000</v>
@@ -56488,7 +56488,7 @@
         <v>17</v>
       </c>
       <c r="T426" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U426" s="3" t="s">
         <v>46</v>
@@ -56515,7 +56515,7 @@
         <v>31</v>
       </c>
       <c r="AC426" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD426" s="3" t="s">
         <v>922</v>
@@ -56524,10 +56524,10 @@
         <v>923</v>
       </c>
       <c r="AF426" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG426" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH426" s="7">
         <v>12400000</v>
@@ -56604,16 +56604,16 @@
         <v>156</v>
       </c>
       <c r="Q427" s="5">
+        <v>13</v>
+      </c>
+      <c r="R427" s="5">
         <v>12</v>
       </c>
-      <c r="R427" s="5">
-        <v>11</v>
-      </c>
       <c r="S427" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T427" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U427" s="3" t="s">
         <v>46</v>
@@ -56640,7 +56640,7 @@
         <v>31</v>
       </c>
       <c r="AC427" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD427" s="3" t="s">
         <v>922</v>
@@ -56649,10 +56649,10 @@
         <v>923</v>
       </c>
       <c r="AF427" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG427" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH427" s="7">
         <v>12400000</v>
@@ -56738,7 +56738,7 @@
         <v>15</v>
       </c>
       <c r="T428" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U428" s="3" t="s">
         <v>46</v>
@@ -56765,7 +56765,7 @@
         <v>31</v>
       </c>
       <c r="AC428" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD428" s="3" t="s">
         <v>922</v>
@@ -56774,10 +56774,10 @@
         <v>923</v>
       </c>
       <c r="AF428" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG428" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH428" s="7">
         <v>12400000</v>
@@ -56863,7 +56863,7 @@
         <v>14</v>
       </c>
       <c r="T429" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U429" s="3" t="s">
         <v>46</v>
@@ -56890,7 +56890,7 @@
         <v>31</v>
       </c>
       <c r="AC429" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD429" s="3" t="s">
         <v>922</v>
@@ -56899,10 +56899,10 @@
         <v>923</v>
       </c>
       <c r="AF429" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG429" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH429" s="7">
         <v>12400000</v>
@@ -56979,16 +56979,16 @@
         <v>128</v>
       </c>
       <c r="Q430" s="5">
+        <v>28</v>
+      </c>
+      <c r="R430" s="5">
         <v>26</v>
       </c>
-      <c r="R430" s="5">
-        <v>24</v>
-      </c>
       <c r="S430" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T430" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U430" s="3" t="s">
         <v>46</v>
@@ -57009,13 +57009,13 @@
         <v>46</v>
       </c>
       <c r="AA430" s="7">
-        <v>962500</v>
+        <v>1252900</v>
       </c>
       <c r="AB430" s="7">
         <v>31</v>
       </c>
       <c r="AC430" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD430" s="3" t="s">
         <v>922</v>
@@ -57024,10 +57024,10 @@
         <v>923</v>
       </c>
       <c r="AF430" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG430" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH430" s="7">
         <v>12400000</v>
@@ -57080,13 +57080,13 @@
         <v>921</v>
       </c>
       <c r="I431" s="3" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="J431" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="K431" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="L431" s="3" t="s">
         <v>50</v>
@@ -57113,7 +57113,7 @@
         <v>14</v>
       </c>
       <c r="T431" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U431" s="3" t="s">
         <v>46</v>
@@ -57140,7 +57140,7 @@
         <v>31</v>
       </c>
       <c r="AC431" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD431" s="3" t="s">
         <v>922</v>
@@ -57149,10 +57149,10 @@
         <v>923</v>
       </c>
       <c r="AF431" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG431" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH431" s="7">
         <v>12400000</v>
@@ -57229,16 +57229,16 @@
         <v>128</v>
       </c>
       <c r="Q432" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R432" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="S432" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T432" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U432" s="3" t="s">
         <v>46</v>
@@ -57265,7 +57265,7 @@
         <v>31</v>
       </c>
       <c r="AC432" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD432" s="3" t="s">
         <v>922</v>
@@ -57274,10 +57274,10 @@
         <v>923</v>
       </c>
       <c r="AF432" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG432" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH432" s="7">
         <v>12400000</v>
@@ -57354,16 +57354,16 @@
         <v>72</v>
       </c>
       <c r="Q433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S433" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T433" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U433" s="3" t="s">
         <v>46</v>
@@ -57390,7 +57390,7 @@
         <v>31</v>
       </c>
       <c r="AC433" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD433" s="3" t="s">
         <v>922</v>
@@ -57399,10 +57399,10 @@
         <v>923</v>
       </c>
       <c r="AF433" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG433" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH433" s="7">
         <v>12400000</v>
@@ -57479,16 +57479,16 @@
         <v>54</v>
       </c>
       <c r="Q434" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="R434" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S434" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="T434" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U434" s="3" t="s">
         <v>46</v>
@@ -57515,7 +57515,7 @@
         <v>31</v>
       </c>
       <c r="AC434" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD434" s="3" t="s">
         <v>922</v>
@@ -57524,10 +57524,10 @@
         <v>923</v>
       </c>
       <c r="AF434" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG434" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH434" s="7">
         <v>12400000</v>
@@ -57604,16 +57604,16 @@
         <v>156</v>
       </c>
       <c r="Q435" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R435" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S435" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T435" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U435" s="3" t="s">
         <v>46</v>
@@ -57640,7 +57640,7 @@
         <v>31</v>
       </c>
       <c r="AC435" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD435" s="3" t="s">
         <v>922</v>
@@ -57649,10 +57649,10 @@
         <v>923</v>
       </c>
       <c r="AF435" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG435" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH435" s="7">
         <v>12400000</v>
@@ -57738,7 +57738,7 @@
         <v>33</v>
       </c>
       <c r="T436" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U436" s="3" t="s">
         <v>46</v>
@@ -57759,13 +57759,13 @@
         <v>46</v>
       </c>
       <c r="AA436" s="7">
-        <v>3084711</v>
+        <v>4011791</v>
       </c>
       <c r="AB436" s="7">
         <v>31</v>
       </c>
       <c r="AC436" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD436" s="3" t="s">
         <v>922</v>
@@ -57774,10 +57774,10 @@
         <v>923</v>
       </c>
       <c r="AF436" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG436" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH436" s="7">
         <v>12400000</v>
@@ -57854,16 +57854,16 @@
         <v>128</v>
       </c>
       <c r="Q437" s="5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="R437" s="5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="S437" s="5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="T437" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U437" s="3" t="s">
         <v>46</v>
@@ -57890,7 +57890,7 @@
         <v>31</v>
       </c>
       <c r="AC437" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD437" s="3" t="s">
         <v>922</v>
@@ -57899,10 +57899,10 @@
         <v>923</v>
       </c>
       <c r="AF437" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG437" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH437" s="7">
         <v>12400000</v>
@@ -57979,16 +57979,16 @@
         <v>108</v>
       </c>
       <c r="Q438" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R438" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S438" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T438" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U438" s="3" t="s">
         <v>46</v>
@@ -58015,7 +58015,7 @@
         <v>31</v>
       </c>
       <c r="AC438" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD438" s="3" t="s">
         <v>922</v>
@@ -58024,10 +58024,10 @@
         <v>923</v>
       </c>
       <c r="AF438" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG438" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH438" s="7">
         <v>12400000</v>
@@ -58113,7 +58113,7 @@
         <v>13</v>
       </c>
       <c r="T439" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U439" s="3" t="s">
         <v>46</v>
@@ -58140,7 +58140,7 @@
         <v>31</v>
       </c>
       <c r="AC439" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD439" s="3" t="s">
         <v>922</v>
@@ -58149,10 +58149,10 @@
         <v>923</v>
       </c>
       <c r="AF439" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG439" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH439" s="7">
         <v>12400000</v>
@@ -58229,16 +58229,16 @@
         <v>118</v>
       </c>
       <c r="Q440" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R440" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S440" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T440" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U440" s="3" t="s">
         <v>46</v>
@@ -58265,7 +58265,7 @@
         <v>31</v>
       </c>
       <c r="AC440" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD440" s="3" t="s">
         <v>922</v>
@@ -58274,10 +58274,10 @@
         <v>923</v>
       </c>
       <c r="AF440" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG440" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH440" s="7">
         <v>12400000</v>
@@ -58354,16 +58354,16 @@
         <v>54</v>
       </c>
       <c r="Q441" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R441" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S441" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T441" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U441" s="3" t="s">
         <v>46</v>
@@ -58384,13 +58384,13 @@
         <v>46</v>
       </c>
       <c r="AA441" s="7">
-        <v>1854160</v>
+        <v>3237002</v>
       </c>
       <c r="AB441" s="7">
         <v>31</v>
       </c>
       <c r="AC441" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD441" s="3" t="s">
         <v>922</v>
@@ -58399,10 +58399,10 @@
         <v>923</v>
       </c>
       <c r="AF441" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG441" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH441" s="7">
         <v>12400000</v>
@@ -58479,16 +58479,16 @@
         <v>54</v>
       </c>
       <c r="Q442" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R442" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S442" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T442" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U442" s="3" t="s">
         <v>46</v>
@@ -58515,7 +58515,7 @@
         <v>31</v>
       </c>
       <c r="AC442" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD442" s="3" t="s">
         <v>922</v>
@@ -58524,10 +58524,10 @@
         <v>923</v>
       </c>
       <c r="AF442" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG442" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH442" s="7">
         <v>12400000</v>
@@ -58613,7 +58613,7 @@
         <v>14</v>
       </c>
       <c r="T443" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U443" s="3" t="s">
         <v>46</v>
@@ -58640,7 +58640,7 @@
         <v>31</v>
       </c>
       <c r="AC443" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD443" s="3" t="s">
         <v>922</v>
@@ -58649,10 +58649,10 @@
         <v>923</v>
       </c>
       <c r="AF443" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG443" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH443" s="7">
         <v>12400000</v>
@@ -58729,16 +58729,16 @@
         <v>134</v>
       </c>
       <c r="Q444" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R444" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S444" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T444" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U444" s="3" t="s">
         <v>46</v>
@@ -58765,7 +58765,7 @@
         <v>31</v>
       </c>
       <c r="AC444" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD444" s="3" t="s">
         <v>922</v>
@@ -58774,10 +58774,10 @@
         <v>923</v>
       </c>
       <c r="AF444" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG444" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH444" s="7">
         <v>12400000</v>
@@ -58863,7 +58863,7 @@
         <v>9</v>
       </c>
       <c r="T445" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U445" s="3" t="s">
         <v>46</v>
@@ -58890,7 +58890,7 @@
         <v>31</v>
       </c>
       <c r="AC445" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD445" s="3" t="s">
         <v>922</v>
@@ -58899,10 +58899,10 @@
         <v>923</v>
       </c>
       <c r="AF445" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG445" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH445" s="7">
         <v>12400000</v>
@@ -58988,7 +58988,7 @@
         <v>8</v>
       </c>
       <c r="T446" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U446" s="3" t="s">
         <v>46</v>
@@ -59015,7 +59015,7 @@
         <v>31</v>
       </c>
       <c r="AC446" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD446" s="3" t="s">
         <v>922</v>
@@ -59024,10 +59024,10 @@
         <v>923</v>
       </c>
       <c r="AF446" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG446" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH446" s="7">
         <v>12400000</v>
@@ -59104,16 +59104,16 @@
         <v>82</v>
       </c>
       <c r="Q447" s="5">
+        <v>13</v>
+      </c>
+      <c r="R447" s="5">
         <v>12</v>
       </c>
-      <c r="R447" s="5">
-        <v>11</v>
-      </c>
       <c r="S447" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T447" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U447" s="3" t="s">
         <v>46</v>
@@ -59140,7 +59140,7 @@
         <v>31</v>
       </c>
       <c r="AC447" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD447" s="3" t="s">
         <v>922</v>
@@ -59149,10 +59149,10 @@
         <v>923</v>
       </c>
       <c r="AF447" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG447" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH447" s="7">
         <v>12400000</v>
@@ -59238,7 +59238,7 @@
         <v>19</v>
       </c>
       <c r="T448" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U448" s="3" t="s">
         <v>46</v>
@@ -59265,7 +59265,7 @@
         <v>31</v>
       </c>
       <c r="AC448" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD448" s="3" t="s">
         <v>922</v>
@@ -59274,10 +59274,10 @@
         <v>923</v>
       </c>
       <c r="AF448" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG448" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH448" s="7">
         <v>12400000</v>
@@ -59363,7 +59363,7 @@
         <v>8</v>
       </c>
       <c r="T449" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U449" s="3" t="s">
         <v>46</v>
@@ -59384,13 +59384,13 @@
         <v>46</v>
       </c>
       <c r="AA449" s="7">
-        <v>1391208</v>
+        <v>3245368</v>
       </c>
       <c r="AB449" s="7">
         <v>31</v>
       </c>
       <c r="AC449" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD449" s="3" t="s">
         <v>922</v>
@@ -59399,10 +59399,10 @@
         <v>923</v>
       </c>
       <c r="AF449" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG449" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH449" s="7">
         <v>12400000</v>
@@ -59479,16 +59479,16 @@
         <v>156</v>
       </c>
       <c r="Q450" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R450" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S450" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T450" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U450" s="3" t="s">
         <v>46</v>
@@ -59515,7 +59515,7 @@
         <v>31</v>
       </c>
       <c r="AC450" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD450" s="3" t="s">
         <v>922</v>
@@ -59524,10 +59524,10 @@
         <v>923</v>
       </c>
       <c r="AF450" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG450" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH450" s="7">
         <v>12400000</v>
@@ -59604,16 +59604,16 @@
         <v>128</v>
       </c>
       <c r="Q451" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R451" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S451" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T451" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U451" s="3" t="s">
         <v>46</v>
@@ -59640,7 +59640,7 @@
         <v>31</v>
       </c>
       <c r="AC451" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD451" s="3" t="s">
         <v>922</v>
@@ -59649,10 +59649,10 @@
         <v>923</v>
       </c>
       <c r="AF451" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG451" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH451" s="7">
         <v>12400000</v>
@@ -59738,7 +59738,7 @@
         <v>16</v>
       </c>
       <c r="T452" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U452" s="3" t="s">
         <v>46</v>
@@ -59765,7 +59765,7 @@
         <v>31</v>
       </c>
       <c r="AC452" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD452" s="3" t="s">
         <v>922</v>
@@ -59774,10 +59774,10 @@
         <v>923</v>
       </c>
       <c r="AF452" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG452" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH452" s="7">
         <v>12400000</v>
@@ -59854,16 +59854,16 @@
         <v>128</v>
       </c>
       <c r="Q453" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R453" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S453" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T453" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U453" s="3" t="s">
         <v>46</v>
@@ -59890,7 +59890,7 @@
         <v>31</v>
       </c>
       <c r="AC453" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD453" s="3" t="s">
         <v>922</v>
@@ -59899,10 +59899,10 @@
         <v>923</v>
       </c>
       <c r="AF453" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG453" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH453" s="7">
         <v>12400000</v>
@@ -59988,7 +59988,7 @@
         <v>8</v>
       </c>
       <c r="T454" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U454" s="3" t="s">
         <v>46</v>
@@ -60015,7 +60015,7 @@
         <v>31</v>
       </c>
       <c r="AC454" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD454" s="3" t="s">
         <v>922</v>
@@ -60024,10 +60024,10 @@
         <v>923</v>
       </c>
       <c r="AF454" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG454" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH454" s="7">
         <v>12400000</v>
@@ -60113,7 +60113,7 @@
         <v>9</v>
       </c>
       <c r="T455" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U455" s="3" t="s">
         <v>46</v>
@@ -60140,7 +60140,7 @@
         <v>31</v>
       </c>
       <c r="AC455" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD455" s="3" t="s">
         <v>922</v>
@@ -60149,10 +60149,10 @@
         <v>923</v>
       </c>
       <c r="AF455" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG455" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH455" s="7">
         <v>12400000</v>
@@ -60205,13 +60205,13 @@
         <v>921</v>
       </c>
       <c r="I456" s="3" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="J456" s="3" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="L456" s="3" t="s">
         <v>50</v>
@@ -60238,7 +60238,7 @@
         <v>14</v>
       </c>
       <c r="T456" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U456" s="3" t="s">
         <v>46</v>
@@ -60259,13 +60259,13 @@
         <v>46</v>
       </c>
       <c r="AA456" s="7">
-        <v>15155995</v>
+        <v>22791835</v>
       </c>
       <c r="AB456" s="7">
         <v>31</v>
       </c>
       <c r="AC456" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD456" s="3" t="s">
         <v>922</v>
@@ -60274,10 +60274,10 @@
         <v>923</v>
       </c>
       <c r="AF456" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG456" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH456" s="7">
         <v>12400000</v>
@@ -60354,16 +60354,16 @@
         <v>54</v>
       </c>
       <c r="Q457" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R457" s="5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="S457" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="T457" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U457" s="3" t="s">
         <v>46</v>
@@ -60390,7 +60390,7 @@
         <v>31</v>
       </c>
       <c r="AC457" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD457" s="3" t="s">
         <v>922</v>
@@ -60399,10 +60399,10 @@
         <v>923</v>
       </c>
       <c r="AF457" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG457" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH457" s="7">
         <v>12400000</v>
@@ -60479,16 +60479,16 @@
         <v>118</v>
       </c>
       <c r="Q458" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R458" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S458" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T458" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U458" s="3" t="s">
         <v>46</v>
@@ -60515,7 +60515,7 @@
         <v>31</v>
       </c>
       <c r="AC458" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD458" s="3" t="s">
         <v>922</v>
@@ -60524,10 +60524,10 @@
         <v>923</v>
       </c>
       <c r="AF458" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG458" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH458" s="7">
         <v>12400000</v>
@@ -60613,7 +60613,7 @@
         <v>11</v>
       </c>
       <c r="T459" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U459" s="3" t="s">
         <v>46</v>
@@ -60640,7 +60640,7 @@
         <v>31</v>
       </c>
       <c r="AC459" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD459" s="3" t="s">
         <v>922</v>
@@ -60649,10 +60649,10 @@
         <v>923</v>
       </c>
       <c r="AF459" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG459" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH459" s="7">
         <v>12400000</v>
@@ -60729,16 +60729,16 @@
         <v>65</v>
       </c>
       <c r="Q460" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R460" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S460" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T460" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U460" s="3" t="s">
         <v>46</v>
@@ -60765,7 +60765,7 @@
         <v>31</v>
       </c>
       <c r="AC460" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD460" s="3" t="s">
         <v>922</v>
@@ -60774,10 +60774,10 @@
         <v>923</v>
       </c>
       <c r="AF460" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG460" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH460" s="7">
         <v>12400000</v>
@@ -60854,16 +60854,16 @@
         <v>128</v>
       </c>
       <c r="Q461" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="R461" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S461" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T461" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U461" s="3" t="s">
         <v>46</v>
@@ -60890,7 +60890,7 @@
         <v>31</v>
       </c>
       <c r="AC461" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD461" s="3" t="s">
         <v>922</v>
@@ -60899,10 +60899,10 @@
         <v>923</v>
       </c>
       <c r="AF461" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG461" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH461" s="7">
         <v>12400000</v>
@@ -60988,7 +60988,7 @@
         <v>8</v>
       </c>
       <c r="T462" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U462" s="3" t="s">
         <v>46</v>
@@ -61008,14 +61008,14 @@
       <c r="Z462" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA462" s="3" t="s">
-        <v>46</v>
+      <c r="AA462" s="7">
+        <v>1103427</v>
       </c>
       <c r="AB462" s="7">
         <v>31</v>
       </c>
       <c r="AC462" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD462" s="3" t="s">
         <v>922</v>
@@ -61024,10 +61024,10 @@
         <v>923</v>
       </c>
       <c r="AF462" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG462" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH462" s="7">
         <v>12400000</v>
@@ -61113,7 +61113,7 @@
         <v>14</v>
       </c>
       <c r="T463" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U463" s="3" t="s">
         <v>46</v>
@@ -61140,7 +61140,7 @@
         <v>31</v>
       </c>
       <c r="AC463" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD463" s="3" t="s">
         <v>922</v>
@@ -61149,10 +61149,10 @@
         <v>923</v>
       </c>
       <c r="AF463" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG463" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH463" s="7">
         <v>12400000</v>
@@ -61229,16 +61229,16 @@
         <v>72</v>
       </c>
       <c r="Q464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S464" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T464" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U464" s="3" t="s">
         <v>46</v>
@@ -61265,7 +61265,7 @@
         <v>31</v>
       </c>
       <c r="AC464" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD464" s="3" t="s">
         <v>922</v>
@@ -61274,10 +61274,10 @@
         <v>923</v>
       </c>
       <c r="AF464" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG464" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH464" s="7">
         <v>6200000</v>
@@ -61354,16 +61354,16 @@
         <v>156</v>
       </c>
       <c r="Q465" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R465" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S465" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T465" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U465" s="3" t="s">
         <v>46</v>
@@ -61390,7 +61390,7 @@
         <v>31</v>
       </c>
       <c r="AC465" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD465" s="3" t="s">
         <v>922</v>
@@ -61399,10 +61399,10 @@
         <v>923</v>
       </c>
       <c r="AF465" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG465" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH465" s="7">
         <v>6200000</v>
@@ -61479,16 +61479,16 @@
         <v>134</v>
       </c>
       <c r="Q466" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R466" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S466" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T466" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U466" s="3" t="s">
         <v>46</v>
@@ -61515,7 +61515,7 @@
         <v>31</v>
       </c>
       <c r="AC466" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD466" s="3" t="s">
         <v>922</v>
@@ -61524,10 +61524,10 @@
         <v>923</v>
       </c>
       <c r="AF466" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG466" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH466" s="7">
         <v>6200000</v>
@@ -61604,16 +61604,16 @@
         <v>128</v>
       </c>
       <c r="Q467" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="R467" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S467" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="T467" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U467" s="3" t="s">
         <v>46</v>
@@ -61634,13 +61634,13 @@
         <v>46</v>
       </c>
       <c r="AA467" s="7">
-        <v>712800</v>
+        <v>942800</v>
       </c>
       <c r="AB467" s="7">
         <v>31</v>
       </c>
       <c r="AC467" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD467" s="3" t="s">
         <v>922</v>
@@ -61649,10 +61649,10 @@
         <v>923</v>
       </c>
       <c r="AF467" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG467" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH467" s="7">
         <v>6200000</v>
@@ -61738,7 +61738,7 @@
         <v>14</v>
       </c>
       <c r="T468" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U468" s="3" t="s">
         <v>46</v>
@@ -61765,7 +61765,7 @@
         <v>31</v>
       </c>
       <c r="AC468" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD468" s="3" t="s">
         <v>922</v>
@@ -61774,10 +61774,10 @@
         <v>923</v>
       </c>
       <c r="AF468" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG468" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH468" s="7">
         <v>6200000</v>
@@ -61854,16 +61854,16 @@
         <v>156</v>
       </c>
       <c r="Q469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S469" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T469" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U469" s="3" t="s">
         <v>46</v>
@@ -61890,7 +61890,7 @@
         <v>31</v>
       </c>
       <c r="AC469" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD469" s="3" t="s">
         <v>922</v>
@@ -61899,10 +61899,10 @@
         <v>923</v>
       </c>
       <c r="AF469" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG469" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH469" s="7">
         <v>6200000</v>
@@ -61979,16 +61979,16 @@
         <v>54</v>
       </c>
       <c r="Q470" s="5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R470" s="5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S470" s="5">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T470" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U470" s="3" t="s">
         <v>46</v>
@@ -62009,13 +62009,13 @@
         <v>46</v>
       </c>
       <c r="AA470" s="7">
-        <v>910800</v>
+        <v>1165291</v>
       </c>
       <c r="AB470" s="7">
         <v>31</v>
       </c>
       <c r="AC470" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD470" s="3" t="s">
         <v>922</v>
@@ -62024,10 +62024,10 @@
         <v>923</v>
       </c>
       <c r="AF470" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG470" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH470" s="7">
         <v>6200000</v>
@@ -62113,7 +62113,7 @@
         <v>8</v>
       </c>
       <c r="T471" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U471" s="3" t="s">
         <v>46</v>
@@ -62140,7 +62140,7 @@
         <v>31</v>
       </c>
       <c r="AC471" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD471" s="3" t="s">
         <v>922</v>
@@ -62149,10 +62149,10 @@
         <v>923</v>
       </c>
       <c r="AF471" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG471" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH471" s="7">
         <v>6200000</v>
@@ -62229,16 +62229,16 @@
         <v>156</v>
       </c>
       <c r="Q472" s="5">
+        <v>8</v>
+      </c>
+      <c r="R472" s="5">
         <v>6</v>
       </c>
-      <c r="R472" s="5">
-        <v>4</v>
-      </c>
       <c r="S472" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T472" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U472" s="3" t="s">
         <v>46</v>
@@ -62265,7 +62265,7 @@
         <v>31</v>
       </c>
       <c r="AC472" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD472" s="3" t="s">
         <v>922</v>
@@ -62274,10 +62274,10 @@
         <v>923</v>
       </c>
       <c r="AF472" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG472" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH472" s="7">
         <v>6200000</v>
@@ -62354,16 +62354,16 @@
         <v>156</v>
       </c>
       <c r="Q473" s="5">
+        <v>9</v>
+      </c>
+      <c r="R473" s="5">
         <v>6</v>
       </c>
-      <c r="R473" s="5">
-        <v>3</v>
-      </c>
       <c r="S473" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T473" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U473" s="3" t="s">
         <v>46</v>
@@ -62390,7 +62390,7 @@
         <v>31</v>
       </c>
       <c r="AC473" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD473" s="3" t="s">
         <v>922</v>
@@ -62399,10 +62399,10 @@
         <v>923</v>
       </c>
       <c r="AF473" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG473" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH473" s="7">
         <v>6200000</v>
@@ -62488,7 +62488,7 @@
         <v>19</v>
       </c>
       <c r="T474" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U474" s="3" t="s">
         <v>46</v>
@@ -62509,13 +62509,13 @@
         <v>46</v>
       </c>
       <c r="AA474" s="7">
-        <v>928100</v>
+        <v>1838900</v>
       </c>
       <c r="AB474" s="7">
         <v>31</v>
       </c>
       <c r="AC474" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD474" s="3" t="s">
         <v>922</v>
@@ -62524,10 +62524,10 @@
         <v>923</v>
       </c>
       <c r="AF474" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG474" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH474" s="7">
         <v>6200000</v>
@@ -62604,16 +62604,16 @@
         <v>156</v>
       </c>
       <c r="Q475" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R475" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S475" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T475" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U475" s="3" t="s">
         <v>46</v>
@@ -62640,7 +62640,7 @@
         <v>31</v>
       </c>
       <c r="AC475" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD475" s="3" t="s">
         <v>922</v>
@@ -62649,10 +62649,10 @@
         <v>923</v>
       </c>
       <c r="AF475" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG475" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH475" s="7">
         <v>6200000</v>
@@ -62705,10 +62705,10 @@
         <v>45</v>
       </c>
       <c r="I476" s="3" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="J476" s="3" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="K476" s="3" t="s">
         <v>813</v>
@@ -62729,16 +62729,16 @@
         <v>134</v>
       </c>
       <c r="Q476" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R476" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S476" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T476" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U476" s="3" t="s">
         <v>46</v>
@@ -62765,7 +62765,7 @@
         <v>31</v>
       </c>
       <c r="AC476" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD476" s="3" t="s">
         <v>922</v>
@@ -62774,10 +62774,10 @@
         <v>923</v>
       </c>
       <c r="AF476" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG476" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH476" s="7">
         <v>6200000</v>
@@ -62863,7 +62863,7 @@
         <v>6</v>
       </c>
       <c r="T477" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U477" s="3" t="s">
         <v>46</v>
@@ -62890,7 +62890,7 @@
         <v>31</v>
       </c>
       <c r="AC477" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD477" s="3" t="s">
         <v>922</v>
@@ -62899,10 +62899,10 @@
         <v>923</v>
       </c>
       <c r="AF477" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG477" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH477" s="7">
         <v>6200000</v>
@@ -62979,16 +62979,16 @@
         <v>134</v>
       </c>
       <c r="Q478" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R478" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S478" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T478" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U478" s="3" t="s">
         <v>46</v>
@@ -63015,7 +63015,7 @@
         <v>31</v>
       </c>
       <c r="AC478" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD478" s="3" t="s">
         <v>922</v>
@@ -63024,10 +63024,10 @@
         <v>923</v>
       </c>
       <c r="AF478" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG478" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH478" s="7">
         <v>6200000</v>
@@ -63104,16 +63104,16 @@
         <v>72</v>
       </c>
       <c r="Q479" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R479" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S479" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T479" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U479" s="3" t="s">
         <v>46</v>
@@ -63140,7 +63140,7 @@
         <v>31</v>
       </c>
       <c r="AC479" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD479" s="3" t="s">
         <v>922</v>
@@ -63149,10 +63149,10 @@
         <v>923</v>
       </c>
       <c r="AF479" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG479" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH479" s="7">
         <v>6200000</v>
@@ -63238,7 +63238,7 @@
         <v>9</v>
       </c>
       <c r="T480" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U480" s="3" t="s">
         <v>46</v>
@@ -63265,7 +63265,7 @@
         <v>31</v>
       </c>
       <c r="AC480" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD480" s="3" t="s">
         <v>922</v>
@@ -63274,10 +63274,10 @@
         <v>923</v>
       </c>
       <c r="AF480" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG480" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH480" s="7">
         <v>6200000</v>
@@ -63354,16 +63354,16 @@
         <v>72</v>
       </c>
       <c r="Q481" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R481" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S481" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T481" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U481" s="3" t="s">
         <v>46</v>
@@ -63390,7 +63390,7 @@
         <v>31</v>
       </c>
       <c r="AC481" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD481" s="3" t="s">
         <v>922</v>
@@ -63399,10 +63399,10 @@
         <v>923</v>
       </c>
       <c r="AF481" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG481" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH481" s="7">
         <v>6200000</v>
@@ -63488,7 +63488,7 @@
         <v>11</v>
       </c>
       <c r="T482" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U482" s="3" t="s">
         <v>46</v>
@@ -63515,7 +63515,7 @@
         <v>31</v>
       </c>
       <c r="AC482" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD482" s="3" t="s">
         <v>922</v>
@@ -63524,10 +63524,10 @@
         <v>923</v>
       </c>
       <c r="AF482" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG482" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH482" s="7">
         <v>6200000</v>
@@ -63580,13 +63580,13 @@
         <v>45</v>
       </c>
       <c r="I483" s="3" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="J483" s="3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="K483" s="3" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="L483" s="3" t="s">
         <v>50</v>
@@ -63613,7 +63613,7 @@
         <v>10</v>
       </c>
       <c r="T483" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U483" s="3" t="s">
         <v>46</v>
@@ -63640,7 +63640,7 @@
         <v>31</v>
       </c>
       <c r="AC483" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD483" s="3" t="s">
         <v>922</v>
@@ -63649,10 +63649,10 @@
         <v>923</v>
       </c>
       <c r="AF483" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG483" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH483" s="7">
         <v>6200000</v>
@@ -63705,13 +63705,13 @@
         <v>45</v>
       </c>
       <c r="I484" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="J484" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="L484" s="3" t="s">
         <v>50</v>
@@ -63729,16 +63729,16 @@
         <v>134</v>
       </c>
       <c r="Q484" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R484" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S484" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T484" s="3" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="U484" s="3" t="s">
         <v>46</v>
@@ -63765,7 +63765,7 @@
         <v>31</v>
       </c>
       <c r="AC484" s="3" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="AD484" s="3" t="s">
         <v>922</v>
@@ -63774,10 +63774,10 @@
         <v>923</v>
       </c>
       <c r="AF484" s="3" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="AG484" s="3" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="AH484" s="7">
         <v>6200000</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15339" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15330" uniqueCount="1039">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -6603,14 +6603,14 @@
       <c r="P27" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>46</v>
+      <c r="Q27" s="5">
+        <v>1</v>
+      </c>
+      <c r="R27" s="5">
+        <v>1</v>
+      </c>
+      <c r="S27" s="5">
+        <v>1</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>46</v>
@@ -7478,14 +7478,14 @@
       <c r="P34" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>46</v>
+      <c r="Q34" s="5">
+        <v>1</v>
+      </c>
+      <c r="R34" s="5">
+        <v>1</v>
+      </c>
+      <c r="S34" s="5">
+        <v>1</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>46</v>
@@ -11728,14 +11728,14 @@
       <c r="P68" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Q68" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="R68" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>46</v>
+      <c r="Q68" s="5">
+        <v>1</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="5">
+        <v>1</v>
       </c>
       <c r="T68" s="3" t="s">
         <v>46</v>
@@ -44104,13 +44104,13 @@
         <v>72</v>
       </c>
       <c r="Q327" s="5">
+        <v>32</v>
+      </c>
+      <c r="R327" s="5">
         <v>31</v>
       </c>
-      <c r="R327" s="5">
-        <v>30</v>
-      </c>
       <c r="S327" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T327" s="3" t="s">
         <v>885</v>
@@ -44479,13 +44479,13 @@
         <v>128</v>
       </c>
       <c r="Q330" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R330" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S330" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T330" s="3" t="s">
         <v>885</v>
@@ -44604,13 +44604,13 @@
         <v>128</v>
       </c>
       <c r="Q331" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R331" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S331" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T331" s="3" t="s">
         <v>885</v>
@@ -45979,13 +45979,13 @@
         <v>72</v>
       </c>
       <c r="Q342" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R342" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S342" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T342" s="3" t="s">
         <v>885</v>
@@ -46104,13 +46104,13 @@
         <v>128</v>
       </c>
       <c r="Q343" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R343" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S343" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T343" s="3" t="s">
         <v>885</v>
@@ -47729,13 +47729,13 @@
         <v>72</v>
       </c>
       <c r="Q356" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R356" s="5">
         <v>29</v>
       </c>
       <c r="S356" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>885</v>
@@ -51979,13 +51979,13 @@
         <v>72</v>
       </c>
       <c r="Q390" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R390" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S390" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T390" s="3" t="s">
         <v>885</v>
@@ -55104,13 +55104,13 @@
         <v>72</v>
       </c>
       <c r="Q415" s="5">
+        <v>33</v>
+      </c>
+      <c r="R415" s="5">
         <v>32</v>
       </c>
-      <c r="R415" s="5">
-        <v>31</v>
-      </c>
       <c r="S415" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T415" s="3" t="s">
         <v>885</v>
@@ -57354,13 +57354,13 @@
         <v>72</v>
       </c>
       <c r="Q433" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R433" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S433" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T433" s="3" t="s">
         <v>885</v>
@@ -58354,13 +58354,13 @@
         <v>54</v>
       </c>
       <c r="Q441" s="5">
+        <v>34</v>
+      </c>
+      <c r="R441" s="5">
         <v>33</v>
       </c>
-      <c r="R441" s="5">
-        <v>32</v>
-      </c>
       <c r="S441" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T441" s="3" t="s">
         <v>885</v>
@@ -59229,13 +59229,13 @@
         <v>128</v>
       </c>
       <c r="Q448" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R448" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S448" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T448" s="3" t="s">
         <v>885</v>
@@ -61229,13 +61229,13 @@
         <v>72</v>
       </c>
       <c r="Q464" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R464" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S464" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T464" s="3" t="s">
         <v>885</v>
@@ -61979,13 +61979,13 @@
         <v>54</v>
       </c>
       <c r="Q470" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R470" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S470" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T470" s="3" t="s">
         <v>885</v>
@@ -62479,13 +62479,13 @@
         <v>128</v>
       </c>
       <c r="Q474" s="5">
+        <v>21</v>
+      </c>
+      <c r="R474" s="5">
         <v>19</v>
       </c>
-      <c r="R474" s="5">
-        <v>18</v>
-      </c>
       <c r="S474" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T474" s="3" t="s">
         <v>885</v>
@@ -63104,13 +63104,13 @@
         <v>72</v>
       </c>
       <c r="Q479" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R479" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S479" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T479" s="3" t="s">
         <v>885</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -53229,13 +53229,13 @@
         <v>118</v>
       </c>
       <c r="Q400" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R400" s="5">
         <v>9</v>
       </c>
       <c r="S400" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T400" s="3" t="s">
         <v>879</v>
@@ -53354,13 +53354,13 @@
         <v>54</v>
       </c>
       <c r="Q401" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R401" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S401" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T401" s="3" t="s">
         <v>879</v>
@@ -54729,13 +54729,13 @@
         <v>118</v>
       </c>
       <c r="Q412" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R412" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S412" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T412" s="3" t="s">
         <v>879</v>
@@ -57729,13 +57729,13 @@
         <v>82</v>
       </c>
       <c r="Q436" s="5">
+        <v>14</v>
+      </c>
+      <c r="R436" s="5">
         <v>13</v>
       </c>
-      <c r="R436" s="5">
-        <v>12</v>
-      </c>
       <c r="S436" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T436" s="3" t="s">
         <v>879</v>
@@ -58854,13 +58854,13 @@
         <v>118</v>
       </c>
       <c r="Q445" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R445" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S445" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T445" s="3" t="s">
         <v>879</v>
@@ -58979,13 +58979,13 @@
         <v>54</v>
       </c>
       <c r="Q446" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R446" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S446" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T446" s="3" t="s">
         <v>879</v>
@@ -59729,13 +59729,13 @@
         <v>82</v>
       </c>
       <c r="Q452" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R452" s="5">
         <v>6</v>
       </c>
       <c r="S452" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T452" s="3" t="s">
         <v>879</v>
@@ -60354,13 +60354,13 @@
         <v>101</v>
       </c>
       <c r="Q457" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R457" s="5">
         <v>13</v>
       </c>
       <c r="S457" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T457" s="3" t="s">
         <v>879</v>
@@ -60729,13 +60729,13 @@
         <v>118</v>
       </c>
       <c r="Q460" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R460" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S460" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T460" s="3" t="s">
         <v>879</v>
@@ -62854,13 +62854,13 @@
         <v>108</v>
       </c>
       <c r="Q477" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R477" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S477" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T477" s="3" t="s">
         <v>879</v>
@@ -63229,13 +63229,13 @@
         <v>128</v>
       </c>
       <c r="Q480" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R480" s="5">
         <v>9</v>
       </c>
       <c r="S480" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T480" s="3" t="s">
         <v>879</v>
@@ -63354,13 +63354,13 @@
         <v>72</v>
       </c>
       <c r="Q481" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R481" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S481" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T481" s="3" t="s">
         <v>879</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -56979,13 +56979,13 @@
         <v>54</v>
       </c>
       <c r="Q430" s="5">
+        <v>36</v>
+      </c>
+      <c r="R430" s="5">
         <v>35</v>
       </c>
-      <c r="R430" s="5">
-        <v>34</v>
-      </c>
       <c r="S430" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T430" s="3" t="s">
         <v>879</v>
@@ -61979,13 +61979,13 @@
         <v>54</v>
       </c>
       <c r="Q470" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R470" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S470" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T470" s="3" t="s">
         <v>879</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -44854,13 +44854,13 @@
         <v>128</v>
       </c>
       <c r="Q333" s="5">
+        <v>33</v>
+      </c>
+      <c r="R333" s="5">
         <v>32</v>
       </c>
-      <c r="R333" s="5">
-        <v>31</v>
-      </c>
       <c r="S333" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T333" s="3" t="s">
         <v>879</v>
@@ -53729,13 +53729,13 @@
         <v>128</v>
       </c>
       <c r="Q404" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R404" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S404" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T404" s="3" t="s">
         <v>879</v>
@@ -59479,13 +59479,13 @@
         <v>128</v>
       </c>
       <c r="Q450" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R450" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S450" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T450" s="3" t="s">
         <v>879</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -45979,13 +45979,13 @@
         <v>72</v>
       </c>
       <c r="Q342" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R342" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S342" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T342" s="3" t="s">
         <v>879</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -45729,13 +45729,13 @@
         <v>128</v>
       </c>
       <c r="Q340" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R340" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S340" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T340" s="3" t="s">
         <v>879</v>
@@ -47604,13 +47604,13 @@
         <v>128</v>
       </c>
       <c r="Q355" s="5">
+        <v>30</v>
+      </c>
+      <c r="R355" s="5">
         <v>29</v>
       </c>
-      <c r="R355" s="5">
-        <v>28</v>
-      </c>
       <c r="S355" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T355" s="3" t="s">
         <v>879</v>
@@ -47729,13 +47729,13 @@
         <v>128</v>
       </c>
       <c r="Q356" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R356" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S356" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T356" s="3" t="s">
         <v>879</v>
@@ -54479,13 +54479,13 @@
         <v>128</v>
       </c>
       <c r="Q410" s="5">
+        <v>27</v>
+      </c>
+      <c r="R410" s="5">
         <v>26</v>
       </c>
-      <c r="R410" s="5">
-        <v>25</v>
-      </c>
       <c r="S410" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T410" s="3" t="s">
         <v>879</v>
@@ -54604,13 +54604,13 @@
         <v>128</v>
       </c>
       <c r="Q411" s="5">
+        <v>21</v>
+      </c>
+      <c r="R411" s="5">
         <v>20</v>
       </c>
-      <c r="R411" s="5">
-        <v>19</v>
-      </c>
       <c r="S411" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T411" s="3" t="s">
         <v>879</v>
@@ -60604,13 +60604,13 @@
         <v>128</v>
       </c>
       <c r="Q459" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R459" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S459" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T459" s="3" t="s">
         <v>879</v>

--- a/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
+++ b/data/Thang10/DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15296" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15279" uniqueCount="1039">
   <si>
     <t>DANH_SACH_KET_QUA_CUA_HANG_THAM_GIA_CHUONG_TRINH</t>
   </si>
@@ -2623,6 +2623,78 @@
     <t>49, Nguyễn Tư Nghiêm</t>
   </si>
   <si>
+    <t>999305122</t>
+  </si>
+  <si>
+    <t>Minh Hải 1</t>
+  </si>
+  <si>
+    <t>34, Lò Lu</t>
+  </si>
+  <si>
+    <t>999754600</t>
+  </si>
+  <si>
+    <t>Chị Loan</t>
+  </si>
+  <si>
+    <t>6/2, Đường Số 6</t>
+  </si>
+  <si>
+    <t>Đạt</t>
+  </si>
+  <si>
+    <t>POSM</t>
+  </si>
+  <si>
+    <t>97KM04228</t>
+  </si>
+  <si>
+    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
+  </si>
+  <si>
+    <t>Cai</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>999762653</t>
+  </si>
+  <si>
+    <t>Cà Phê Thúy Vy</t>
+  </si>
+  <si>
+    <t>Số 1351, Đường Nguyễn Thị Định</t>
+  </si>
+  <si>
+    <t>999765789</t>
+  </si>
+  <si>
+    <t>TH Hoa Phượng</t>
+  </si>
+  <si>
+    <t>34/33, Đường Số 2</t>
+  </si>
+  <si>
+    <t>99918654</t>
+  </si>
+  <si>
+    <t>Dâu Tây</t>
+  </si>
+  <si>
+    <t>534, Đường Liên Phường</t>
+  </si>
+  <si>
+    <t>999263598</t>
+  </si>
+  <si>
+    <t>Anh Thư</t>
+  </si>
+  <si>
+    <t>74A, Đường Cầu Bình</t>
+  </si>
+  <si>
     <t>99926585</t>
   </si>
   <si>
@@ -2632,13 +2704,58 @@
     <t>D43 Dragon, Đường 15</t>
   </si>
   <si>
-    <t>999305122</t>
-  </si>
-  <si>
-    <t>Minh Hải 1</t>
-  </si>
-  <si>
-    <t>34, Lò Lu</t>
+    <t>3362</t>
+  </si>
+  <si>
+    <t>Thủy Kết</t>
+  </si>
+  <si>
+    <t>107, Lò Lu</t>
+  </si>
+  <si>
+    <t>4264</t>
+  </si>
+  <si>
+    <t>Chín Lộc</t>
+  </si>
+  <si>
+    <t>152, Lò Lu</t>
+  </si>
+  <si>
+    <t>4766</t>
+  </si>
+  <si>
+    <t>Hai Thạnh</t>
+  </si>
+  <si>
+    <t>22 Đường 18, Long Phước</t>
+  </si>
+  <si>
+    <t>2765237</t>
+  </si>
+  <si>
+    <t>Ngọc Gia Hân</t>
+  </si>
+  <si>
+    <t>2, Lê Hiến Mai</t>
+  </si>
+  <si>
+    <t>2004898</t>
+  </si>
+  <si>
+    <t>Tạp Hóa Kim Thoa</t>
+  </si>
+  <si>
+    <t>40 Cảng Phú Hữu, Nguyễn Duy Trinh</t>
+  </si>
+  <si>
+    <t>2344002</t>
+  </si>
+  <si>
+    <t>Thịnh Thoa</t>
+  </si>
+  <si>
+    <t>34, Đường 4</t>
   </si>
   <si>
     <t>2460082</t>
@@ -2648,123 +2765,6 @@
   </si>
   <si>
     <t>42D, Đường Gò Cát</t>
-  </si>
-  <si>
-    <t>Đạt</t>
-  </si>
-  <si>
-    <t>POSM</t>
-  </si>
-  <si>
-    <t>97KM04228</t>
-  </si>
-  <si>
-    <t>Thùng nhựa trong có bánh xe 30L (527x372x270)mm</t>
-  </si>
-  <si>
-    <t>Cai</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>999754600</t>
-  </si>
-  <si>
-    <t>Chị Loan</t>
-  </si>
-  <si>
-    <t>6/2, Đường Số 6</t>
-  </si>
-  <si>
-    <t>999762653</t>
-  </si>
-  <si>
-    <t>Cà Phê Thúy Vy</t>
-  </si>
-  <si>
-    <t>Số 1351, Đường Nguyễn Thị Định</t>
-  </si>
-  <si>
-    <t>999765789</t>
-  </si>
-  <si>
-    <t>TH Hoa Phượng</t>
-  </si>
-  <si>
-    <t>34/33, Đường Số 2</t>
-  </si>
-  <si>
-    <t>99918654</t>
-  </si>
-  <si>
-    <t>Dâu Tây</t>
-  </si>
-  <si>
-    <t>534, Đường Liên Phường</t>
-  </si>
-  <si>
-    <t>999263598</t>
-  </si>
-  <si>
-    <t>Anh Thư</t>
-  </si>
-  <si>
-    <t>74A, Đường Cầu Bình</t>
-  </si>
-  <si>
-    <t>3362</t>
-  </si>
-  <si>
-    <t>Thủy Kết</t>
-  </si>
-  <si>
-    <t>107, Lò Lu</t>
-  </si>
-  <si>
-    <t>4264</t>
-  </si>
-  <si>
-    <t>Chín Lộc</t>
-  </si>
-  <si>
-    <t>152, Lò Lu</t>
-  </si>
-  <si>
-    <t>4766</t>
-  </si>
-  <si>
-    <t>Hai Thạnh</t>
-  </si>
-  <si>
-    <t>22 Đường 18, Long Phước</t>
-  </si>
-  <si>
-    <t>2765237</t>
-  </si>
-  <si>
-    <t>Ngọc Gia Hân</t>
-  </si>
-  <si>
-    <t>2, Lê Hiến Mai</t>
-  </si>
-  <si>
-    <t>2004898</t>
-  </si>
-  <si>
-    <t>Tạp Hóa Kim Thoa</t>
-  </si>
-  <si>
-    <t>40 Cảng Phú Hữu, Nguyễn Duy Trinh</t>
-  </si>
-  <si>
-    <t>2344002</t>
-  </si>
-  <si>
-    <t>Thịnh Thoa</t>
-  </si>
-  <si>
-    <t>34, Đường 4</t>
   </si>
   <si>
     <t>1-6JP933U</t>
@@ -39955,28 +39955,28 @@
         <v>46</v>
       </c>
       <c r="I294" s="3" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="J294" s="3" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="K294" s="3" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="L294" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M294" s="3" t="s">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="N294" s="3" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="O294" s="3" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="P294" s="3" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="Q294" s="3" t="s">
         <v>46</v>
@@ -40039,7 +40039,7 @@
         <v>58</v>
       </c>
       <c r="AK294" s="6">
-        <v>46298.31634892361</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL294" s="3" t="s">
         <v>46</v>
@@ -40051,7 +40051,7 @@
         <v>58</v>
       </c>
       <c r="AO294" s="6">
-        <v>46298.31634892361</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="295" spans="1:41" x14ac:dyDescent="0.25">
@@ -40080,28 +40080,28 @@
         <v>46</v>
       </c>
       <c r="I295" s="3" t="s">
-        <v>259</v>
+        <v>861</v>
       </c>
       <c r="J295" s="3" t="s">
-        <v>260</v>
+        <v>862</v>
       </c>
       <c r="K295" s="3" t="s">
-        <v>261</v>
+        <v>863</v>
       </c>
       <c r="L295" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M295" s="3" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="N295" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="O295" s="3" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="P295" s="3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="Q295" s="3" t="s">
         <v>46</v>
@@ -40205,28 +40205,28 @@
         <v>46</v>
       </c>
       <c r="I296" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="J296" s="3" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="K296" s="3" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="L296" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M296" s="3" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="N296" s="3" t="s">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="O296" s="3" t="s">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="P296" s="3" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="Q296" s="3" t="s">
         <v>46</v>
@@ -40289,7 +40289,7 @@
         <v>58</v>
       </c>
       <c r="AK296" s="6">
-        <v>46298.66540524305</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL296" s="3" t="s">
         <v>46</v>
@@ -40301,7 +40301,7 @@
         <v>58</v>
       </c>
       <c r="AO296" s="6">
-        <v>46298.66540524305</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="297" spans="1:41" x14ac:dyDescent="0.25">
@@ -40330,28 +40330,28 @@
         <v>46</v>
       </c>
       <c r="I297" s="3" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="J297" s="3" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="K297" s="3" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="L297" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M297" s="3" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="N297" s="3" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="O297" s="3" t="s">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="P297" s="3" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="Q297" s="3" t="s">
         <v>46</v>
@@ -40414,7 +40414,7 @@
         <v>58</v>
       </c>
       <c r="AK297" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL297" s="3" t="s">
         <v>46</v>
@@ -40426,7 +40426,7 @@
         <v>58</v>
       </c>
       <c r="AO297" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="298" spans="1:41" x14ac:dyDescent="0.25">
@@ -40455,28 +40455,28 @@
         <v>46</v>
       </c>
       <c r="I298" s="3" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="J298" s="3" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="K298" s="3" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="L298" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M298" s="3" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="N298" s="3" t="s">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="O298" s="3" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="P298" s="3" t="s">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="Q298" s="3" t="s">
         <v>46</v>
@@ -40539,7 +40539,7 @@
         <v>58</v>
       </c>
       <c r="AK298" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL298" s="3" t="s">
         <v>46</v>
@@ -40551,7 +40551,7 @@
         <v>58</v>
       </c>
       <c r="AO298" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="299" spans="1:41" x14ac:dyDescent="0.25">
@@ -40580,28 +40580,28 @@
         <v>46</v>
       </c>
       <c r="I299" s="3" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="J299" s="3" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="K299" s="3" t="s">
-        <v>872</v>
+        <v>852</v>
       </c>
       <c r="L299" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M299" s="3" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="N299" s="3" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="O299" s="3" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="P299" s="3" t="s">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="Q299" s="3" t="s">
         <v>46</v>
@@ -40664,7 +40664,7 @@
         <v>58</v>
       </c>
       <c r="AK299" s="6">
-        <v>46311.29832241898</v>
+        <v>46302.48940038194</v>
       </c>
       <c r="AL299" s="3" t="s">
         <v>46</v>
@@ -40676,7 +40676,7 @@
         <v>58</v>
       </c>
       <c r="AO299" s="6">
-        <v>46311.29832241898</v>
+        <v>46302.48940038194</v>
       </c>
     </row>
     <row r="300" spans="1:41" x14ac:dyDescent="0.25">
@@ -40702,7 +40702,7 @@
         <v>45</v>
       </c>
       <c r="H300" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I300" s="3" t="s">
         <v>873</v>
@@ -40717,16 +40717,16 @@
         <v>50</v>
       </c>
       <c r="M300" s="3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="N300" s="3" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="O300" s="3" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="P300" s="3" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="Q300" s="3" t="s">
         <v>46</v>
@@ -40738,7 +40738,7 @@
         <v>46</v>
       </c>
       <c r="T300" s="3" t="s">
-        <v>46</v>
+        <v>876</v>
       </c>
       <c r="U300" s="3" t="s">
         <v>46</v>
@@ -40755,41 +40755,41 @@
       <c r="Y300" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z300" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA300" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB300" s="3" t="s">
-        <v>46</v>
+      <c r="Z300" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA300" s="7">
+        <v>10.75</v>
+      </c>
+      <c r="AB300" s="7">
+        <v>1</v>
       </c>
       <c r="AC300" s="3" t="s">
-        <v>46</v>
+        <v>877</v>
       </c>
       <c r="AD300" s="3" t="s">
-        <v>46</v>
+        <v>878</v>
       </c>
       <c r="AE300" s="3" t="s">
-        <v>46</v>
+        <v>879</v>
       </c>
       <c r="AF300" s="3" t="s">
-        <v>46</v>
+        <v>880</v>
       </c>
       <c r="AG300" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH300" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI300" s="3" t="s">
-        <v>46</v>
+        <v>881</v>
+      </c>
+      <c r="AH300" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI300" s="3">
+        <v>0</v>
       </c>
       <c r="AJ300" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK300" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
       <c r="AL300" s="3" t="s">
         <v>46</v>
@@ -40801,7 +40801,7 @@
         <v>58</v>
       </c>
       <c r="AO300" s="6">
-        <v>46298.66540524305</v>
+        <v>46312.58308098379</v>
       </c>
     </row>
     <row r="301" spans="1:41" x14ac:dyDescent="0.25">
@@ -40827,31 +40827,31 @@
         <v>45</v>
       </c>
       <c r="H301" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I301" s="3" t="s">
-        <v>850</v>
+        <v>882</v>
       </c>
       <c r="J301" s="3" t="s">
-        <v>851</v>
+        <v>883</v>
       </c>
       <c r="K301" s="3" t="s">
-        <v>852</v>
+        <v>884</v>
       </c>
       <c r="L301" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M301" s="3" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="N301" s="3" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="O301" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="P301" s="3" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="Q301" s="3" t="s">
         <v>46</v>
@@ -40863,7 +40863,7 @@
         <v>46</v>
       </c>
       <c r="T301" s="3" t="s">
-        <v>46</v>
+        <v>876</v>
       </c>
       <c r="U301" s="3" t="s">
         <v>46</v>
@@ -40880,41 +40880,41 @@
       <c r="Y301" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z301" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA301" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB301" s="3" t="s">
-        <v>46</v>
+      <c r="Z301" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA301" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB301" s="7">
+        <v>1</v>
       </c>
       <c r="AC301" s="3" t="s">
-        <v>46</v>
+        <v>877</v>
       </c>
       <c r="AD301" s="3" t="s">
-        <v>46</v>
+        <v>878</v>
       </c>
       <c r="AE301" s="3" t="s">
-        <v>46</v>
+        <v>879</v>
       </c>
       <c r="AF301" s="3" t="s">
-        <v>46</v>
+        <v>880</v>
       </c>
       <c r="AG301" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH301" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI301" s="3" t="s">
-        <v>46</v>
+        <v>881</v>
+      </c>
+      <c r="AH301" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI301" s="3">
+        <v>0</v>
       </c>
       <c r="AJ301" s="3" t="s">
         <v>58</v>
       </c>
       <c r="AK301" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
       <c r="AL301" s="3" t="s">
         <v>46</v>
@@ -40926,7 +40926,7 @@
         <v>58</v>
       </c>
       <c r="AO301" s="6">
-        <v>46302.48940038194</v>
+        <v>46310.439036655094</v>
       </c>
     </row>
     <row r="302" spans="1:41" x14ac:dyDescent="0.25">
@@ -40952,16 +40952,16 @@
         <v>45</v>
       </c>
       <c r="H302" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I302" s="3" t="s">
-        <v>705</v>
+        <v>885</v>
       </c>
       <c r="J302" s="3" t="s">
-        <v>706</v>
+        <v>886</v>
       </c>
       <c r="K302" s="3" t="s">
-        <v>707</v>
+        <v>887</v>
       </c>
       <c r="L302" s="3" t="s">
         <v>50</v>
@@ -40988,7 +40988,7 @@
         <v>46</v>
       </c>
       <c r="T302" s="3" t="s">
-        <v>46</v>
+        <v>876</v>
       </c>
       <c r="U302" s="3" t="s">
         <v>46</v>
@@ -41005,35 +41005,35 @@
       <c r="Y302" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z302" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA302" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB302" s="3" t="s">
-        <v>46</v>
+      <c r="Z302" s="7">
+        <v>10</v>
+      </c>
+      <c r="AA302" s="7">
+        <v>10</v>
+      </c>
+      <c r="AB302" s="7">
+        <v>1</v>
       </c>
       <c r="AC302" s="3" t="s">
-        <v>46</v>
+        <v>877</v>
       </c>
       <c r="AD302" s="3" t="s">
-        <v>46</v>
+        <v>878</v>
       </c>
       <c r="AE302" s="3" t="s">
-        <v>46</v>
+        <v>879</v>
       </c>
       <c r="AF302" s="3" t="s">
-        <v>46</v>
+        <v>880</v>
       </c>
       <c r="AG302" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH302" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI302" s="3" t="s">
-        <v>46</v>
+        <v>881</v>
+      </c>
+      <c r="AH302" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI302" s="3">
+        <v>0</v>
       </c>
       <c r="AJ302" s="3" t="s">
         <v>58</v>
@@ -41080,13 +41080,13 @@
         <v>45</v>
       </c>
       <c r="I303" s="3" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="J303" s="3" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="K303" s="3" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="L303" s="3" t="s">
         <v>50</v>
@@ -41113,7 +41113,7 @@
         <v>46</v>
       </c>
       <c r="T303" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U303" s="3" t="s">
         <v>46</v>
@@ -41140,19 +41140,19 @@
         <v>1</v>
       </c>
       <c r="AC303" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD303" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE303" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF303" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD303" s="3" t="s">
+      <c r="AG303" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE303" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF303" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG303" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH303" s="7">
         <v>1</v>
@@ -41164,7 +41164,7 @@
         <v>58</v>
       </c>
       <c r="AK303" s="6">
-        <v>46298.66540524305</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL303" s="3" t="s">
         <v>46</v>
@@ -41176,7 +41176,7 @@
         <v>58</v>
       </c>
       <c r="AO303" s="6">
-        <v>46298.66540524305</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="304" spans="1:41" x14ac:dyDescent="0.25">
@@ -41205,28 +41205,28 @@
         <v>45</v>
       </c>
       <c r="I304" s="3" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="J304" s="3" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="K304" s="3" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="L304" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M304" s="3" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="N304" s="3" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="O304" s="3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="P304" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="Q304" s="3" t="s">
         <v>46</v>
@@ -41238,7 +41238,7 @@
         <v>46</v>
       </c>
       <c r="T304" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U304" s="3" t="s">
         <v>46</v>
@@ -41259,25 +41259,25 @@
         <v>10</v>
       </c>
       <c r="AA304" s="7">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="AB304" s="7">
         <v>1</v>
       </c>
       <c r="AC304" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD304" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE304" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF304" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD304" s="3" t="s">
+      <c r="AG304" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE304" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF304" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG304" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH304" s="7">
         <v>1</v>
@@ -41289,7 +41289,7 @@
         <v>58</v>
       </c>
       <c r="AK304" s="6">
-        <v>46312.58308098379</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL304" s="3" t="s">
         <v>46</v>
@@ -41301,7 +41301,7 @@
         <v>58</v>
       </c>
       <c r="AO304" s="6">
-        <v>46312.58308098379</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="305" spans="1:41" x14ac:dyDescent="0.25">
@@ -41330,28 +41330,28 @@
         <v>45</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="J305" s="3" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="K305" s="3" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="L305" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M305" s="3" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="N305" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="O305" s="3" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="P305" s="3" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="Q305" s="3" t="s">
         <v>46</v>
@@ -41363,7 +41363,7 @@
         <v>46</v>
       </c>
       <c r="T305" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U305" s="3" t="s">
         <v>46</v>
@@ -41390,19 +41390,19 @@
         <v>1</v>
       </c>
       <c r="AC305" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD305" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE305" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF305" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD305" s="3" t="s">
+      <c r="AG305" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE305" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF305" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG305" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH305" s="7">
         <v>1</v>
@@ -41414,7 +41414,7 @@
         <v>58</v>
       </c>
       <c r="AK305" s="6">
-        <v>46310.439036655094</v>
+        <v>46311.29832241898</v>
       </c>
       <c r="AL305" s="3" t="s">
         <v>46</v>
@@ -41426,7 +41426,7 @@
         <v>58</v>
       </c>
       <c r="AO305" s="6">
-        <v>46310.439036655094</v>
+        <v>46311.29832241898</v>
       </c>
     </row>
     <row r="306" spans="1:41" x14ac:dyDescent="0.25">
@@ -41455,13 +41455,13 @@
         <v>45</v>
       </c>
       <c r="I306" s="3" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="J306" s="3" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="K306" s="3" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="L306" s="3" t="s">
         <v>50</v>
@@ -41488,7 +41488,7 @@
         <v>46</v>
       </c>
       <c r="T306" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U306" s="3" t="s">
         <v>46</v>
@@ -41515,19 +41515,19 @@
         <v>1</v>
       </c>
       <c r="AC306" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD306" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE306" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF306" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD306" s="3" t="s">
+      <c r="AG306" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE306" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF306" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG306" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH306" s="7">
         <v>1</v>
@@ -41539,7 +41539,7 @@
         <v>58</v>
       </c>
       <c r="AK306" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL306" s="3" t="s">
         <v>46</v>
@@ -41551,7 +41551,7 @@
         <v>58</v>
       </c>
       <c r="AO306" s="6">
-        <v>46301.30899568287</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="307" spans="1:41" x14ac:dyDescent="0.25">
@@ -41580,28 +41580,28 @@
         <v>45</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>894</v>
+        <v>455</v>
       </c>
       <c r="J307" s="3" t="s">
-        <v>895</v>
+        <v>456</v>
       </c>
       <c r="K307" s="3" t="s">
-        <v>896</v>
+        <v>457</v>
       </c>
       <c r="L307" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M307" s="3" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="N307" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="O307" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="P307" s="3" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="Q307" s="3" t="s">
         <v>46</v>
@@ -41613,7 +41613,7 @@
         <v>46</v>
       </c>
       <c r="T307" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U307" s="3" t="s">
         <v>46</v>
@@ -41640,19 +41640,19 @@
         <v>1</v>
       </c>
       <c r="AC307" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD307" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE307" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF307" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD307" s="3" t="s">
+      <c r="AG307" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE307" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF307" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG307" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH307" s="7">
         <v>1</v>
@@ -41664,7 +41664,7 @@
         <v>58</v>
       </c>
       <c r="AK307" s="6">
-        <v>46301.5776272338</v>
+        <v>46302.48940038194</v>
       </c>
       <c r="AL307" s="3" t="s">
         <v>46</v>
@@ -41676,7 +41676,7 @@
         <v>58</v>
       </c>
       <c r="AO307" s="6">
-        <v>46301.5776272338</v>
+        <v>46302.48940038194</v>
       </c>
     </row>
     <row r="308" spans="1:41" x14ac:dyDescent="0.25">
@@ -41705,13 +41705,13 @@
         <v>45</v>
       </c>
       <c r="I308" s="3" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="J308" s="3" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="K308" s="3" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="L308" s="3" t="s">
         <v>50</v>
@@ -41738,7 +41738,7 @@
         <v>46</v>
       </c>
       <c r="T308" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U308" s="3" t="s">
         <v>46</v>
@@ -41765,19 +41765,19 @@
         <v>1</v>
       </c>
       <c r="AC308" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD308" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE308" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF308" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD308" s="3" t="s">
+      <c r="AG308" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE308" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF308" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG308" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH308" s="7">
         <v>1</v>
@@ -41789,7 +41789,7 @@
         <v>58</v>
       </c>
       <c r="AK308" s="6">
-        <v>46301.30899568287</v>
+        <v>46315.54901207176</v>
       </c>
       <c r="AL308" s="3" t="s">
         <v>46</v>
@@ -41801,7 +41801,7 @@
         <v>58</v>
       </c>
       <c r="AO308" s="6">
-        <v>46301.30899568287</v>
+        <v>46315.54901207176</v>
       </c>
     </row>
     <row r="309" spans="1:41" x14ac:dyDescent="0.25">
@@ -41830,13 +41830,13 @@
         <v>45</v>
       </c>
       <c r="I309" s="3" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="J309" s="3" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="K309" s="3" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="L309" s="3" t="s">
         <v>50</v>
@@ -41863,7 +41863,7 @@
         <v>46</v>
       </c>
       <c r="T309" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U309" s="3" t="s">
         <v>46</v>
@@ -41890,19 +41890,19 @@
         <v>1</v>
       </c>
       <c r="AC309" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD309" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE309" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF309" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD309" s="3" t="s">
+      <c r="AG309" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE309" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF309" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG309" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH309" s="7">
         <v>1</v>
@@ -41914,7 +41914,7 @@
         <v>58</v>
       </c>
       <c r="AK309" s="6">
-        <v>46298.66540524305</v>
+        <v>46304.293035104165</v>
       </c>
       <c r="AL309" s="3" t="s">
         <v>46</v>
@@ -41926,7 +41926,7 @@
         <v>58</v>
       </c>
       <c r="AO309" s="6">
-        <v>46298.66540524305</v>
+        <v>46304.293035104165</v>
       </c>
     </row>
     <row r="310" spans="1:41" x14ac:dyDescent="0.25">
@@ -41955,28 +41955,28 @@
         <v>45</v>
       </c>
       <c r="I310" s="3" t="s">
-        <v>455</v>
+        <v>906</v>
       </c>
       <c r="J310" s="3" t="s">
-        <v>456</v>
+        <v>907</v>
       </c>
       <c r="K310" s="3" t="s">
-        <v>457</v>
+        <v>908</v>
       </c>
       <c r="L310" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M310" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="N310" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="O310" s="3" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="P310" s="3" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="Q310" s="3" t="s">
         <v>46</v>
@@ -41988,7 +41988,7 @@
         <v>46</v>
       </c>
       <c r="T310" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U310" s="3" t="s">
         <v>46</v>
@@ -42015,19 +42015,19 @@
         <v>1</v>
       </c>
       <c r="AC310" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD310" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE310" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF310" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD310" s="3" t="s">
+      <c r="AG310" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE310" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF310" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG310" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH310" s="7">
         <v>1</v>
@@ -42039,7 +42039,7 @@
         <v>58</v>
       </c>
       <c r="AK310" s="6">
-        <v>46302.48940038194</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL310" s="3" t="s">
         <v>46</v>
@@ -42051,7 +42051,7 @@
         <v>58</v>
       </c>
       <c r="AO310" s="6">
-        <v>46302.48940038194</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="311" spans="1:41" x14ac:dyDescent="0.25">
@@ -42080,28 +42080,28 @@
         <v>45</v>
       </c>
       <c r="I311" s="3" t="s">
-        <v>903</v>
+        <v>271</v>
       </c>
       <c r="J311" s="3" t="s">
-        <v>904</v>
+        <v>272</v>
       </c>
       <c r="K311" s="3" t="s">
-        <v>905</v>
+        <v>273</v>
       </c>
       <c r="L311" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M311" s="3" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="N311" s="3" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="O311" s="3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="P311" s="3" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="Q311" s="3" t="s">
         <v>46</v>
@@ -42113,7 +42113,7 @@
         <v>46</v>
       </c>
       <c r="T311" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U311" s="3" t="s">
         <v>46</v>
@@ -42140,19 +42140,19 @@
         <v>1</v>
       </c>
       <c r="AC311" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD311" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE311" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF311" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD311" s="3" t="s">
+      <c r="AG311" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE311" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF311" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG311" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH311" s="7">
         <v>1</v>
@@ -42164,7 +42164,7 @@
         <v>58</v>
       </c>
       <c r="AK311" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.5776272338</v>
       </c>
       <c r="AL311" s="3" t="s">
         <v>46</v>
@@ -42176,7 +42176,7 @@
         <v>58</v>
       </c>
       <c r="AO311" s="6">
-        <v>46315.54901207176</v>
+        <v>46301.5776272338</v>
       </c>
     </row>
     <row r="312" spans="1:41" x14ac:dyDescent="0.25">
@@ -42205,28 +42205,28 @@
         <v>45</v>
       </c>
       <c r="I312" s="3" t="s">
-        <v>906</v>
+        <v>322</v>
       </c>
       <c r="J312" s="3" t="s">
-        <v>907</v>
+        <v>323</v>
       </c>
       <c r="K312" s="3" t="s">
-        <v>908</v>
+        <v>324</v>
       </c>
       <c r="L312" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M312" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N312" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O312" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P312" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Q312" s="3" t="s">
         <v>46</v>
@@ -42238,7 +42238,7 @@
         <v>46</v>
       </c>
       <c r="T312" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U312" s="3" t="s">
         <v>46</v>
@@ -42259,25 +42259,25 @@
         <v>10</v>
       </c>
       <c r="AA312" s="7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB312" s="7">
         <v>1</v>
       </c>
       <c r="AC312" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD312" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE312" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF312" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD312" s="3" t="s">
+      <c r="AG312" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE312" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF312" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG312" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH312" s="7">
         <v>1</v>
@@ -42289,7 +42289,7 @@
         <v>58</v>
       </c>
       <c r="AK312" s="6">
-        <v>46304.293035104165</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL312" s="3" t="s">
         <v>46</v>
@@ -42301,7 +42301,7 @@
         <v>58</v>
       </c>
       <c r="AO312" s="6">
-        <v>46304.293035104165</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="313" spans="1:41" x14ac:dyDescent="0.25">
@@ -42342,16 +42342,16 @@
         <v>50</v>
       </c>
       <c r="M313" s="3" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="N313" s="3" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="O313" s="3" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="P313" s="3" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="Q313" s="3" t="s">
         <v>46</v>
@@ -42363,7 +42363,7 @@
         <v>46</v>
       </c>
       <c r="T313" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U313" s="3" t="s">
         <v>46</v>
@@ -42390,19 +42390,19 @@
         <v>1</v>
       </c>
       <c r="AC313" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD313" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE313" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF313" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD313" s="3" t="s">
+      <c r="AG313" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE313" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF313" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG313" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH313" s="7">
         <v>1</v>
@@ -42414,7 +42414,7 @@
         <v>58</v>
       </c>
       <c r="AK313" s="6">
-        <v>46298.66540524305</v>
+        <v>46316.79383703704</v>
       </c>
       <c r="AL313" s="3" t="s">
         <v>46</v>
@@ -42426,7 +42426,7 @@
         <v>58</v>
       </c>
       <c r="AO313" s="6">
-        <v>46298.66540524305</v>
+        <v>46316.79383703704</v>
       </c>
     </row>
     <row r="314" spans="1:41" x14ac:dyDescent="0.25">
@@ -42455,28 +42455,28 @@
         <v>45</v>
       </c>
       <c r="I314" s="3" t="s">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="J314" s="3" t="s">
-        <v>272</v>
+        <v>139</v>
       </c>
       <c r="K314" s="3" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="L314" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M314" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="N314" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="O314" s="3" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="P314" s="3" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="Q314" s="3" t="s">
         <v>46</v>
@@ -42488,7 +42488,7 @@
         <v>46</v>
       </c>
       <c r="T314" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U314" s="3" t="s">
         <v>46</v>
@@ -42509,25 +42509,25 @@
         <v>10</v>
       </c>
       <c r="AA314" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB314" s="7">
         <v>1</v>
       </c>
       <c r="AC314" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD314" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE314" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF314" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD314" s="3" t="s">
+      <c r="AG314" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE314" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF314" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG314" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH314" s="7">
         <v>1</v>
@@ -42539,7 +42539,7 @@
         <v>58</v>
       </c>
       <c r="AK314" s="6">
-        <v>46301.5776272338</v>
+        <v>46303.59483915509</v>
       </c>
       <c r="AL314" s="3" t="s">
         <v>46</v>
@@ -42551,7 +42551,7 @@
         <v>58</v>
       </c>
       <c r="AO314" s="6">
-        <v>46301.5776272338</v>
+        <v>46303.59483915509</v>
       </c>
     </row>
     <row r="315" spans="1:41" x14ac:dyDescent="0.25">
@@ -42580,28 +42580,28 @@
         <v>45</v>
       </c>
       <c r="I315" s="3" t="s">
-        <v>322</v>
+        <v>144</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>323</v>
+        <v>145</v>
       </c>
       <c r="K315" s="3" t="s">
-        <v>324</v>
+        <v>146</v>
       </c>
       <c r="L315" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M315" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="N315" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="O315" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="P315" s="3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="Q315" s="3" t="s">
         <v>46</v>
@@ -42613,7 +42613,7 @@
         <v>46</v>
       </c>
       <c r="T315" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U315" s="3" t="s">
         <v>46</v>
@@ -42634,25 +42634,25 @@
         <v>10</v>
       </c>
       <c r="AA315" s="7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB315" s="7">
         <v>1</v>
       </c>
       <c r="AC315" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD315" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE315" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF315" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD315" s="3" t="s">
+      <c r="AG315" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE315" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF315" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG315" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH315" s="7">
         <v>1</v>
@@ -42664,7 +42664,7 @@
         <v>58</v>
       </c>
       <c r="AK315" s="6">
-        <v>46303.59483915509</v>
+        <v>46302.48940038194</v>
       </c>
       <c r="AL315" s="3" t="s">
         <v>46</v>
@@ -42676,7 +42676,7 @@
         <v>58</v>
       </c>
       <c r="AO315" s="6">
-        <v>46303.59483915509</v>
+        <v>46302.48940038194</v>
       </c>
     </row>
     <row r="316" spans="1:41" x14ac:dyDescent="0.25">
@@ -42705,28 +42705,28 @@
         <v>45</v>
       </c>
       <c r="I316" s="3" t="s">
-        <v>912</v>
+        <v>150</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>913</v>
+        <v>151</v>
       </c>
       <c r="K316" s="3" t="s">
-        <v>914</v>
+        <v>152</v>
       </c>
       <c r="L316" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M316" s="3" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="N316" s="3" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="O316" s="3" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="P316" s="3" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="Q316" s="3" t="s">
         <v>46</v>
@@ -42738,7 +42738,7 @@
         <v>46</v>
       </c>
       <c r="T316" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U316" s="3" t="s">
         <v>46</v>
@@ -42765,19 +42765,19 @@
         <v>1</v>
       </c>
       <c r="AC316" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD316" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE316" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF316" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD316" s="3" t="s">
+      <c r="AG316" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE316" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF316" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG316" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH316" s="7">
         <v>1</v>
@@ -42789,7 +42789,7 @@
         <v>58</v>
       </c>
       <c r="AK316" s="6">
-        <v>46316.79383703704</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL316" s="3" t="s">
         <v>46</v>
@@ -42801,7 +42801,7 @@
         <v>58</v>
       </c>
       <c r="AO316" s="6">
-        <v>46316.79383703704</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="317" spans="1:41" x14ac:dyDescent="0.25">
@@ -42830,28 +42830,28 @@
         <v>45</v>
       </c>
       <c r="I317" s="3" t="s">
-        <v>138</v>
+        <v>912</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>139</v>
+        <v>913</v>
       </c>
       <c r="K317" s="3" t="s">
-        <v>140</v>
+        <v>914</v>
       </c>
       <c r="L317" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M317" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="N317" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="O317" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="P317" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="Q317" s="3" t="s">
         <v>46</v>
@@ -42863,7 +42863,7 @@
         <v>46</v>
       </c>
       <c r="T317" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U317" s="3" t="s">
         <v>46</v>
@@ -42884,25 +42884,25 @@
         <v>10</v>
       </c>
       <c r="AA317" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB317" s="7">
         <v>1</v>
       </c>
       <c r="AC317" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD317" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE317" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF317" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD317" s="3" t="s">
+      <c r="AG317" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE317" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF317" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG317" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH317" s="7">
         <v>1</v>
@@ -42914,7 +42914,7 @@
         <v>58</v>
       </c>
       <c r="AK317" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
       <c r="AL317" s="3" t="s">
         <v>46</v>
@@ -42926,7 +42926,7 @@
         <v>58</v>
       </c>
       <c r="AO317" s="6">
-        <v>46303.59483915509</v>
+        <v>46298.66540524305</v>
       </c>
     </row>
     <row r="318" spans="1:41" x14ac:dyDescent="0.25">
@@ -42955,28 +42955,28 @@
         <v>45</v>
       </c>
       <c r="I318" s="3" t="s">
-        <v>144</v>
+        <v>705</v>
       </c>
       <c r="J318" s="3" t="s">
-        <v>145</v>
+        <v>706</v>
       </c>
       <c r="K318" s="3" t="s">
-        <v>146</v>
+        <v>707</v>
       </c>
       <c r="L318" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M318" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="N318" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="O318" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="P318" s="3" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="Q318" s="3" t="s">
         <v>46</v>
@@ -42988,7 +42988,7 @@
         <v>46</v>
       </c>
       <c r="T318" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U318" s="3" t="s">
         <v>46</v>
@@ -43015,19 +43015,19 @@
         <v>1</v>
       </c>
       <c r="AC318" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD318" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE318" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF318" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD318" s="3" t="s">
+      <c r="AG318" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE318" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF318" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG318" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH318" s="7">
         <v>1</v>
@@ -43039,7 +43039,7 @@
         <v>58</v>
       </c>
       <c r="AK318" s="6">
-        <v>46302.48940038194</v>
+        <v>46301.30899568287</v>
       </c>
       <c r="AL318" s="3" t="s">
         <v>46</v>
@@ -43051,7 +43051,7 @@
         <v>58</v>
       </c>
       <c r="AO318" s="6">
-        <v>46302.48940038194</v>
+        <v>46301.30899568287</v>
       </c>
     </row>
     <row r="319" spans="1:41" x14ac:dyDescent="0.25">
@@ -43080,28 +43080,28 @@
         <v>45</v>
       </c>
       <c r="I319" s="3" t="s">
-        <v>150</v>
+        <v>915</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>151</v>
+        <v>916</v>
       </c>
       <c r="K319" s="3" t="s">
-        <v>152</v>
+        <v>917</v>
       </c>
       <c r="L319" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M319" s="3" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="N319" s="3" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="O319" s="3" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="P319" s="3" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="Q319" s="3" t="s">
         <v>46</v>
@@ -43113,7 +43113,7 @@
         <v>46</v>
       </c>
       <c r="T319" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U319" s="3" t="s">
         <v>46</v>
@@ -43140,19 +43140,19 @@
         <v>1</v>
       </c>
       <c r="AC319" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD319" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE319" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF319" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD319" s="3" t="s">
+      <c r="AG319" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE319" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF319" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG319" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH319" s="7">
         <v>1</v>
@@ -43205,28 +43205,28 @@
         <v>45</v>
       </c>
       <c r="I320" s="3" t="s">
-        <v>915</v>
+        <v>238</v>
       </c>
       <c r="J320" s="3" t="s">
-        <v>916</v>
+        <v>239</v>
       </c>
       <c r="K320" s="3" t="s">
-        <v>917</v>
+        <v>240</v>
       </c>
       <c r="L320" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M320" s="3" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="N320" s="3" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="O320" s="3" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="P320" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="Q320" s="3" t="s">
         <v>46</v>
@@ -43238,7 +43238,7 @@
         <v>46</v>
       </c>
       <c r="T320" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U320" s="3" t="s">
         <v>46</v>
@@ -43265,19 +43265,19 @@
         <v>1</v>
       </c>
       <c r="AC320" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="AD320" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE320" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF320" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="AD320" s="3" t="s">
+      <c r="AG320" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="AE320" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="AF320" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="AG320" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="AH320" s="7">
         <v>1</v>
@@ -43289,7 +43289,7 @@
         <v>58</v>
       </c>
       <c r="AK320" s="6">
-        <v>46298.66540524305</v>
+        <v>46298.31634892361</v>
       </c>
       <c r="AL320" s="3" t="s">
         <v>46</v>
@@ -43301,7 +43301,7 @@
         <v>58</v>
       </c>
       <c r="AO320" s="6">
-        <v>46298.66540524305</v>
+        <v>46298.31634892361</v>
       </c>
     </row>
     <row r="321" spans="1:41" x14ac:dyDescent="0.25">
@@ -43363,7 +43363,7 @@
         <v>17</v>
       </c>
       <c r="T321" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U321" s="3" t="s">
         <v>46</v>
@@ -43390,7 +43390,7 @@
         <v>31</v>
       </c>
       <c r="AC321" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD321" s="3" t="s">
         <v>922</v>
@@ -43399,10 +43399,10 @@
         <v>923</v>
       </c>
       <c r="AF321" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG321" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH321" s="7">
         <v>12400000</v>
@@ -43455,40 +43455,40 @@
         <v>921</v>
       </c>
       <c r="I322" s="3" t="s">
-        <v>755</v>
+        <v>925</v>
       </c>
       <c r="J322" s="3" t="s">
-        <v>756</v>
+        <v>926</v>
       </c>
       <c r="K322" s="3" t="s">
-        <v>757</v>
+        <v>927</v>
       </c>
       <c r="L322" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M322" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="N322" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O322" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P322" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Q322" s="5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R322" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S322" s="5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T322" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U322" s="3" t="s">
         <v>46</v>
@@ -43509,13 +43509,13 @@
         <v>46</v>
       </c>
       <c r="AA322" s="7">
-        <v>818901</v>
+        <v>1294672</v>
       </c>
       <c r="AB322" s="7">
         <v>31</v>
       </c>
       <c r="AC322" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD322" s="3" t="s">
         <v>922</v>
@@ -43524,10 +43524,10 @@
         <v>923</v>
       </c>
       <c r="AF322" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG322" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH322" s="7">
         <v>12400000</v>
@@ -43580,40 +43580,40 @@
         <v>921</v>
       </c>
       <c r="I323" s="3" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="J323" s="3" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="K323" s="3" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="L323" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M323" s="3" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="N323" s="3" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="O323" s="3" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="P323" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="Q323" s="5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R323" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S323" s="5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T323" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U323" s="3" t="s">
         <v>46</v>
@@ -43634,13 +43634,13 @@
         <v>46</v>
       </c>
       <c r="AA323" s="7">
-        <v>1173312</v>
+        <v>818901</v>
       </c>
       <c r="AB323" s="7">
         <v>31</v>
       </c>
       <c r="AC323" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD323" s="3" t="s">
         <v>922</v>
@@ -43649,10 +43649,10 @@
         <v>923</v>
       </c>
       <c r="AF323" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG323" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH323" s="7">
         <v>12400000</v>
@@ -43705,40 +43705,40 @@
         <v>921</v>
       </c>
       <c r="I324" s="3" t="s">
-        <v>464</v>
+        <v>761</v>
       </c>
       <c r="J324" s="3" t="s">
-        <v>465</v>
+        <v>762</v>
       </c>
       <c r="K324" s="3" t="s">
-        <v>466</v>
+        <v>763</v>
       </c>
       <c r="L324" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M324" s="3" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="N324" s="3" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="O324" s="3" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="P324" s="3" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="Q324" s="5">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="R324" s="5">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="S324" s="5">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="T324" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U324" s="3" t="s">
         <v>46</v>
@@ -43758,14 +43758,14 @@
       <c r="Z324" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA324" s="3" t="s">
-        <v>46</v>
+      <c r="AA324" s="7">
+        <v>1173312</v>
       </c>
       <c r="AB324" s="7">
         <v>31</v>
       </c>
       <c r="AC324" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD324" s="3" t="s">
         <v>922</v>
@@ -43774,10 +43774,10 @@
         <v>923</v>
       </c>
       <c r="AF324" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG324" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH324" s="7">
         <v>12400000</v>
@@ -43830,40 +43830,40 @@
         <v>921</v>
       </c>
       <c r="I325" s="3" t="s">
-        <v>838</v>
+        <v>464</v>
       </c>
       <c r="J325" s="3" t="s">
-        <v>839</v>
+        <v>465</v>
       </c>
       <c r="K325" s="3" t="s">
-        <v>840</v>
+        <v>466</v>
       </c>
       <c r="L325" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M325" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="N325" s="3" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="O325" s="3" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="P325" s="3" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="Q325" s="5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R325" s="5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="S325" s="5">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="T325" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U325" s="3" t="s">
         <v>46</v>
@@ -43883,14 +43883,14 @@
       <c r="Z325" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA325" s="7">
-        <v>1829136</v>
+      <c r="AA325" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB325" s="7">
         <v>31</v>
       </c>
       <c r="AC325" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD325" s="3" t="s">
         <v>922</v>
@@ -43899,10 +43899,10 @@
         <v>923</v>
       </c>
       <c r="AF325" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG325" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH325" s="7">
         <v>12400000</v>
@@ -43955,40 +43955,40 @@
         <v>921</v>
       </c>
       <c r="I326" s="3" t="s">
-        <v>925</v>
+        <v>838</v>
       </c>
       <c r="J326" s="3" t="s">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="K326" s="3" t="s">
-        <v>927</v>
+        <v>840</v>
       </c>
       <c r="L326" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M326" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="N326" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="O326" s="3" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="P326" s="3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="Q326" s="5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="R326" s="5">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S326" s="5">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="T326" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U326" s="3" t="s">
         <v>46</v>
@@ -44009,13 +44009,13 @@
         <v>46</v>
       </c>
       <c r="AA326" s="7">
-        <v>1294672</v>
+        <v>1829136</v>
       </c>
       <c r="AB326" s="7">
         <v>31</v>
       </c>
       <c r="AC326" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD326" s="3" t="s">
         <v>922</v>
@@ -44024,10 +44024,10 @@
         <v>923</v>
       </c>
       <c r="AF326" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG326" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH326" s="7">
         <v>12400000</v>
@@ -44113,7 +44113,7 @@
         <v>34</v>
       </c>
       <c r="T327" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U327" s="3" t="s">
         <v>46</v>
@@ -44140,7 +44140,7 @@
         <v>31</v>
       </c>
       <c r="AC327" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD327" s="3" t="s">
         <v>922</v>
@@ -44149,10 +44149,10 @@
         <v>923</v>
       </c>
       <c r="AF327" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG327" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH327" s="7">
         <v>12400000</v>
@@ -44238,7 +44238,7 @@
         <v>32</v>
       </c>
       <c r="T328" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U328" s="3" t="s">
         <v>46</v>
@@ -44265,7 +44265,7 @@
         <v>31</v>
       </c>
       <c r="AC328" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD328" s="3" t="s">
         <v>922</v>
@@ -44274,10 +44274,10 @@
         <v>923</v>
       </c>
       <c r="AF328" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG328" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH328" s="7">
         <v>12400000</v>
@@ -44354,16 +44354,16 @@
         <v>128</v>
       </c>
       <c r="Q329" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R329" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S329" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T329" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U329" s="3" t="s">
         <v>46</v>
@@ -44390,7 +44390,7 @@
         <v>31</v>
       </c>
       <c r="AC329" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD329" s="3" t="s">
         <v>922</v>
@@ -44399,10 +44399,10 @@
         <v>923</v>
       </c>
       <c r="AF329" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG329" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH329" s="7">
         <v>12400000</v>
@@ -44488,7 +44488,7 @@
         <v>17</v>
       </c>
       <c r="T330" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U330" s="3" t="s">
         <v>46</v>
@@ -44515,7 +44515,7 @@
         <v>31</v>
       </c>
       <c r="AC330" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD330" s="3" t="s">
         <v>922</v>
@@ -44524,10 +44524,10 @@
         <v>923</v>
       </c>
       <c r="AF330" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG330" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH330" s="7">
         <v>12400000</v>
@@ -44613,7 +44613,7 @@
         <v>21</v>
       </c>
       <c r="T331" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U331" s="3" t="s">
         <v>46</v>
@@ -44640,7 +44640,7 @@
         <v>31</v>
       </c>
       <c r="AC331" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD331" s="3" t="s">
         <v>922</v>
@@ -44649,10 +44649,10 @@
         <v>923</v>
       </c>
       <c r="AF331" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG331" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH331" s="7">
         <v>12400000</v>
@@ -44738,7 +44738,7 @@
         <v>4</v>
       </c>
       <c r="T332" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U332" s="3" t="s">
         <v>46</v>
@@ -44765,7 +44765,7 @@
         <v>31</v>
       </c>
       <c r="AC332" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD332" s="3" t="s">
         <v>922</v>
@@ -44774,10 +44774,10 @@
         <v>923</v>
       </c>
       <c r="AF332" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG332" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH332" s="7">
         <v>12400000</v>
@@ -44863,7 +44863,7 @@
         <v>33</v>
       </c>
       <c r="T333" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U333" s="3" t="s">
         <v>46</v>
@@ -44890,7 +44890,7 @@
         <v>31</v>
       </c>
       <c r="AC333" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD333" s="3" t="s">
         <v>922</v>
@@ -44899,10 +44899,10 @@
         <v>923</v>
       </c>
       <c r="AF333" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG333" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH333" s="7">
         <v>12400000</v>
@@ -44988,7 +44988,7 @@
         <v>10</v>
       </c>
       <c r="T334" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U334" s="3" t="s">
         <v>46</v>
@@ -45015,7 +45015,7 @@
         <v>31</v>
       </c>
       <c r="AC334" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD334" s="3" t="s">
         <v>922</v>
@@ -45024,10 +45024,10 @@
         <v>923</v>
       </c>
       <c r="AF334" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG334" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH334" s="7">
         <v>12400000</v>
@@ -45080,40 +45080,40 @@
         <v>932</v>
       </c>
       <c r="I335" s="3" t="s">
-        <v>274</v>
+        <v>399</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>275</v>
+        <v>96</v>
       </c>
       <c r="K335" s="3" t="s">
-        <v>276</v>
+        <v>400</v>
       </c>
       <c r="L335" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M335" s="3" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="N335" s="3" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="O335" s="3" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="P335" s="3" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="Q335" s="5">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="R335" s="5">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="S335" s="5">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="T335" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U335" s="3" t="s">
         <v>46</v>
@@ -45133,14 +45133,14 @@
       <c r="Z335" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA335" s="3" t="s">
-        <v>46</v>
+      <c r="AA335" s="7">
+        <v>1109008</v>
       </c>
       <c r="AB335" s="7">
         <v>31</v>
       </c>
       <c r="AC335" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD335" s="3" t="s">
         <v>922</v>
@@ -45149,10 +45149,10 @@
         <v>923</v>
       </c>
       <c r="AF335" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG335" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH335" s="7">
         <v>12400000</v>
@@ -45205,40 +45205,40 @@
         <v>932</v>
       </c>
       <c r="I336" s="3" t="s">
-        <v>399</v>
+        <v>274</v>
       </c>
       <c r="J336" s="3" t="s">
-        <v>96</v>
+        <v>275</v>
       </c>
       <c r="K336" s="3" t="s">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="L336" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M336" s="3" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="N336" s="3" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="O336" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="P336" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="Q336" s="5">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="R336" s="5">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="S336" s="5">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="T336" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U336" s="3" t="s">
         <v>46</v>
@@ -45258,14 +45258,14 @@
       <c r="Z336" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA336" s="7">
-        <v>1109008</v>
+      <c r="AA336" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="AB336" s="7">
         <v>31</v>
       </c>
       <c r="AC336" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD336" s="3" t="s">
         <v>922</v>
@@ -45274,10 +45274,10 @@
         <v>923</v>
       </c>
       <c r="AF336" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG336" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH336" s="7">
         <v>12400000</v>
@@ -45363,7 +45363,7 @@
         <v>9</v>
       </c>
       <c r="T337" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U337" s="3" t="s">
         <v>46</v>
@@ -45390,7 +45390,7 @@
         <v>31</v>
       </c>
       <c r="AC337" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD337" s="3" t="s">
         <v>922</v>
@@ -45399,10 +45399,10 @@
         <v>923</v>
       </c>
       <c r="AF337" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG337" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH337" s="7">
         <v>12400000</v>
@@ -45488,7 +45488,7 @@
         <v>39</v>
       </c>
       <c r="T338" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U338" s="3" t="s">
         <v>46</v>
@@ -45515,7 +45515,7 @@
         <v>31</v>
       </c>
       <c r="AC338" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD338" s="3" t="s">
         <v>922</v>
@@ -45524,10 +45524,10 @@
         <v>923</v>
       </c>
       <c r="AF338" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG338" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH338" s="7">
         <v>12400000</v>
@@ -45613,7 +45613,7 @@
         <v>13</v>
       </c>
       <c r="T339" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U339" s="3" t="s">
         <v>46</v>
@@ -45640,7 +45640,7 @@
         <v>31</v>
       </c>
       <c r="AC339" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD339" s="3" t="s">
         <v>922</v>
@@ -45649,10 +45649,10 @@
         <v>923</v>
       </c>
       <c r="AF339" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG339" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH339" s="7">
         <v>12400000</v>
@@ -45738,7 +45738,7 @@
         <v>31</v>
       </c>
       <c r="T340" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U340" s="3" t="s">
         <v>46</v>
@@ -45765,7 +45765,7 @@
         <v>31</v>
       </c>
       <c r="AC340" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD340" s="3" t="s">
         <v>922</v>
@@ -45774,10 +45774,10 @@
         <v>923</v>
       </c>
       <c r="AF340" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG340" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH340" s="7">
         <v>12400000</v>
@@ -45863,7 +45863,7 @@
         <v>13</v>
       </c>
       <c r="T341" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U341" s="3" t="s">
         <v>46</v>
@@ -45890,7 +45890,7 @@
         <v>31</v>
       </c>
       <c r="AC341" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD341" s="3" t="s">
         <v>922</v>
@@ -45899,10 +45899,10 @@
         <v>923</v>
       </c>
       <c r="AF341" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG341" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH341" s="7">
         <v>12400000</v>
@@ -45988,7 +45988,7 @@
         <v>34</v>
       </c>
       <c r="T342" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U342" s="3" t="s">
         <v>46</v>
@@ -46015,7 +46015,7 @@
         <v>31</v>
       </c>
       <c r="AC342" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD342" s="3" t="s">
         <v>922</v>
@@ -46024,10 +46024,10 @@
         <v>923</v>
       </c>
       <c r="AF342" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG342" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH342" s="7">
         <v>18600000</v>
@@ -46113,7 +46113,7 @@
         <v>21</v>
       </c>
       <c r="T343" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U343" s="3" t="s">
         <v>46</v>
@@ -46140,7 +46140,7 @@
         <v>31</v>
       </c>
       <c r="AC343" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD343" s="3" t="s">
         <v>922</v>
@@ -46149,10 +46149,10 @@
         <v>923</v>
       </c>
       <c r="AF343" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG343" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH343" s="7">
         <v>18600000</v>
@@ -46238,7 +46238,7 @@
         <v>33</v>
       </c>
       <c r="T344" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U344" s="3" t="s">
         <v>46</v>
@@ -46265,7 +46265,7 @@
         <v>31</v>
       </c>
       <c r="AC344" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD344" s="3" t="s">
         <v>922</v>
@@ -46274,10 +46274,10 @@
         <v>923</v>
       </c>
       <c r="AF344" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG344" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH344" s="7">
         <v>12400000</v>
@@ -46363,7 +46363,7 @@
         <v>35</v>
       </c>
       <c r="T345" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U345" s="3" t="s">
         <v>46</v>
@@ -46390,7 +46390,7 @@
         <v>31</v>
       </c>
       <c r="AC345" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD345" s="3" t="s">
         <v>922</v>
@@ -46399,10 +46399,10 @@
         <v>923</v>
       </c>
       <c r="AF345" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG345" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH345" s="7">
         <v>12400000</v>
@@ -46488,7 +46488,7 @@
         <v>10</v>
       </c>
       <c r="T346" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U346" s="3" t="s">
         <v>46</v>
@@ -46515,7 +46515,7 @@
         <v>31</v>
       </c>
       <c r="AC346" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD346" s="3" t="s">
         <v>922</v>
@@ -46524,10 +46524,10 @@
         <v>923</v>
       </c>
       <c r="AF346" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG346" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH346" s="7">
         <v>12400000</v>
@@ -46613,7 +46613,7 @@
         <v>8</v>
       </c>
       <c r="T347" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U347" s="3" t="s">
         <v>46</v>
@@ -46640,7 +46640,7 @@
         <v>31</v>
       </c>
       <c r="AC347" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD347" s="3" t="s">
         <v>922</v>
@@ -46649,10 +46649,10 @@
         <v>923</v>
       </c>
       <c r="AF347" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG347" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH347" s="7">
         <v>12400000</v>
@@ -46738,7 +46738,7 @@
         <v>13</v>
       </c>
       <c r="T348" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U348" s="3" t="s">
         <v>46</v>
@@ -46765,7 +46765,7 @@
         <v>31</v>
       </c>
       <c r="AC348" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD348" s="3" t="s">
         <v>922</v>
@@ -46774,10 +46774,10 @@
         <v>923</v>
       </c>
       <c r="AF348" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG348" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH348" s="7">
         <v>12400000</v>
@@ -46863,7 +46863,7 @@
         <v>8</v>
       </c>
       <c r="T349" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U349" s="3" t="s">
         <v>46</v>
@@ -46890,7 +46890,7 @@
         <v>31</v>
       </c>
       <c r="AC349" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD349" s="3" t="s">
         <v>922</v>
@@ -46899,10 +46899,10 @@
         <v>923</v>
       </c>
       <c r="AF349" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG349" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH349" s="7">
         <v>12400000</v>
@@ -46988,7 +46988,7 @@
         <v>30</v>
       </c>
       <c r="T350" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U350" s="3" t="s">
         <v>46</v>
@@ -47015,7 +47015,7 @@
         <v>31</v>
       </c>
       <c r="AC350" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD350" s="3" t="s">
         <v>922</v>
@@ -47024,10 +47024,10 @@
         <v>923</v>
       </c>
       <c r="AF350" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG350" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH350" s="7">
         <v>12400000</v>
@@ -47113,7 +47113,7 @@
         <v>15</v>
       </c>
       <c r="T351" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U351" s="3" t="s">
         <v>46</v>
@@ -47140,7 +47140,7 @@
         <v>31</v>
       </c>
       <c r="AC351" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD351" s="3" t="s">
         <v>922</v>
@@ -47149,10 +47149,10 @@
         <v>923</v>
       </c>
       <c r="AF351" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG351" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH351" s="7">
         <v>12400000</v>
@@ -47238,7 +47238,7 @@
         <v>38</v>
       </c>
       <c r="T352" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U352" s="3" t="s">
         <v>46</v>
@@ -47265,7 +47265,7 @@
         <v>31</v>
       </c>
       <c r="AC352" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD352" s="3" t="s">
         <v>922</v>
@@ -47274,10 +47274,10 @@
         <v>923</v>
       </c>
       <c r="AF352" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG352" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH352" s="7">
         <v>12400000</v>
@@ -47363,7 +47363,7 @@
         <v>32</v>
       </c>
       <c r="T353" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U353" s="3" t="s">
         <v>46</v>
@@ -47384,13 +47384,13 @@
         <v>46</v>
       </c>
       <c r="AA353" s="7">
-        <v>925650</v>
+        <v>1526650</v>
       </c>
       <c r="AB353" s="7">
         <v>31</v>
       </c>
       <c r="AC353" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD353" s="3" t="s">
         <v>922</v>
@@ -47399,10 +47399,10 @@
         <v>923</v>
       </c>
       <c r="AF353" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG353" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH353" s="7">
         <v>12400000</v>
@@ -47488,7 +47488,7 @@
         <v>6</v>
       </c>
       <c r="T354" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U354" s="3" t="s">
         <v>46</v>
@@ -47515,7 +47515,7 @@
         <v>31</v>
       </c>
       <c r="AC354" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD354" s="3" t="s">
         <v>922</v>
@@ -47524,10 +47524,10 @@
         <v>923</v>
       </c>
       <c r="AF354" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG354" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH354" s="7">
         <v>12400000</v>
@@ -47613,7 +47613,7 @@
         <v>31</v>
       </c>
       <c r="T355" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U355" s="3" t="s">
         <v>46</v>
@@ -47640,7 +47640,7 @@
         <v>31</v>
       </c>
       <c r="AC355" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD355" s="3" t="s">
         <v>922</v>
@@ -47649,10 +47649,10 @@
         <v>923</v>
       </c>
       <c r="AF355" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG355" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH355" s="7">
         <v>12400000</v>
@@ -47738,7 +47738,7 @@
         <v>22</v>
       </c>
       <c r="T356" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U356" s="3" t="s">
         <v>46</v>
@@ -47765,7 +47765,7 @@
         <v>31</v>
       </c>
       <c r="AC356" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD356" s="3" t="s">
         <v>922</v>
@@ -47774,10 +47774,10 @@
         <v>923</v>
       </c>
       <c r="AF356" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG356" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH356" s="7">
         <v>12400000</v>
@@ -47863,7 +47863,7 @@
         <v>28</v>
       </c>
       <c r="T357" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U357" s="3" t="s">
         <v>46</v>
@@ -47890,7 +47890,7 @@
         <v>31</v>
       </c>
       <c r="AC357" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD357" s="3" t="s">
         <v>922</v>
@@ -47899,10 +47899,10 @@
         <v>923</v>
       </c>
       <c r="AF357" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG357" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH357" s="7">
         <v>12400000</v>
@@ -47955,13 +47955,13 @@
         <v>951</v>
       </c>
       <c r="I358" s="3" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="J358" s="3" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="K358" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="L358" s="3" t="s">
         <v>50</v>
@@ -47988,7 +47988,7 @@
         <v>12</v>
       </c>
       <c r="T358" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U358" s="3" t="s">
         <v>46</v>
@@ -48015,7 +48015,7 @@
         <v>31</v>
       </c>
       <c r="AC358" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD358" s="3" t="s">
         <v>922</v>
@@ -48024,10 +48024,10 @@
         <v>923</v>
       </c>
       <c r="AF358" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG358" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH358" s="7">
         <v>12400000</v>
@@ -48113,7 +48113,7 @@
         <v>3</v>
       </c>
       <c r="T359" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U359" s="3" t="s">
         <v>46</v>
@@ -48134,7 +48134,7 @@
         <v>46</v>
       </c>
       <c r="AA359" s="7">
-        <v>646676</v>
+        <v>1216916</v>
       </c>
       <c r="AB359" s="7">
         <v>1</v>
@@ -48238,7 +48238,7 @@
         <v>2</v>
       </c>
       <c r="T360" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U360" s="3" t="s">
         <v>46</v>
@@ -48363,7 +48363,7 @@
         <v>2</v>
       </c>
       <c r="T361" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U361" s="3" t="s">
         <v>46</v>
@@ -48488,7 +48488,7 @@
         <v>2</v>
       </c>
       <c r="T362" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U362" s="3" t="s">
         <v>46</v>
@@ -48613,7 +48613,7 @@
         <v>2</v>
       </c>
       <c r="T363" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U363" s="3" t="s">
         <v>46</v>
@@ -48738,7 +48738,7 @@
         <v>1</v>
       </c>
       <c r="T364" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U364" s="3" t="s">
         <v>46</v>
@@ -48863,7 +48863,7 @@
         <v>2</v>
       </c>
       <c r="T365" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U365" s="3" t="s">
         <v>46</v>
@@ -48884,7 +48884,7 @@
         <v>46</v>
       </c>
       <c r="AA365" s="7">
-        <v>1227480</v>
+        <v>1600480</v>
       </c>
       <c r="AB365" s="7">
         <v>1</v>
@@ -48988,7 +48988,7 @@
         <v>1</v>
       </c>
       <c r="T366" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U366" s="3" t="s">
         <v>46</v>
@@ -49113,7 +49113,7 @@
         <v>2</v>
       </c>
       <c r="T367" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U367" s="3" t="s">
         <v>46</v>
@@ -49238,7 +49238,7 @@
         <v>2</v>
       </c>
       <c r="T368" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U368" s="3" t="s">
         <v>46</v>
@@ -49363,7 +49363,7 @@
         <v>2</v>
       </c>
       <c r="T369" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U369" s="3" t="s">
         <v>46</v>
@@ -49488,7 +49488,7 @@
         <v>4</v>
       </c>
       <c r="T370" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U370" s="3" t="s">
         <v>46</v>
@@ -49613,7 +49613,7 @@
         <v>2</v>
       </c>
       <c r="T371" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U371" s="3" t="s">
         <v>46</v>
@@ -49634,7 +49634,7 @@
         <v>46</v>
       </c>
       <c r="AA371" s="7">
-        <v>5131620</v>
+        <v>5853330</v>
       </c>
       <c r="AB371" s="7">
         <v>1</v>
@@ -49738,7 +49738,7 @@
         <v>1</v>
       </c>
       <c r="T372" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U372" s="3" t="s">
         <v>46</v>
@@ -49863,7 +49863,7 @@
         <v>2</v>
       </c>
       <c r="T373" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U373" s="3" t="s">
         <v>46</v>
@@ -49988,7 +49988,7 @@
         <v>2</v>
       </c>
       <c r="T374" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U374" s="3" t="s">
         <v>46</v>
@@ -50113,7 +50113,7 @@
         <v>2</v>
       </c>
       <c r="T375" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U375" s="3" t="s">
         <v>46</v>
@@ -50238,7 +50238,7 @@
         <v>2</v>
       </c>
       <c r="T376" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U376" s="3" t="s">
         <v>46</v>
@@ -50363,7 +50363,7 @@
         <v>2</v>
       </c>
       <c r="T377" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U377" s="3" t="s">
         <v>46</v>
@@ -50384,7 +50384,7 @@
         <v>46</v>
       </c>
       <c r="AA377" s="7">
-        <v>771000</v>
+        <v>963000</v>
       </c>
       <c r="AB377" s="7">
         <v>1</v>
@@ -50488,7 +50488,7 @@
         <v>2</v>
       </c>
       <c r="T378" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U378" s="3" t="s">
         <v>46</v>
@@ -50509,7 +50509,7 @@
         <v>46</v>
       </c>
       <c r="AA378" s="7">
-        <v>698000</v>
+        <v>890000</v>
       </c>
       <c r="AB378" s="7">
         <v>1</v>
@@ -50613,7 +50613,7 @@
         <v>2</v>
       </c>
       <c r="T379" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U379" s="3" t="s">
         <v>46</v>
@@ -50738,7 +50738,7 @@
         <v>2</v>
       </c>
       <c r="T380" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U380" s="3" t="s">
         <v>46</v>
@@ -50863,7 +50863,7 @@
         <v>2</v>
       </c>
       <c r="T381" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U381" s="3" t="s">
         <v>46</v>
@@ -50884,7 +50884,7 @@
         <v>46</v>
       </c>
       <c r="AA381" s="7">
-        <v>839166</v>
+        <v>1013166</v>
       </c>
       <c r="AB381" s="7">
         <v>1</v>
@@ -50988,7 +50988,7 @@
         <v>2</v>
       </c>
       <c r="T382" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U382" s="3" t="s">
         <v>46</v>
@@ -51113,7 +51113,7 @@
         <v>1</v>
       </c>
       <c r="T383" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U383" s="3" t="s">
         <v>46</v>
@@ -51238,7 +51238,7 @@
         <v>2</v>
       </c>
       <c r="T384" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U384" s="3" t="s">
         <v>46</v>
@@ -51363,7 +51363,7 @@
         <v>2</v>
       </c>
       <c r="T385" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U385" s="3" t="s">
         <v>46</v>
@@ -51455,13 +51455,13 @@
         <v>45</v>
       </c>
       <c r="I386" s="3" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="J386" s="3" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
       <c r="L386" s="3" t="s">
         <v>50</v>
@@ -51488,7 +51488,7 @@
         <v>2</v>
       </c>
       <c r="T386" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U386" s="3" t="s">
         <v>46</v>
@@ -51509,7 +51509,7 @@
         <v>46</v>
       </c>
       <c r="AA386" s="7">
-        <v>1928113</v>
+        <v>2972113</v>
       </c>
       <c r="AB386" s="7">
         <v>1</v>
@@ -51613,7 +51613,7 @@
         <v>2</v>
       </c>
       <c r="T387" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U387" s="3" t="s">
         <v>46</v>
@@ -51634,7 +51634,7 @@
         <v>46</v>
       </c>
       <c r="AA387" s="7">
-        <v>645000</v>
+        <v>819000</v>
       </c>
       <c r="AB387" s="7">
         <v>1</v>
@@ -51738,7 +51738,7 @@
         <v>2</v>
       </c>
       <c r="T388" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U388" s="3" t="s">
         <v>46</v>
@@ -51863,7 +51863,7 @@
         <v>2</v>
       </c>
       <c r="T389" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U389" s="3" t="s">
         <v>46</v>
@@ -51988,7 +51988,7 @@
         <v>34</v>
       </c>
       <c r="T390" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U390" s="3" t="s">
         <v>46</v>
@@ -52015,7 +52015,7 @@
         <v>31</v>
       </c>
       <c r="AC390" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD390" s="3" t="s">
         <v>922</v>
@@ -52024,10 +52024,10 @@
         <v>923</v>
       </c>
       <c r="AF390" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG390" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH390" s="7">
         <v>6200000</v>
@@ -52113,7 +52113,7 @@
         <v>33</v>
       </c>
       <c r="T391" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U391" s="3" t="s">
         <v>46</v>
@@ -52140,7 +52140,7 @@
         <v>31</v>
       </c>
       <c r="AC391" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD391" s="3" t="s">
         <v>922</v>
@@ -52149,10 +52149,10 @@
         <v>923</v>
       </c>
       <c r="AF391" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG391" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH391" s="7">
         <v>6200000</v>
@@ -52229,16 +52229,16 @@
         <v>128</v>
       </c>
       <c r="Q392" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R392" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S392" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T392" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U392" s="3" t="s">
         <v>46</v>
@@ -52259,13 +52259,13 @@
         <v>46</v>
       </c>
       <c r="AA392" s="7">
-        <v>4069058</v>
+        <v>4156058</v>
       </c>
       <c r="AB392" s="7">
         <v>31</v>
       </c>
       <c r="AC392" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD392" s="3" t="s">
         <v>922</v>
@@ -52274,10 +52274,10 @@
         <v>923</v>
       </c>
       <c r="AF392" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG392" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH392" s="7">
         <v>6200000</v>
@@ -52363,7 +52363,7 @@
         <v>17</v>
       </c>
       <c r="T393" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U393" s="3" t="s">
         <v>46</v>
@@ -52390,7 +52390,7 @@
         <v>31</v>
       </c>
       <c r="AC393" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD393" s="3" t="s">
         <v>922</v>
@@ -52399,10 +52399,10 @@
         <v>923</v>
       </c>
       <c r="AF393" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG393" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH393" s="7">
         <v>6200000</v>
@@ -52455,13 +52455,13 @@
         <v>45</v>
       </c>
       <c r="I394" s="3" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="J394" s="3" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="L394" s="3" t="s">
         <v>50</v>
@@ -52488,7 +52488,7 @@
         <v>10</v>
       </c>
       <c r="T394" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U394" s="3" t="s">
         <v>46</v>
@@ -52515,7 +52515,7 @@
         <v>31</v>
       </c>
       <c r="AC394" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD394" s="3" t="s">
         <v>922</v>
@@ -52524,10 +52524,10 @@
         <v>923</v>
       </c>
       <c r="AF394" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG394" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH394" s="7">
         <v>6200000</v>
@@ -52613,7 +52613,7 @@
         <v>15</v>
       </c>
       <c r="T395" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U395" s="3" t="s">
         <v>46</v>
@@ -52634,13 +52634,13 @@
         <v>46</v>
       </c>
       <c r="AA395" s="7">
-        <v>1819500</v>
+        <v>2167500</v>
       </c>
       <c r="AB395" s="7">
         <v>31</v>
       </c>
       <c r="AC395" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD395" s="3" t="s">
         <v>922</v>
@@ -52649,10 +52649,10 @@
         <v>923</v>
       </c>
       <c r="AF395" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG395" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH395" s="7">
         <v>6200000</v>
@@ -52738,7 +52738,7 @@
         <v>17</v>
       </c>
       <c r="T396" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U396" s="3" t="s">
         <v>46</v>
@@ -52759,13 +52759,13 @@
         <v>46</v>
       </c>
       <c r="AA396" s="7">
-        <v>11082045</v>
+        <v>11952045</v>
       </c>
       <c r="AB396" s="7">
         <v>31</v>
       </c>
       <c r="AC396" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD396" s="3" t="s">
         <v>922</v>
@@ -52774,10 +52774,10 @@
         <v>923</v>
       </c>
       <c r="AF396" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG396" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH396" s="7">
         <v>6200000</v>
@@ -52863,7 +52863,7 @@
         <v>7</v>
       </c>
       <c r="T397" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U397" s="3" t="s">
         <v>46</v>
@@ -52890,7 +52890,7 @@
         <v>31</v>
       </c>
       <c r="AC397" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD397" s="3" t="s">
         <v>922</v>
@@ -52899,10 +52899,10 @@
         <v>923</v>
       </c>
       <c r="AF397" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG397" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH397" s="7">
         <v>6200000</v>
@@ -52988,7 +52988,7 @@
         <v>13</v>
       </c>
       <c r="T398" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U398" s="3" t="s">
         <v>46</v>
@@ -53015,7 +53015,7 @@
         <v>31</v>
       </c>
       <c r="AC398" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD398" s="3" t="s">
         <v>922</v>
@@ -53024,10 +53024,10 @@
         <v>923</v>
       </c>
       <c r="AF398" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG398" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH398" s="7">
         <v>6200000</v>
@@ -53104,16 +53104,16 @@
         <v>128</v>
       </c>
       <c r="Q399" s="5">
+        <v>32</v>
+      </c>
+      <c r="R399" s="5">
         <v>31</v>
       </c>
-      <c r="R399" s="5">
-        <v>30</v>
-      </c>
       <c r="S399" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T399" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U399" s="3" t="s">
         <v>46</v>
@@ -53134,13 +53134,13 @@
         <v>46</v>
       </c>
       <c r="AA399" s="7">
-        <v>570240</v>
+        <v>657240</v>
       </c>
       <c r="AB399" s="7">
         <v>31</v>
       </c>
       <c r="AC399" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD399" s="3" t="s">
         <v>922</v>
@@ -53149,10 +53149,10 @@
         <v>923</v>
       </c>
       <c r="AF399" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG399" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH399" s="7">
         <v>6200000</v>
@@ -53205,13 +53205,13 @@
         <v>45</v>
       </c>
       <c r="I400" s="3" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J400" s="3" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="K400" s="3" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="L400" s="3" t="s">
         <v>50</v>
@@ -53238,7 +53238,7 @@
         <v>13</v>
       </c>
       <c r="T400" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U400" s="3" t="s">
         <v>46</v>
@@ -53265,7 +53265,7 @@
         <v>31</v>
       </c>
       <c r="AC400" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD400" s="3" t="s">
         <v>922</v>
@@ -53274,10 +53274,10 @@
         <v>923</v>
       </c>
       <c r="AF400" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG400" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH400" s="7">
         <v>6200000</v>
@@ -53363,7 +53363,7 @@
         <v>33</v>
       </c>
       <c r="T401" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U401" s="3" t="s">
         <v>46</v>
@@ -53390,7 +53390,7 @@
         <v>31</v>
       </c>
       <c r="AC401" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD401" s="3" t="s">
         <v>922</v>
@@ -53399,10 +53399,10 @@
         <v>923</v>
       </c>
       <c r="AF401" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG401" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH401" s="7">
         <v>6200000</v>
@@ -53488,7 +53488,7 @@
         <v>15</v>
       </c>
       <c r="T402" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U402" s="3" t="s">
         <v>46</v>
@@ -53515,7 +53515,7 @@
         <v>31</v>
       </c>
       <c r="AC402" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD402" s="3" t="s">
         <v>922</v>
@@ -53524,10 +53524,10 @@
         <v>923</v>
       </c>
       <c r="AF402" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG402" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH402" s="7">
         <v>6200000</v>
@@ -53613,7 +53613,7 @@
         <v>12</v>
       </c>
       <c r="T403" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U403" s="3" t="s">
         <v>46</v>
@@ -53640,7 +53640,7 @@
         <v>31</v>
       </c>
       <c r="AC403" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD403" s="3" t="s">
         <v>922</v>
@@ -53649,10 +53649,10 @@
         <v>923</v>
       </c>
       <c r="AF403" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG403" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH403" s="7">
         <v>6200000</v>
@@ -53738,7 +53738,7 @@
         <v>32</v>
       </c>
       <c r="T404" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U404" s="3" t="s">
         <v>46</v>
@@ -53758,14 +53758,14 @@
       <c r="Z404" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA404" s="3" t="s">
-        <v>46</v>
+      <c r="AA404" s="7">
+        <v>348000</v>
       </c>
       <c r="AB404" s="7">
         <v>31</v>
       </c>
       <c r="AC404" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD404" s="3" t="s">
         <v>922</v>
@@ -53774,10 +53774,10 @@
         <v>923</v>
       </c>
       <c r="AF404" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG404" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH404" s="7">
         <v>6200000</v>
@@ -53863,7 +53863,7 @@
         <v>38</v>
       </c>
       <c r="T405" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U405" s="3" t="s">
         <v>46</v>
@@ -53890,7 +53890,7 @@
         <v>31</v>
       </c>
       <c r="AC405" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD405" s="3" t="s">
         <v>922</v>
@@ -53899,10 +53899,10 @@
         <v>923</v>
       </c>
       <c r="AF405" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG405" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH405" s="7">
         <v>6200000</v>
@@ -53988,7 +53988,7 @@
         <v>14</v>
       </c>
       <c r="T406" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U406" s="3" t="s">
         <v>46</v>
@@ -54015,7 +54015,7 @@
         <v>31</v>
       </c>
       <c r="AC406" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD406" s="3" t="s">
         <v>922</v>
@@ -54024,10 +54024,10 @@
         <v>923</v>
       </c>
       <c r="AF406" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG406" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH406" s="7">
         <v>6200000</v>
@@ -54113,7 +54113,7 @@
         <v>31</v>
       </c>
       <c r="T407" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U407" s="3" t="s">
         <v>46</v>
@@ -54134,13 +54134,13 @@
         <v>46</v>
       </c>
       <c r="AA407" s="7">
-        <v>839166</v>
+        <v>1013166</v>
       </c>
       <c r="AB407" s="7">
         <v>31</v>
       </c>
       <c r="AC407" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD407" s="3" t="s">
         <v>922</v>
@@ -54149,10 +54149,10 @@
         <v>923</v>
       </c>
       <c r="AF407" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG407" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH407" s="7">
         <v>6200000</v>
@@ -54238,7 +54238,7 @@
         <v>8</v>
       </c>
       <c r="T408" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U408" s="3" t="s">
         <v>46</v>
@@ -54265,7 +54265,7 @@
         <v>31</v>
       </c>
       <c r="AC408" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD408" s="3" t="s">
         <v>922</v>
@@ -54274,10 +54274,10 @@
         <v>923</v>
       </c>
       <c r="AF408" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG408" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH408" s="7">
         <v>6200000</v>
@@ -54363,7 +54363,7 @@
         <v>8</v>
       </c>
       <c r="T409" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U409" s="3" t="s">
         <v>46</v>
@@ -54390,7 +54390,7 @@
         <v>31</v>
       </c>
       <c r="AC409" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD409" s="3" t="s">
         <v>922</v>
@@ -54399,10 +54399,10 @@
         <v>923</v>
       </c>
       <c r="AF409" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG409" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH409" s="7">
         <v>6200000</v>
@@ -54488,7 +54488,7 @@
         <v>28</v>
       </c>
       <c r="T410" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U410" s="3" t="s">
         <v>46</v>
@@ -54509,13 +54509,13 @@
         <v>46</v>
       </c>
       <c r="AA410" s="7">
-        <v>645000</v>
+        <v>819000</v>
       </c>
       <c r="AB410" s="7">
         <v>31</v>
       </c>
       <c r="AC410" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD410" s="3" t="s">
         <v>922</v>
@@ -54524,10 +54524,10 @@
         <v>923</v>
       </c>
       <c r="AF410" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG410" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH410" s="7">
         <v>6200000</v>
@@ -54613,7 +54613,7 @@
         <v>22</v>
       </c>
       <c r="T411" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U411" s="3" t="s">
         <v>46</v>
@@ -54640,7 +54640,7 @@
         <v>31</v>
       </c>
       <c r="AC411" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD411" s="3" t="s">
         <v>922</v>
@@ -54649,10 +54649,10 @@
         <v>923</v>
       </c>
       <c r="AF411" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG411" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH411" s="7">
         <v>6200000</v>
@@ -54705,13 +54705,13 @@
         <v>45</v>
       </c>
       <c r="I412" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="J412" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="L412" s="3" t="s">
         <v>50</v>
@@ -54738,7 +54738,7 @@
         <v>15</v>
       </c>
       <c r="T412" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U412" s="3" t="s">
         <v>46</v>
@@ -54765,7 +54765,7 @@
         <v>31</v>
       </c>
       <c r="AC412" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD412" s="3" t="s">
         <v>922</v>
@@ -54774,10 +54774,10 @@
         <v>923</v>
       </c>
       <c r="AF412" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG412" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH412" s="7">
         <v>6200000</v>
@@ -54863,7 +54863,7 @@
         <v>15</v>
       </c>
       <c r="T413" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U413" s="3" t="s">
         <v>46</v>
@@ -54890,7 +54890,7 @@
         <v>31</v>
       </c>
       <c r="AC413" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD413" s="3" t="s">
         <v>922</v>
@@ -54899,10 +54899,10 @@
         <v>923</v>
       </c>
       <c r="AF413" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG413" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH413" s="7">
         <v>6200000</v>
@@ -54988,7 +54988,7 @@
         <v>26</v>
       </c>
       <c r="T414" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U414" s="3" t="s">
         <v>46</v>
@@ -55015,7 +55015,7 @@
         <v>31</v>
       </c>
       <c r="AC414" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD414" s="3" t="s">
         <v>922</v>
@@ -55024,10 +55024,10 @@
         <v>923</v>
       </c>
       <c r="AF414" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG414" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH414" s="7">
         <v>6200000</v>
@@ -55113,7 +55113,7 @@
         <v>35</v>
       </c>
       <c r="T415" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U415" s="3" t="s">
         <v>46</v>
@@ -55140,7 +55140,7 @@
         <v>31</v>
       </c>
       <c r="AC415" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD415" s="3" t="s">
         <v>922</v>
@@ -55149,10 +55149,10 @@
         <v>923</v>
       </c>
       <c r="AF415" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG415" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH415" s="7">
         <v>18600000</v>
@@ -55205,40 +55205,40 @@
         <v>999</v>
       </c>
       <c r="I416" s="3" t="s">
-        <v>964</v>
+        <v>461</v>
       </c>
       <c r="J416" s="3" t="s">
-        <v>965</v>
+        <v>462</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>813</v>
+        <v>463</v>
       </c>
       <c r="L416" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M416" s="3" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="N416" s="3" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="O416" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="P416" s="3" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="Q416" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R416" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S416" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T416" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U416" s="3" t="s">
         <v>46</v>
@@ -55259,13 +55259,13 @@
         <v>46</v>
       </c>
       <c r="AA416" s="7">
-        <v>685286</v>
+        <v>1425000</v>
       </c>
       <c r="AB416" s="7">
         <v>31</v>
       </c>
       <c r="AC416" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD416" s="3" t="s">
         <v>922</v>
@@ -55274,10 +55274,10 @@
         <v>923</v>
       </c>
       <c r="AF416" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG416" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH416" s="7">
         <v>18600000</v>
@@ -55330,40 +55330,40 @@
         <v>999</v>
       </c>
       <c r="I417" s="3" t="s">
-        <v>461</v>
+        <v>964</v>
       </c>
       <c r="J417" s="3" t="s">
-        <v>462</v>
+        <v>965</v>
       </c>
       <c r="K417" s="3" t="s">
-        <v>463</v>
+        <v>813</v>
       </c>
       <c r="L417" s="3" t="s">
         <v>50</v>
       </c>
       <c r="M417" s="3" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="N417" s="3" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="O417" s="3" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="P417" s="3" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="Q417" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R417" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S417" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T417" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U417" s="3" t="s">
         <v>46</v>
@@ -55384,13 +55384,13 @@
         <v>46</v>
       </c>
       <c r="AA417" s="7">
-        <v>1425000</v>
+        <v>685286</v>
       </c>
       <c r="AB417" s="7">
         <v>31</v>
       </c>
       <c r="AC417" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD417" s="3" t="s">
         <v>922</v>
@@ -55399,10 +55399,10 @@
         <v>923</v>
       </c>
       <c r="AF417" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG417" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH417" s="7">
         <v>18600000</v>
@@ -55488,7 +55488,7 @@
         <v>16</v>
       </c>
       <c r="T418" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U418" s="3" t="s">
         <v>46</v>
@@ -55515,7 +55515,7 @@
         <v>31</v>
       </c>
       <c r="AC418" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD418" s="3" t="s">
         <v>922</v>
@@ -55524,10 +55524,10 @@
         <v>923</v>
       </c>
       <c r="AF418" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG418" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH418" s="7">
         <v>18600000</v>
@@ -55613,7 +55613,7 @@
         <v>31</v>
       </c>
       <c r="T419" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U419" s="3" t="s">
         <v>46</v>
@@ -55640,7 +55640,7 @@
         <v>31</v>
       </c>
       <c r="AC419" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD419" s="3" t="s">
         <v>922</v>
@@ -55649,10 +55649,10 @@
         <v>923</v>
       </c>
       <c r="AF419" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG419" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH419" s="7">
         <v>18600000</v>
@@ -55738,7 +55738,7 @@
         <v>11</v>
       </c>
       <c r="T420" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U420" s="3" t="s">
         <v>46</v>
@@ -55765,7 +55765,7 @@
         <v>31</v>
       </c>
       <c r="AC420" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD420" s="3" t="s">
         <v>922</v>
@@ -55774,10 +55774,10 @@
         <v>923</v>
       </c>
       <c r="AF420" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG420" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH420" s="7">
         <v>18600000</v>
@@ -55863,7 +55863,7 @@
         <v>18</v>
       </c>
       <c r="T421" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U421" s="3" t="s">
         <v>46</v>
@@ -55890,7 +55890,7 @@
         <v>31</v>
       </c>
       <c r="AC421" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD421" s="3" t="s">
         <v>922</v>
@@ -55899,10 +55899,10 @@
         <v>923</v>
       </c>
       <c r="AF421" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG421" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH421" s="7">
         <v>18600000</v>
@@ -55988,7 +55988,7 @@
         <v>35</v>
       </c>
       <c r="T422" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U422" s="3" t="s">
         <v>46</v>
@@ -56015,7 +56015,7 @@
         <v>31</v>
       </c>
       <c r="AC422" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD422" s="3" t="s">
         <v>922</v>
@@ -56024,10 +56024,10 @@
         <v>923</v>
       </c>
       <c r="AF422" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG422" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH422" s="7">
         <v>12400000</v>
@@ -56113,7 +56113,7 @@
         <v>27</v>
       </c>
       <c r="T423" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U423" s="3" t="s">
         <v>46</v>
@@ -56133,14 +56133,14 @@
       <c r="Z423" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AA423" s="3" t="s">
-        <v>46</v>
+      <c r="AA423" s="7">
+        <v>2350040</v>
       </c>
       <c r="AB423" s="7">
         <v>31</v>
       </c>
       <c r="AC423" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD423" s="3" t="s">
         <v>922</v>
@@ -56149,10 +56149,10 @@
         <v>923</v>
       </c>
       <c r="AF423" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG423" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH423" s="7">
         <v>12400000</v>
@@ -56238,7 +56238,7 @@
         <v>13</v>
       </c>
       <c r="T424" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U424" s="3" t="s">
         <v>46</v>
@@ -56265,7 +56265,7 @@
         <v>31</v>
       </c>
       <c r="AC424" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD424" s="3" t="s">
         <v>922</v>
@@ -56274,10 +56274,10 @@
         <v>923</v>
       </c>
       <c r="AF424" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG424" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH424" s="7">
         <v>12400000</v>
@@ -56363,7 +56363,7 @@
         <v>33</v>
       </c>
       <c r="T425" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U425" s="3" t="s">
         <v>46</v>
@@ -56390,7 +56390,7 @@
         <v>31</v>
       </c>
       <c r="AC425" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD425" s="3" t="s">
         <v>922</v>
@@ -56399,10 +56399,10 @@
         <v>923</v>
       </c>
       <c r="AF425" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG425" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH425" s="7">
         <v>12400000</v>
@@ -56479,16 +56479,16 @@
         <v>128</v>
       </c>
       <c r="Q426" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R426" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S426" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T426" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U426" s="3" t="s">
         <v>46</v>
@@ -56509,13 +56509,13 @@
         <v>46</v>
       </c>
       <c r="AA426" s="7">
-        <v>1413080</v>
+        <v>3312160</v>
       </c>
       <c r="AB426" s="7">
         <v>31</v>
       </c>
       <c r="AC426" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD426" s="3" t="s">
         <v>922</v>
@@ -56524,10 +56524,10 @@
         <v>923</v>
       </c>
       <c r="AF426" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG426" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH426" s="7">
         <v>12400000</v>
@@ -56613,7 +56613,7 @@
         <v>17</v>
       </c>
       <c r="T427" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U427" s="3" t="s">
         <v>46</v>
@@ -56640,7 +56640,7 @@
         <v>31</v>
       </c>
       <c r="AC427" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD427" s="3" t="s">
         <v>922</v>
@@ -56649,10 +56649,10 @@
         <v>923</v>
       </c>
       <c r="AF427" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG427" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH427" s="7">
         <v>12400000</v>
@@ -56738,7 +56738,7 @@
         <v>16</v>
       </c>
       <c r="T428" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U428" s="3" t="s">
         <v>46</v>
@@ -56765,7 +56765,7 @@
         <v>31</v>
       </c>
       <c r="AC428" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD428" s="3" t="s">
         <v>922</v>
@@ -56774,10 +56774,10 @@
         <v>923</v>
       </c>
       <c r="AF428" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG428" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH428" s="7">
         <v>12400000</v>
@@ -56863,7 +56863,7 @@
         <v>15</v>
       </c>
       <c r="T429" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U429" s="3" t="s">
         <v>46</v>
@@ -56884,13 +56884,13 @@
         <v>46</v>
       </c>
       <c r="AA429" s="7">
-        <v>6522488</v>
+        <v>8872528</v>
       </c>
       <c r="AB429" s="7">
         <v>31</v>
       </c>
       <c r="AC429" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD429" s="3" t="s">
         <v>922</v>
@@ -56899,10 +56899,10 @@
         <v>923</v>
       </c>
       <c r="AF429" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG429" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH429" s="7">
         <v>12400000</v>
@@ -56988,7 +56988,7 @@
         <v>36</v>
       </c>
       <c r="T430" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U430" s="3" t="s">
         <v>46</v>
@@ -57015,7 +57015,7 @@
         <v>31</v>
       </c>
       <c r="AC430" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD430" s="3" t="s">
         <v>922</v>
@@ -57024,10 +57024,10 @@
         <v>923</v>
       </c>
       <c r="AF430" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG430" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH430" s="7">
         <v>12400000</v>
@@ -57113,7 +57113,7 @@
         <v>17</v>
       </c>
       <c r="T431" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U431" s="3" t="s">
         <v>46</v>
@@ -57140,7 +57140,7 @@
         <v>31</v>
       </c>
       <c r="AC431" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD431" s="3" t="s">
         <v>922</v>
@@ -57149,10 +57149,10 @@
         <v>923</v>
       </c>
       <c r="AF431" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG431" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH431" s="7">
         <v>12400000</v>
@@ -57205,13 +57205,13 @@
         <v>921</v>
       </c>
       <c r="I432" s="3" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="J432" s="3" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="L432" s="3" t="s">
         <v>50</v>
@@ -57238,7 +57238,7 @@
         <v>15</v>
       </c>
       <c r="T432" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U432" s="3" t="s">
         <v>46</v>
@@ -57265,7 +57265,7 @@
         <v>31</v>
       </c>
       <c r="AC432" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD432" s="3" t="s">
         <v>922</v>
@@ -57274,10 +57274,10 @@
         <v>923</v>
       </c>
       <c r="AF432" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG432" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH432" s="7">
         <v>12400000</v>
@@ -57363,7 +57363,7 @@
         <v>10</v>
       </c>
       <c r="T433" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U433" s="3" t="s">
         <v>46</v>
@@ -57390,7 +57390,7 @@
         <v>31</v>
       </c>
       <c r="AC433" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD433" s="3" t="s">
         <v>922</v>
@@ -57399,10 +57399,10 @@
         <v>923</v>
       </c>
       <c r="AF433" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG433" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH433" s="7">
         <v>12400000</v>
@@ -57488,7 +57488,7 @@
         <v>9</v>
       </c>
       <c r="T434" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U434" s="3" t="s">
         <v>46</v>
@@ -57515,7 +57515,7 @@
         <v>31</v>
       </c>
       <c r="AC434" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD434" s="3" t="s">
         <v>922</v>
@@ -57524,10 +57524,10 @@
         <v>923</v>
       </c>
       <c r="AF434" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG434" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH434" s="7">
         <v>12400000</v>
@@ -57613,7 +57613,7 @@
         <v>8</v>
       </c>
       <c r="T435" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U435" s="3" t="s">
         <v>46</v>
@@ -57640,7 +57640,7 @@
         <v>31</v>
       </c>
       <c r="AC435" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD435" s="3" t="s">
         <v>922</v>
@@ -57649,10 +57649,10 @@
         <v>923</v>
       </c>
       <c r="AF435" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG435" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH435" s="7">
         <v>12400000</v>
@@ -57738,7 +57738,7 @@
         <v>14</v>
       </c>
       <c r="T436" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U436" s="3" t="s">
         <v>46</v>
@@ -57765,7 +57765,7 @@
         <v>31</v>
       </c>
       <c r="AC436" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD436" s="3" t="s">
         <v>922</v>
@@ -57774,10 +57774,10 @@
         <v>923</v>
       </c>
       <c r="AF436" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG436" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH436" s="7">
         <v>12400000</v>
@@ -57863,7 +57863,7 @@
         <v>21</v>
       </c>
       <c r="T437" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U437" s="3" t="s">
         <v>46</v>
@@ -57890,7 +57890,7 @@
         <v>31</v>
       </c>
       <c r="AC437" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD437" s="3" t="s">
         <v>922</v>
@@ -57899,10 +57899,10 @@
         <v>923</v>
       </c>
       <c r="AF437" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG437" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH437" s="7">
         <v>12400000</v>
@@ -57988,7 +57988,7 @@
         <v>8</v>
       </c>
       <c r="T438" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U438" s="3" t="s">
         <v>46</v>
@@ -58015,7 +58015,7 @@
         <v>31</v>
       </c>
       <c r="AC438" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD438" s="3" t="s">
         <v>922</v>
@@ -58024,10 +58024,10 @@
         <v>923</v>
       </c>
       <c r="AF438" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG438" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH438" s="7">
         <v>12400000</v>
@@ -58113,7 +58113,7 @@
         <v>10</v>
       </c>
       <c r="T439" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U439" s="3" t="s">
         <v>46</v>
@@ -58134,13 +58134,13 @@
         <v>46</v>
       </c>
       <c r="AA439" s="7">
-        <v>796700</v>
+        <v>1033200</v>
       </c>
       <c r="AB439" s="7">
         <v>31</v>
       </c>
       <c r="AC439" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD439" s="3" t="s">
         <v>922</v>
@@ -58149,10 +58149,10 @@
         <v>923</v>
       </c>
       <c r="AF439" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG439" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH439" s="7">
         <v>12400000</v>
@@ -58238,7 +58238,7 @@
         <v>13</v>
       </c>
       <c r="T440" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U440" s="3" t="s">
         <v>46</v>
@@ -58265,7 +58265,7 @@
         <v>31</v>
       </c>
       <c r="AC440" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD440" s="3" t="s">
         <v>922</v>
@@ -58274,10 +58274,10 @@
         <v>923</v>
       </c>
       <c r="AF440" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG440" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH440" s="7">
         <v>12400000</v>
@@ -58363,7 +58363,7 @@
         <v>18</v>
       </c>
       <c r="T441" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U441" s="3" t="s">
         <v>46</v>
@@ -58390,7 +58390,7 @@
         <v>31</v>
       </c>
       <c r="AC441" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD441" s="3" t="s">
         <v>922</v>
@@ -58399,10 +58399,10 @@
         <v>923</v>
       </c>
       <c r="AF441" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG441" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH441" s="7">
         <v>12400000</v>
@@ -58479,16 +58479,16 @@
         <v>128</v>
       </c>
       <c r="Q442" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R442" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S442" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T442" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U442" s="3" t="s">
         <v>46</v>
@@ -58515,7 +58515,7 @@
         <v>31</v>
       </c>
       <c r="AC442" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD442" s="3" t="s">
         <v>922</v>
@@ -58524,10 +58524,10 @@
         <v>923</v>
       </c>
       <c r="AF442" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG442" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH442" s="7">
         <v>12400000</v>
@@ -58613,7 +58613,7 @@
         <v>9</v>
       </c>
       <c r="T443" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U443" s="3" t="s">
         <v>46</v>
@@ -58640,7 +58640,7 @@
         <v>31</v>
       </c>
       <c r="AC443" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD443" s="3" t="s">
         <v>922</v>
@@ -58649,10 +58649,10 @@
         <v>923</v>
       </c>
       <c r="AF443" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG443" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH443" s="7">
         <v>12400000</v>
@@ -58738,7 +58738,7 @@
         <v>9</v>
       </c>
       <c r="T444" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U444" s="3" t="s">
         <v>46</v>
@@ -58765,7 +58765,7 @@
         <v>31</v>
       </c>
       <c r="AC444" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD444" s="3" t="s">
         <v>922</v>
@@ -58774,10 +58774,10 @@
         <v>923</v>
       </c>
       <c r="AF444" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG444" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH444" s="7">
         <v>12400000</v>
@@ -58830,13 +58830,13 @@
         <v>921</v>
       </c>
       <c r="I445" s="3" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="J445" s="3" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="K445" s="3" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="L445" s="3" t="s">
         <v>50</v>
@@ -58863,7 +58863,7 @@
         <v>16</v>
       </c>
       <c r="T445" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U445" s="3" t="s">
         <v>46</v>
@@ -58890,7 +58890,7 @@
         <v>31</v>
       </c>
       <c r="AC445" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD445" s="3" t="s">
         <v>922</v>
@@ -58899,10 +58899,10 @@
         <v>923</v>
       </c>
       <c r="AF445" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG445" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH445" s="7">
         <v>12400000</v>
@@ -58988,7 +58988,7 @@
         <v>34</v>
       </c>
       <c r="T446" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U446" s="3" t="s">
         <v>46</v>
@@ -59015,7 +59015,7 @@
         <v>31</v>
       </c>
       <c r="AC446" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD446" s="3" t="s">
         <v>922</v>
@@ -59024,10 +59024,10 @@
         <v>923</v>
       </c>
       <c r="AF446" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG446" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH446" s="7">
         <v>12400000</v>
@@ -59113,7 +59113,7 @@
         <v>15</v>
       </c>
       <c r="T447" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U447" s="3" t="s">
         <v>46</v>
@@ -59140,7 +59140,7 @@
         <v>31</v>
       </c>
       <c r="AC447" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD447" s="3" t="s">
         <v>922</v>
@@ -59149,10 +59149,10 @@
         <v>923</v>
       </c>
       <c r="AF447" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG447" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH447" s="7">
         <v>12400000</v>
@@ -59238,7 +59238,7 @@
         <v>13</v>
       </c>
       <c r="T448" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U448" s="3" t="s">
         <v>46</v>
@@ -59265,7 +59265,7 @@
         <v>31</v>
       </c>
       <c r="AC448" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD448" s="3" t="s">
         <v>922</v>
@@ -59274,10 +59274,10 @@
         <v>923</v>
       </c>
       <c r="AF448" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG448" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH448" s="7">
         <v>12400000</v>
@@ -59363,7 +59363,7 @@
         <v>11</v>
       </c>
       <c r="T449" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U449" s="3" t="s">
         <v>46</v>
@@ -59390,7 +59390,7 @@
         <v>31</v>
       </c>
       <c r="AC449" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD449" s="3" t="s">
         <v>922</v>
@@ -59399,10 +59399,10 @@
         <v>923</v>
       </c>
       <c r="AF449" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG449" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH449" s="7">
         <v>12400000</v>
@@ -59488,7 +59488,7 @@
         <v>32</v>
       </c>
       <c r="T450" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U450" s="3" t="s">
         <v>46</v>
@@ -59515,7 +59515,7 @@
         <v>31</v>
       </c>
       <c r="AC450" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD450" s="3" t="s">
         <v>922</v>
@@ -59524,10 +59524,10 @@
         <v>923</v>
       </c>
       <c r="AF450" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG450" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH450" s="7">
         <v>12400000</v>
@@ -59613,7 +59613,7 @@
         <v>9</v>
       </c>
       <c r="T451" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U451" s="3" t="s">
         <v>46</v>
@@ -59640,7 +59640,7 @@
         <v>31</v>
       </c>
       <c r="AC451" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD451" s="3" t="s">
         <v>922</v>
@@ -59649,10 +59649,10 @@
         <v>923</v>
       </c>
       <c r="AF451" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG451" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH451" s="7">
         <v>12400000</v>
@@ -59738,7 +59738,7 @@
         <v>7</v>
       </c>
       <c r="T452" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U452" s="3" t="s">
         <v>46</v>
@@ -59765,7 +59765,7 @@
         <v>31</v>
       </c>
       <c r="AC452" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD452" s="3" t="s">
         <v>922</v>
@@ -59774,10 +59774,10 @@
         <v>923</v>
       </c>
       <c r="AF452" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG452" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH452" s="7">
         <v>12400000</v>
@@ -59863,7 +59863,7 @@
         <v>10</v>
       </c>
       <c r="T453" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U453" s="3" t="s">
         <v>46</v>
@@ -59890,7 +59890,7 @@
         <v>31</v>
       </c>
       <c r="AC453" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD453" s="3" t="s">
         <v>922</v>
@@ -59899,10 +59899,10 @@
         <v>923</v>
       </c>
       <c r="AF453" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG453" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH453" s="7">
         <v>12400000</v>
@@ -59988,7 +59988,7 @@
         <v>39</v>
       </c>
       <c r="T454" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U454" s="3" t="s">
         <v>46</v>
@@ -60015,7 +60015,7 @@
         <v>31</v>
       </c>
       <c r="AC454" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD454" s="3" t="s">
         <v>922</v>
@@ -60024,10 +60024,10 @@
         <v>923</v>
       </c>
       <c r="AF454" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG454" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH454" s="7">
         <v>12400000</v>
@@ -60113,7 +60113,7 @@
         <v>19</v>
       </c>
       <c r="T455" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U455" s="3" t="s">
         <v>46</v>
@@ -60140,7 +60140,7 @@
         <v>31</v>
       </c>
       <c r="AC455" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD455" s="3" t="s">
         <v>922</v>
@@ -60149,10 +60149,10 @@
         <v>923</v>
       </c>
       <c r="AF455" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG455" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH455" s="7">
         <v>12400000</v>
@@ -60238,7 +60238,7 @@
         <v>13</v>
       </c>
       <c r="T456" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U456" s="3" t="s">
         <v>46</v>
@@ -60265,7 +60265,7 @@
         <v>31</v>
       </c>
       <c r="AC456" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD456" s="3" t="s">
         <v>922</v>
@@ -60274,10 +60274,10 @@
         <v>923</v>
       </c>
       <c r="AF456" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG456" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH456" s="7">
         <v>12400000</v>
@@ -60363,7 +60363,7 @@
         <v>16</v>
       </c>
       <c r="T457" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U457" s="3" t="s">
         <v>46</v>
@@ -60390,7 +60390,7 @@
         <v>31</v>
       </c>
       <c r="AC457" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD457" s="3" t="s">
         <v>922</v>
@@ -60399,10 +60399,10 @@
         <v>923</v>
       </c>
       <c r="AF457" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG457" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH457" s="7">
         <v>12400000</v>
@@ -60488,7 +60488,7 @@
         <v>15</v>
       </c>
       <c r="T458" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U458" s="3" t="s">
         <v>46</v>
@@ -60515,7 +60515,7 @@
         <v>31</v>
       </c>
       <c r="AC458" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD458" s="3" t="s">
         <v>922</v>
@@ -60524,10 +60524,10 @@
         <v>923</v>
       </c>
       <c r="AF458" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG458" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH458" s="7">
         <v>12400000</v>
@@ -60613,7 +60613,7 @@
         <v>29</v>
       </c>
       <c r="T459" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U459" s="3" t="s">
         <v>46</v>
@@ -60640,7 +60640,7 @@
         <v>31</v>
       </c>
       <c r="AC459" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD459" s="3" t="s">
         <v>922</v>
@@ -60649,10 +60649,10 @@
         <v>923</v>
       </c>
       <c r="AF459" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG459" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH459" s="7">
         <v>12400000</v>
@@ -60705,13 +60705,13 @@
         <v>921</v>
       </c>
       <c r="I460" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="J460" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="K460" s="3" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="L460" s="3" t="s">
         <v>50</v>
@@ -60738,7 +60738,7 @@
         <v>16</v>
       </c>
       <c r="T460" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U460" s="3" t="s">
         <v>46</v>
@@ -60765,7 +60765,7 @@
         <v>31</v>
       </c>
       <c r="AC460" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD460" s="3" t="s">
         <v>922</v>
@@ -60774,10 +60774,10 @@
         <v>923</v>
       </c>
       <c r="AF460" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG460" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH460" s="7">
         <v>12400000</v>
@@ -60863,7 +60863,7 @@
         <v>24</v>
       </c>
       <c r="T461" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U461" s="3" t="s">
         <v>46</v>
@@ -60890,7 +60890,7 @@
         <v>31</v>
       </c>
       <c r="AC461" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD461" s="3" t="s">
         <v>922</v>
@@ -60899,10 +60899,10 @@
         <v>923</v>
       </c>
       <c r="AF461" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG461" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH461" s="7">
         <v>12400000</v>
@@ -60988,7 +60988,7 @@
         <v>9</v>
       </c>
       <c r="T462" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U462" s="3" t="s">
         <v>46</v>
@@ -61015,7 +61015,7 @@
         <v>31</v>
       </c>
       <c r="AC462" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD462" s="3" t="s">
         <v>922</v>
@@ -61024,10 +61024,10 @@
         <v>923</v>
       </c>
       <c r="AF462" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG462" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH462" s="7">
         <v>12400000</v>
@@ -61113,7 +61113,7 @@
         <v>16</v>
       </c>
       <c r="T463" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U463" s="3" t="s">
         <v>46</v>
@@ -61140,7 +61140,7 @@
         <v>31</v>
       </c>
       <c r="AC463" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD463" s="3" t="s">
         <v>922</v>
@@ -61149,10 +61149,10 @@
         <v>923</v>
       </c>
       <c r="AF463" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG463" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH463" s="7">
         <v>12400000</v>
@@ -61238,7 +61238,7 @@
         <v>34</v>
       </c>
       <c r="T464" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U464" s="3" t="s">
         <v>46</v>
@@ -61265,7 +61265,7 @@
         <v>31</v>
       </c>
       <c r="AC464" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD464" s="3" t="s">
         <v>922</v>
@@ -61274,10 +61274,10 @@
         <v>923</v>
       </c>
       <c r="AF464" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG464" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH464" s="7">
         <v>6200000</v>
@@ -61363,7 +61363,7 @@
         <v>11</v>
       </c>
       <c r="T465" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U465" s="3" t="s">
         <v>46</v>
@@ -61390,7 +61390,7 @@
         <v>31</v>
       </c>
       <c r="AC465" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD465" s="3" t="s">
         <v>922</v>
@@ -61399,10 +61399,10 @@
         <v>923</v>
       </c>
       <c r="AF465" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG465" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH465" s="7">
         <v>6200000</v>
@@ -61488,7 +61488,7 @@
         <v>10</v>
       </c>
       <c r="T466" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U466" s="3" t="s">
         <v>46</v>
@@ -61515,7 +61515,7 @@
         <v>31</v>
       </c>
       <c r="AC466" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD466" s="3" t="s">
         <v>922</v>
@@ -61524,10 +61524,10 @@
         <v>923</v>
       </c>
       <c r="AF466" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG466" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH466" s="7">
         <v>6200000</v>
@@ -61604,16 +61604,16 @@
         <v>128</v>
       </c>
       <c r="Q467" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R467" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S467" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T467" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U467" s="3" t="s">
         <v>46</v>
@@ -61634,13 +61634,13 @@
         <v>46</v>
       </c>
       <c r="AA467" s="7">
-        <v>942800</v>
+        <v>1172800</v>
       </c>
       <c r="AB467" s="7">
         <v>31</v>
       </c>
       <c r="AC467" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD467" s="3" t="s">
         <v>922</v>
@@ -61649,10 +61649,10 @@
         <v>923</v>
       </c>
       <c r="AF467" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG467" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH467" s="7">
         <v>6200000</v>
@@ -61738,7 +61738,7 @@
         <v>17</v>
       </c>
       <c r="T468" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U468" s="3" t="s">
         <v>46</v>
@@ -61765,7 +61765,7 @@
         <v>31</v>
       </c>
       <c r="AC468" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD468" s="3" t="s">
         <v>922</v>
@@ -61774,10 +61774,10 @@
         <v>923</v>
       </c>
       <c r="AF468" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG468" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH468" s="7">
         <v>6200000</v>
@@ -61863,7 +61863,7 @@
         <v>12</v>
       </c>
       <c r="T469" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U469" s="3" t="s">
         <v>46</v>
@@ -61890,7 +61890,7 @@
         <v>31</v>
       </c>
       <c r="AC469" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD469" s="3" t="s">
         <v>922</v>
@@ -61899,10 +61899,10 @@
         <v>923</v>
       </c>
       <c r="AF469" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG469" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH469" s="7">
         <v>6200000</v>
@@ -61988,7 +61988,7 @@
         <v>22</v>
       </c>
       <c r="T470" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U470" s="3" t="s">
         <v>46</v>
@@ -62015,7 +62015,7 @@
         <v>31</v>
       </c>
       <c r="AC470" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD470" s="3" t="s">
         <v>922</v>
@@ -62024,10 +62024,10 @@
         <v>923</v>
       </c>
       <c r="AF470" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG470" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH470" s="7">
         <v>6200000</v>
@@ -62113,7 +62113,7 @@
         <v>8</v>
       </c>
       <c r="T471" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U471" s="3" t="s">
         <v>46</v>
@@ -62140,7 +62140,7 @@
         <v>31</v>
       </c>
       <c r="AC471" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD471" s="3" t="s">
         <v>922</v>
@@ -62149,10 +62149,10 @@
         <v>923</v>
       </c>
       <c r="AF471" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG471" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH471" s="7">
         <v>6200000</v>
@@ -62238,7 +62238,7 @@
         <v>9</v>
       </c>
       <c r="T472" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U472" s="3" t="s">
         <v>46</v>
@@ -62265,7 +62265,7 @@
         <v>31</v>
       </c>
       <c r="AC472" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD472" s="3" t="s">
         <v>922</v>
@@ -62274,10 +62274,10 @@
         <v>923</v>
       </c>
       <c r="AF472" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG472" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH472" s="7">
         <v>6200000</v>
@@ -62363,7 +62363,7 @@
         <v>9</v>
       </c>
       <c r="T473" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U473" s="3" t="s">
         <v>46</v>
@@ -62390,7 +62390,7 @@
         <v>31</v>
       </c>
       <c r="AC473" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD473" s="3" t="s">
         <v>922</v>
@@ -62399,10 +62399,10 @@
         <v>923</v>
       </c>
       <c r="AF473" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG473" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH473" s="7">
         <v>6200000</v>
@@ -62488,7 +62488,7 @@
         <v>21</v>
       </c>
       <c r="T474" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U474" s="3" t="s">
         <v>46</v>
@@ -62515,7 +62515,7 @@
         <v>31</v>
       </c>
       <c r="AC474" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD474" s="3" t="s">
         <v>922</v>
@@ -62524,10 +62524,10 @@
         <v>923</v>
       </c>
       <c r="AF474" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG474" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH474" s="7">
         <v>6200000</v>
@@ -62613,7 +62613,7 @@
         <v>10</v>
       </c>
       <c r="T475" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U475" s="3" t="s">
         <v>46</v>
@@ -62634,13 +62634,13 @@
         <v>46</v>
       </c>
       <c r="AA475" s="7">
-        <v>1321100</v>
+        <v>1781100</v>
       </c>
       <c r="AB475" s="7">
         <v>31</v>
       </c>
       <c r="AC475" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD475" s="3" t="s">
         <v>922</v>
@@ -62649,10 +62649,10 @@
         <v>923</v>
       </c>
       <c r="AF475" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG475" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH475" s="7">
         <v>6200000</v>
@@ -62738,7 +62738,7 @@
         <v>11</v>
       </c>
       <c r="T476" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U476" s="3" t="s">
         <v>46</v>
@@ -62765,7 +62765,7 @@
         <v>31</v>
       </c>
       <c r="AC476" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD476" s="3" t="s">
         <v>922</v>
@@ -62774,10 +62774,10 @@
         <v>923</v>
       </c>
       <c r="AF476" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG476" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH476" s="7">
         <v>6200000</v>
@@ -62863,7 +62863,7 @@
         <v>7</v>
       </c>
       <c r="T477" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U477" s="3" t="s">
         <v>46</v>
@@ -62890,7 +62890,7 @@
         <v>31</v>
       </c>
       <c r="AC477" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD477" s="3" t="s">
         <v>922</v>
@@ -62899,10 +62899,10 @@
         <v>923</v>
       </c>
       <c r="AF477" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG477" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH477" s="7">
         <v>6200000</v>
@@ -62988,7 +62988,7 @@
         <v>28</v>
       </c>
       <c r="T478" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U478" s="3" t="s">
         <v>46</v>
@@ -63015,7 +63015,7 @@
         <v>31</v>
       </c>
       <c r="AC478" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD478" s="3" t="s">
         <v>922</v>
@@ -63024,10 +63024,10 @@
         <v>923</v>
       </c>
       <c r="AF478" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG478" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH478" s="7">
         <v>6200000</v>
@@ -63113,7 +63113,7 @@
         <v>22</v>
       </c>
       <c r="T479" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U479" s="3" t="s">
         <v>46</v>
@@ -63140,7 +63140,7 @@
         <v>31</v>
       </c>
       <c r="AC479" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD479" s="3" t="s">
         <v>922</v>
@@ -63149,10 +63149,10 @@
         <v>923</v>
       </c>
       <c r="AF479" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG479" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH479" s="7">
         <v>6200000</v>
@@ -63238,7 +63238,7 @@
         <v>10</v>
       </c>
       <c r="T480" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U480" s="3" t="s">
         <v>46</v>
@@ -63265,7 +63265,7 @@
         <v>31</v>
       </c>
       <c r="AC480" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD480" s="3" t="s">
         <v>922</v>
@@ -63274,10 +63274,10 @@
         <v>923</v>
       </c>
       <c r="AF480" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG480" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH480" s="7">
         <v>6200000</v>
@@ -63363,7 +63363,7 @@
         <v>18</v>
       </c>
       <c r="T481" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U481" s="3" t="s">
         <v>46</v>
@@ -63390,7 +63390,7 @@
         <v>31</v>
       </c>
       <c r="AC481" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD481" s="3" t="s">
         <v>922</v>
@@ -63399,10 +63399,10 @@
         <v>923</v>
       </c>
       <c r="AF481" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG481" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH481" s="7">
         <v>6200000</v>
@@ -63488,7 +63488,7 @@
         <v>12</v>
       </c>
       <c r="T482" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U482" s="3" t="s">
         <v>46</v>
@@ -63515,7 +63515,7 @@
         <v>31</v>
       </c>
       <c r="AC482" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD482" s="3" t="s">
         <v>922</v>
@@ -63524,10 +63524,10 @@
         <v>923</v>
       </c>
       <c r="AF482" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG482" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH482" s="7">
         <v>6200000</v>
@@ -63613,7 +63613,7 @@
         <v>10</v>
       </c>
       <c r="T483" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U483" s="3" t="s">
         <v>46</v>
@@ -63640,7 +63640,7 @@
         <v>31</v>
       </c>
       <c r="AC483" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD483" s="3" t="s">
         <v>922</v>
@@ -63649,10 +63649,10 @@
         <v>923</v>
       </c>
       <c r="AF483" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG483" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH483" s="7">
         <v>6200000</v>
@@ -63705,13 +63705,13 @@
         <v>45</v>
       </c>
       <c r="I484" s="3" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="J484" s="3" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
       <c r="L484" s="3" t="s">
         <v>50</v>
@@ -63738,7 +63738,7 @@
         <v>16</v>
       </c>
       <c r="T484" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="U484" s="3" t="s">
         <v>46</v>
@@ -63759,13 +63759,13 @@
         <v>46</v>
       </c>
       <c r="AA484" s="7">
-        <v>1199318</v>
+        <v>1429318</v>
       </c>
       <c r="AB484" s="7">
         <v>31</v>
       </c>
       <c r="AC484" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="AD484" s="3" t="s">
         <v>922</v>
@@ -63774,10 +63774,10 @@
         <v>923</v>
       </c>
       <c r="AF484" s="3" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="AG484" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="AH484" s="7">
         <v>6200000</v>
